--- a/LATEST_SCHEMA/schema_azure_mssql_dbo.xlsx
+++ b/LATEST_SCHEMA/schema_azure_mssql_dbo.xlsx
@@ -1476,7 +1476,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>The `po_id` column is a non-nullable bigint serving as the primary key for uniquely identifying purchase orders in the `purchase_orders` table.</t>
+          <t>The `po_id` column is a non-nullable bigint serving as the primary key for uniquely identifying purchase orders in the `dbo.purchase_orders` table.</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -1554,7 +1554,7 @@
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>References the unique identifier of the supplier associated with the purchase order, linking to the `suppliers.supplier_id` column.</t>
+          <t>The `supplier_id` column in the `purchase_orders` table is a non-nullable bigint that references the `supplier_id` column in the `suppliers` table, identifying the supplier associated with each purchase order.</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -1632,7 +1632,7 @@
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Represents the identifier of the store associated with the purchase order, referencing the `store_id` column in the `stores` table.</t>
+          <t>References the unique identifier of the store associated with the purchase order, linking to the `stores.store_id` column.</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Indicates the current state of the purchase order, such as 'Ordered' or 'Received', stored as a non-nullable nvarchar value.</t>
+          <t>Indicates the current state of a purchase order, such as 'Ordered' or 'Received'.</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>The "order_date" column in the "purchase_orders" table stores the non-nullable date when the purchase order was placed.</t>
+          <t>The `order_date` column stores the non-null date when a purchase order was placed.</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>The "expected_date" column in the "purchase_orders" table stores the anticipated delivery date of a purchase order and allows null values.</t>
+          <t>The "expected_date" column in the "purchase_orders" table stores the anticipated delivery date of a purchase order, allowing null values.</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>The "created_at" column stores the non-nullable timestamp indicating when the purchase order record was created.</t>
+          <t>The `created_at` column stores the non-nullable timestamp indicating when the purchase order record was initially created.</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Tracks the timestamp of the most recent update to a purchase order record, stored as a non-nullable datetime value.</t>
+          <t>The `updated_at` column stores the non-null timestamp indicating the last modification date and time of a purchase order record.</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3314,7 +3314,7 @@
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Unique identifier for each sales order item, serving as the primary key in the sales_order_items table.</t>
+          <t>The `sales_order_item_id` column is a non-nullable bigint serving as the primary key for uniquely identifying records in the `sales_order_items` table.</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -3392,7 +3392,7 @@
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>References the unique identifier of the associated sales order in the sales_orders table.</t>
+          <t>Links each sales order item to its corresponding sales order in the `sales_orders` table via a non-null foreign key.</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3474,7 +3474,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Represents the unique identifier of a product associated with a sales order item, referencing the `product_id` column in the `products` table.</t>
+          <t>References the unique identifier of a product from the products table, establishing a mandatory relationship between sales order items and products.</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>The "quantity" column in the "sales_order_items" table stores a non-null integer representing the number of items in a sales order.</t>
+          <t>Represents the non-null integer quantity of a product in a sales order item.</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>The "unit_price" column stores the non-null numeric price per unit of a sales order item, with up to 15 digits and 2 decimal places, in a currency amount format.</t>
+          <t>Represents the non-null unit price of a sales order item, stored as a numeric value with up to 15 digits and 2 decimal places.</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Records the timestamp when the sales order item was created, stored as a non-nullable datetime value.</t>
+          <t>The `created_at` column records the non-nullable timestamp indicating when the sales order item was created.</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3834,7 +3834,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>The "updated_at" column stores the non-nullable timestamp of the last update made to a sales order item record.</t>
+          <t>The `updated_at` column in the `sales_order_items` table stores the non-nullable timestamp indicating the last update to a sales order item record.</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Represents the numeric value of the sold quantity for a sales order item, allowing nulls.</t>
+          <t>Represents the numeric value of the sold quantity for a sales order item, allowing up to two decimal places and nullable.</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -5268,7 +5268,7 @@
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Unique identifier for each sales order in the table.</t>
+          <t>The `sales_order_id` column is a non-nullable bigint serving as the primary key for uniquely identifying sales orders in the `sales_orders` table.</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>The "customer_id" column in the "sales_orders" table is a nullable bigint that references the "customer_id" column in the "customers" table, identifying the customer associated with a sales order.</t>
+          <t>Represents the identifier of the customer associated with the sales order, referencing the `customer_id` column in the `customers` table; nullable.</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -5510,7 +5510,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Represents the unique identifier of the employee associated with the sales order, referencing the employees table.</t>
+          <t>Represents the unique identifier of the employee associated with the sales order, referencing the `employees.employee_id` column.</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>The "order_date" column stores the date and time when a sales order was placed, using the datetime2 data type, and cannot be null.</t>
+          <t>The `order_date` column in the `sales_orders` table stores the non-nullable timestamp indicating when the sales order was placed.</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -5682,7 +5682,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Indicates the current state of a sales order, such as 'Pending' or 'Completed'.</t>
+          <t>Indicates the current state of a sales order, such as 'Pending' or 'Completed', stored as a non-nullable text category.</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -5768,7 +5768,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Represents the total monetary amount for a sales order, stored as a non-null numeric value with up to 12 digits and 2 decimal places.</t>
+          <t>The `total_amount` column stores the total monetary value of a sales order as a non-null numeric value with up to 12 digits, including 2 decimal places.</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -5854,7 +5854,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Records the timestamp when the sales order entry was created, stored as a non-nullable datetime value.</t>
+          <t>The "created_at" column in the "sales_orders" table stores the non-nullable timestamp indicating when the sales order record was created.</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>The "stores" table contains information about individual store locations, including identifiers, contact details, and timestamps for record creation and updates.</t>
+          <t>The `stores` table stores information about retail locations, including unique identifiers, names, contact details, addresses, and timestamps for record creation and updates.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -7054,7 +7054,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>The "store_id" column is a non-nullable bigint serving as the primary key for uniquely identifying each store in the "stores" table.</t>
+          <t>The `store_id` column is a non-nullable bigint serving as the primary key for uniquely identifying each store in the `stores` table.</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -7132,7 +7132,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>The "name" column in the "stores" table is a non-nullable nvarchar field intended to store the name of a store.</t>
+          <t>The "name" column in the "stores" table is a non-nullable nvarchar field intended to store the name of a store, though sample data is unavailable.</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -7210,7 +7210,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>A non-nullable nvarchar(450) column storing unique alphanumeric identifiers for stores.</t>
+          <t>The "code" column in the "stores" table is a non-nullable nvarchar(450) field intended to store unique identifiers or short codes for each store.</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -7284,7 +7284,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>The "address" column in the "stores" table stores the address of a store as a nullable nvarchar string.</t>
+          <t>Stores.address is an optional nvarchar column storing the physical address of a store, with case-insensitive collation.</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -7362,7 +7362,7 @@
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Stores.city is a nullable nvarchar column storing the name of the city where a store is located.</t>
+          <t>The "city" column in the "stores" table stores the name of the city where the store is located, allowing null values.</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -7432,7 +7432,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>This column stores the state or province associated with a store, allowing null values.</t>
+          <t>This nullable nvarchar column stores the state or province associated with a store's address.</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -7506,7 +7506,7 @@
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>The "postal_code" column in the "stores" table stores optional alphanumeric postal codes for store locations.</t>
+          <t>The "postal_code" column in the "stores" table stores the postal or ZIP code of a store as a nullable nvarchar string.</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -7596,7 +7596,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Stores.phone is an optional nvarchar column storing contact phone numbers for stores.</t>
+          <t>Stores.phone is an optional nvarchar column storing contact phone numbers for stores, formatted as text.</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -7682,7 +7682,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>The "created_at" column stores the non-nullable timestamp indicating when a store record was initially created.</t>
+          <t>The `created_at` column stores the non-nullable timestamp indicating when a store record was created.</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -7768,7 +7768,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>The "updated_at" column stores the non-nullable timestamp indicating the last update time of a store record.</t>
+          <t>The `updated_at` column in the `stores` table records the non-nullable timestamp of the most recent update to a store's record.</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -9106,7 +9106,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Unique identifier for each supplier, serving as the non-nullable primary key of the table.</t>
+          <t>Unique identifier for each supplier, serving as the primary key for the suppliers table.</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -9184,7 +9184,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Stores the name of the supplier as a non-null Unicode string.</t>
+          <t>The "name" column in the "suppliers" table is a non-nullable nvarchar field intended to store supplier names, though sample data indicates it is currently unused.</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9270,7 +9270,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Stores the name of the contact person for a supplier, allowing null values.</t>
+          <t>The "contact_name" column in the "suppliers" table stores the name of a contact person for the supplier, allowing null values.</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>The "email" column in the "suppliers" table stores the supplier's email address as a nullable nvarchar value with case-insensitive collation.</t>
+          <t>The "email" column in the "suppliers" table stores the email address of a supplier as a nullable nvarchar value, used for contact purposes.</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9442,7 +9442,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Stores the supplier's phone number as a nullable text field.</t>
+          <t>Stores the supplier's phone number as a nullable string, primarily for contact purposes.</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -9528,7 +9528,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>The "created_at" column stores the non-nullable timestamp indicating when a supplier record was created.</t>
+          <t>The `created_at` column stores the non-nullable timestamp indicating when a supplier record was created.</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -9614,7 +9614,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>The "updated_at" column stores the non-nullable timestamp of the last update to a supplier record.</t>
+          <t>The `updated_at` column stores the non-nullable timestamp of the most recent update to a supplier record in the `suppliers` table.</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{"metadata":{"generated_at":"2026-03-30T08:36:23.118377+00:00","database_url":"pioneertest.database.windows.net:1433/free-sql-db-3300567?driver=ODBC+Driver+18+for+SQL+Server&amp;TrustServerCertificate=yes","schema_filter":"dbo","total_tables":10,"total_rows":1364,"total_findings":64},"connection":{"host":"pioneertest.database.windows.net","port":"1433","database":"free-sql-db-3300567","driver":"mssql","timezone":"(UTC) Coordinated Universal Time"},"source_system_context":{"contacts":[],"delete_management_instruction":"","restrictions":"","late_arriving_data_manual":"","volume_size_projection_manual":"","system_description":"","db_analysis_config":{"exclude_schemas":["prediction"],"exclude_tables":[],"max_row_limit":100}},"concept_registry":{"version":1,"taxonomy":"domain-dot","generated_from_tables":10,"concepts":[{"concept_id":"contact.address","column_count":2,"table_count":1,"avg_confidence":0.55,"alias_groups":["address","postal_code"],"sample_columns":["stores.address","stores.postal_code"],"signals":["name","type"]},{"concept_id":"contact.email","column_count":3,"table_count":3,"avg_confidence":1.0,"alias_groups":["email"],"sample_columns":["customers.email","employees.email","suppliers.email"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"contact.person_name","column_count":8,"table_count":5,"avg_confidence":0.56,"alias_groups":["contact_name","first_name","last_name","name"],"sample_columns":["customers.first_name","customers.last_name","employees.first_name","employees.last_name","products.name"],"signals":["name","table_context","type"]},{"concept_id":"contact.phone","column_count":3,"table_count":3,"avg_confidence":1.0,"alias_groups":["phone"],"sample_columns":["customers.phone","stores.phone","suppliers.phone"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"entity.category","column_count":1,"table_count":1,"avg_confidence":0.8,"alias_groups":["category"],"sample_columns":["products.category"],"signals":["name","profile","type"]},{"concept_id":"entity.status","column_count":2,"table_count":2,"avg_confidence":1.0,"alias_groups":["statu"],"sample_columns":["purchase_orders.status","sales_orders.status"],"signals":["name","profile","type","values"]},{"concept_id":"entity.type","column_count":1,"table_count":1,"avg_confidence":0.65,"alias_groups":["role"],"sample_columns":["employees.role"],"signals":["name","profile","type"]},{"concept_id":"finance.currency_amount","column_count":5,"table_count":4,"avg_confidence":1.0,"alias_groups":["amount","price","unit_cost"],"sample_columns":["products.unit_price","products.cost_price","purchase_order_items.unit_cost","sales_order_items.unit_price","sales_orders.total_amount"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"identifier.foreign_key","column_count":26,"table_count":10,"avg_confidence":0.78,"alias_groups":["id"],"sample_columns":["customers.customer_id","employees.employee_id","employees.store_id","inventory.inventory_id","inventory.store_id"],"signals":["cross_table_consensus","name","profile","type"]},{"concept_id":"identifier.product_code","column_count":1,"table_count":1,"avg_confidence":0.7,"alias_groups":["sku"],"sample_columns":["products.sku"],"signals":["name","profile","type"]},{"concept_id":"measure.quantity","column_count":7,"table_count":3,"avg_confidence":1.0,"alias_groups":["ordered_qty","ordered_qty_unit","quantity","quantity_on_hand","sold_qty","sold_qty_unit"],"sample_columns":["inventory.quantity_on_hand","purchase_order_items.quantity","purchase_order_items.ordered_qty_value","purchase_order_items.ordered_qty_unit","sales_order_items.quantity"],"signals":["name","profile","type","values"]},{"concept_id":"temporal.created_at","column_count":10,"table_count":10,"avg_confidence":1.0,"alias_groups":["created_at"],"sample_columns":["customers.created_at","employees.created_at","inventory.created_at","products.created_at","purchase_order_items.created_at"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"temporal.date_only","column_count":4,"table_count":3,"avg_confidence":0.97,"alias_groups":["expected_date","hire_date","order_date"],"sample_columns":["employees.hire_date","purchase_orders.order_date","purchase_orders.expected_date","sales_orders.order_date"],"signals":["cross_table_consensus","name","profile","table_context","type","values"]},{"concept_id":"temporal.event_time","column_count":1,"table_count":1,"avg_confidence":1.0,"alias_groups":["last_restocked_at"],"sample_columns":["inventory.last_restocked_at"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"temporal.updated_at","column_count":10,"table_count":10,"avg_confidence":1.0,"alias_groups":["updated_at"],"sample_columns":["customers.updated_at","employees.updated_at","inventory.updated_at","products.updated_at","purchase_order_items.updated_at"],"signals":["name","profile","table_context","type","values"]}]},"data_quality_summary":{"critical":0,"warning":27,"info":37,"by_check":{"controlled_value_candidate":7,"nullable_but_never_null":13,"missing_primary_key":0,"missing_foreign_key":0,"format_inconsistency":0,"range_violation":0,"timestamp_ordering":10,"delete_management":10,"late_arriving_data":3,"timezone":10,"unit_unknown":11,"unit_noncanonical_but_convertible":0,"unit_mismatch_within_semantic_group":0},"constraints_found":{"check_constraints":0,"enum_columns":0,"unique_constraints":10}},"tables":[{"table":"customers","schema":"dbo","columns":[{"name":"customer_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for each customer, serving as the primary key for the customers table.","cardinality":100,"null_count":0,"data_range":{"min":"404","max":"503"},"data_category":"discrete","semantic_class":"customer_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"first_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"The \"first_name\" column in the \"customers\" table stores non-nullable given names of customers as nvarchar strings using the \"SQL_Latin1_General_CP1_CI_AS\" collation.","cardinality":100,"null_count":0,"data_range":{"min":"Customer1","max":"Customer99"},"data_category":"nominal","semantic_class":"given_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.6,"concept_evidence":["name token: first_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","table context: customers"],"concept_sources":["name","table_context","type"],"concept_alias_group":"first_name"},{"name":"last_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"The \"last_name\" column in the \"customers\" table stores the non-nullable family name of a customer as a case-insensitive Unicode string.","cardinality":100,"null_count":0,"data_range":{"min":"LastName1 (updated)","max":"LastName99"},"data_category":"nominal","semantic_class":"family_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.6,"concept_evidence":["name token: last_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","table context: customers"],"concept_sources":["name","table_context","type"],"concept_alias_group":"last_name"},{"name":"email","type":"nvarchar(450)","nullable":true,"is_incremental":false,"column_description":"Stores the customer's email address, allowing up to 450 Unicode characters, and can be null.","cardinality":100,"null_count":0,"data_range":{"min":"customer1@example.com","max":"customer99@example.com"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.email","concept_confidence":1.0,"concept_evidence":["name token: email","type hint: nvarchar(450)","legacy field classification: contact","value pattern: email","table context: customers","sensitive hint: pii_contact"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"email"},{"name":"phone","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"Stores the customer's phone number as a nullable Unicode string.","cardinality":100,"null_count":0,"data_range":{"min":"555-1001","max":"555-1100"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.phone","concept_confidence":1.0,"concept_evidence":["name token: phone","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: contact","value pattern: phone","table context: customers","sensitive hint: pii_contact"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"phone"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The \"created_at\" column stores the non-nullable timestamp indicating when a customer record was created.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":95,"null_count":0,"data_range":{"min":"2021-03-23 15:38:57.201565","max":"2026-02-26 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: customers"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The \"updated_at\" column stores the timestamp of the most recent update to a customer record and is required (non-null).","column_timezone":"(UTC) Coordinated Universal Time","cardinality":95,"null_count":0,"data_range":{"min":"2021-03-23 15:38:57.201565","max":"2026-03-26 08:52:49.252228"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: customers"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"}],"table_description":"The \"customers\" table stores information about customers, including their unique ID, name, contact details, and timestamps for record creation and updates.","primary_keys":["customer_id"],"foreign_keys":[],"row_count":100,"field_classifications":{"customer_id":"identifier","first_name":"person_name","last_name":"person_name","email":"contact","phone":"contact","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{"email":"pii_contact","phone":"pii_contact"},"incremental_columns":["updated_at"],"join_candidates":[],"unit_summary":{"columns_with_units":0,"columns_without_units":7,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":false,"has_sensitive_fields":true,"row_count_projection_1y":126,"row_count_projection_2y":152,"row_count_projection_5y":232,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.email":1,"contact.person_name":2,"contact.phone":1,"identifier.foreign_key":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"findings":[{"column":"email","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 100 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"phone","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 100 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}},{"table":"employees","schema":"dbo","columns":[{"name":"employee_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"The \"employee_id\" column is a non-nullable bigint serving as the primary key for uniquely identifying employees in the \"employees\" table.","cardinality":20,"null_count":0,"data_range":{"min":"64","max":"83"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Represents the identifier of the store associated with an employee, referencing the `store_id` column in the `stores` table.","cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"first_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"The \"first_name\" column in the \"employees\" table stores the given name of an employee as a non-null, case-insensitive Unicode string.","cardinality":20,"null_count":0,"data_range":{"min":"Employee1","max":"Employee9"},"data_category":"nominal","semantic_class":"given_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: first_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"first_name"},{"name":"last_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"The \"last_name\" column in the \"employees\" table stores the non-nullable family name of an employee as a case-insensitive Unicode string.","cardinality":20,"null_count":0,"data_range":{"min":"LastName1","max":"LastName9"},"data_category":"nominal","semantic_class":"family_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: last_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"last_name"},{"name":"email","type":"nvarchar(450)","nullable":false,"is_incremental":false,"column_description":"Stores the unique email address of an employee as a non-null nvarchar value up to 450 characters.","cardinality":20,"null_count":0,"data_range":{"min":"emp1@example.com","max":"emp9@example.com"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.email","concept_confidence":1.0,"concept_evidence":["name token: email","type hint: nvarchar(450)","legacy field classification: contact","value pattern: email","sensitive hint: pii_contact"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"email"},{"name":"role","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"Stores the job role of an employee as a non-null, case-insensitive string.","cardinality":4,"null_count":0,"data_range":{"min":"Cashier","max":"Stock"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"entity.type","concept_confidence":0.65,"concept_evidence":["name token: role","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","profile heuristic matched"],"concept_sources":["name","profile","type"],"concept_alias_group":"role"},{"name":"hire_date","type":"date","nullable":false,"is_incremental":false,"column_description":"The \"hire_date\" column in the \"employees\" table stores the non-nullable date an employee was hired.","cardinality":20,"null_count":0,"data_range":{"min":"2021-05-03","max":"2025-01-26"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.date_only","concept_confidence":1.0,"concept_evidence":["name token: hire_date","type hint: date","legacy field classification: temporal","value pattern: date_only","table context: employees"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"hire_date"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The \"created_at\" column stores the non-nullable timestamp indicating when the employee record was created.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":20,"null_count":0,"data_range":{"min":"2021-05-03 15:38:57.201565","max":"2025-01-26 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: employees"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The \"updated_at\" column stores the non-nullable timestamp of the most recent update to an employee record.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":20,"null_count":0,"data_range":{"min":"2021-05-03 15:38:57.201565","max":"2025-01-26 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: employees"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"}],"table_description":"The \"employees\" table stores information about employees, including their unique identifier, associated store, personal details, job role, hire date, and record timestamps.","primary_keys":["employee_id"],"foreign_keys":[{"column":"store_id","references":"stores.store_id"}],"row_count":20,"field_classifications":{"first_name":"person_name","last_name":"person_name","email":"contact","hire_date":"temporal","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{"email":"pii_contact"},"incremental_columns":["updated_at"],"join_candidates":[{"column":"store_id","target_table":"stores","target_column":"store_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":9,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":true,"row_count_projection_1y":35,"row_count_projection_2y":50,"row_count_projection_5y":96,"partition_columns_candidates":["hire_date","created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.email":1,"contact.person_name":2,"entity.type":1,"identifier.foreign_key":2,"temporal.created_at":1,"temporal.date_only":1,"temporal.updated_at":1},"low_confidence_columns":["first_name","last_name"]},"data_quality":{"findings":[{"column":"role","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 4 distinct value(s) ('Cashier', 'Manager', 'Sales', 'Stock') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Cashier","Manager","Sales","Stock"],"cardinality":4},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":"hire_date","check":"late_arriving_data","severity":"info","detail":"Minor arrival delay \u2014 max lag between 'hire_date' and 'created_at' is 15.7h (avg 15.7h, P95 15.7h).","recommendation":"Use 'created_at' as the watermark (preferred). If using 'hire_date', add a 1\u20132 day lookback buffer.","business_date_column":"hire_date","system_ts_column":"created_at","lag_stats":{"total_rows_compared":20,"min_lag_hours":15.65,"avg_lag_hours":15.65,"p95_lag_hours":15.65,"max_lag_hours":15.65,"max_lag_days":0.7,"rows_late_over_1d":0,"rows_late_over_7d":0},"recommended_lookback_days":2},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}},{"table":"inventory","schema":"dbo","columns":[{"name":"inventory_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"The `inventory_id` column is a non-nullable bigint serving as the primary key for uniquely identifying records in the `inventory` table.","cardinality":100,"null_count":0,"data_range":{"min":"8","max":"107"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Represents the unique identifier of a store, referencing the `store_id` column in the `stores` table.","cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"product_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"References the unique identifier of a product in the products table, establishing a foreign key relationship.","cardinality":47,"null_count":0,"data_range":{"min":"156","max":"205"},"data_category":"discrete","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"quantity_on_hand","type":"integer","nullable":false,"is_incremental":false,"column_description":"Represents the current quantity of a product in stock, stored as a non-null integer.","cardinality":68,"null_count":0,"data_range":{"min":"2","max":"98"},"data_category":"discrete","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: quantity_on_hand","type hint: integer","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"quantity_on_hand"},{"name":"reorder_level","type":"integer","nullable":false,"is_incremental":false,"column_description":"Indicates the minimum stock quantity at which inventory should be reordered, stored as a non-null integer.","cardinality":20,"null_count":0,"data_range":{"min":"10","max":"29"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: integer","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"last_restocked_at","type":"datetime2","nullable":true,"is_incremental":false,"column_description":"The \"last_restocked_at\" column records the timestamp of the most recent restocking event for an inventory item and allows null values.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":89,"null_count":0,"data_range":{"min":"2024-03-14 15:38:57.201565","max":"2026-03-07 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.event_time","concept_confidence":1.0,"concept_evidence":["name token: last_restocked_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: inventory"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"last_restocked_at"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The `created_at` column in the `inventory` table stores the non-nullable timestamp indicating when a record was initially created.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":91,"null_count":0,"data_range":{"min":"2024-03-05 15:38:57.201565","max":"2026-02-23 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: inventory"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The `updated_at` column in the `inventory` table stores the non-nullable timestamp indicating the last update to a record.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":89,"null_count":0,"data_range":{"min":"2024-03-14 15:38:57.201565","max":"2026-03-07 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: inventory"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"stock_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"column_description":"Represents the monetary value of stock for an inventory item, stored as a numeric value with up to 10 digits and 2 decimal places, and may be null.","cardinality":0,"null_count":100,"data_category":"continuous","semantic_class":null,"unit_context":null,"concept_id":null,"co</t>
+          <t>{"metadata":{"generated_at":"2026-04-01T10:39:15.579372+00:00","database_url":"pioneertest.database.windows.net:1433/free-sql-db-3300567?driver=ODBC+Driver+18+for+SQL+Server&amp;TrustServerCertificate=yes","schema_filter":"dbo","total_tables":10,"total_rows":1364,"total_findings":64},"connection":{"host":"pioneertest.database.windows.net","port":"1433","database":"free-sql-db-3300567","driver":"mssql","timezone":"(UTC) Coordinated Universal Time"},"source_system_context":{"contacts":[],"delete_management_instruction":"","restrictions":"","late_arriving_data_manual":"","volume_size_projection_manual":"","system_description":"Retail operations source system covering customers, stores, employees, suppliers, products, inventory, purchase orders, and sales orders used for day-to-day store, procurement, and sales transaction management.","db_analysis_config":{"exclude_schemas":["prediction"],"exclude_tables":[],"max_row_limit":100}},"concept_registry":{"version":1,"taxonomy":"domain-dot","generated_from_tables":10,"concepts":[{"concept_id":"contact.address","column_count":2,"table_count":1,"avg_confidence":0.55,"alias_groups":["address","postal_code"],"sample_columns":["stores.address","stores.postal_code"],"signals":["name","type"]},{"concept_id":"contact.email","column_count":3,"table_count":3,"avg_confidence":1.0,"alias_groups":["email"],"sample_columns":["customers.email","employees.email","suppliers.email"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"contact.person_name","column_count":8,"table_count":5,"avg_confidence":0.56,"alias_groups":["contact_name","first_name","last_name","name"],"sample_columns":["customers.first_name","customers.last_name","employees.first_name","employees.last_name","products.name"],"signals":["name","table_context","type"]},{"concept_id":"contact.phone","column_count":3,"table_count":3,"avg_confidence":1.0,"alias_groups":["phone"],"sample_columns":["customers.phone","stores.phone","suppliers.phone"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"entity.category","column_count":1,"table_count":1,"avg_confidence":0.8,"alias_groups":["category"],"sample_columns":["products.category"],"signals":["name","profile","type"]},{"concept_id":"entity.status","column_count":2,"table_count":2,"avg_confidence":1.0,"alias_groups":["statu"],"sample_columns":["purchase_orders.status","sales_orders.status"],"signals":["name","profile","type","values"]},{"concept_id":"entity.type","column_count":1,"table_count":1,"avg_confidence":0.65,"alias_groups":["role"],"sample_columns":["employees.role"],"signals":["name","profile","type"]},{"concept_id":"finance.currency_amount","column_count":5,"table_count":4,"avg_confidence":1.0,"alias_groups":["amount","price","unit_cost"],"sample_columns":["products.unit_price","products.cost_price","purchase_order_items.unit_cost","sales_order_items.unit_price","sales_orders.total_amount"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"identifier.foreign_key","column_count":26,"table_count":10,"avg_confidence":0.78,"alias_groups":["id"],"sample_columns":["customers.customer_id","employees.employee_id","employees.store_id","inventory.inventory_id","inventory.store_id"],"signals":["cross_table_consensus","name","profile","type"]},{"concept_id":"identifier.product_code","column_count":1,"table_count":1,"avg_confidence":0.7,"alias_groups":["sku"],"sample_columns":["products.sku"],"signals":["name","profile","type"]},{"concept_id":"measure.quantity","column_count":7,"table_count":3,"avg_confidence":1.0,"alias_groups":["ordered_qty","ordered_qty_unit","quantity","quantity_on_hand","sold_qty","sold_qty_unit"],"sample_columns":["inventory.quantity_on_hand","purchase_order_items.quantity","purchase_order_items.ordered_qty_value","purchase_order_items.ordered_qty_unit","sales_order_items.quantity"],"signals":["name","profile","type","values"]},{"concept_id":"temporal.created_at","column_count":10,"table_count":10,"avg_confidence":1.0,"alias_groups":["created_at"],"sample_columns":["customers.created_at","employees.created_at","inventory.created_at","products.created_at","purchase_order_items.created_at"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"temporal.date_only","column_count":4,"table_count":3,"avg_confidence":0.97,"alias_groups":["expected_date","hire_date","order_date"],"sample_columns":["employees.hire_date","purchase_orders.order_date","purchase_orders.expected_date","sales_orders.order_date"],"signals":["cross_table_consensus","name","profile","table_context","type","values"]},{"concept_id":"temporal.event_time","column_count":1,"table_count":1,"avg_confidence":1.0,"alias_groups":["last_restocked_at"],"sample_columns":["inventory.last_restocked_at"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"temporal.updated_at","column_count":10,"table_count":10,"avg_confidence":1.0,"alias_groups":["updated_at"],"sample_columns":["customers.updated_at","employees.updated_at","inventory.updated_at","products.updated_at","purchase_order_items.updated_at"],"signals":["name","profile","table_context","type","values"]}]},"data_quality_summary":{"critical":0,"warning":27,"info":37,"by_check":{"controlled_value_candidate":7,"nullable_but_never_null":13,"missing_primary_key":0,"missing_foreign_key":0,"format_inconsistency":0,"range_violation":0,"timestamp_ordering":10,"delete_management":10,"late_arriving_data":3,"timezone":10,"unit_unknown":11,"unit_noncanonical_but_convertible":0,"unit_mismatch_within_semantic_group":0},"constraints_found":{"check_constraints":0,"enum_columns":0,"unique_constraints":10}},"tables":[{"table":"customers","schema":"dbo","columns":[{"name":"customer_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"The `customer_id` column is a non-nullable bigint serving as the primary key and unique identifier for each customer in the `customers` table.","cardinality":100,"null_count":0,"data_range":{"min":"404","max":"503"},"data_category":"discrete","semantic_class":"customer_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"first_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"The \"first_name\" column in the \"customers\" table stores non-nullable given names as nvarchar strings using the \"sql_latin1_general_cp1_ci_as\" collation.","cardinality":100,"null_count":0,"data_range":{"min":"Customer1","max":"Customer99"},"data_category":"nominal","semantic_class":"given_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.6,"concept_evidence":["name token: first_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","table context: customers"],"concept_sources":["name","table_context","type"],"concept_alias_group":"first_name"},{"name":"last_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"The \"last_name\" column in the \"customers\" table stores the non-nullable family name of a customer as a case-insensitive Unicode string.","cardinality":100,"null_count":0,"data_range":{"min":"LastName1 (updated)","max":"LastName99"},"data_category":"nominal","semantic_class":"family_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.6,"concept_evidence":["name token: last_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","table context: customers"],"concept_sources":["name","table_context","type"],"concept_alias_group":"last_name"},{"name":"email","type":"nvarchar(450)","nullable":true,"is_incremental":false,"column_description":"Stores the customer's email address, allowing null values, with a maximum length of 450 characters.","cardinality":100,"null_count":0,"data_range":{"min":"customer1@example.com","max":"customer99@example.com"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.email","concept_confidence":1.0,"concept_evidence":["name token: email","type hint: nvarchar(450)","legacy field classification: contact","value pattern: email","table context: customers","sensitive hint: pii_contact"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"email"},{"name":"phone","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"Stores the customer's phone number as a nullable text field with case-insensitive collation.","cardinality":100,"null_count":0,"data_range":{"min":"555-1001","max":"555-1100"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.phone","concept_confidence":1.0,"concept_evidence":["name token: phone","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: contact","value pattern: phone","table context: customers","sensitive hint: pii_contact"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"phone"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The `created_at` column stores the non-nullable timestamp indicating when a customer record was initially created.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":95,"null_count":0,"data_range":{"min":"2021-03-23 15:38:57.201565","max":"2026-02-26 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: customers"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The `updated_at` column stores the non-nullable timestamp of the most recent update to a customer's record.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":95,"null_count":0,"data_range":{"min":"2021-03-23 15:38:57.201565","max":"2026-03-26 08:52:49.252228"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: customers"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"}],"table_description":"The `customers` table stores information about customers, including their unique identifier, name, contact details, and timestamps for record creation and updates.","primary_keys":["customer_id"],"foreign_keys":[],"row_count":100,"field_classifications":{"customer_id":"identifier","first_name":"person_name","last_name":"person_name","email":"contact","phone":"contact","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{"email":"pii_contact","phone":"pii_contact"},"incremental_columns":["updated_at"],"join_candidates":[],"unit_summary":{"columns_with_units":0,"columns_without_units":7,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":false,"has_sensitive_fields":true,"row_count_projection_1y":126,"row_count_projection_2y":152,"row_count_projection_5y":232,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.email":1,"contact.person_name":2,"contact.phone":1,"identifier.foreign_key":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"findings":[{"column":"email","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 100 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"phone","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 100 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}},{"table":"employees","schema":"dbo","columns":[{"name":"employee_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"The `employee_id` column is a non-nullable bigint serving as the primary key for uniquely identifying employees in the `employees` table.","cardinality":20,"null_count":0,"data_range":{"min":"64","max":"83"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"The `store_id` column in the `employees` table is a non-nullable bigint that serves as a foreign key referencing the `store_id` column in the `stores` table.","cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"first_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"The \"first_name\" column in the \"employees\" table stores the given name of an employee as a non-null, case-insensitive Unicode string.","cardinality":20,"null_count":0,"data_range":{"min":"Employee1","max":"Employee9"},"data_category":"nominal","semantic_class":"given_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: first_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"first_name"},{"name":"last_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"The \"last_name\" column in the \"employees\" table stores the non-nullable family name of an employee as a case-insensitive Unicode string.","cardinality":20,"null_count":0,"data_range":{"min":"LastName1","max":"LastName9"},"data_category":"nominal","semantic_class":"family_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: last_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"last_name"},{"name":"email","type":"nvarchar(450)","nullable":false,"is_incremental":false,"column_description":"The \"email\" column stores the unique email address of each employee as a non-null nvarchar string with a maximum length of 450 characters.","cardinality":20,"null_count":0,"data_range":{"min":"emp1@example.com","max":"emp9@example.com"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.email","concept_confidence":1.0,"concept_evidence":["name token: email","type hint: nvarchar(450)","legacy field classification: contact","value pattern: email","sensitive hint: pii_contact"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"email"},{"name":"role","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"The \"role\" column in the \"employees\" table stores the job title or position of an employee as a non-null nvarchar string.","cardinality":4,"null_count":0,"data_range":{"min":"Cashier","max":"Stock"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"entity.type","concept_confidence":0.65,"concept_evidence":["name token: role","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","profile heuristic matched"],"concept_sources":["name","profile","type"],"concept_alias_group":"role"},{"name":"hire_date","type":"date","nullable":false,"is_incremental":false,"column_description":"The `hire_date` column stores the non-null date an employee was hired.","cardinality":20,"null_count":0,"data_range":{"min":"2021-05-03","max":"2025-01-26"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.date_only","concept_confidence":1.0,"concept_evidence":["name token: hire_date","type hint: date","legacy field classification: temporal","value pattern: date_only","table context: employees"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"hire_date"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The \"created_at\" column stores the non-nullable timestamp indicating when the employee record was initially created.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":20,"null_count":0,"data_range":{"min":"2021-05-03 15:38:57.201565","max":"2025-01-26 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: employees"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The `updated_at` column stores the non-nullable timestamp indicating the last update time for an employee record.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":20,"null_count":0,"data_range":{"min":"2021-05-03 15:38:57.201565","max":"2025-01-26 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: employees"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"}],"table_description":"The `employees` table stores information about employees, including their unique ID, associated store, personal details, role, hire date, and record timestamps.","primary_keys":["employee_id"],"foreign_keys":[{"column":"store_id","references":"stores.store_id"}],"row_count":20,"field_classifications":{"first_name":"person_name","last_name":"person_name","email":"contact","hire_date":"temporal","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{"email":"pii_contact"},"incremental_columns":["updated_at"],"join_candidates":[{"column":"store_id","target_table":"stores","target_column":"store_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":9,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":true,"row_count_projection_1y":35,"row_count_projection_2y":50,"row_count_projection_5y":96,"partition_columns_candidates":["hire_date","created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.email":1,"contact.person_name":2,"entity.type":1,"identifier.foreign_key":2,"temporal.created_at":1,"temporal.date_only":1,"temporal.updated_at":1},"low_confidence_columns":["first_name","last_name"]},"data_quality":{"findings":[{"column":"role","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 4 distinct value(s) ('Cashier', 'Manager', 'Sales', 'Stock') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Cashier","Manager","Sales","Stock"],"cardinality":4},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":"hire_date","check":"late_arriving_data","severity":"info","detail":"Minor arrival delay \u2014 max lag between 'hire_date' and 'created_at' is 15.7h (avg 15.7h, P95 15.7h).","recommendation":"Use 'created_at' as the watermark (preferred). If using 'hire_date', add a 1\u20132 day lookback buffer.","business_date_column":"hire_date","system_ts_column":"created_at","lag_stats":{"total_rows_compared":20,"min_lag_hours":15.65,"avg_lag_hours":15.65,"p95_lag_hours":15.65,"max_lag_hours":15.65,"max_lag_days":0.7,"rows_late_over_1d":0,"rows_late_over_7d":0},"recommended_lookback_days":2},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}},{"table":"inventory","schema":"dbo","columns":[{"name":"inventory_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"The `inventory_id` column is a non-nullable bigint serving as the primary key for uniquely identifying records in the `inventory` table.","cardinality":100,"null_count":0,"data_range":{"min":"8","max":"107"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"The `store_id` column in the `inventory` table is a non-nullable bigint that references the `store_id` column in the `stores` table, establishing a foreign key relationship.","cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"product_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"References the unique identifier of a product from the products table, establishing a foreign key relationship.","cardinality":47,"null_count":0,"data_range":{"min":"156","max":"205"},"data_category":"discrete","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"quantity_on_hand","type":"integer","nullable":false,"is_incremental":false,"column_description":"Tracks the current stock quantity of an item in inventory, stored as a non-null integer.","cardinality":68,"null_count":0,"data_range":{"min":"2","max":"98"},"data_category":"discrete","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: quantity_on_hand","type hint: integer","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"quantity_on_hand"},{"name":"reorder_level","type":"integer","nullable":false,"is_incremental":false,"column_description":"The `reorder_level` column in the `inventory` table stores a non-null integer indicating the threshold quantity at which stock should be reordered.","cardinality":20,"null_count":0,"data_range":{"min":"10","max":"29"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: integer","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"last_restocked_at","type":"datetime2","nullable":true,"is_incremental":false,"column_description":"The `last_restocked_at` column records the timestamp of the most recent inventory restocking event and allows null values.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":89,"null_count":0,"data_range":{"min":"2024-03-14 15:38:57.201565","max":"2026-03-07 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.event_time","concept_confidence":1.0,"concept_evidence":["name token: last_restocked_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: inventory"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"last_restocked_at"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The \"created_at\" column stores the non-nullable timestamp indicating when the inventory record was initially created.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":91,"null_count":0,"data_range":{"min":"2024-03-05 15:38:57.201565","max":"2026-02-23 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: inventory"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The `updated_at` column in the `inventory` table stores the non-null timestamp of the most recent update to a record, using the `datetime2` data type.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":89,"null_count":0,"data_range":{"min":"2024-03-14 15:38:57.201565","max":"2026-03-07 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ncept_confidence":0.0,"concept_evidence":["type hint: numeric(10,2)","ambiguous runner-up concept"],"concept_sources":["type"],"concept_alias_group":null},{"name":"stock_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Current stock unit label.","cardinality":0,"null_count":100,"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.15,"concept_evidence":["value pattern: quantity","ambiguous runner-up concept"],"concept_sources":["values"],"concept_alias_group":null}],"table_description":"Current stock levels with normalized stock unit representation.","primary_keys":["inventory_id"],"foreign_keys":[{"column":"product_id","references":"products.product_id"},{"column":"store_id","references":"stores.store_id"}],"row_count":100,"field_classifications":{"quantity_on_hand":"quantity","last_restocked_at":"temporal","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"product_id","target_table":"products","target_column":"product_id","confidence":"high"},{"column":"store_id","target_table":"stores","target_column":"store_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":10,"mixed_unit_groups":[],"unknown_unit_columns":["quantity_on_hand"]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":146,"row_count_projection_2y":193,"row_count_projection_5y":334,"partition_columns_candidates":["last_restocked_at","created_at","updated_at"],"classification_summary":{"concept_counts":{"identifier.foreign_key":3,"measure.quantity":1,"temporal.created_at":1,"temporal.event_time":1,"temporal.updated_at":1},"low_confidence_columns":["reorder_level","stock_unit"]},"data_quality":{"findings":[{"column":"last_restocked_at","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 100 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 3 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"last_restocked_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":3},{"column":"quantity_on_hand","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."}]}},{"table":"products","schema":"dbo","columns":[{"name":"product_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"The `product_id` column is a non-nullable bigint serving as the primary key for uniquely identifying products in the `products` table.","cardinality":50,"null_count":0,"data_range":{"min":"156","max":"205"},"data_category":"discrete","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"supplier_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Represents the unique identifier of the supplier associated with a product, referencing the `supplier_id` column in the `suppliers` table.","cardinality":10,"null_count":0,"data_range":{"min":"33","max":"42"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"sku","type":"nvarchar(450)","nullable":false,"is_incremental":false,"column_description":"The \"sku\" column stores a unique alphanumeric identifier for products, with a maximum length of 450 characters, and cannot be null.","cardinality":50,"null_count":0,"data_range":{"min":"SKU-0001","max":"SKU-0050"},"data_category":"nominal","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.product_code","concept_confidence":0.7,"concept_evidence":["name token: sku","type hint: nvarchar(450)","semantic class hint: product_identifier"],"concept_sources":["name","profile","type"],"concept_alias_group":"sku"},{"name":"name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"Stores the name of the product as a non-null Unicode string.","cardinality":50,"null_count":0,"data_range":{"min":"Product 1","max":"Product 9"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"name"},{"name":"category","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"Indicates the category of the product, stored as a non-null case-insensitive Unicode string.","cardinality":5,"null_count":0,"data_range":{"min":"Books","max":"Sports"},"data_category":"nominal","semantic_class":"category","unit_context":null,"concept_id":"entity.category","concept_confidence":0.8,"concept_evidence":["name token: category","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: categorical","profile heuristic matched"],"concept_sources":["name","profile","type"],"concept_alias_group":"category"},{"name":"unit_price","type":"numeric(10,2)","nullable":false,"is_incremental":false,"column_description":"Stores the price per unit of a product as a non-null numeric value with up to 10 digits and 2 decimal places.","cardinality":50,"null_count":0,"data_range":{"min":"11.09","max":"490.43"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: price","type hint: numeric(10,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"price"},{"name":"cost_price","type":"numeric(10,2)","nullable":false,"is_incremental":false,"column_description":"Represents the non-null numeric cost price of a product, stored with up to 10 digits and 2 decimal places.","cardinality":50,"null_count":0,"data_range":{"min":"5.55","max":"358.59"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: price","type hint: numeric(10,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"price"},{"name":"active","type":"bit","nullable":false,"is_incremental":false,"column_description":"Indicates whether the product is active (True) or inactive (False).","cardinality":1,"null_count":0,"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.0,"concept_evidence":["profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile"],"concept_alias_group":null},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"Indicates the timestamp when the product record was created, stored as a non-nullable datetime2 value.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":50,"null_count":0,"data_range":{"min":"2021-03-20 15:38:57.201565","max":"2024-12-25 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: products"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The \"updated_at\" column stores the non-nullable timestamp of the last update made to a product record.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":50,"null_count":0,"data_range":{"min":"2021-03-20 15:38:57.201565","max":"2024-12-25 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: products"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"weight_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Source weight unit (kg/lb) used for unit inference testing.","cardinality":0,"null_count":50,"data_category":"nominal","semantic_class":"mass","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":null,"concept_confidence":0.15,"concept_evidence":["value pattern: quantity","ambiguous runner-up concept"],"concept_sources":["values"],"concept_alias_group":null},{"name":"weight_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"column_description":"Stores the weight of the product as a numeric value with up to 10 digits and 2 decimal places, nullable.","cardinality":0,"null_count":50,"data_category":"continuous","semantic_class":"mass","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":null,"concept_confidence":0.0,"concept_evidence":["type hint: numeric(10,2)","ambiguous runner-up concept"],"concept_sources":["type"],"concept_alias_group":null},{"name":"length_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"column_description":"Stores the length measurement of a product as a numeric value with up to 10 digits and 2 decimal places, which can be null.","cardinality":0,"null_count":50,"data_category":"continuous","semantic_class":"length","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":null,"concept_confidence":0.0,"concept_evidence":["type hint: numeric(10,2)","ambiguous runner-up concept"],"concept_sources":["type"],"concept_alias_group":null},{"name":"length_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Source length unit (cm/in) used for unit inference testing.","cardinality":0,"null_count":50,"data_category":"nominal","semantic_class":"length","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":null,"concept_confidence":0.15,"concept_evidence":["value pattern: quantity","ambiguous runner-up concept"],"concept_sources":["values"],"concept_alias_group":null},{"name":"product_description","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"Stores an optional textual description of the product.","cardinality":0,"null_count":50,"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"primary_supplier_id","type":"bigint","nullable":true,"is_incremental":false,"column_description":"Primary supplier relationship used for join candidate detection.","cardinality":10,"null_count":0,"data_range":{"min":"33","max":"42"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"}],"table_description":"Master product catalog including physical units for analyzer unit-context testing.","primary_keys":["product_id"],"foreign_keys":[{"column":"primary_supplier_id","references":"suppliers.supplier_id"},{"column":"supplier_id","references":"suppliers.supplier_id"}],"row_count":50,"field_classifications":{"category":"categorical","unit_price":"pricing","cost_price":"pricing","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"primary_supplier_id","target_table":"suppliers","target_column":"supplier_id","confidence":"high"},{"column":"supplier_id","target_table":"suppliers","target_column":"supplier_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":16,"mixed_unit_groups":[],"unknown_unit_columns":["length_unit","length_value","weight_unit","weight_value"]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":68,"row_count_projection_2y":86,"row_count_projection_5y":141,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.person_name":1,"entity.category":1,"finance.currency_amount":2,"identifier.foreign_key":3,"identifier.product_code":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":["length_unit","name","product_description","weight_unit"]},"data_quality":{"findings":[{"column":"category","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 5 distinct value(s) ('Books', 'Clothing', 'Electronics', 'Home', 'Sports') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Books","Clothing","Electronics","Home","Sports"],"cardinality":5},{"column":"primary_supplier_id","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 50 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":"active","check":"delete_management","severity":"info","detail":"Active-flag column 'active' (boolean) detected \u2014 rows with active=false are logically deleted. Current distribution: True=50.","recommendation":"Filter on \"active\" = true for current records during ingestion.","delete_strategy":"soft_delete","soft_delete_column":"active","soft_delete_type":"active_flag","has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2},{"column":"weight_unit","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'mass' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"weight_value","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'mass' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"length_value","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'length' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"length_unit","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'length' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."}]}},{"table":"purchase_order_items","schema":"dbo","columns":[{"name":"po_item_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for each purchase order item, serving as the primary key for the table.","cardinality":246,"null_count":0,"data_range":{"min":"268","max":"513"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"po_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"References the unique identifier of the associated purchase order in the purchase_orders table.","cardinality":125,"null_count":0,"data_range":{"min":"128","max":"252"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"product_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Identifies the associated product in the purchase order item, referencing the `products.product_id` column.","cardinality":49,"null_count":0,"data_range":{"min":"156","max":"205"},"data_category":"discrete","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"quantity","type":"integer","nullable":false,"is_incremental":false,"column_description":"The \"quantity\" column in the \"purchase_order_items\" table stores a non-null integer representing the number of items in a purchase order.","cardinality":41,"null_count":0,"data_range":{"min":"10","max":"50"},"data_category":"discrete","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: quantity","type hint: integer","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"quantity"},{"name":"unit_cost","type":"numeric(10,2)","nullable":false,"is_incremental":false,"column_description":"Represents the per-unit cost of a purchase order item, stored as a non-null numeric value with up to 10 digits and 2 decimal places.","cardinality":49,"null_count":0,"data_range":{"min":"5.55","max":"358.59"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: unit_cost","type hint: numeric(10,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount","table context: purchase_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"unit_cost"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The \"created_at\" column stores the non-nullable timestamp indicating when the purchase order item record was created.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":246,"null_count":0,"data_range":{"min":"2026-03-12 15:44:18.668789","max":"2026-03-12 15:45:45.174099"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: purchase_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"Records the timestamp of the most recent update to the purchase_order_items entry, stored as a non-nullable datetime2 value.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":246,"null_count":0,"data_range":{"min":"2026-03-12 15:44:18.668794","max":"2026-03-12 15:45:45.174104"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: purchase_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"ordered_qty_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"column_description":"Represents the numeric value of the ordered quantity for a purchase order item, allowing up to 10 digits with 2 decimal places, and can be null.","cardinality":0,"null_count":246,"data_category":"continuous","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: ordered_qty","type hint: numeric(10,2)","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"ordered_qty"},{"name":"ordered_qty_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Ordered quantity unit (ea/box).","cardinality":0,"null_count":246,"data_category":"nominal","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: ordered_qty_unit","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity"],"concept_sources":["name","profile","values"],"concept_alias_group":"ordered_qty_unit"}],"table_description":"Line items with order quantities and explicit unit labels.","primary_keys":["po_item_id"],"foreign_keys":[{"column":"po_id","references":"purchase_orders.po_id"},{"column":"product_id","references":"products.product_id"}],"row_count":246,"field_classifications":{"quantity":"quantity","unit_cost":"pricing","created_at":"temporal","updated_at":"temporal","ordered_qty_value":"quantity","ordered_qty_unit":"quantity"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"po_id","target_table":"purchase_orders","target_column":"po_id","confidence":"high"},{"column":"product_id","target_table":"products","target_column":"product_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":9,"mixed_unit_groups":[],"unknown_unit_columns":["ordered_qty_unit","ordered_qty_value","quantity"]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":246,"row_count_projection_2y":246,"row_count_projection_5y":246,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"finance.currency_amount":1,"identifier.foreign_key":3,"measure.quantity":3,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"findings":[{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2},{"column":"quantity","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"ordered_qty_value","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"ordered_qty_unit","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."}]}},{"table":"purchase_orders","schema":"dbo","columns":[{"name":"po_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"The `po_id` column is a non-nullable bigint serving as the primary key for uniquely identifying purchase orders in the `purchase_orders` table.","cardinality":125,"null_count":0,"data_range":{"min":"128","max":"252"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier</t>
+          <t>: inventory"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"stock_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"column_description":"Represents the monetary value of stock for an inventory item, stored as a numeric value with up to 10 digits and 2 decimal places, and may be null.","cardinality":0,"null_count":100,"data_category":"continuous","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.0,"concept_evidence":["type hint: numeric(10,2)","ambiguous runner-up concept"],"concept_sources":["type"],"concept_alias_group":null},{"name":"stock_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Current stock unit label.","cardinality":0,"null_count":100,"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.15,"concept_evidence":["value pattern: quantity","ambiguous runner-up concept"],"concept_sources":["values"],"concept_alias_group":null}],"table_description":"Current stock levels with normalized stock unit representation.","primary_keys":["inventory_id"],"foreign_keys":[{"column":"product_id","references":"products.product_id"},{"column":"store_id","references":"stores.store_id"}],"row_count":100,"field_classifications":{"quantity_on_hand":"quantity","last_restocked_at":"temporal","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"product_id","target_table":"products","target_column":"product_id","confidence":"high"},{"column":"store_id","target_table":"stores","target_column":"store_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":10,"mixed_unit_groups":[],"unknown_unit_columns":["quantity_on_hand"]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":146,"row_count_projection_2y":193,"row_count_projection_5y":334,"partition_columns_candidates":["last_restocked_at","created_at","updated_at"],"classification_summary":{"concept_counts":{"identifier.foreign_key":3,"measure.quantity":1,"temporal.created_at":1,"temporal.event_time":1,"temporal.updated_at":1},"low_confidence_columns":["reorder_level","stock_unit"]},"data_quality":{"findings":[{"column":"last_restocked_at","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 100 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 3 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"last_restocked_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":3},{"column":"quantity_on_hand","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."}]}},{"table":"products","schema":"dbo","columns":[{"name":"product_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for each product in the products table.","cardinality":50,"null_count":0,"data_range":{"min":"156","max":"205"},"data_category":"discrete","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"supplier_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"The `supplier_id` column in the `products` table is a non-nullable bigint that serves as a foreign key referencing the `supplier_id` column in the `suppliers` table.","cardinality":10,"null_count":0,"data_range":{"min":"33","max":"42"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"sku","type":"nvarchar(450)","nullable":false,"is_incremental":false,"column_description":"The \"sku\" column stores a unique alphanumeric identifier for each product, with a maximum length of 450 characters, and cannot be null.","cardinality":50,"null_count":0,"data_range":{"min":"SKU-0001","max":"SKU-0050"},"data_category":"nominal","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.product_code","concept_confidence":0.7,"concept_evidence":["name token: sku","type hint: nvarchar(450)","semantic class hint: product_identifier"],"concept_sources":["name","profile","type"],"concept_alias_group":"sku"},{"name":"name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"The \"name\" column in the \"products\" table stores the non-nullable name of the product as a Unicode string.","cardinality":50,"null_count":0,"data_range":{"min":"Product 1","max":"Product 9"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"name"},{"name":"category","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"The \"category\" column stores the product category as a non-null, case-insensitive string (e.g., \"Books\", \"Clothing\", \"Electronics\").","cardinality":5,"null_count":0,"data_range":{"min":"Books","max":"Sports"},"data_category":"nominal","semantic_class":"category","unit_context":null,"concept_id":"entity.category","concept_confidence":0.8,"concept_evidence":["name token: category","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: categorical","profile heuristic matched"],"concept_sources":["name","profile","type"],"concept_alias_group":"category"},{"name":"unit_price","type":"numeric(10,2)","nullable":false,"is_incremental":false,"column_description":"The `unit_price` column stores the non-null numeric value (up to 10 digits with 2 decimal places) representing the selling price of a product in currency.","cardinality":50,"null_count":0,"data_range":{"min":"11.09","max":"490.43"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: price","type hint: numeric(10,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"price"},{"name":"cost_price","type":"numeric(10,2)","nullable":false,"is_incremental":false,"column_description":"The `cost_price` column stores the non-null numeric cost value of a product with up to 10 digits, including 2 decimal places, representing its monetary amount.","cardinality":50,"null_count":0,"data_range":{"min":"5.55","max":"358.59"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: price","type hint: numeric(10,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"price"},{"name":"active","type":"bit","nullable":false,"is_incremental":false,"column_description":"Indicates whether the product is active (True) or inactive (False); cannot be null.","cardinality":1,"null_count":0,"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.0,"concept_evidence":["profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile"],"concept_alias_group":null},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The `created_at` column stores the non-nullable timestamp indicating when a product record was initially created.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":50,"null_count":0,"data_range":{"min":"2021-03-20 15:38:57.201565","max":"2024-12-25 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: products"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The `updated_at` column stores the non-nullable timestamp indicating the last update time of a product record.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":50,"null_count":0,"data_range":{"min":"2021-03-20 15:38:57.201565","max":"2024-12-25 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: products"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"weight_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Source weight unit (kg/lb) used for unit inference testing.","cardinality":0,"null_count":50,"data_category":"nominal","semantic_class":"mass","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":null,"concept_confidence":0.15,"concept_evidence":["value pattern: quantity","ambiguous runner-up concept"],"concept_sources":["values"],"concept_alias_group":null},{"name":"weight_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"column_description":"The `weight_value` column stores the weight of a product as a numeric value with up to 10 digits and 2 decimal places, and it is nullable.","cardinality":0,"null_count":50,"data_category":"continuous","semantic_class":"mass","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":null,"concept_confidence":0.0,"concept_evidence":["type hint: numeric(10,2)","ambiguous runner-up concept"],"concept_sources":["type"],"concept_alias_group":null},{"name":"length_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"column_description":"The `length_value` column stores the numeric length measurement of a product, allowing up to two decimal places, and can be null.","cardinality":0,"null_count":50,"data_category":"continuous","semantic_class":"length","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":null,"concept_confidence":0.0,"concept_evidence":["type hint: numeric(10,2)","ambiguous runner-up concept"],"concept_sources":["type"],"concept_alias_group":null},{"name":"length_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Source length unit (cm/in) used for unit inference testing.","cardinality":0,"null_count":50,"data_category":"nominal","semantic_class":"length","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":null,"concept_confidence":0.15,"concept_evidence":["value pattern: quantity","ambiguous runner-up concept"],"concept_sources":["values"],"concept_alias_group":null},{"name":"product_description","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"Stores an optional textual description of the product.","cardinality":0,"null_count":50,"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"primary_supplier_id","type":"bigint","nullable":true,"is_incremental":false,"column_description":"Primary supplier relationship used for join candidate detection.","cardinality":10,"null_count":0,"data_range":{"min":"33","max":"42"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"}],"table_description":"Master product catalog including physical units for analyzer unit-context testing.","primary_keys":["product_id"],"foreign_keys":[{"column":"primary_supplier_id","references":"suppliers.supplier_id"},{"column":"supplier_id","references":"suppliers.supplier_id"}],"row_count":50,"field_classifications":{"category":"categorical","unit_price":"pricing","cost_price":"pricing","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"primary_supplier_id","target_table":"suppliers","target_column":"supplier_id","confidence":"high"},{"column":"supplier_id","target_table":"suppliers","target_column":"supplier_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":16,"mixed_unit_groups":[],"unknown_unit_columns":["length_unit","length_value","weight_unit","weight_value"]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":68,"row_count_projection_2y":86,"row_count_projection_5y":141,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.person_name":1,"entity.category":1,"finance.currency_amount":2,"identifier.foreign_key":3,"identifier.product_code":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":["length_unit","name","product_description","weight_unit"]},"data_quality":{"findings":[{"column":"category","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 5 distinct value(s) ('Books', 'Clothing', 'Electronics', 'Home', 'Sports') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Books","Clothing","Electronics","Home","Sports"],"cardinality":5},{"column":"primary_supplier_id","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 50 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":"active","check":"delete_management","severity":"info","detail":"Active-flag column 'active' (boolean) detected \u2014 rows with active=false are logically deleted. Current distribution: True=50.","recommendation":"Filter on \"active\" = true for current records during ingestion.","delete_strategy":"soft_delete","soft_delete_column":"active","soft_delete_type":"active_flag","has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2},{"column":"weight_unit","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'mass' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"weight_value","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'mass' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"length_value","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'length' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"length_unit","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'length' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."}]}},{"table":"purchase_order_items","schema":"dbo","columns":[{"name":"po_item_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"The `po_item_id` column is a non-nullable bigint serving as the primary key for uniquely identifying each record in the `purchase_order_items` table.","cardinality":246,"null_count":0,"data_range":{"min":"268","max":"513"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"po_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"References the unique identifier of the associated purchase order in the purchase_orders table.","cardinality":125,"null_count":0,"data_range":{"min":"128","max":"252"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"product_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Represents the unique identifier of a product associated with a purchase order item, referencing the `product_id` column in the `products` table.","cardinality":49,"null_count":0,"data_range":{"min":"156","max":"205"},"data_category":"discrete","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"quantity","type":"integer","nullable":false,"is_incremental":false,"column_description":"The \"quantity\" column in the \"purchase_order_items\" table is a non-null integer representing the number of items in a purchase order.","cardinality":41,"null_count":0,"data_range":{"min":"10","max":"50"},"data_category":"discrete","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: quantity","type hint: integer","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"quantity"},{"name":"unit_cost","type":"numeric(10,2)","nullable":false,"is_incremental":false,"column_description":"Represents the non-null unit cost of a purchase order item, stored as a numeric value with up to 10 digits and 2 decimal places.","cardinality":49,"null_count":0,"data_range":{"min":"5.55","max":"358.59"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: unit_cost","type hint: numeric(10,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount","table context: purchase_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"unit_cost"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The `created_at` column stores the non-nullable timestamp indicating when the purchase order item record was created.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":246,"null_count":0,"data_range":{"min":"2026-03-12 15:44:18.668789","max":"2026-03-12 15:45:45.174099"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: purchase_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The `updated_at` column in the `purchase_order_items` table stores the non-nullable timestamp indicating the last update to a record.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":246,"null_count":0,"data_range":{"min":"2026-03-12 15:44:18.668794","max":"2026-03-12 15:45:45.174104"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: purchase_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"ordered_qty_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"column_description":"Represents the numeric value of the quantity ordered for a purchase order item, allowing up to 10 digits with 2 decimal places, and can be null.","cardinality":0,"null_count":246,"data_category":"continuous","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: ordered_qty","type hint: numeric(10,2)","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"ordered_qty"},{"name":"ordered_qty_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Ordered quantity unit (ea/box).","cardinality":0,"null_count":246,"data_category":"nominal","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: ordered_qty_unit","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity"],"concept_sources":["name","profile","values"],"concept_alias_group":"ordered_qty_unit"}],"table_description":"Line items with order quantities and explicit unit labels.","primary_keys":["po_item_id"],"foreign_keys":[{"column":"po_id","references":"purchase_orders.po_id"},{"column":"product_id","references":"products.product_id"}],"row_count":246,"field_classifications":{"quantity":"quantity","unit_cost":"pricing","created_at":"temporal","updated_at":"temporal","ordered_qty_value":"quantity","ordered_qty_unit":"quantity"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"po_id","target_table":"purchase_orders","target_column":"po_id","confidence":"high"},{"column":"product_id","target_table":"products","target_column":"product_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":9,"mixed_unit_groups":[],"unknown_unit_columns":["ordered_qty_unit","ordered_qty_value","quantity"]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":246,"row_count_projection_2y":246,"row_count_projection_5y":246,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"finance.currency_amount":1,"identifier.foreign_key":3,"measure.quantity":3,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"findings":[{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2},{"column":"quantity","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"ordered_qty_value","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has</t>
         </is>
       </c>
     </row>
@@ -10215,7 +10215,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"supplier_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"References the unique identifier of the supplier associated with the purchase order, linking to the `suppliers.supplier_id` column.","cardinality":10,"null_count":0,"data_range":{"min":"33","max":"42"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Represents the identifier of the store associated with the purchase order, referencing the `store_id` column in the `stores` table.","cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"status","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"Indicates the current state of the purchase order, such as 'Ordered' or 'Received', stored as a non-nullable nvarchar value.","cardinality":3,"null_count":0,"data_range":{"min":"Ordered","max":"Received"},"data_category":"nominal","semantic_class":"category","unit_context":null,"concept_id":"entity.status","concept_confidence":1.0,"concept_evidence":["name token: statu","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: categorical","value pattern: status","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"statu"},{"name":"order_date","type":"date","nullable":false,"is_incremental":false,"column_description":"The \"order_date\" column in the \"purchase_orders\" table stores the non-nullable date when the purchase order was placed.","cardinality":123,"null_count":0,"data_range":{"min":"2021-04-09","max":"2026-03-12"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.date_only","concept_confidence":1.0,"concept_evidence":["name token: order_date","type hint: date","legacy field classification: temporal","value pattern: date_only","table context: purchase_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"order_date"},{"name":"expected_date","type":"date","nullable":true,"is_incremental":false,"column_description":"The \"expected_date\" column in the \"purchase_orders\" table stores the anticipated delivery date of a purchase order and allows null values.","cardinality":123,"null_count":0,"data_range":{"min":"2021-04-27","max":"2026-03-31"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.date_only","concept_confidence":1.0,"concept_evidence":["name token: expected_date","type hint: date","legacy field classification: temporal","value pattern: date_only","table context: purchase_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"expected_date"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The \"created_at\" column stores the non-nullable timestamp indicating when the purchase order record was created.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":123,"null_count":0,"data_range":{"min":"2021-04-09 15:38:57.201565","max":"2026-03-12 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: purchase_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"Tracks the timestamp of the most recent update to a purchase order record, stored as a non-nullable datetime value.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":123,"null_count":0,"data_range":{"min":"2021-04-09 15:38:57.201565","max":"2026-03-12 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: purchase_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"approver_employee_id","type":"bigint","nullable":true,"is_incremental":false,"column_description":"Approver employee foreign key for procurement workflow.","cardinality":0,"null_count":125,"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"}],"table_description":"Procurement headers including approver employee relationship.","primary_keys":["po_id"],"foreign_keys":[{"column":"approver_employee_id","references":"employees.employee_id"},{"column":"store_id","references":"stores.store_id"},{"column":"supplier_id","references":"suppliers.supplier_id"}],"row_count":125,"field_classifications":{"status":"categorical","order_date":"temporal","expected_date":"temporal","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"approver_employee_id","target_table":"employees","target_column":"employee_id","confidence":"high"},{"column":"store_id","target_table":"stores","target_column":"store_id","confidence":"high"},{"column":"supplier_id","target_table":"suppliers","target_column":"supplier_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":9,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":155,"row_count_projection_2y":185,"row_count_projection_5y":276,"partition_columns_candidates":["order_date","expected_date","created_at","updated_at"],"classification_summary":{"concept_counts":{"entity.status":1,"identifier.foreign_key":4,"temporal.created_at":1,"temporal.date_only":2,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"findings":[{"column":"status","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 3 distinct value(s) ('Ordered', 'Pending', 'Received') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Ordered","Pending","Received"],"cardinality":3},{"column":"expected_date","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 125 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":"order_date","check":"late_arriving_data","severity":"info","detail":"Minor arrival delay \u2014 max lag between 'order_date' and 'created_at' is 15.7h (avg 15.7h, P95 15.7h).","recommendation":"Use 'created_at' as the watermark (preferred). If using 'order_date', add a 1\u20132 day lookback buffer.","business_date_column":"order_date","system_ts_column":"created_at","lag_stats":{"total_rows_compared":125,"min_lag_hours":15.65,"avg_lag_hours":15.65,"p95_lag_hours":15.65,"max_lag_hours":15.65,"max_lag_days":0.7,"rows_late_over_1d":0,"rows_late_over_7d":0},"recommended_lookback_days":2},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}},{"table":"sales_order_items","schema":"dbo","columns":[{"name":"sales_order_item_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for each sales order item, serving as the primary key in the sales_order_items table.","cardinality":508,"null_count":0,"data_range":{"min":"497","max":"1004"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"sales_order_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"References the unique identifier of the associated sales order in the sales_orders table.","cardinality":200,"null_count":0,"data_range":{"min":"375","max":"574"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"product_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Represents the unique identifier of a product associated with a sales order item, referencing the `product_id` column in the `products` table.","cardinality":50,"null_count":0,"data_range":{"min":"156","max":"205"},"data_category":"discrete","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"quantity","type":"integer","nullable":false,"is_incremental":false,"column_description":"The \"quantity\" column in the \"sales_order_items\" table stores a non-null integer representing the number of items in a sales order.","cardinality":5,"null_count":0,"data_range":{"min":"1","max":"5"},"data_category":"discrete","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: quantity","type hint: integer","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"quantity"},{"name":"unit_price","type":"numeric(15,2)","nullable":false,"is_incremental":false,"column_description":"The \"unit_price\" column stores the non-null numeric price per unit of a sales order item, with up to 15 digits and 2 decimal places, in a currency amount format.","cardinality":50,"null_count":0,"data_range":{"min":"11.09","max":"490.43"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: price","type hint: numeric(15,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount","table context: sales_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"price"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"Records the timestamp when the sales order item was created, stored as a non-nullable datetime value.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":508,"null_count":0,"data_range":{"min":"2026-03-12 15:41:01.155388","max":"2026-03-12 15:43:38.264437"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: sales_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The \"updated_at\" column stores the non-nullable timestamp of the last update made to a sales order item record.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":508,"null_count":0,"data_range":{"min":"2026-03-12 15:41:01.155390","max":"2026-03-12 15:43:38.264447"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: sales_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"sold_qty_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"column_description":"Represents the numeric value of the sold quantity for a sales order item, allowing nulls.","cardinality":0,"null_count":508,"data_category":"continuous","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: sold_qty","type hint: numeric(10,2)","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"sold_qty"},{"name":"sold_qty_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Sold quantity unit (ea/box).","cardinality":0,"null_count":508,"data_category":"nominal","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: sold_qty_unit","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity"],"concept_sources":["name","profile","values"],"concept_alias_group":"sold_qty_unit"}],"table_description":"Sales line items with sold quantity and explicit unit labels.","primary_keys":["sales_order_item_id"],"foreign_keys":[{"column":"product_id","references":"products.product_id"},{"column":"sales_order_id","references":"sales_orders.sales_order_id"}],"row_count":508,"field_classifications":{"quantity":"quantity","unit_price":"pricing","created_at":"temporal","updated_at":"temporal","sold_qty_value":"quantity","sold_qty_unit":"quantity"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"product_id","target_table":"products","target_column":"product_id","confidence":"high"},{"column":"sales_order_id","target_table":"sales_orders","target_column":"sales_order_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":9,"mixed_unit_groups":[],"unknown_unit_columns":["quantity","sold_qty_unit","sold_qty_value"]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":508,"row_count_projection_2y":508,"row_count_projection_5y":508,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"finance.currency_amount":1,"identifier.foreign_key":3,"measure.quantity":3,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"findings":[{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2},{"column":"quantity","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"sold_qty_value","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"sold_qty_unit","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."}]}},{"table":"sales_orders","schema":"dbo","columns":[{"name":"sales_order_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for each sales order in the table.","cardinality":200,"null_count":0,"data_range":{"min":"375","max":"574"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Represents the unique identifier of the store associated with the sales order, referencing the `store_id` column in the `stores` table.","cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"customer_id","type":"bigint","nullable":true,"is_incremental":false,"column_description":"The \"customer_id\" column in the \"sales_orders\" table is a nullable bigint that references the \"customer_id\" column in the \"customers\" table, identifying the customer associated with a sales order.","cardinality":76,"null_count":0,"data_range":{"min":"404","max":"502"},"data_category":"discrete","semantic_class":"customer_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"employee_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Represents the unique identifier of the employee associated with the sales order, referencing the employees table.","cardinality":20,"null_count":0,"data_range":{"min":"64","max":"83"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"order_date","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The \"order_date\" column stores the date and time when a sales order was placed, using the datetime2 data type, and cannot be null.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":191,"null_count":0,"data_range":{"min":"2021-03-14 15:38:57.201565","max":"2026-03-11 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.date_only","concept_confidence":0.9,"concept_evidence":["name token: order_date","type hint: datetime2","legacy field classification: temporal","table context: sales_orders","cross-table consensus: 2 similar columns"],"concept_sources":["cross_table_consensus","name","profile","table_context","type"],"concept_alias_group":"order_date"},{"name":"status","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"Indicates the current state of a sales order, such as 'Pending' or 'Completed'.","cardinality":3,"null_count":0,"data_range":{"min":"Completed","max":"Shipped"},"data_category":"nominal","semantic_class":"category","unit_context":null,"concept_id":"entity.status","concept_confidence":1.0,"concept_evidence":["name token: statu","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: categorical","value pattern: status","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"statu"},{"name":"total_amount","type":"numeric(12,2)","nullable":false,"is_incremental":false,"column_description":"Represents the total monetary amount for a sales order, stored as a non-null numeric value with up to 12 digits and 2 decimal places.","cardinality":200,"null_count":0,"data_range":{"min":"66.47","max":"998.76"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: amount","type hint: numeric(12,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount","table context: sales_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"amount"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"Records the timestamp when the sales order entry was created, stored as a non-nullable datetime value.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":191,"null_count":0,"data_range":{"min":"2021-03-14 15:38:57.201565","max":"2026-03-11 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: sales_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The \"updated_at\" column stores the non-nullable timestamp of the most recent update to a sales order record.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":191,"null_count":0,"data_range":{"min":"2021-03-14 15:38:57.201565","max":"2026-03-11 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: sales_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"sales_rep_employee_id","type":"bigint","nullable":true,"is_incremental":false,"column_description":"Sales representative foreign key for order ownership.","cardinality":0,"null_count":200,"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"}],"table_description":"Sales headers including assigned sales representative relationship.","primary_keys":["sales_order_id"],"foreign_keys":[{"column":"customer_id","references":"customers.customer_id"},{"column":"employee_id","references":"employees.employee_id"},{"column":"sales_rep_employee_id","references":"employees.employee_id"},{"column":"store_id","references":"stores.store_id"}],"row_count":200,"field_classifications":{"customer_id":"identifier","order_date":"temporal","status":"categorical","total_amount":"pricing","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"customer_id","target_table":"customers","target_column":"customer_id","confidence":"high"},{"column":"employee_id","target_table":"employees","target_column":"employee_id","confidence":"high"},{"column":"sales_rep_employee_id","target_table":"employees","target_column":"employee_id","confidence":"high"},{"column":"store_id","target_table":"stores","target_column":"store_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":10,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":242,"row_count_projection_2y":284,"row_count_projection_5y":412,"partition_columns_candidates":["order_date","created_at","updated_at"],"classification_summary":{"concept_counts":{"entity.status":1,"finance.currency_amount":1,"identifier.foreign_key":5,"temporal.created_at":1,"temporal.date_only":1,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"findings":[{"column":"status","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 3 distinct value(s) ('Completed', 'Pending', 'Shipped') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Completed","Pending","Shipped"],"cardinality":3},{"column":"customer_id","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 200 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"wa</t>
+          <t xml:space="preserve"> unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"ordered_qty_unit","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."}]}},{"table":"purchase_orders","schema":"dbo","columns":[{"name":"po_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"The `po_id` column is a non-nullable bigint serving as the primary key for uniquely identifying purchase orders in the `dbo.purchase_orders` table.","cardinality":125,"null_count":0,"data_range":{"min":"128","max":"252"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"supplier_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"The `supplier_id` column in the `purchase_orders` table is a non-nullable bigint that references the `supplier_id` column in the `suppliers` table, identifying the supplier associated with each purchase order.","cardinality":10,"null_count":0,"data_range":{"min":"33","max":"42"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"References the unique identifier of the store associated with the purchase order, linking to the `stores.store_id` column.","cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"status","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"Indicates the current state of a purchase order, such as 'Ordered' or 'Received'.","cardinality":3,"null_count":0,"data_range":{"min":"Ordered","max":"Received"},"data_category":"nominal","semantic_class":"category","unit_context":null,"concept_id":"entity.status","concept_confidence":1.0,"concept_evidence":["name token: statu","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: categorical","value pattern: status","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"statu"},{"name":"order_date","type":"date","nullable":false,"is_incremental":false,"column_description":"The `order_date` column stores the non-null date when a purchase order was placed.","cardinality":123,"null_count":0,"data_range":{"min":"2021-04-09","max":"2026-03-12"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.date_only","concept_confidence":1.0,"concept_evidence":["name token: order_date","type hint: date","legacy field classification: temporal","value pattern: date_only","table context: purchase_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"order_date"},{"name":"expected_date","type":"date","nullable":true,"is_incremental":false,"column_description":"The \"expected_date\" column in the \"purchase_orders\" table stores the anticipated delivery date of a purchase order, allowing null values.","cardinality":123,"null_count":0,"data_range":{"min":"2021-04-27","max":"2026-03-31"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.date_only","concept_confidence":1.0,"concept_evidence":["name token: expected_date","type hint: date","legacy field classification: temporal","value pattern: date_only","table context: purchase_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"expected_date"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The `created_at` column stores the non-nullable timestamp indicating when the purchase order record was initially created.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":123,"null_count":0,"data_range":{"min":"2021-04-09 15:38:57.201565","max":"2026-03-12 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: purchase_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The `updated_at` column stores the non-null timestamp indicating the last modification date and time of a purchase order record.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":123,"null_count":0,"data_range":{"min":"2021-04-09 15:38:57.201565","max":"2026-03-12 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: purchase_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"approver_employee_id","type":"bigint","nullable":true,"is_incremental":false,"column_description":"Approver employee foreign key for procurement workflow.","cardinality":0,"null_count":125,"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"}],"table_description":"Procurement headers including approver employee relationship.","primary_keys":["po_id"],"foreign_keys":[{"column":"approver_employee_id","references":"employees.employee_id"},{"column":"store_id","references":"stores.store_id"},{"column":"supplier_id","references":"suppliers.supplier_id"}],"row_count":125,"field_classifications":{"status":"categorical","order_date":"temporal","expected_date":"temporal","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"approver_employee_id","target_table":"employees","target_column":"employee_id","confidence":"high"},{"column":"store_id","target_table":"stores","target_column":"store_id","confidence":"high"},{"column":"supplier_id","target_table":"suppliers","target_column":"supplier_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":9,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":155,"row_count_projection_2y":185,"row_count_projection_5y":276,"partition_columns_candidates":["order_date","expected_date","created_at","updated_at"],"classification_summary":{"concept_counts":{"entity.status":1,"identifier.foreign_key":4,"temporal.created_at":1,"temporal.date_only":2,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"findings":[{"column":"status","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 3 distinct value(s) ('Ordered', 'Pending', 'Received') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Ordered","Pending","Received"],"cardinality":3},{"column":"expected_date","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 125 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":"order_date","check":"late_arriving_data","severity":"info","detail":"Minor arrival delay \u2014 max lag between 'order_date' and 'created_at' is 15.7h (avg 15.7h, P95 15.7h).","recommendation":"Use 'created_at' as the watermark (preferred). If using 'order_date', add a 1\u20132 day lookback buffer.","business_date_column":"order_date","system_ts_column":"created_at","lag_stats":{"total_rows_compared":125,"min_lag_hours":15.65,"avg_lag_hours":15.65,"p95_lag_hours":15.65,"max_lag_hours":15.65,"max_lag_days":0.7,"rows_late_over_1d":0,"rows_late_over_7d":0},"recommended_lookback_days":2},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}},{"table":"sales_order_items","schema":"dbo","columns":[{"name":"sales_order_item_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"The `sales_order_item_id` column is a non-nullable bigint serving as the primary key for uniquely identifying records in the `sales_order_items` table.","cardinality":508,"null_count":0,"data_range":{"min":"497","max":"1004"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"sales_order_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Links each sales order item to its corresponding sales order in the `sales_orders` table via a non-null foreign key.","cardinality":200,"null_count":0,"data_range":{"min":"375","max":"574"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"product_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"References the unique identifier of a product from the products table, establishing a mandatory relationship between sales order items and products.","cardinality":50,"null_count":0,"data_range":{"min":"156","max":"205"},"data_category":"discrete","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"quantity","type":"integer","nullable":false,"is_incremental":false,"column_description":"Represents the non-null integer quantity of a product in a sales order item.","cardinality":5,"null_count":0,"data_range":{"min":"1","max":"5"},"data_category":"discrete","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: quantity","type hint: integer","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"quantity"},{"name":"unit_price","type":"numeric(15,2)","nullable":false,"is_incremental":false,"column_description":"Represents the non-null unit price of a sales order item, stored as a numeric value with up to 15 digits and 2 decimal places.","cardinality":50,"null_count":0,"data_range":{"min":"11.09","max":"490.43"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: price","type hint: numeric(15,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount","table context: sales_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"price"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The `created_at` column records the non-nullable timestamp indicating when the sales order item was created.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":508,"null_count":0,"data_range":{"min":"2026-03-12 15:41:01.155388","max":"2026-03-12 15:43:38.264437"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: sales_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The `updated_at` column in the `sales_order_items` table stores the non-nullable timestamp indicating the last update to a sales order item record.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":508,"null_count":0,"data_range":{"min":"2026-03-12 15:41:01.155390","max":"2026-03-12 15:43:38.264447"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: sales_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"sold_qty_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"column_description":"Represents the numeric value of the sold quantity for a sales order item, allowing up to two decimal places and nullable.","cardinality":0,"null_count":508,"data_category":"continuous","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: sold_qty","type hint: numeric(10,2)","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"sold_qty"},{"name":"sold_qty_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Sold quantity unit (ea/box).","cardinality":0,"null_count":508,"data_category":"nominal","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: sold_qty_unit","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity"],"concept_sources":["name","profile","values"],"concept_alias_group":"sold_qty_unit"}],"table_description":"Sales line items with sold quantity and explicit unit labels.","primary_keys":["sales_order_item_id"],"foreign_keys":[{"column":"product_id","references":"products.product_id"},{"column":"sales_order_id","references":"sales_orders.sales_order_id"}],"row_count":508,"field_classifications":{"quantity":"quantity","unit_price":"pricing","created_at":"temporal","updated_at":"temporal","sold_qty_value":"quantity","sold_qty_unit":"quantity"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"product_id","target_table":"products","target_column":"product_id","confidence":"high"},{"column":"sales_order_id","target_table":"sales_orders","target_column":"sales_order_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":9,"mixed_unit_groups":[],"unknown_unit_columns":["quantity","sold_qty_unit","sold_qty_value"]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":508,"row_count_projection_2y":508,"row_count_projection_5y":508,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"finance.currency_amount":1,"identifier.foreign_key":3,"measure.quantity":3,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"findings":[{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2},{"column":"quantity","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"sold_qty_value","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"sold_qty_unit","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."}]}},{"table":"sales_orders","schema":"dbo","columns":[{"name":"sales_order_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"The `sales_order_id` column is a non-nullable bigint serving as the primary key for uniquely identifying sales orders in the `sales_orders` table.","cardinality":200,"null_count":0,"data_range":{"min":"375","max":"574"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Represents the unique identifier of the store associated with the sales order, referencing the `store_id` column in the `stores` table.","cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"customer_id","type":"bigint","nullable":true,"is_incremental":false,"column_description":"Represents the identifier of the customer associated with the sales order, referencing the `customer_id` column in the `customers` table; nullable.","cardinality":76,"null_count":0,"data_range":{"min":"404","max":"502"},"data_category":"discrete","semantic_class":"customer_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"employee_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Represents the unique identifier of the employee associated with the sales order, referencing the `employees.employee_id` column.","cardinality":20,"null_count":0,"data_range":{"min":"64","max":"83"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"order_date","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The `order_date` column in the `sales_orders` table stores the non-nullable timestamp indicating when the sales order was placed.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":191,"null_count":0,"data_range":{"min":"2021-03-14 15:38:57.201565","max":"2026-03-11 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.date_only","concept_confidence":0.9,"concept_evidence":["name token: order_date","type hint: datetime2","legacy field classification: temporal","table context: sales_orders","cross-table consensus: 2 similar columns"],"concept_sources":["cross_table_consensus","name","profile","table_context","type"],"concept_alias_group":"order_date"},{"name":"status","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"Indicates the current state of a sales order, such as 'Pending' or 'Completed', stored as a non-nullable text category.","cardinality":3,"null_count":0,"data_range":{"min":"Completed","max":"Shipped"},"data_category":"nominal","semantic_class":"category","unit_context":null,"concept_id":"entity.status","concept_confidence":1.0,"concept_evidence":["name token: statu","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: categorical","value pattern: status","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"statu"},{"name":"total_amount","type":"numeric(12,2)","nullable":false,"is_incremental":false,"column_description":"The `total_amount` column stores the total monetary value of a sales order as a non-null numeric value with up to 12 digits, including 2 decimal places.","cardinality":200,"null_count":0,"data_range":{"min":"66.47","max":"998.76"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: amount","type hint: numeric(12,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount","table context: sales_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"amount"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The \"created_at\" column in the \"sales_orders\" table stores the non-nullable timestamp indicating when the sales order record was created.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":191,"null_count":0,"data_range":{"min":"2021-03-14 15:38:57.201565","max":"2026-03-11 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: sales_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The \"updated_at\" column stores the non-nullable timestamp of the most recent update to a sales order record.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":191,"null_count":0,"data_range":{"min":"2021-03-14 15:38:57.201565","max":"2026-03-11 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: sales_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"sales_rep_employee_id","type":"bigint","nullable":true,"is_incremental":false,"column_description":"Sales representative foreign key for order ownership.","cardinality":0,"null_count":200,"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"}],"table_description":"Sales headers including assigned sales representative relationship.","primary_keys":["sales_order_id"],"foreign_keys":[{"column":"customer_id","references":"customers.customer_id"},{"column":"employee_id","references":"employees.employee_id"},{"column":"sales_rep_employee_id","references":"employees.employee_id"},{"column":"store_id","references":"stores.store_id"}],"row_count":200,"field_classifications":{"customer_id":"identifier","order_date":"temporal","status":"categorical","total_amount":"pricing","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"customer_id","target_table":"customers","target_column":"customer_id","confidence":"high"},{"column":"employee_id","target_table":"employees","target_column":"employee_id","confidence":"high"},{"column":"sales_rep_employee_id","target_table":"employees","target_column":"employee_id","confidence":"high"},{"column":"store_id","target_table":"stores","target_column":"store_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":10,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":242,"row_count_projection_2y":284,"row_count_projection_5y":412,"partition_columns_candidates":["order_date","created_at","updated_at"],"classification_summary":{"concept_counts":{"entity.status":1,"finance.currency_amount":1,"identifier.foreign_key":5,"temporal.created_at":1,"temporal.date_only":1,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"f</t>
         </is>
       </c>
     </row>
@@ -10225,7 +10225,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>rning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":"order_date","check":"late_arriving_data","severity":"info","detail":"Data arrives promptly \u2014 max lag between 'order_date' and 'created_at' is 0.0h. Standard watermarking on 'created_at' is safe.","recommendation":"Use 'created_at' as the incremental watermark. No special lookback window needed.","business_date_column":"order_date","system_ts_column":"created_at","lag_stats":{"total_rows_compared":200,"min_lag_hours":0.0,"avg_lag_hours":0.0,"p95_lag_hours":0.0,"max_lag_hours":0.0,"max_lag_days":0.0,"rows_late_over_1d":0,"rows_late_over_7d":0},"recommended_lookback_days":1},{"column":null,"check":"timezone","severity":"info","detail":"All 3 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"order_date","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":3}]}},{"table":"stores","schema":"dbo","columns":[{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"The \"store_id\" column is a non-nullable bigint serving as the primary key for uniquely identifying each store in the \"stores\" table.","cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"The \"name\" column in the \"stores\" table is a non-nullable nvarchar field intended to store the name of a store.","cardinality":5,"null_count":0,"data_range":{"min":"Airport Shop","max":"Suburb Store"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"name"},{"name":"code","type":"nvarchar(450)","nullable":false,"is_incremental":false,"column_description":"A non-nullable nvarchar(450) column storing unique alphanumeric identifiers for stores.","cardinality":5,"null_count":0,"data_range":{"min":"AIR","max":"SUB"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: nvarchar(450)","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"address","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"The \"address\" column in the \"stores\" table stores the address of a store as a nullable nvarchar string.","cardinality":5,"null_count":0,"data_range":{"min":"1 Main St","max":"5 Main St"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.address","concept_confidence":0.55,"concept_evidence":["name token: address","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"address"},{"name":"city","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"Stores.city is a nullable nvarchar column storing the name of the city where a store is located.","cardinality":3,"null_count":0,"data_range":{"min":"Cork","max":"Limerick"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"state","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"This column stores the state or province associated with a store, allowing null values.","cardinality":3,"null_count":0,"data_range":{"min":"Connacht","max":"Munster"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"postal_code","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"The \"postal_code\" column in the \"stores\" table stores optional alphanumeric postal codes for store locations.","cardinality":5,"null_count":0,"data_range":{"min":"10000","max":"10004"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.address","concept_confidence":0.55,"concept_evidence":["name token: postal_code","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"postal_code"},{"name":"phone","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"Stores.phone is an optional nvarchar column storing contact phone numbers for stores.","cardinality":5,"null_count":0,"data_range":{"min":"555-3000","max":"555-3004"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.phone","concept_confidence":1.0,"concept_evidence":["name token: phone","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: contact","value pattern: phone","sensitive hint: pii_contact"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"phone"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The \"created_at\" column stores the non-nullable timestamp indicating when a store record was initially created.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":5,"null_count":0,"data_range":{"min":"2021-07-26 15:38:57.201565","max":"2025-01-31 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: stores"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The \"updated_at\" column stores the non-nullable timestamp indicating the last update time of a store record.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":5,"null_count":0,"data_range":{"min":"2021-07-26 15:38:57.201565","max":"2025-01-31 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: stores"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"}],"table_description":"The \"stores\" table contains information about individual store locations, including identifiers, contact details, and timestamps for record creation and updates.","primary_keys":["store_id"],"foreign_keys":[],"row_count":5,"field_classifications":{"phone":"contact","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{"address":"pii_address","postal_code":"pii_address","phone":"pii_contact"},"incremental_columns":["updated_at"],"join_candidates":[],"unit_summary":{"columns_with_units":0,"columns_without_units":10,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":false,"has_sensitive_fields":true,"row_count_projection_1y":17,"row_count_projection_2y":29,"row_count_projection_5y":65,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.address":2,"contact.person_name":1,"contact.phone":1,"identifier.foreign_key":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":["address","city","code","name","postal_code","state"]},"data_quality":{"findings":[{"column":"city","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 3 distinct value(s) ('Cork', 'Galway', 'Limerick') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Cork","Galway","Limerick"],"cardinality":3},{"column":"state","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 3 distinct value(s) ('Connacht', 'Leinster', 'Munster') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Connacht","Leinster","Munster"],"cardinality":3},{"column":"postal_code","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 5 distinct value(s) ('10000', '10001', '10002', '10003', '10004') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["10000","10001","10002","10003","10004"],"cardinality":5},{"column":"address","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"city","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"state","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"postal_code","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"phone","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}},{"table":"suppliers","schema":"dbo","columns":[{"name":"supplier_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for each supplier, serving as the non-nullable primary key of the table.","cardinality":10,"null_count":0,"data_range":{"min":"33","max":"42"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"Stores the name of the supplier as a non-null Unicode string.","cardinality":10,"null_count":0,"data_range":{"min":"Supplier 1","max":"Supplier 9"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"name"},{"name":"contact_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"Stores the name of the contact person for a supplier, allowing null values.","cardinality":0,"null_count":10,"data_category":"nominal","semantic_class":"person_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: contact_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"contact_name"},{"name":"email","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"The \"email\" column in the \"suppliers\" table stores the supplier's email address as a nullable nvarchar value with case-insensitive collation.","cardinality":10,"null_count":0,"data_range":{"min":"supplier1@example.com","max":"supplier9@example.com"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.email","concept_confidence":1.0,"concept_evidence":["name token: email","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: contact","value pattern: email","sensitive hint: pii_contact"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"email"},{"name":"phone","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"Stores the supplier's phone number as a nullable text field.","cardinality":10,"null_count":0,"data_range":{"min":"555-2001","max":"555-2010"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.phone","concept_confidence":1.0,"concept_evidence":["name token: phone","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: contact","value pattern: phone","sensitive hint: pii_contact"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"phone"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The \"created_at\" column stores the non-nullable timestamp indicating when a supplier record was created.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":10,"null_count":0,"data_range":{"min":"2021-03-22 15:38:57.201565","max":"2024-02-25 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: suppliers"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The \"updated_at\" column stores the non-nullable timestamp of the last update to a supplier record.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":10,"null_count":0,"data_range":{"min":"2021-03-22 15:38:57.201565","max":"2024-02-25 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: suppliers"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"}],"table_description":"The \"suppliers\" table stores information about suppliers, including their unique identifier, name, contact details, and timestamps for record creation and updates.","primary_keys":["supplier_id"],"foreign_keys":[],"row_count":10,"field_classifications":{"contact_name":"person_name","email":"contact","phone":"contact","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{"email":"pii_contact","phone":"pii_contact"},"incremental_columns":["updated_at"],"join_candidates":[],"unit_summary":{"columns_with_units":0,"columns_without_units":7,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":false,"has_sensitive_fields":true,"row_count_projection_1y":22,"row_count_projection_2y":35,"row_count_projection_5y":74,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.email":1,"contact.person_name":2,"contact.phone":1,"identifier.foreign_key":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":["contact_name","name"]},"data_quality":{"findings":[{"column":"email","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 10 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"phone","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 10 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}}]}</t>
+          <t>indings":[{"column":"status","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 3 distinct value(s) ('Completed', 'Pending', 'Shipped') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Completed","Pending","Shipped"],"cardinality":3},{"column":"customer_id","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 200 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":"order_date","check":"late_arriving_data","severity":"info","detail":"Data arrives promptly \u2014 max lag between 'order_date' and 'created_at' is 0.0h. Standard watermarking on 'created_at' is safe.","recommendation":"Use 'created_at' as the incremental watermark. No special lookback window needed.","business_date_column":"order_date","system_ts_column":"created_at","lag_stats":{"total_rows_compared":200,"min_lag_hours":0.0,"avg_lag_hours":0.0,"p95_lag_hours":0.0,"max_lag_hours":0.0,"max_lag_days":0.0,"rows_late_over_1d":0,"rows_late_over_7d":0},"recommended_lookback_days":1},{"column":null,"check":"timezone","severity":"info","detail":"All 3 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"order_date","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":3}]}},{"table":"stores","schema":"dbo","columns":[{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"The `store_id` column is a non-nullable bigint serving as the primary key for uniquely identifying each store in the `stores` table.","cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"The \"name\" column in the \"stores\" table is a non-nullable nvarchar field intended to store the name of a store, though sample data is unavailable.","cardinality":5,"null_count":0,"data_range":{"min":"Airport Shop","max":"Suburb Store"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"name"},{"name":"code","type":"nvarchar(450)","nullable":false,"is_incremental":false,"column_description":"The \"code\" column in the \"stores\" table is a non-nullable nvarchar(450) field intended to store unique identifiers or short codes for each store.","cardinality":5,"null_count":0,"data_range":{"min":"AIR","max":"SUB"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: nvarchar(450)","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"address","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"Stores.address is an optional nvarchar column storing the physical address of a store, with case-insensitive collation.","cardinality":5,"null_count":0,"data_range":{"min":"1 Main St","max":"5 Main St"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.address","concept_confidence":0.55,"concept_evidence":["name token: address","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"address"},{"name":"city","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"The \"city\" column in the \"stores\" table stores the name of the city where the store is located, allowing null values.","cardinality":3,"null_count":0,"data_range":{"min":"Cork","max":"Limerick"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"state","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"This nullable nvarchar column stores the state or province associated with a store's address.","cardinality":3,"null_count":0,"data_range":{"min":"Connacht","max":"Munster"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"postal_code","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"The \"postal_code\" column in the \"stores\" table stores the postal or ZIP code of a store as a nullable nvarchar string.","cardinality":5,"null_count":0,"data_range":{"min":"10000","max":"10004"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.address","concept_confidence":0.55,"concept_evidence":["name token: postal_code","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"postal_code"},{"name":"phone","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"Stores.phone is an optional nvarchar column storing contact phone numbers for stores, formatted as text.","cardinality":5,"null_count":0,"data_range":{"min":"555-3000","max":"555-3004"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.phone","concept_confidence":1.0,"concept_evidence":["name token: phone","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: contact","value pattern: phone","sensitive hint: pii_contact"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"phone"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The `created_at` column stores the non-nullable timestamp indicating when a store record was created.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":5,"null_count":0,"data_range":{"min":"2021-07-26 15:38:57.201565","max":"2025-01-31 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: stores"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The `updated_at` column in the `stores` table records the non-nullable timestamp of the most recent update to a store's record.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":5,"null_count":0,"data_range":{"min":"2021-07-26 15:38:57.201565","max":"2025-01-31 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: stores"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"}],"table_description":"The `stores` table stores information about retail locations, including unique identifiers, names, contact details, addresses, and timestamps for record creation and updates.","primary_keys":["store_id"],"foreign_keys":[],"row_count":5,"field_classifications":{"phone":"contact","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{"address":"pii_address","postal_code":"pii_address","phone":"pii_contact"},"incremental_columns":["updated_at"],"join_candidates":[],"unit_summary":{"columns_with_units":0,"columns_without_units":10,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":false,"has_sensitive_fields":true,"row_count_projection_1y":17,"row_count_projection_2y":29,"row_count_projection_5y":65,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.address":2,"contact.person_name":1,"contact.phone":1,"identifier.foreign_key":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":["address","city","code","name","postal_code","state"]},"data_quality":{"findings":[{"column":"city","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 3 distinct value(s) ('Cork', 'Galway', 'Limerick') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Cork","Galway","Limerick"],"cardinality":3},{"column":"state","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 3 distinct value(s) ('Connacht', 'Leinster', 'Munster') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Connacht","Leinster","Munster"],"cardinality":3},{"column":"postal_code","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 5 distinct value(s) ('10000', '10001', '10002', '10003', '10004') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["10000","10001","10002","10003","10004"],"cardinality":5},{"column":"address","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"city","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"state","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"postal_code","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"phone","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}},{"table":"suppliers","schema":"dbo","columns":[{"name":"supplier_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for each supplier, serving as the primary key for the suppliers table.","cardinality":10,"null_count":0,"data_range":{"min":"33","max":"42"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"The \"name\" column in the \"suppliers\" table is a non-nullable nvarchar field intended to store supplier names, though sample data indicates it is currently unused.","cardinality":10,"null_count":0,"data_range":{"min":"Supplier 1","max":"Supplier 9"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"name"},{"name":"contact_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"The \"contact_name\" column in the \"suppliers\" table stores the name of a contact person for the supplier, allowing null values.","cardinality":0,"null_count":10,"data_category":"nominal","semantic_class":"person_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: contact_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"contact_name"},{"name":"email","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"The \"email\" column in the \"suppliers\" table stores the email address of a supplier as a nullable nvarchar value, used for contact purposes.","cardinality":10,"null_count":0,"data_range":{"min":"supplier1@example.com","max":"supplier9@example.com"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.email","concept_confidence":1.0,"concept_evidence":["name token: email","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: contact","value pattern: email","sensitive hint: pii_contact"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"email"},{"name":"phone","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"Stores the supplier's phone number as a nullable string, primarily for contact purposes.","cardinality":10,"null_count":0,"data_range":{"min":"555-2001","max":"555-2010"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.phone","concept_confidence":1.0,"concept_evidence":["name token: phone","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: contact","value pattern: phone","sensitive hint: pii_contact"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"phone"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The `created_at` column stores the non-nullable timestamp indicating when a supplier record was created.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":10,"null_count":0,"data_range":{"min":"2021-03-22 15:38:57.201565","max":"2024-02-25 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: suppliers"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The `updated_at` column stores the non-nullable timestamp of the most recent update to a supplier record in the `suppliers` table.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":10,"null_count":0,"data_range":{"min":"2021-03-22 15:38:57.201565","max":"2024-02-25 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: suppliers"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"}],"table_description":"The \"suppliers\" table stores information about suppliers, including their unique identifier, name, contact details, and timestamps for record creation and updates.","primary_keys":["supplier_id"],"foreign_keys":[],"row_count":10,"field_classifications":{"contact_name":"person_name","email":"contact","phone":"contact","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{"email":"pii_contact","phone":"pii_contact"},"incremental_columns":["updated_at"],"join_candidates":[],"unit_summary":{"columns_with_units":0,"columns_without_units":7,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":false,"has_sensitive_fields":true,"row_count_projection_1y":22,"row_count_projection_2y":35,"row_count_projection_5y":74,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.email":1,"contact.person_name":2,"contact.phone":1,"identifier.foreign_key":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":["contact_name","name"]},"data_quality":{"findings":[{"column":"email","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 10 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"phone","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 10 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}}]}</t>
         </is>
       </c>
     </row>
@@ -10285,7 +10285,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-03-30T08:36:23.118377+00:00</t>
+          <t>2026-04-01T10:39:15.579372+00:00</t>
         </is>
       </c>
       <c r="C3" s="4" t="n"/>
@@ -15522,7 +15522,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>The "customers" table stores information about customers, including their unique ID, name, contact details, and timestamps for record creation and updates.</t>
+          <t>The `customers` table stores information about customers, including their unique identifier, name, contact details, and timestamps for record creation and updates.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -15858,7 +15858,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Unique identifier for each customer, serving as the primary key for the customers table.</t>
+          <t>The `customer_id` column is a non-nullable bigint serving as the primary key and unique identifier for each customer in the `customers` table.</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -15944,7 +15944,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>The "first_name" column in the "customers" table stores non-nullable given names of customers as nvarchar strings using the "SQL_Latin1_General_CP1_CI_AS" collation.</t>
+          <t>The "first_name" column in the "customers" table stores non-nullable given names as nvarchar strings using the "sql_latin1_general_cp1_ci_as" collation.</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -16120,7 +16120,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Stores the customer's email address, allowing up to 450 Unicode characters, and can be null.</t>
+          <t>Stores the customer's email address, allowing null values, with a maximum length of 450 characters.</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -16210,7 +16210,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Stores the customer's phone number as a nullable Unicode string.</t>
+          <t>Stores the customer's phone number as a nullable text field with case-insensitive collation.</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -16296,7 +16296,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>The "created_at" column stores the non-nullable timestamp indicating when a customer record was created.</t>
+          <t>The `created_at` column stores the non-nullable timestamp indicating when a customer record was initially created.</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -16382,7 +16382,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>The "updated_at" column stores the timestamp of the most recent update to a customer record and is required (non-null).</t>
+          <t>The `updated_at` column stores the non-nullable timestamp of the most recent update to a customer's record.</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -17026,7 +17026,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>The "employees" table stores information about employees, including their unique identifier, associated store, personal details, job role, hire date, and record timestamps.</t>
+          <t>The `employees` table stores information about employees, including their unique ID, associated store, personal details, role, hire date, and record timestamps.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -17468,7 +17468,7 @@
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>The "employee_id" column is a non-nullable bigint serving as the primary key for uniquely identifying employees in the "employees" table.</t>
+          <t>The `employee_id` column is a non-nullable bigint serving as the primary key for uniquely identifying employees in the `employees` table.</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -17546,7 +17546,7 @@
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Represents the identifier of the store associated with an employee, referencing the `store_id` column in the `stores` table.</t>
+          <t>The `store_id` column in the `employees` table is a non-nullable bigint that serves as a foreign key referencing the `store_id` column in the `stores` table.</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -17808,7 +17808,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Stores the unique email address of an employee as a non-null nvarchar value up to 450 characters.</t>
+          <t>The "email" column stores the unique email address of each employee as a non-null nvarchar string with a maximum length of 450 characters.</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -17886,7 +17886,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Stores the job role of an employee as a non-null, case-insensitive string.</t>
+          <t>The "role" column in the "employees" table stores the job title or position of an employee as a non-null nvarchar string.</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -17972,7 +17972,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>The "hire_date" column in the "employees" table stores the non-nullable date an employee was hired.</t>
+          <t>The `hire_date` column stores the non-null date an employee was hired.</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -18058,7 +18058,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>The "created_at" column stores the non-nullable timestamp indicating when the employee record was created.</t>
+          <t>The "created_at" column stores the non-nullable timestamp indicating when the employee record was initially created.</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -18144,7 +18144,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>The "updated_at" column stores the non-nullable timestamp of the most recent update to an employee record.</t>
+          <t>The `updated_at` column stores the non-nullable timestamp indicating the last update time for an employee record.</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -19356,7 +19356,7 @@
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Represents the unique identifier of a store, referencing the `store_id` column in the `stores` table.</t>
+          <t>The `store_id` column in the `inventory` table is a non-nullable bigint that references the `store_id` column in the `stores` table, establishing a foreign key relationship.</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -19438,7 +19438,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>References the unique identifier of a product in the products table, establishing a foreign key relationship.</t>
+          <t>References the unique identifier of a product from the products table, establishing a foreign key relationship.</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -19524,7 +19524,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Represents the current quantity of a product in stock, stored as a non-null integer.</t>
+          <t>Tracks the current stock quantity of an item in inventory, stored as a non-null integer.</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -19618,7 +19618,7 @@
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Indicates the minimum stock quantity at which inventory should be reordered, stored as a non-null integer.</t>
+          <t>The `reorder_level` column in the `inventory` table stores a non-null integer indicating the threshold quantity at which stock should be reordered.</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -19696,7 +19696,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>The "last_restocked_at" column records the timestamp of the most recent restocking event for an inventory item and allows null values.</t>
+          <t>The `last_restocked_at` column records the timestamp of the most recent inventory restocking event and allows null values.</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -19782,7 +19782,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>The `created_at` column in the `inventory` table stores the non-nullable timestamp indicating when a record was initially created.</t>
+          <t>The "created_at" column stores the non-nullable timestamp indicating when the inventory record was initially created.</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -19868,7 +19868,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>The `updated_at` column in the `inventory` table stores the non-nullable timestamp indicating the last update to a record.</t>
+          <t>The `updated_at` column in the `inventory` table stores the non-null timestamp of the most recent update to a record, using the `datetime2` data type.</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -21106,7 +21106,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>The `product_id` column is a non-nullable bigint serving as the primary key for uniquely identifying products in the `products` table.</t>
+          <t>Unique identifier for each product in the products table.</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -21184,7 +21184,7 @@
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Represents the unique identifier of the supplier associated with a product, referencing the `supplier_id` column in the `suppliers` table.</t>
+          <t>The `supplier_id` column in the `products` table is a non-nullable bigint that serves as a foreign key referencing the `supplier_id` column in the `suppliers` table.</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -21266,7 +21266,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>The "sku" column stores a unique alphanumeric identifier for products, with a maximum length of 450 characters, and cannot be null.</t>
+          <t>The "sku" column stores a unique alphanumeric identifier for each product, with a maximum length of 450 characters, and cannot be null.</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -21344,7 +21344,7 @@
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Stores the name of the product as a non-null Unicode string.</t>
+          <t>The "name" column in the "products" table stores the non-nullable name of the product as a Unicode string.</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -21430,7 +21430,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Indicates the category of the product, stored as a non-null case-insensitive Unicode string.</t>
+          <t>The "category" column stores the product category as a non-null, case-insensitive string (e.g., "Books", "Clothing", "Electronics").</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -21516,7 +21516,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Stores the price per unit of a product as a non-null numeric value with up to 10 digits and 2 decimal places.</t>
+          <t>The `unit_price` column stores the non-null numeric value (up to 10 digits with 2 decimal places) representing the selling price of a product in currency.</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -21602,7 +21602,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Represents the non-null numeric cost price of a product, stored with up to 10 digits and 2 decimal places.</t>
+          <t>The `cost_price` column stores the non-null numeric cost value of a product with up to 10 digits, including 2 decimal places, representing its monetary amount.</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -21680,7 +21680,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Indicates whether the product is active (True) or inactive (False).</t>
+          <t>Indicates whether the product is active (True) or inactive (False); cannot be null.</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -21750,7 +21750,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Indicates the timestamp when the product record was created, stored as a non-nullable datetime2 value.</t>
+          <t>The `created_at` column stores the non-nullable timestamp indicating when a product record was initially created.</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -21836,7 +21836,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>The "updated_at" column stores the non-nullable timestamp of the last update made to a product record.</t>
+          <t>The `updated_at` column stores the non-nullable timestamp indicating the last update time of a product record.</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -22000,7 +22000,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Stores the weight of the product as a numeric value with up to 10 digits and 2 decimal places, nullable.</t>
+          <t>The `weight_value` column stores the weight of a product as a numeric value with up to 10 digits and 2 decimal places, and it is nullable.</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -22082,7 +22082,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Stores the length measurement of a product as a numeric value with up to 10 digits and 2 decimal places, which can be null.</t>
+          <t>The `length_value` column stores the numeric length measurement of a product, allowing up to two decimal places, and can be null.</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -23664,7 +23664,7 @@
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Unique identifier for each purchase order item, serving as the primary key for the table.</t>
+          <t>The `po_item_id` column is a non-nullable bigint serving as the primary key for uniquely identifying each record in the `purchase_order_items` table.</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -23824,7 +23824,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Identifies the associated product in the purchase order item, referencing the `products.product_id` column.</t>
+          <t>Represents the unique identifier of a product associated with a purchase order item, referencing the `product_id` column in the `products` table.</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -23910,7 +23910,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>The "quantity" column in the "purchase_order_items" table stores a non-null integer representing the number of items in a purchase order.</t>
+          <t>The "quantity" column in the "purchase_order_items" table is a non-null integer representing the number of items in a purchase order.</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -24012,7 +24012,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Represents the per-unit cost of a purchase order item, stored as a non-null numeric value with up to 10 digits and 2 decimal places.</t>
+          <t>Represents the non-null unit cost of a purchase order item, stored as a numeric value with up to 10 digits and 2 decimal places.</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -24098,7 +24098,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>The "created_at" column stores the non-nullable timestamp indicating when the purchase order item record was created.</t>
+          <t>The `created_at` column stores the non-nullable timestamp indicating when the purchase order item record was created.</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -24184,7 +24184,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Records the timestamp of the most recent update to the purchase_order_items entry, stored as a non-nullable datetime2 value.</t>
+          <t>The `updated_at` column in the `purchase_order_items` table stores the non-nullable timestamp indicating the last update to a record.</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -24270,7 +24270,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Represents the numeric value of the ordered quantity for a purchase order item, allowing up to 10 digits with 2 decimal places, and can be null.</t>
+          <t>Represents the numeric value of the quantity ordered for a purchase order item, allowing up to 10 digits with 2 decimal places, and can be null.</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">

--- a/LATEST_SCHEMA/schema_azure_mssql_dbo.xlsx
+++ b/LATEST_SCHEMA/schema_azure_mssql_dbo.xlsx
@@ -26,7 +26,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'DataQualityFindings'!$A$1:$Z$65</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Glossary'!$A$1:$B$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Glossary'!$A$1:$B$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'__rt_meta'!$A$1:$B$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'__rt_payload'!$A$1:$B$5</definedName>
   </definedNames>
@@ -815,7 +815,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z51"/>
+  <dimension ref="A1:AA51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -826,24 +826,25 @@
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="80" customWidth="1" min="7" max="7"/>
     <col width="80" customWidth="1" min="8" max="8"/>
-    <col width="80" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
     <col width="80" customWidth="1" min="10" max="10"/>
-    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="80" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
     <col width="25" customWidth="1" min="13" max="13"/>
-    <col width="80" customWidth="1" min="14" max="14"/>
-    <col width="52" customWidth="1" min="15" max="15"/>
-    <col width="17" customWidth="1" min="16" max="16"/>
+    <col width="25" customWidth="1" min="14" max="14"/>
+    <col width="80" customWidth="1" min="15" max="15"/>
+    <col width="52" customWidth="1" min="16" max="16"/>
     <col width="22" customWidth="1" min="17" max="17"/>
     <col width="18" customWidth="1" min="18" max="18"/>
     <col width="34" customWidth="1" min="19" max="19"/>
     <col width="80" customWidth="1" min="20" max="20"/>
     <col width="34" customWidth="1" min="21" max="21"/>
-    <col width="21" customWidth="1" min="22" max="22"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
     <col width="21" customWidth="1" min="23" max="23"/>
-    <col width="20" customWidth="1" min="24" max="24"/>
-    <col width="28" customWidth="1" min="25" max="25"/>
+    <col width="21" customWidth="1" min="24" max="24"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
     <col width="63" customWidth="1" min="26" max="26"/>
+    <col width="28" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -896,25 +897,30 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
+          <t>glossary_terms</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
           <t>classification_summary_json</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>unit_summary_json</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>row_count_projection_1y</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>row_count_projection_2y</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>row_count_projection_5y</t>
         </is>
@@ -959,23 +965,24 @@
           <t>Procurement headers including approver employee relationship.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
         <is>
           <t>{"concept_counts":{"entity.status":1,"identifier.foreign_key":4,"temporal.created_at":1,"temporal.date_only":2,"temporal.updated_at":1},"low_confidence_columns":[]}</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>{"columns_with_units":0,"columns_without_units":9,"mixed_unit_groups":[],"unknown_unit_columns":[]}</t>
         </is>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>155</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>185</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>276</v>
       </c>
     </row>
@@ -1009,6 +1016,7 @@
       <c r="K6" s="2" t="n"/>
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
+      <c r="N6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1050,6 +1058,7 @@
       <c r="K10" s="2" t="n"/>
       <c r="L10" s="2" t="n"/>
       <c r="M10" s="2" t="n"/>
+      <c r="N10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1117,6 +1126,7 @@
       <c r="K16" s="2" t="n"/>
       <c r="L16" s="2" t="n"/>
       <c r="M16" s="2" t="n"/>
+      <c r="N16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1158,6 +1168,7 @@
       <c r="K20" s="2" t="n"/>
       <c r="L20" s="2" t="n"/>
       <c r="M20" s="2" t="n"/>
+      <c r="N20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1237,6 +1248,7 @@
       <c r="K27" s="2" t="n"/>
       <c r="L27" s="2" t="n"/>
       <c r="M27" s="2" t="n"/>
+      <c r="N27" s="2" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1365,80 +1377,85 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
+          <t>glossary_terms</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
           <t>concept_id</t>
         </is>
       </c>
-      <c r="L33" s="2" t="inlineStr">
+      <c r="M33" s="2" t="inlineStr">
         <is>
           <t>concept_confidence</t>
         </is>
       </c>
-      <c r="M33" s="2" t="inlineStr">
+      <c r="N33" s="2" t="inlineStr">
         <is>
           <t>concept_alias_group</t>
         </is>
       </c>
-      <c r="N33" s="2" t="inlineStr">
+      <c r="O33" s="2" t="inlineStr">
         <is>
           <t>concept_evidence_json</t>
         </is>
       </c>
-      <c r="O33" s="2" t="inlineStr">
+      <c r="P33" s="2" t="inlineStr">
         <is>
           <t>concept_sources_json</t>
         </is>
       </c>
-      <c r="P33" s="2" t="inlineStr">
+      <c r="Q33" s="2" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="Q33" s="2" t="inlineStr">
+      <c r="R33" s="2" t="inlineStr">
         <is>
           <t>unit_source</t>
         </is>
       </c>
-      <c r="R33" s="2" t="inlineStr">
+      <c r="S33" s="2" t="inlineStr">
         <is>
           <t>canonical_unit</t>
         </is>
       </c>
-      <c r="S33" s="2" t="inlineStr">
+      <c r="T33" s="2" t="inlineStr">
         <is>
           <t>unit_system</t>
         </is>
       </c>
-      <c r="T33" s="2" t="inlineStr">
+      <c r="U33" s="2" t="inlineStr">
         <is>
           <t>unit_confidence</t>
         </is>
       </c>
-      <c r="U33" s="2" t="inlineStr">
+      <c r="V33" s="2" t="inlineStr">
         <is>
           <t>unit_notes</t>
         </is>
       </c>
-      <c r="V33" s="2" t="inlineStr">
+      <c r="W33" s="2" t="inlineStr">
         <is>
           <t>factor_to_canonical</t>
         </is>
       </c>
-      <c r="W33" s="2" t="inlineStr">
+      <c r="X33" s="2" t="inlineStr">
         <is>
           <t>offset_to_canonical</t>
         </is>
       </c>
-      <c r="X33" s="2" t="inlineStr">
+      <c r="Y33" s="2" t="inlineStr">
         <is>
           <t>conversion_formula</t>
         </is>
       </c>
-      <c r="Y33" s="2" t="inlineStr">
+      <c r="Z33" s="2" t="inlineStr">
         <is>
           <t>range_min</t>
         </is>
       </c>
-      <c r="Z33" s="2" t="inlineStr">
+      <c r="AA33" s="2" t="inlineStr">
         <is>
           <t>range_max</t>
         </is>
@@ -1476,33 +1493,33 @@
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>The `po_id` column is a non-nullable bigint serving as the primary key for uniquely identifying purchase orders in the `dbo.purchase_orders` table.</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
+          <t>Unique identifier for purchase orders in the retail operations system.</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
         </is>
       </c>
-      <c r="L34" t="n">
+      <c r="M34" t="n">
         <v>0.6</v>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"]</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>["cross_table_consensus","name","type"]</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
@@ -1511,12 +1528,13 @@
       <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr"/>
       <c r="X34" t="inlineStr"/>
-      <c r="Y34" t="inlineStr">
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr">
         <is>
           <t>128</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
+      <c r="AA34" t="inlineStr">
         <is>
           <t>252</t>
         </is>
@@ -1554,33 +1572,33 @@
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>The `supplier_id` column in the `purchase_orders` table is a non-nullable bigint that references the `supplier_id` column in the `suppliers` table, identifying the supplier associated with each purchase order.</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
+          <t>References the unique identifier of the supplier associated with a purchase order, linking to the `suppliers.supplier_id` column.</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
         </is>
       </c>
-      <c r="L35" t="n">
+      <c r="M35" t="n">
         <v>0.9</v>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>["name token: id","type hint: bigint","structural hint: join candidate"]</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>["name","profile","type"]</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr"/>
@@ -1589,12 +1607,13 @@
       <c r="V35" t="inlineStr"/>
       <c r="W35" t="inlineStr"/>
       <c r="X35" t="inlineStr"/>
-      <c r="Y35" t="inlineStr">
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
+      <c r="AA35" t="inlineStr">
         <is>
           <t>42</t>
         </is>
@@ -1632,33 +1651,33 @@
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>References the unique identifier of the store associated with the purchase order, linking to the `stores.store_id` column.</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
+          <t>Identifies the store associated with the purchase order, referencing the `store_id` column in the `stores` table.</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
         </is>
       </c>
-      <c r="L36" t="n">
+      <c r="M36" t="n">
         <v>0.9</v>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>["name token: id","type hint: bigint","structural hint: join candidate"]</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>["name","profile","type"]</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr"/>
@@ -1667,12 +1686,13 @@
       <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr"/>
-      <c r="Y36" t="inlineStr">
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
+      <c r="AA36" t="inlineStr">
         <is>
           <t>23</t>
         </is>
@@ -1718,33 +1738,33 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Indicates the current state of a purchase order, such as 'Ordered' or 'Received'.</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
+          <t>Indicates the current state of a purchase order, such as 'Ordered' or 'Received', using predefined category values.</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
         <is>
           <t>entity.status</t>
         </is>
       </c>
-      <c r="L37" t="n">
+      <c r="M37" t="n">
         <v>1</v>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>statu</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>["name token: statu","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: categorical","value pattern: status","profile heuristic matched"]</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>["name","profile","type","values"]</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr"/>
@@ -1753,12 +1773,13 @@
       <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr"/>
       <c r="X37" t="inlineStr"/>
-      <c r="Y37" t="inlineStr">
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr">
         <is>
           <t>Ordered</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
+      <c r="AA37" t="inlineStr">
         <is>
           <t>Received</t>
         </is>
@@ -1804,33 +1825,33 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>The `order_date` column stores the non-null date when a purchase order was placed.</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
+          <t>The `order_date` column in the `purchase_orders` table records the date a purchase order was placed and cannot be null.</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
         <is>
           <t>temporal.date_only</t>
         </is>
       </c>
-      <c r="L38" t="n">
+      <c r="M38" t="n">
         <v>1</v>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>order_date</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>["name token: order_date","type hint: date","legacy field classification: temporal","value pattern: date_only","table context: purchase_orders"]</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
+      <c r="P38" t="inlineStr">
         <is>
           <t>["name","profile","table_context","type","values"]</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
@@ -1839,12 +1860,13 @@
       <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr"/>
       <c r="X38" t="inlineStr"/>
-      <c r="Y38" t="inlineStr">
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr">
         <is>
           <t>2021-04-09</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
+      <c r="AA38" t="inlineStr">
         <is>
           <t>2026-03-12</t>
         </is>
@@ -1890,33 +1912,33 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>The "expected_date" column in the "purchase_orders" table stores the anticipated delivery date of a purchase order, allowing null values.</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
+          <t>The `expected_date` column in the `purchase_orders` table records the anticipated delivery date for a purchase order, allowing null values.</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
         <is>
           <t>temporal.date_only</t>
         </is>
       </c>
-      <c r="L39" t="n">
+      <c r="M39" t="n">
         <v>1</v>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>expected_date</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>["name token: expected_date","type hint: date","legacy field classification: temporal","value pattern: date_only","table context: purchase_orders"]</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="P39" t="inlineStr">
         <is>
           <t>["name","profile","table_context","type","values"]</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr"/>
@@ -1925,12 +1947,13 @@
       <c r="V39" t="inlineStr"/>
       <c r="W39" t="inlineStr"/>
       <c r="X39" t="inlineStr"/>
-      <c r="Y39" t="inlineStr">
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr">
         <is>
           <t>2021-04-27</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
+      <c r="AA39" t="inlineStr">
         <is>
           <t>2026-03-31</t>
         </is>
@@ -1976,33 +1999,33 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>The `created_at` column stores the non-nullable timestamp indicating when the purchase order record was initially created.</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
+          <t>The `created_at` column records the timestamp when a purchase order record is initially created in the system and cannot be null.</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
         <is>
           <t>temporal.created_at</t>
         </is>
       </c>
-      <c r="L40" t="n">
+      <c r="M40" t="n">
         <v>1</v>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: purchase_orders"]</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
+      <c r="P40" t="inlineStr">
         <is>
           <t>["name","profile","table_context","type","values"]</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr"/>
@@ -2011,12 +2034,13 @@
       <c r="V40" t="inlineStr"/>
       <c r="W40" t="inlineStr"/>
       <c r="X40" t="inlineStr"/>
-      <c r="Y40" t="inlineStr">
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr">
         <is>
           <t>2021-04-09 15:38:57.201565</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
+      <c r="AA40" t="inlineStr">
         <is>
           <t>2026-03-12 15:38:57.201565</t>
         </is>
@@ -2065,30 +2089,30 @@
           <t>The `updated_at` column stores the non-null timestamp indicating the last modification date and time of a purchase order record.</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
         <is>
           <t>temporal.updated_at</t>
         </is>
       </c>
-      <c r="L41" t="n">
+      <c r="M41" t="n">
         <v>1</v>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: purchase_orders"]</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="P41" t="inlineStr">
         <is>
           <t>["name","profile","table_context","type","values"]</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr"/>
@@ -2097,12 +2121,13 @@
       <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr"/>
       <c r="X41" t="inlineStr"/>
-      <c r="Y41" t="inlineStr">
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr">
         <is>
           <t>2021-04-09 15:38:57.201565</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
+      <c r="AA41" t="inlineStr">
         <is>
           <t>2026-03-12 15:38:57.201565</t>
         </is>
@@ -2143,30 +2168,30 @@
           <t>Approver employee foreign key for procurement workflow.</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
         </is>
       </c>
-      <c r="L42" t="n">
+      <c r="M42" t="n">
         <v>0.9</v>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>["name token: id","type hint: bigint","structural hint: join candidate"]</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="P42" t="inlineStr">
         <is>
           <t>["name","profile","type"]</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr"/>
@@ -2177,6 +2202,7 @@
       <c r="X42" t="inlineStr"/>
       <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr"/>
     </row>
     <row r="43"/>
     <row r="44">
@@ -2317,6 +2343,7 @@
           <t>extra_json</t>
         </is>
       </c>
+      <c r="AA45" s="2" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2707,7 +2734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z47"/>
+  <dimension ref="A1:AA47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -2718,24 +2745,25 @@
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="80" customWidth="1" min="7" max="7"/>
     <col width="80" customWidth="1" min="8" max="8"/>
-    <col width="80" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
     <col width="80" customWidth="1" min="10" max="10"/>
-    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="80" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
     <col width="25" customWidth="1" min="13" max="13"/>
-    <col width="80" customWidth="1" min="14" max="14"/>
-    <col width="52" customWidth="1" min="15" max="15"/>
-    <col width="17" customWidth="1" min="16" max="16"/>
+    <col width="25" customWidth="1" min="14" max="14"/>
+    <col width="80" customWidth="1" min="15" max="15"/>
+    <col width="52" customWidth="1" min="16" max="16"/>
     <col width="22" customWidth="1" min="17" max="17"/>
     <col width="18" customWidth="1" min="18" max="18"/>
     <col width="34" customWidth="1" min="19" max="19"/>
     <col width="80" customWidth="1" min="20" max="20"/>
-    <col width="80" customWidth="1" min="21" max="21"/>
-    <col width="21" customWidth="1" min="22" max="22"/>
+    <col width="34" customWidth="1" min="21" max="21"/>
+    <col width="80" customWidth="1" min="22" max="22"/>
     <col width="21" customWidth="1" min="23" max="23"/>
-    <col width="20" customWidth="1" min="24" max="24"/>
-    <col width="28" customWidth="1" min="25" max="25"/>
+    <col width="21" customWidth="1" min="24" max="24"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
     <col width="63" customWidth="1" min="26" max="26"/>
+    <col width="28" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2788,25 +2816,30 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
+          <t>glossary_terms</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
           <t>classification_summary_json</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>unit_summary_json</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>row_count_projection_1y</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>row_count_projection_2y</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>row_count_projection_5y</t>
         </is>
@@ -2851,23 +2884,24 @@
           <t>Sales line items with sold quantity and explicit unit labels.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
         <is>
           <t>{"concept_counts":{"finance.currency_amount":1,"identifier.foreign_key":3,"measure.quantity":3,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":[]}</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>{"columns_with_units":0,"columns_without_units":9,"mixed_unit_groups":[],"unknown_unit_columns":["quantity","sold_qty_unit","sold_qty_value"]}</t>
         </is>
-      </c>
-      <c r="K3" t="n">
-        <v>508</v>
       </c>
       <c r="L3" t="n">
         <v>508</v>
       </c>
       <c r="M3" t="n">
+        <v>508</v>
+      </c>
+      <c r="N3" t="n">
         <v>508</v>
       </c>
     </row>
@@ -2901,6 +2935,7 @@
       <c r="K6" s="2" t="n"/>
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
+      <c r="N6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -2942,6 +2977,7 @@
       <c r="K10" s="2" t="n"/>
       <c r="L10" s="2" t="n"/>
       <c r="M10" s="2" t="n"/>
+      <c r="N10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2997,6 +3033,7 @@
       <c r="K15" s="2" t="n"/>
       <c r="L15" s="2" t="n"/>
       <c r="M15" s="2" t="n"/>
+      <c r="N15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -3038,6 +3075,7 @@
       <c r="K19" s="2" t="n"/>
       <c r="L19" s="2" t="n"/>
       <c r="M19" s="2" t="n"/>
+      <c r="N19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3097,6 +3135,7 @@
       <c r="K24" s="2" t="n"/>
       <c r="L24" s="2" t="n"/>
       <c r="M24" s="2" t="n"/>
+      <c r="N24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3203,80 +3242,85 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
+          <t>glossary_terms</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
           <t>concept_id</t>
         </is>
       </c>
-      <c r="L29" s="2" t="inlineStr">
+      <c r="M29" s="2" t="inlineStr">
         <is>
           <t>concept_confidence</t>
         </is>
       </c>
-      <c r="M29" s="2" t="inlineStr">
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>concept_alias_group</t>
         </is>
       </c>
-      <c r="N29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
         <is>
           <t>concept_evidence_json</t>
         </is>
       </c>
-      <c r="O29" s="2" t="inlineStr">
+      <c r="P29" s="2" t="inlineStr">
         <is>
           <t>concept_sources_json</t>
         </is>
       </c>
-      <c r="P29" s="2" t="inlineStr">
+      <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="Q29" s="2" t="inlineStr">
+      <c r="R29" s="2" t="inlineStr">
         <is>
           <t>unit_source</t>
         </is>
       </c>
-      <c r="R29" s="2" t="inlineStr">
+      <c r="S29" s="2" t="inlineStr">
         <is>
           <t>canonical_unit</t>
         </is>
       </c>
-      <c r="S29" s="2" t="inlineStr">
+      <c r="T29" s="2" t="inlineStr">
         <is>
           <t>unit_system</t>
         </is>
       </c>
-      <c r="T29" s="2" t="inlineStr">
+      <c r="U29" s="2" t="inlineStr">
         <is>
           <t>unit_confidence</t>
         </is>
       </c>
-      <c r="U29" s="2" t="inlineStr">
+      <c r="V29" s="2" t="inlineStr">
         <is>
           <t>unit_notes</t>
         </is>
       </c>
-      <c r="V29" s="2" t="inlineStr">
+      <c r="W29" s="2" t="inlineStr">
         <is>
           <t>factor_to_canonical</t>
         </is>
       </c>
-      <c r="W29" s="2" t="inlineStr">
+      <c r="X29" s="2" t="inlineStr">
         <is>
           <t>offset_to_canonical</t>
         </is>
       </c>
-      <c r="X29" s="2" t="inlineStr">
+      <c r="Y29" s="2" t="inlineStr">
         <is>
           <t>conversion_formula</t>
         </is>
       </c>
-      <c r="Y29" s="2" t="inlineStr">
+      <c r="Z29" s="2" t="inlineStr">
         <is>
           <t>range_min</t>
         </is>
       </c>
-      <c r="Z29" s="2" t="inlineStr">
+      <c r="AA29" s="2" t="inlineStr">
         <is>
           <t>range_max</t>
         </is>
@@ -3314,33 +3358,33 @@
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>The `sales_order_item_id` column is a non-nullable bigint serving as the primary key for uniquely identifying records in the `sales_order_items` table.</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
+          <t>Unique identifier for individual items within a sales order, serving as the primary key for the `sales_order_items` table.</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
         </is>
       </c>
-      <c r="L30" t="n">
+      <c r="M30" t="n">
         <v>0.6</v>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"]</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>["cross_table_consensus","name","type"]</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr"/>
@@ -3349,12 +3393,13 @@
       <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr"/>
-      <c r="Y30" t="inlineStr">
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr">
         <is>
           <t>497</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
+      <c r="AA30" t="inlineStr">
         <is>
           <t>1004</t>
         </is>
@@ -3392,33 +3437,33 @@
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Links each sales order item to its corresponding sales order in the `sales_orders` table via a non-null foreign key.</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
+          <t>Identifier linking each sales order item to its associated sales order in the `sales_orders` table.</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
         </is>
       </c>
-      <c r="L31" t="n">
+      <c r="M31" t="n">
         <v>0.9</v>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>["name token: id","type hint: bigint","structural hint: join candidate"]</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>["name","profile","type"]</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr"/>
@@ -3427,12 +3472,13 @@
       <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr"/>
-      <c r="Y31" t="inlineStr">
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr">
         <is>
           <t>375</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
+      <c r="AA31" t="inlineStr">
         <is>
           <t>574</t>
         </is>
@@ -3474,33 +3520,33 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>References the unique identifier of a product from the products table, establishing a mandatory relationship between sales order items and products.</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
+          <t>References the unique identifier of the product associated with a sales order item, linking to the `products.product_id` column.</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
         </is>
       </c>
-      <c r="L32" t="n">
+      <c r="M32" t="n">
         <v>0.9</v>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>["name token: id","type hint: bigint","structural hint: join candidate"]</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>["name","profile","type"]</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
@@ -3509,12 +3555,13 @@
       <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr"/>
-      <c r="Y32" t="inlineStr">
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr">
         <is>
           <t>156</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
+      <c r="AA32" t="inlineStr">
         <is>
           <t>205</t>
         </is>
@@ -3560,63 +3607,64 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Represents the non-null integer quantity of a product in a sales order item.</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
+          <t>The "quantity" column in the "sales_order_items" table stores the non-null integer value representing the number of units of a product included in a specific sales order item.</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
         <is>
           <t>measure.quantity</t>
         </is>
       </c>
-      <c r="L33" t="n">
+      <c r="M33" t="n">
         <v>1</v>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>quantity</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>["name token: quantity","type hint: integer","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity","profile heuristic matched"]</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>["name","profile","type","values"]</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr">
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr">
         <is>
           <t>combined</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr">
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
+      <c r="U33" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
+      <c r="V33" t="inlineStr">
         <is>
           <t>Semantic class suggests units, but no explicit source unit token was detected.</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr"/>
-      <c r="Y33" t="inlineStr">
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
+      <c r="AA33" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -3662,33 +3710,33 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Represents the non-null unit price of a sales order item, stored as a numeric value with up to 15 digits and 2 decimal places.</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
+          <t>Represents the per-unit price of a product in a sales order item, stored as a non-null numeric value with up to 15 digits and 2 decimal places.</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
         <is>
           <t>finance.currency_amount</t>
         </is>
       </c>
-      <c r="L34" t="n">
+      <c r="M34" t="n">
         <v>1</v>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>["name token: price","type hint: numeric(15,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount","table context: sales_order_items"]</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>["name","profile","table_context","type","values"]</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
@@ -3697,12 +3745,13 @@
       <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr"/>
       <c r="X34" t="inlineStr"/>
-      <c r="Y34" t="inlineStr">
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr">
         <is>
           <t>11.09</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
+      <c r="AA34" t="inlineStr">
         <is>
           <t>490.43</t>
         </is>
@@ -3748,33 +3797,33 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>The `created_at` column records the non-nullable timestamp indicating when the sales order item was created.</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
+          <t>The `created_at` column in the `sales_order_items` table stores the non-nullable timestamp indicating when a sales order item record was created.</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
         <is>
           <t>temporal.created_at</t>
         </is>
       </c>
-      <c r="L35" t="n">
+      <c r="M35" t="n">
         <v>1</v>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: sales_order_items"]</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>["name","profile","table_context","type","values"]</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr"/>
@@ -3783,12 +3832,13 @@
       <c r="V35" t="inlineStr"/>
       <c r="W35" t="inlineStr"/>
       <c r="X35" t="inlineStr"/>
-      <c r="Y35" t="inlineStr">
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr">
         <is>
           <t>2026-03-12 15:41:01.155388</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
+      <c r="AA35" t="inlineStr">
         <is>
           <t>2026-03-12 15:43:38.264437</t>
         </is>
@@ -3834,33 +3884,33 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>The `updated_at` column in the `sales_order_items` table stores the non-nullable timestamp indicating the last update to a sales order item record.</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
+          <t>The `updated_at` column stores the non-nullable timestamp of the most recent update to a sales order item record for tracking modification history.</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
         <is>
           <t>temporal.updated_at</t>
         </is>
       </c>
-      <c r="L36" t="n">
+      <c r="M36" t="n">
         <v>1</v>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: sales_order_items"]</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>["name","profile","table_context","type","values"]</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr"/>
@@ -3869,12 +3919,13 @@
       <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr"/>
-      <c r="Y36" t="inlineStr">
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr">
         <is>
           <t>2026-03-12 15:41:01.155390</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
+      <c r="AA36" t="inlineStr">
         <is>
           <t>2026-03-12 15:43:38.264447</t>
         </is>
@@ -3920,59 +3971,60 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Represents the numeric value of the sold quantity for a sales order item, allowing up to two decimal places and nullable.</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
+          <t>Represents the numeric value of the quantity sold for a sales order item, allowing up to two decimal places and nullable for cases where the quantity is not recorded.</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
         <is>
           <t>measure.quantity</t>
         </is>
       </c>
-      <c r="L37" t="n">
+      <c r="M37" t="n">
         <v>1</v>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>sold_qty</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>["name token: sold_qty","type hint: numeric(10,2)","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity"]</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>["name","profile","type","values"]</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr">
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr">
         <is>
           <t>combined</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr">
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr">
+      <c r="U37" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr">
+      <c r="V37" t="inlineStr">
         <is>
           <t>Semantic class suggests units, but no explicit source unit token was detected.</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr"/>
       <c r="X37" t="inlineStr"/>
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4017,56 +4069,57 @@
           <t>Sold quantity unit (ea/box).</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
         <is>
           <t>measure.quantity</t>
         </is>
       </c>
-      <c r="L38" t="n">
+      <c r="M38" t="n">
         <v>1</v>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>sold_qty_unit</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>["name token: sold_qty_unit","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity"]</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
+      <c r="P38" t="inlineStr">
         <is>
           <t>["name","profile","values"]</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr">
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr">
         <is>
           <t>combined</t>
         </is>
       </c>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr">
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="T38" t="inlineStr">
+      <c r="U38" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr">
+      <c r="V38" t="inlineStr">
         <is>
           <t>Semantic class suggests units, but no explicit source unit token was detected.</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr"/>
       <c r="X38" t="inlineStr"/>
       <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr"/>
     </row>
     <row r="39"/>
     <row r="40">
@@ -4207,6 +4260,7 @@
           <t>extra_json</t>
         </is>
       </c>
+      <c r="AA41" s="2" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4583,7 +4637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z53"/>
+  <dimension ref="A1:AA53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -4594,24 +4648,25 @@
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="80" customWidth="1" min="7" max="7"/>
     <col width="80" customWidth="1" min="8" max="8"/>
-    <col width="80" customWidth="1" min="9" max="9"/>
+    <col width="29" customWidth="1" min="9" max="9"/>
     <col width="80" customWidth="1" min="10" max="10"/>
-    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="80" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
     <col width="25" customWidth="1" min="13" max="13"/>
-    <col width="80" customWidth="1" min="14" max="14"/>
-    <col width="67" customWidth="1" min="15" max="15"/>
-    <col width="17" customWidth="1" min="16" max="16"/>
+    <col width="25" customWidth="1" min="14" max="14"/>
+    <col width="80" customWidth="1" min="15" max="15"/>
+    <col width="67" customWidth="1" min="16" max="16"/>
     <col width="22" customWidth="1" min="17" max="17"/>
     <col width="18" customWidth="1" min="18" max="18"/>
     <col width="34" customWidth="1" min="19" max="19"/>
     <col width="80" customWidth="1" min="20" max="20"/>
     <col width="34" customWidth="1" min="21" max="21"/>
-    <col width="21" customWidth="1" min="22" max="22"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
     <col width="21" customWidth="1" min="23" max="23"/>
-    <col width="20" customWidth="1" min="24" max="24"/>
-    <col width="28" customWidth="1" min="25" max="25"/>
+    <col width="21" customWidth="1" min="24" max="24"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
     <col width="63" customWidth="1" min="26" max="26"/>
+    <col width="28" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4664,25 +4719,30 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
+          <t>glossary_terms</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
           <t>classification_summary_json</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>unit_summary_json</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>row_count_projection_1y</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>row_count_projection_2y</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>row_count_projection_5y</t>
         </is>
@@ -4727,23 +4787,24 @@
           <t>Sales headers including assigned sales representative relationship.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
         <is>
           <t>{"concept_counts":{"entity.status":1,"finance.currency_amount":1,"identifier.foreign_key":5,"temporal.created_at":1,"temporal.date_only":1,"temporal.updated_at":1},"low_confidence_columns":[]}</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>{"columns_with_units":0,"columns_without_units":10,"mixed_unit_groups":[],"unknown_unit_columns":[]}</t>
         </is>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>242</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>284</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>412</v>
       </c>
     </row>
@@ -4777,6 +4838,7 @@
       <c r="K6" s="2" t="n"/>
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
+      <c r="N6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -4818,6 +4880,7 @@
       <c r="K10" s="2" t="n"/>
       <c r="L10" s="2" t="n"/>
       <c r="M10" s="2" t="n"/>
+      <c r="N10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4897,6 +4960,7 @@
       <c r="K17" s="2" t="n"/>
       <c r="L17" s="2" t="n"/>
       <c r="M17" s="2" t="n"/>
+      <c r="N17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -4938,6 +5002,7 @@
       <c r="K21" s="2" t="n"/>
       <c r="L21" s="2" t="n"/>
       <c r="M21" s="2" t="n"/>
+      <c r="N21" s="2" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -5007,6 +5072,7 @@
       <c r="K27" s="2" t="n"/>
       <c r="L27" s="2" t="n"/>
       <c r="M27" s="2" t="n"/>
+      <c r="N27" s="2" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -5157,80 +5223,85 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
+          <t>glossary_terms</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
           <t>concept_id</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr">
+      <c r="M34" s="2" t="inlineStr">
         <is>
           <t>concept_confidence</t>
         </is>
       </c>
-      <c r="M34" s="2" t="inlineStr">
+      <c r="N34" s="2" t="inlineStr">
         <is>
           <t>concept_alias_group</t>
         </is>
       </c>
-      <c r="N34" s="2" t="inlineStr">
+      <c r="O34" s="2" t="inlineStr">
         <is>
           <t>concept_evidence_json</t>
         </is>
       </c>
-      <c r="O34" s="2" t="inlineStr">
+      <c r="P34" s="2" t="inlineStr">
         <is>
           <t>concept_sources_json</t>
         </is>
       </c>
-      <c r="P34" s="2" t="inlineStr">
+      <c r="Q34" s="2" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="Q34" s="2" t="inlineStr">
+      <c r="R34" s="2" t="inlineStr">
         <is>
           <t>unit_source</t>
         </is>
       </c>
-      <c r="R34" s="2" t="inlineStr">
+      <c r="S34" s="2" t="inlineStr">
         <is>
           <t>canonical_unit</t>
         </is>
       </c>
-      <c r="S34" s="2" t="inlineStr">
+      <c r="T34" s="2" t="inlineStr">
         <is>
           <t>unit_system</t>
         </is>
       </c>
-      <c r="T34" s="2" t="inlineStr">
+      <c r="U34" s="2" t="inlineStr">
         <is>
           <t>unit_confidence</t>
         </is>
       </c>
-      <c r="U34" s="2" t="inlineStr">
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t>unit_notes</t>
         </is>
       </c>
-      <c r="V34" s="2" t="inlineStr">
+      <c r="W34" s="2" t="inlineStr">
         <is>
           <t>factor_to_canonical</t>
         </is>
       </c>
-      <c r="W34" s="2" t="inlineStr">
+      <c r="X34" s="2" t="inlineStr">
         <is>
           <t>offset_to_canonical</t>
         </is>
       </c>
-      <c r="X34" s="2" t="inlineStr">
+      <c r="Y34" s="2" t="inlineStr">
         <is>
           <t>conversion_formula</t>
         </is>
       </c>
-      <c r="Y34" s="2" t="inlineStr">
+      <c r="Z34" s="2" t="inlineStr">
         <is>
           <t>range_min</t>
         </is>
       </c>
-      <c r="Z34" s="2" t="inlineStr">
+      <c r="AA34" s="2" t="inlineStr">
         <is>
           <t>range_max</t>
         </is>
@@ -5268,33 +5339,33 @@
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>The `sales_order_id` column is a non-nullable bigint serving as the primary key for uniquely identifying sales orders in the `sales_orders` table.</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
+          <t>Unique identifier for each sales order in the system.</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
         </is>
       </c>
-      <c r="L35" t="n">
+      <c r="M35" t="n">
         <v>0.6</v>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"]</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>["cross_table_consensus","name","type"]</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr"/>
@@ -5303,12 +5374,13 @@
       <c r="V35" t="inlineStr"/>
       <c r="W35" t="inlineStr"/>
       <c r="X35" t="inlineStr"/>
-      <c r="Y35" t="inlineStr">
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr">
         <is>
           <t>375</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
+      <c r="AA35" t="inlineStr">
         <is>
           <t>574</t>
         </is>
@@ -5346,33 +5418,33 @@
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Represents the unique identifier of the store associated with the sales order, referencing the `store_id` column in the `stores` table.</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
+          <t>Identifies the store associated with a sales order, referencing the `store_id` column in the `stores` table.</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
         </is>
       </c>
-      <c r="L36" t="n">
+      <c r="M36" t="n">
         <v>0.9</v>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>["name token: id","type hint: bigint","structural hint: join candidate"]</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>["name","profile","type"]</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr"/>
@@ -5381,12 +5453,13 @@
       <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr"/>
-      <c r="Y36" t="inlineStr">
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
+      <c r="AA36" t="inlineStr">
         <is>
           <t>23</t>
         </is>
@@ -5432,33 +5505,33 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Represents the identifier of the customer associated with the sales order, referencing the `customer_id` column in the `customers` table; nullable.</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
+          <t>Identifies the customer associated with a sales order, referencing the `customer_id` column in the `customers` table; nullable to accommodate orders without a registered customer.</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
         </is>
       </c>
-      <c r="L37" t="n">
+      <c r="M37" t="n">
         <v>0.9</v>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>["name token: id","type hint: bigint","structural hint: join candidate"]</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>["name","profile","type"]</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr"/>
@@ -5467,12 +5540,13 @@
       <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr"/>
       <c r="X37" t="inlineStr"/>
-      <c r="Y37" t="inlineStr">
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr">
         <is>
           <t>404</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
+      <c r="AA37" t="inlineStr">
         <is>
           <t>502</t>
         </is>
@@ -5510,33 +5584,33 @@
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Represents the unique identifier of the employee associated with the sales order, referencing the `employees.employee_id` column.</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
+          <t>Identifies the employee responsible for processing the sales order, referencing the `employees.employee_id` column.</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
         </is>
       </c>
-      <c r="L38" t="n">
+      <c r="M38" t="n">
         <v>0.9</v>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>["name token: id","type hint: bigint","structural hint: join candidate"]</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
+      <c r="P38" t="inlineStr">
         <is>
           <t>["name","profile","type"]</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
@@ -5545,12 +5619,13 @@
       <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr"/>
       <c r="X38" t="inlineStr"/>
-      <c r="Y38" t="inlineStr">
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr">
         <is>
           <t>64</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
+      <c r="AA38" t="inlineStr">
         <is>
           <t>83</t>
         </is>
@@ -5596,33 +5671,33 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>The `order_date` column in the `sales_orders` table stores the non-nullable timestamp indicating when the sales order was placed.</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
+          <t>The `order_date` column records the date and time when a sales order was placed, stored as a non-nullable `datetime2` value.</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
         <is>
           <t>temporal.date_only</t>
         </is>
       </c>
-      <c r="L39" t="n">
+      <c r="M39" t="n">
         <v>0.9</v>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>order_date</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>["name token: order_date","type hint: datetime2","legacy field classification: temporal","table context: sales_orders","cross-table consensus: 2 similar columns"]</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="P39" t="inlineStr">
         <is>
           <t>["cross_table_consensus","name","profile","table_context","type"]</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr"/>
@@ -5631,12 +5706,13 @@
       <c r="V39" t="inlineStr"/>
       <c r="W39" t="inlineStr"/>
       <c r="X39" t="inlineStr"/>
-      <c r="Y39" t="inlineStr">
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr">
         <is>
           <t>2021-03-14 15:38:57.201565</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
+      <c r="AA39" t="inlineStr">
         <is>
           <t>2026-03-11 15:38:57.201565</t>
         </is>
@@ -5685,30 +5761,30 @@
           <t>Indicates the current state of a sales order, such as 'Pending' or 'Completed', stored as a non-nullable text category.</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
         <is>
           <t>entity.status</t>
         </is>
       </c>
-      <c r="L40" t="n">
+      <c r="M40" t="n">
         <v>1</v>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>statu</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>["name token: statu","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: categorical","value pattern: status","profile heuristic matched"]</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
+      <c r="P40" t="inlineStr">
         <is>
           <t>["name","profile","type","values"]</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr"/>
@@ -5717,12 +5793,13 @@
       <c r="V40" t="inlineStr"/>
       <c r="W40" t="inlineStr"/>
       <c r="X40" t="inlineStr"/>
-      <c r="Y40" t="inlineStr">
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
+      <c r="AA40" t="inlineStr">
         <is>
           <t>Shipped</t>
         </is>
@@ -5768,33 +5845,33 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>The `total_amount` column stores the total monetary value of a sales order as a non-null numeric value with up to 12 digits, including 2 decimal places.</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
+          <t>The `total_amount` column in the `sales_orders` table stores the non-nullable total monetary value of a sales order as a numeric value with up to 12 digits and 2 decimal places.</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
         <is>
           <t>finance.currency_amount</t>
         </is>
       </c>
-      <c r="L41" t="n">
+      <c r="M41" t="n">
         <v>1</v>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>["name token: amount","type hint: numeric(12,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount","table context: sales_orders"]</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="P41" t="inlineStr">
         <is>
           <t>["name","profile","table_context","type","values"]</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr"/>
@@ -5803,12 +5880,13 @@
       <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr"/>
       <c r="X41" t="inlineStr"/>
-      <c r="Y41" t="inlineStr">
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr">
         <is>
           <t>66.47</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
+      <c r="AA41" t="inlineStr">
         <is>
           <t>998.76</t>
         </is>
@@ -5854,33 +5932,33 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>The "created_at" column in the "sales_orders" table stores the non-nullable timestamp indicating when the sales order record was created.</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
+          <t>The `created_at` column records the timestamp when a sales order entry was initially created, stored as a non-nullable `datetime2` value.</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
         <is>
           <t>temporal.created_at</t>
         </is>
       </c>
-      <c r="L42" t="n">
+      <c r="M42" t="n">
         <v>1</v>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: sales_orders"]</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="P42" t="inlineStr">
         <is>
           <t>["name","profile","table_context","type","values"]</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr"/>
@@ -5889,12 +5967,13 @@
       <c r="V42" t="inlineStr"/>
       <c r="W42" t="inlineStr"/>
       <c r="X42" t="inlineStr"/>
-      <c r="Y42" t="inlineStr">
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr">
         <is>
           <t>2021-03-14 15:38:57.201565</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
+      <c r="AA42" t="inlineStr">
         <is>
           <t>2026-03-11 15:38:57.201565</t>
         </is>
@@ -5940,33 +6019,33 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>The "updated_at" column stores the non-nullable timestamp of the most recent update to a sales order record.</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
+          <t>The `updated_at` column records the timestamp of the most recent update to a sales order, ensuring accurate tracking of modifications, and it is mandatory.</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
         <is>
           <t>temporal.updated_at</t>
         </is>
       </c>
-      <c r="L43" t="n">
+      <c r="M43" t="n">
         <v>1</v>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: sales_orders"]</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="P43" t="inlineStr">
         <is>
           <t>["name","profile","table_context","type","values"]</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr"/>
@@ -5975,12 +6054,13 @@
       <c r="V43" t="inlineStr"/>
       <c r="W43" t="inlineStr"/>
       <c r="X43" t="inlineStr"/>
-      <c r="Y43" t="inlineStr">
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr">
         <is>
           <t>2021-03-14 15:38:57.201565</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
+      <c r="AA43" t="inlineStr">
         <is>
           <t>2026-03-11 15:38:57.201565</t>
         </is>
@@ -6021,30 +6101,30 @@
           <t>Sales representative foreign key for order ownership.</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
         </is>
       </c>
-      <c r="L44" t="n">
+      <c r="M44" t="n">
         <v>0.9</v>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>["name token: id","type hint: bigint","structural hint: join candidate"]</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
+      <c r="P44" t="inlineStr">
         <is>
           <t>["name","profile","type"]</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr"/>
@@ -6055,6 +6135,7 @@
       <c r="X44" t="inlineStr"/>
       <c r="Y44" t="inlineStr"/>
       <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr"/>
     </row>
     <row r="45"/>
     <row r="46">
@@ -6195,6 +6276,7 @@
           <t>extra_json</t>
         </is>
       </c>
+      <c r="AA47" s="2" t="n"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -6585,7 +6667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z43"/>
+  <dimension ref="A1:AA43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -6596,24 +6678,25 @@
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="80" customWidth="1" min="7" max="7"/>
     <col width="80" customWidth="1" min="8" max="8"/>
-    <col width="80" customWidth="1" min="9" max="9"/>
+    <col width="35" customWidth="1" min="9" max="9"/>
     <col width="80" customWidth="1" min="10" max="10"/>
-    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="80" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
     <col width="25" customWidth="1" min="13" max="13"/>
-    <col width="80" customWidth="1" min="14" max="14"/>
-    <col width="52" customWidth="1" min="15" max="15"/>
-    <col width="17" customWidth="1" min="16" max="16"/>
+    <col width="25" customWidth="1" min="14" max="14"/>
+    <col width="80" customWidth="1" min="15" max="15"/>
+    <col width="52" customWidth="1" min="16" max="16"/>
     <col width="22" customWidth="1" min="17" max="17"/>
     <col width="18" customWidth="1" min="18" max="18"/>
     <col width="34" customWidth="1" min="19" max="19"/>
     <col width="80" customWidth="1" min="20" max="20"/>
     <col width="34" customWidth="1" min="21" max="21"/>
-    <col width="21" customWidth="1" min="22" max="22"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
     <col width="21" customWidth="1" min="23" max="23"/>
-    <col width="20" customWidth="1" min="24" max="24"/>
-    <col width="28" customWidth="1" min="25" max="25"/>
+    <col width="21" customWidth="1" min="24" max="24"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
     <col width="63" customWidth="1" min="26" max="26"/>
+    <col width="28" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6666,25 +6749,30 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
+          <t>glossary_terms</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
           <t>classification_summary_json</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>unit_summary_json</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>row_count_projection_1y</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>row_count_projection_2y</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>row_count_projection_5y</t>
         </is>
@@ -6726,26 +6814,27 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>The `stores` table stores information about retail locations, including unique identifiers, names, contact details, addresses, and timestamps for record creation and updates.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
+          <t>The "stores" table contains details about retail store locations, including unique identifiers, names, addresses, contact information, and timestamps for record creation and updates.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
         <is>
           <t>{"concept_counts":{"contact.address":2,"contact.person_name":1,"contact.phone":1,"identifier.foreign_key":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":["address","city","code","name","postal_code","state"]}</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>{"columns_with_units":0,"columns_without_units":10,"mixed_unit_groups":[],"unknown_unit_columns":[]}</t>
         </is>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>17</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>29</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>65</v>
       </c>
     </row>
@@ -6779,6 +6868,7 @@
       <c r="K6" s="2" t="n"/>
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
+      <c r="N6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -6820,6 +6910,7 @@
       <c r="K10" s="2" t="n"/>
       <c r="L10" s="2" t="n"/>
       <c r="M10" s="2" t="n"/>
+      <c r="N10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -6861,6 +6952,7 @@
       <c r="K14" s="2" t="n"/>
       <c r="L14" s="2" t="n"/>
       <c r="M14" s="2" t="n"/>
+      <c r="N14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -6943,80 +7035,85 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
+          <t>glossary_terms</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
           <t>concept_id</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>concept_confidence</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>concept_alias_group</t>
         </is>
       </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>concept_evidence_json</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
         <is>
           <t>concept_sources_json</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="Q19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>unit_source</t>
         </is>
       </c>
-      <c r="R19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>canonical_unit</t>
         </is>
       </c>
-      <c r="S19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
         <is>
           <t>unit_system</t>
         </is>
       </c>
-      <c r="T19" s="2" t="inlineStr">
+      <c r="U19" s="2" t="inlineStr">
         <is>
           <t>unit_confidence</t>
         </is>
       </c>
-      <c r="U19" s="2" t="inlineStr">
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>unit_notes</t>
         </is>
       </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="W19" s="2" t="inlineStr">
         <is>
           <t>factor_to_canonical</t>
         </is>
       </c>
-      <c r="W19" s="2" t="inlineStr">
+      <c r="X19" s="2" t="inlineStr">
         <is>
           <t>offset_to_canonical</t>
         </is>
       </c>
-      <c r="X19" s="2" t="inlineStr">
+      <c r="Y19" s="2" t="inlineStr">
         <is>
           <t>conversion_formula</t>
         </is>
       </c>
-      <c r="Y19" s="2" t="inlineStr">
+      <c r="Z19" s="2" t="inlineStr">
         <is>
           <t>range_min</t>
         </is>
       </c>
-      <c r="Z19" s="2" t="inlineStr">
+      <c r="AA19" s="2" t="inlineStr">
         <is>
           <t>range_max</t>
         </is>
@@ -7054,33 +7151,33 @@
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>The `store_id` column is a non-nullable bigint serving as the primary key for uniquely identifying each store in the `stores` table.</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
+          <t>Unique identifier for each store in the retail operations system.</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
         </is>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>0.6</v>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"]</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>["cross_table_consensus","name","type"]</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr"/>
@@ -7089,12 +7186,13 @@
       <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr">
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
+      <c r="AA20" t="inlineStr">
         <is>
           <t>23</t>
         </is>
@@ -7132,33 +7230,33 @@
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>The "name" column in the "stores" table is a non-nullable nvarchar field intended to store the name of a store, though sample data is unavailable.</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
+          <t>The "name" column in the "stores" table is a non-nullable nvarchar field storing the name of each retail store.</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
         <is>
           <t>contact.person_name</t>
         </is>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>0.55</v>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>["name token: name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""]</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>["name","type"]</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr"/>
@@ -7167,12 +7265,13 @@
       <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr">
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr">
         <is>
           <t>Airport Shop</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
+      <c r="AA21" t="inlineStr">
         <is>
           <t>Suburb Store</t>
         </is>
@@ -7210,25 +7309,25 @@
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>The "code" column in the "stores" table is a non-nullable nvarchar(450) field intended to store unique identifiers or short codes for each store.</t>
+          <t>Unique identifier for a store, typically represented as an alphanumeric code.</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="n">
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="n">
         <v>0.1</v>
       </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
         <is>
           <t>["type hint: nvarchar(450)","profile heuristic matched","ambiguous runner-up concept"]</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>["profile","type"]</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr"/>
@@ -7237,12 +7336,13 @@
       <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="inlineStr">
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr">
         <is>
           <t>AIR</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
+      <c r="AA22" t="inlineStr">
         <is>
           <t>SUB</t>
         </is>
@@ -7284,33 +7384,33 @@
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Stores.address is an optional nvarchar column storing the physical address of a store, with case-insensitive collation.</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
+          <t>The "address" column in the "stores" table stores the street address of a retail store location as a nullable Unicode string.</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
         <is>
           <t>contact.address</t>
         </is>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>0.55</v>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>address</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>["name token: address","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""]</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>["name","type"]</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr"/>
@@ -7319,12 +7419,13 @@
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr">
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr">
         <is>
           <t>1 Main St</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
+      <c r="AA23" t="inlineStr">
         <is>
           <t>5 Main St</t>
         </is>
@@ -7362,25 +7463,25 @@
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>The "city" column in the "stores" table stores the name of the city where the store is located, allowing null values.</t>
+          <t>The "city" column in the "stores" table stores the name of the city where a store is located, allowing null values.</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="n">
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="n">
         <v>0.1</v>
       </c>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
         <is>
           <t>["type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","profile heuristic matched","ambiguous runner-up concept"]</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>["profile","type"]</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr"/>
@@ -7389,12 +7490,13 @@
       <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr"/>
       <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr">
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr">
         <is>
           <t>Cork</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
+      <c r="AA24" t="inlineStr">
         <is>
           <t>Limerick</t>
         </is>
@@ -7432,25 +7534,25 @@
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>This nullable nvarchar column stores the state or province associated with a store's address.</t>
+          <t>Indicates the state or province where the store is located, stored as a nullable text field.</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="n">
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="n">
         <v>0.1</v>
       </c>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr">
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
         <is>
           <t>["type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","profile heuristic matched","ambiguous runner-up concept"]</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>["profile","type"]</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr"/>
@@ -7459,12 +7561,13 @@
       <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr"/>
       <c r="X25" t="inlineStr"/>
-      <c r="Y25" t="inlineStr">
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr">
         <is>
           <t>Connacht</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
+      <c r="AA25" t="inlineStr">
         <is>
           <t>Munster</t>
         </is>
@@ -7506,33 +7609,33 @@
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>The "postal_code" column in the "stores" table stores the postal or ZIP code of a store as a nullable nvarchar string.</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
+          <t>The "postal_code" column in the "stores" table stores the postal or ZIP code of a store location as a nullable, case-insensitive string.</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
         <is>
           <t>contact.address</t>
         </is>
       </c>
-      <c r="L26" t="n">
+      <c r="M26" t="n">
         <v>0.55</v>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>postal_code</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>["name token: postal_code","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""]</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>["name","type"]</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr"/>
@@ -7541,12 +7644,13 @@
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr"/>
       <c r="X26" t="inlineStr"/>
-      <c r="Y26" t="inlineStr">
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
+      <c r="AA26" t="inlineStr">
         <is>
           <t>10004</t>
         </is>
@@ -7596,33 +7700,33 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Stores.phone is an optional nvarchar column storing contact phone numbers for stores, formatted as text.</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
+          <t>Stores.phone is an optional nvarchar column storing the contact phone number for a store location.</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
         <is>
           <t>contact.phone</t>
         </is>
       </c>
-      <c r="L27" t="n">
+      <c r="M27" t="n">
         <v>1</v>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>phone</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>["name token: phone","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: contact","value pattern: phone","sensitive hint: pii_contact"]</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>["name","profile","type","values"]</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr"/>
@@ -7631,12 +7735,13 @@
       <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr"/>
-      <c r="Y27" t="inlineStr">
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr">
         <is>
           <t>555-3000</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
+      <c r="AA27" t="inlineStr">
         <is>
           <t>555-3004</t>
         </is>
@@ -7682,33 +7787,33 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>The `created_at` column stores the non-nullable timestamp indicating when a store record was created.</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
+          <t>The `created_at` column records the non-nullable timestamp indicating when a store record was initially created in the system.</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
         <is>
           <t>temporal.created_at</t>
         </is>
       </c>
-      <c r="L28" t="n">
+      <c r="M28" t="n">
         <v>1</v>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: stores"]</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>["name","profile","table_context","type","values"]</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr"/>
@@ -7717,12 +7822,13 @@
       <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr"/>
-      <c r="Y28" t="inlineStr">
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr">
         <is>
           <t>2021-07-26 15:38:57.201565</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
+      <c r="AA28" t="inlineStr">
         <is>
           <t>2025-01-31 15:38:57.201565</t>
         </is>
@@ -7768,33 +7874,33 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>The `updated_at` column in the `stores` table records the non-nullable timestamp of the most recent update to a store's record.</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
+          <t>The `updated_at` column records the timestamp of the most recent update to a store's record and cannot be null.</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
         <is>
           <t>temporal.updated_at</t>
         </is>
       </c>
-      <c r="L29" t="n">
+      <c r="M29" t="n">
         <v>1</v>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: stores"]</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>["name","profile","table_context","type","values"]</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr"/>
@@ -7803,12 +7909,13 @@
       <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr"/>
       <c r="X29" t="inlineStr"/>
-      <c r="Y29" t="inlineStr">
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr">
         <is>
           <t>2021-07-26 15:38:57.201565</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
+      <c r="AA29" t="inlineStr">
         <is>
           <t>2025-01-31 15:38:57.201565</t>
         </is>
@@ -7953,6 +8060,7 @@
           <t>extra_json</t>
         </is>
       </c>
+      <c r="AA32" s="2" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -8637,7 +8745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z34"/>
+  <dimension ref="A1:AA34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -8648,24 +8756,25 @@
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="80" customWidth="1" min="7" max="7"/>
     <col width="80" customWidth="1" min="8" max="8"/>
-    <col width="80" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
     <col width="80" customWidth="1" min="10" max="10"/>
-    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="80" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
     <col width="25" customWidth="1" min="13" max="13"/>
-    <col width="80" customWidth="1" min="14" max="14"/>
-    <col width="52" customWidth="1" min="15" max="15"/>
-    <col width="17" customWidth="1" min="16" max="16"/>
+    <col width="25" customWidth="1" min="14" max="14"/>
+    <col width="80" customWidth="1" min="15" max="15"/>
+    <col width="52" customWidth="1" min="16" max="16"/>
     <col width="22" customWidth="1" min="17" max="17"/>
     <col width="18" customWidth="1" min="18" max="18"/>
     <col width="34" customWidth="1" min="19" max="19"/>
     <col width="80" customWidth="1" min="20" max="20"/>
     <col width="34" customWidth="1" min="21" max="21"/>
-    <col width="21" customWidth="1" min="22" max="22"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
     <col width="21" customWidth="1" min="23" max="23"/>
-    <col width="20" customWidth="1" min="24" max="24"/>
-    <col width="28" customWidth="1" min="25" max="25"/>
+    <col width="21" customWidth="1" min="24" max="24"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
     <col width="63" customWidth="1" min="26" max="26"/>
+    <col width="28" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8718,25 +8827,30 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
+          <t>glossary_terms</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
           <t>classification_summary_json</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>unit_summary_json</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>row_count_projection_1y</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>row_count_projection_2y</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>row_count_projection_5y</t>
         </is>
@@ -8781,23 +8895,24 @@
           <t>The "suppliers" table stores information about suppliers, including their unique identifier, name, contact details, and timestamps for record creation and updates.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
         <is>
           <t>{"concept_counts":{"contact.email":1,"contact.person_name":2,"contact.phone":1,"identifier.foreign_key":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":["contact_name","name"]}</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>{"columns_with_units":0,"columns_without_units":7,"mixed_unit_groups":[],"unknown_unit_columns":[]}</t>
         </is>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>22</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>35</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>74</v>
       </c>
     </row>
@@ -8831,6 +8946,7 @@
       <c r="K6" s="2" t="n"/>
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
+      <c r="N6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -8872,6 +8988,7 @@
       <c r="K10" s="2" t="n"/>
       <c r="L10" s="2" t="n"/>
       <c r="M10" s="2" t="n"/>
+      <c r="N10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -8913,6 +9030,7 @@
       <c r="K14" s="2" t="n"/>
       <c r="L14" s="2" t="n"/>
       <c r="M14" s="2" t="n"/>
+      <c r="N14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -8995,80 +9113,85 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
+          <t>glossary_terms</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
           <t>concept_id</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>concept_confidence</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>concept_alias_group</t>
         </is>
       </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>concept_evidence_json</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
         <is>
           <t>concept_sources_json</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="Q19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>unit_source</t>
         </is>
       </c>
-      <c r="R19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>canonical_unit</t>
         </is>
       </c>
-      <c r="S19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
         <is>
           <t>unit_system</t>
         </is>
       </c>
-      <c r="T19" s="2" t="inlineStr">
+      <c r="U19" s="2" t="inlineStr">
         <is>
           <t>unit_confidence</t>
         </is>
       </c>
-      <c r="U19" s="2" t="inlineStr">
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>unit_notes</t>
         </is>
       </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="W19" s="2" t="inlineStr">
         <is>
           <t>factor_to_canonical</t>
         </is>
       </c>
-      <c r="W19" s="2" t="inlineStr">
+      <c r="X19" s="2" t="inlineStr">
         <is>
           <t>offset_to_canonical</t>
         </is>
       </c>
-      <c r="X19" s="2" t="inlineStr">
+      <c r="Y19" s="2" t="inlineStr">
         <is>
           <t>conversion_formula</t>
         </is>
       </c>
-      <c r="Y19" s="2" t="inlineStr">
+      <c r="Z19" s="2" t="inlineStr">
         <is>
           <t>range_min</t>
         </is>
       </c>
-      <c r="Z19" s="2" t="inlineStr">
+      <c r="AA19" s="2" t="inlineStr">
         <is>
           <t>range_max</t>
         </is>
@@ -9106,33 +9229,33 @@
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Unique identifier for each supplier, serving as the primary key for the suppliers table.</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
+          <t>Unique identifier for each supplier, serving as the primary key in the suppliers table.</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
         </is>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>0.6</v>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"]</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>["cross_table_consensus","name","type"]</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr"/>
@@ -9141,12 +9264,13 @@
       <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr">
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
+      <c r="AA20" t="inlineStr">
         <is>
           <t>42</t>
         </is>
@@ -9184,33 +9308,33 @@
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>The "name" column in the "suppliers" table is a non-nullable nvarchar field intended to store supplier names, though sample data indicates it is currently unused.</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
+          <t>The "name" column in the "suppliers" table is a non-nullable nvarchar field intended to store the name of the supplier, though sample data indicates it is currently unused.</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
         <is>
           <t>contact.person_name</t>
         </is>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>0.55</v>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>["name token: name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""]</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>["name","type"]</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr"/>
@@ -9219,12 +9343,13 @@
       <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr">
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr">
         <is>
           <t>Supplier 1</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
+      <c r="AA21" t="inlineStr">
         <is>
           <t>Supplier 9</t>
         </is>
@@ -9270,33 +9395,33 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>The "contact_name" column in the "suppliers" table stores the name of a contact person for the supplier, allowing null values.</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
+          <t>The `contact_name` column in the `suppliers` table stores the name of the primary contact person for a supplier, allowing null values.</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
         <is>
           <t>contact.person_name</t>
         </is>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>0.55</v>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>contact_name</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>["name token: contact_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""]</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>["name","type"]</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr"/>
@@ -9307,6 +9432,7 @@
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -9352,33 +9478,33 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>The "email" column in the "suppliers" table stores the email address of a supplier as a nullable nvarchar value, used for contact purposes.</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
+          <t>The "email" column in the "suppliers" table stores the email address of a supplier as a nullable nvarchar value for contact purposes.</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
         <is>
           <t>contact.email</t>
         </is>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>1</v>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>["name token: email","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: contact","value pattern: email","sensitive hint: pii_contact"]</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>["name","profile","type","values"]</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr"/>
@@ -9387,12 +9513,13 @@
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr">
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr">
         <is>
           <t>supplier1@example.com</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
+      <c r="AA23" t="inlineStr">
         <is>
           <t>supplier9@example.com</t>
         </is>
@@ -9442,33 +9569,33 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Stores the supplier's phone number as a nullable string, primarily for contact purposes.</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
+          <t>The "phone" column in the "suppliers" table stores the supplier's contact phone number as a nullable string.</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
         <is>
           <t>contact.phone</t>
         </is>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>1</v>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>phone</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>["name token: phone","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: contact","value pattern: phone","sensitive hint: pii_contact"]</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>["name","profile","type","values"]</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr"/>
@@ -9477,12 +9604,13 @@
       <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr"/>
       <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr">
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr">
         <is>
           <t>555-2001</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
+      <c r="AA24" t="inlineStr">
         <is>
           <t>555-2010</t>
         </is>
@@ -9528,33 +9656,33 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>The `created_at` column stores the non-nullable timestamp indicating when a supplier record was created.</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
+          <t>The `created_at` column records the non-nullable timestamp indicating when a supplier record was initially created in the system.</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
         <is>
           <t>temporal.created_at</t>
         </is>
       </c>
-      <c r="L25" t="n">
+      <c r="M25" t="n">
         <v>1</v>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: suppliers"]</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>["name","profile","table_context","type","values"]</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr"/>
@@ -9563,12 +9691,13 @@
       <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr"/>
       <c r="X25" t="inlineStr"/>
-      <c r="Y25" t="inlineStr">
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr">
         <is>
           <t>2021-03-22 15:38:57.201565</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
+      <c r="AA25" t="inlineStr">
         <is>
           <t>2024-02-25 15:38:57.201565</t>
         </is>
@@ -9614,33 +9743,33 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>The `updated_at` column stores the non-nullable timestamp of the most recent update to a supplier record in the `suppliers` table.</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
+          <t>The `updated_at` column stores the non-nullable timestamp of the most recent update to a supplier record.</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
         <is>
           <t>temporal.updated_at</t>
         </is>
       </c>
-      <c r="L26" t="n">
+      <c r="M26" t="n">
         <v>1</v>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: suppliers"]</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>["name","profile","table_context","type","values"]</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr"/>
@@ -9649,12 +9778,13 @@
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr"/>
       <c r="X26" t="inlineStr"/>
-      <c r="Y26" t="inlineStr">
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr">
         <is>
           <t>2021-03-22 15:38:57.201565</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
+      <c r="AA26" t="inlineStr">
         <is>
           <t>2024-02-25 15:38:57.201565</t>
         </is>
@@ -9799,6 +9929,7 @@
           <t>extra_json</t>
         </is>
       </c>
+      <c r="AA29" s="2" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -10195,7 +10326,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{"metadata":{"generated_at":"2026-04-01T10:39:15.579372+00:00","database_url":"pioneertest.database.windows.net:1433/free-sql-db-3300567?driver=ODBC+Driver+18+for+SQL+Server&amp;TrustServerCertificate=yes","schema_filter":"dbo","total_tables":10,"total_rows":1364,"total_findings":64},"connection":{"host":"pioneertest.database.windows.net","port":"1433","database":"free-sql-db-3300567","driver":"mssql","timezone":"(UTC) Coordinated Universal Time"},"source_system_context":{"contacts":[],"delete_management_instruction":"","restrictions":"","late_arriving_data_manual":"","volume_size_projection_manual":"","system_description":"Retail operations source system covering customers, stores, employees, suppliers, products, inventory, purchase orders, and sales orders used for day-to-day store, procurement, and sales transaction management.","db_analysis_config":{"exclude_schemas":["prediction"],"exclude_tables":[],"max_row_limit":100}},"concept_registry":{"version":1,"taxonomy":"domain-dot","generated_from_tables":10,"concepts":[{"concept_id":"contact.address","column_count":2,"table_count":1,"avg_confidence":0.55,"alias_groups":["address","postal_code"],"sample_columns":["stores.address","stores.postal_code"],"signals":["name","type"]},{"concept_id":"contact.email","column_count":3,"table_count":3,"avg_confidence":1.0,"alias_groups":["email"],"sample_columns":["customers.email","employees.email","suppliers.email"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"contact.person_name","column_count":8,"table_count":5,"avg_confidence":0.56,"alias_groups":["contact_name","first_name","last_name","name"],"sample_columns":["customers.first_name","customers.last_name","employees.first_name","employees.last_name","products.name"],"signals":["name","table_context","type"]},{"concept_id":"contact.phone","column_count":3,"table_count":3,"avg_confidence":1.0,"alias_groups":["phone"],"sample_columns":["customers.phone","stores.phone","suppliers.phone"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"entity.category","column_count":1,"table_count":1,"avg_confidence":0.8,"alias_groups":["category"],"sample_columns":["products.category"],"signals":["name","profile","type"]},{"concept_id":"entity.status","column_count":2,"table_count":2,"avg_confidence":1.0,"alias_groups":["statu"],"sample_columns":["purchase_orders.status","sales_orders.status"],"signals":["name","profile","type","values"]},{"concept_id":"entity.type","column_count":1,"table_count":1,"avg_confidence":0.65,"alias_groups":["role"],"sample_columns":["employees.role"],"signals":["name","profile","type"]},{"concept_id":"finance.currency_amount","column_count":5,"table_count":4,"avg_confidence":1.0,"alias_groups":["amount","price","unit_cost"],"sample_columns":["products.unit_price","products.cost_price","purchase_order_items.unit_cost","sales_order_items.unit_price","sales_orders.total_amount"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"identifier.foreign_key","column_count":26,"table_count":10,"avg_confidence":0.78,"alias_groups":["id"],"sample_columns":["customers.customer_id","employees.employee_id","employees.store_id","inventory.inventory_id","inventory.store_id"],"signals":["cross_table_consensus","name","profile","type"]},{"concept_id":"identifier.product_code","column_count":1,"table_count":1,"avg_confidence":0.7,"alias_groups":["sku"],"sample_columns":["products.sku"],"signals":["name","profile","type"]},{"concept_id":"measure.quantity","column_count":7,"table_count":3,"avg_confidence":1.0,"alias_groups":["ordered_qty","ordered_qty_unit","quantity","quantity_on_hand","sold_qty","sold_qty_unit"],"sample_columns":["inventory.quantity_on_hand","purchase_order_items.quantity","purchase_order_items.ordered_qty_value","purchase_order_items.ordered_qty_unit","sales_order_items.quantity"],"signals":["name","profile","type","values"]},{"concept_id":"temporal.created_at","column_count":10,"table_count":10,"avg_confidence":1.0,"alias_groups":["created_at"],"sample_columns":["customers.created_at","employees.created_at","inventory.created_at","products.created_at","purchase_order_items.created_at"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"temporal.date_only","column_count":4,"table_count":3,"avg_confidence":0.97,"alias_groups":["expected_date","hire_date","order_date"],"sample_columns":["employees.hire_date","purchase_orders.order_date","purchase_orders.expected_date","sales_orders.order_date"],"signals":["cross_table_consensus","name","profile","table_context","type","values"]},{"concept_id":"temporal.event_time","column_count":1,"table_count":1,"avg_confidence":1.0,"alias_groups":["last_restocked_at"],"sample_columns":["inventory.last_restocked_at"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"temporal.updated_at","column_count":10,"table_count":10,"avg_confidence":1.0,"alias_groups":["updated_at"],"sample_columns":["customers.updated_at","employees.updated_at","inventory.updated_at","products.updated_at","purchase_order_items.updated_at"],"signals":["name","profile","table_context","type","values"]}]},"data_quality_summary":{"critical":0,"warning":27,"info":37,"by_check":{"controlled_value_candidate":7,"nullable_but_never_null":13,"missing_primary_key":0,"missing_foreign_key":0,"format_inconsistency":0,"range_violation":0,"timestamp_ordering":10,"delete_management":10,"late_arriving_data":3,"timezone":10,"unit_unknown":11,"unit_noncanonical_but_convertible":0,"unit_mismatch_within_semantic_group":0},"constraints_found":{"check_constraints":0,"enum_columns":0,"unique_constraints":10}},"tables":[{"table":"customers","schema":"dbo","columns":[{"name":"customer_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"The `customer_id` column is a non-nullable bigint serving as the primary key and unique identifier for each customer in the `customers` table.","cardinality":100,"null_count":0,"data_range":{"min":"404","max":"503"},"data_category":"discrete","semantic_class":"customer_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"first_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"The \"first_name\" column in the \"customers\" table stores non-nullable given names as nvarchar strings using the \"sql_latin1_general_cp1_ci_as\" collation.","cardinality":100,"null_count":0,"data_range":{"min":"Customer1","max":"Customer99"},"data_category":"nominal","semantic_class":"given_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.6,"concept_evidence":["name token: first_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","table context: customers"],"concept_sources":["name","table_context","type"],"concept_alias_group":"first_name"},{"name":"last_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"The \"last_name\" column in the \"customers\" table stores the non-nullable family name of a customer as a case-insensitive Unicode string.","cardinality":100,"null_count":0,"data_range":{"min":"LastName1 (updated)","max":"LastName99"},"data_category":"nominal","semantic_class":"family_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.6,"concept_evidence":["name token: last_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","table context: customers"],"concept_sources":["name","table_context","type"],"concept_alias_group":"last_name"},{"name":"email","type":"nvarchar(450)","nullable":true,"is_incremental":false,"column_description":"Stores the customer's email address, allowing null values, with a maximum length of 450 characters.","cardinality":100,"null_count":0,"data_range":{"min":"customer1@example.com","max":"customer99@example.com"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.email","concept_confidence":1.0,"concept_evidence":["name token: email","type hint: nvarchar(450)","legacy field classification: contact","value pattern: email","table context: customers","sensitive hint: pii_contact"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"email"},{"name":"phone","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"Stores the customer's phone number as a nullable text field with case-insensitive collation.","cardinality":100,"null_count":0,"data_range":{"min":"555-1001","max":"555-1100"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.phone","concept_confidence":1.0,"concept_evidence":["name token: phone","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: contact","value pattern: phone","table context: customers","sensitive hint: pii_contact"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"phone"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The `created_at` column stores the non-nullable timestamp indicating when a customer record was initially created.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":95,"null_count":0,"data_range":{"min":"2021-03-23 15:38:57.201565","max":"2026-02-26 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: customers"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The `updated_at` column stores the non-nullable timestamp of the most recent update to a customer's record.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":95,"null_count":0,"data_range":{"min":"2021-03-23 15:38:57.201565","max":"2026-03-26 08:52:49.252228"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: customers"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"}],"table_description":"The `customers` table stores information about customers, including their unique identifier, name, contact details, and timestamps for record creation and updates.","primary_keys":["customer_id"],"foreign_keys":[],"row_count":100,"field_classifications":{"customer_id":"identifier","first_name":"person_name","last_name":"person_name","email":"contact","phone":"contact","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{"email":"pii_contact","phone":"pii_contact"},"incremental_columns":["updated_at"],"join_candidates":[],"unit_summary":{"columns_with_units":0,"columns_without_units":7,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":false,"has_sensitive_fields":true,"row_count_projection_1y":126,"row_count_projection_2y":152,"row_count_projection_5y":232,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.email":1,"contact.person_name":2,"contact.phone":1,"identifier.foreign_key":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"findings":[{"column":"email","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 100 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"phone","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 100 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}},{"table":"employees","schema":"dbo","columns":[{"name":"employee_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"The `employee_id` column is a non-nullable bigint serving as the primary key for uniquely identifying employees in the `employees` table.","cardinality":20,"null_count":0,"data_range":{"min":"64","max":"83"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"The `store_id` column in the `employees` table is a non-nullable bigint that serves as a foreign key referencing the `store_id` column in the `stores` table.","cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"first_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"The \"first_name\" column in the \"employees\" table stores the given name of an employee as a non-null, case-insensitive Unicode string.","cardinality":20,"null_count":0,"data_range":{"min":"Employee1","max":"Employee9"},"data_category":"nominal","semantic_class":"given_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: first_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"first_name"},{"name":"last_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"The \"last_name\" column in the \"employees\" table stores the non-nullable family name of an employee as a case-insensitive Unicode string.","cardinality":20,"null_count":0,"data_range":{"min":"LastName1","max":"LastName9"},"data_category":"nominal","semantic_class":"family_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: last_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"last_name"},{"name":"email","type":"nvarchar(450)","nullable":false,"is_incremental":false,"column_description":"The \"email\" column stores the unique email address of each employee as a non-null nvarchar string with a maximum length of 450 characters.","cardinality":20,"null_count":0,"data_range":{"min":"emp1@example.com","max":"emp9@example.com"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.email","concept_confidence":1.0,"concept_evidence":["name token: email","type hint: nvarchar(450)","legacy field classification: contact","value pattern: email","sensitive hint: pii_contact"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"email"},{"name":"role","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"The \"role\" column in the \"employees\" table stores the job title or position of an employee as a non-null nvarchar string.","cardinality":4,"null_count":0,"data_range":{"min":"Cashier","max":"Stock"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"entity.type","concept_confidence":0.65,"concept_evidence":["name token: role","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","profile heuristic matched"],"concept_sources":["name","profile","type"],"concept_alias_group":"role"},{"name":"hire_date","type":"date","nullable":false,"is_incremental":false,"column_description":"The `hire_date` column stores the non-null date an employee was hired.","cardinality":20,"null_count":0,"data_range":{"min":"2021-05-03","max":"2025-01-26"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.date_only","concept_confidence":1.0,"concept_evidence":["name token: hire_date","type hint: date","legacy field classification: temporal","value pattern: date_only","table context: employees"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"hire_date"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The \"created_at\" column stores the non-nullable timestamp indicating when the employee record was initially created.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":20,"null_count":0,"data_range":{"min":"2021-05-03 15:38:57.201565","max":"2025-01-26 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: employees"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The `updated_at` column stores the non-nullable timestamp indicating the last update time for an employee record.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":20,"null_count":0,"data_range":{"min":"2021-05-03 15:38:57.201565","max":"2025-01-26 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: employees"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"}],"table_description":"The `employees` table stores information about employees, including their unique ID, associated store, personal details, role, hire date, and record timestamps.","primary_keys":["employee_id"],"foreign_keys":[{"column":"store_id","references":"stores.store_id"}],"row_count":20,"field_classifications":{"first_name":"person_name","last_name":"person_name","email":"contact","hire_date":"temporal","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{"email":"pii_contact"},"incremental_columns":["updated_at"],"join_candidates":[{"column":"store_id","target_table":"stores","target_column":"store_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":9,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":true,"row_count_projection_1y":35,"row_count_projection_2y":50,"row_count_projection_5y":96,"partition_columns_candidates":["hire_date","created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.email":1,"contact.person_name":2,"entity.type":1,"identifier.foreign_key":2,"temporal.created_at":1,"temporal.date_only":1,"temporal.updated_at":1},"low_confidence_columns":["first_name","last_name"]},"data_quality":{"findings":[{"column":"role","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 4 distinct value(s) ('Cashier', 'Manager', 'Sales', 'Stock') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Cashier","Manager","Sales","Stock"],"cardinality":4},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":"hire_date","check":"late_arriving_data","severity":"info","detail":"Minor arrival delay \u2014 max lag between 'hire_date' and 'created_at' is 15.7h (avg 15.7h, P95 15.7h).","recommendation":"Use 'created_at' as the watermark (preferred). If using 'hire_date', add a 1\u20132 day lookback buffer.","business_date_column":"hire_date","system_ts_column":"created_at","lag_stats":{"total_rows_compared":20,"min_lag_hours":15.65,"avg_lag_hours":15.65,"p95_lag_hours":15.65,"max_lag_hours":15.65,"max_lag_days":0.7,"rows_late_over_1d":0,"rows_late_over_7d":0},"recommended_lookback_days":2},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}},{"table":"inventory","schema":"dbo","columns":[{"name":"inventory_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"The `inventory_id` column is a non-nullable bigint serving as the primary key for uniquely identifying records in the `inventory` table.","cardinality":100,"null_count":0,"data_range":{"min":"8","max":"107"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"The `store_id` column in the `inventory` table is a non-nullable bigint that references the `store_id` column in the `stores` table, establishing a foreign key relationship.","cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"product_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"References the unique identifier of a product from the products table, establishing a foreign key relationship.","cardinality":47,"null_count":0,"data_range":{"min":"156","max":"205"},"data_category":"discrete","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"quantity_on_hand","type":"integer","nullable":false,"is_incremental":false,"column_description":"Tracks the current stock quantity of an item in inventory, stored as a non-null integer.","cardinality":68,"null_count":0,"data_range":{"min":"2","max":"98"},"data_category":"discrete","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: quantity_on_hand","type hint: integer","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"quantity_on_hand"},{"name":"reorder_level","type":"integer","nullable":false,"is_incremental":false,"column_description":"The `reorder_level` column in the `inventory` table stores a non-null integer indicating the threshold quantity at which stock should be reordered.","cardinality":20,"null_count":0,"data_range":{"min":"10","max":"29"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: integer","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"last_restocked_at","type":"datetime2","nullable":true,"is_incremental":false,"column_description":"The `last_restocked_at` column records the timestamp of the most recent inventory restocking event and allows null values.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":89,"null_count":0,"data_range":{"min":"2024-03-14 15:38:57.201565","max":"2026-03-07 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.event_time","concept_confidence":1.0,"concept_evidence":["name token: last_restocked_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: inventory"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"last_restocked_at"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The \"created_at\" column stores the non-nullable timestamp indicating when the inventory record was initially created.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":91,"null_count":0,"data_range":{"min":"2024-03-05 15:38:57.201565","max":"2026-02-23 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: inventory"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The `updated_at` column in the `inventory` table stores the non-null timestamp of the most recent update to a record, using the `datetime2` data type.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":89,"null_count":0,"data_range":{"min":"2024-03-14 15:38:57.201565","max":"2026-03-07 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context</t>
+          <t>{"metadata":{"generated_at":"2026-04-03T12:09:52.790221+00:00","database_url":"pioneertest.database.windows.net:1433/free-sql-db-3300567?driver=ODBC+Driver+18+for+SQL+Server&amp;TrustServerCertificate=yes","schema_filter":"dbo","total_tables":10,"total_rows":1364,"total_findings":64},"connection":{"host":"pioneertest.database.windows.net","port":"1433","database":"free-sql-db-3300567","driver":"mssql","timezone":"(UTC) Coordinated Universal Time"},"source_system_context":{"contacts":[],"delete_management_instruction":"","restrictions":"","late_arriving_data_manual":"","volume_size_projection_manual":"","system_description":"Retail operations source system covering customers, stores, employees, suppliers, products, inventory, purchase orders, and sales orders used for day-to-day store, procurement, and sales transaction management.","openmetadata_enrichment":{"enabled":false,"configured":false,"database_service_name":"","schema":"dbo","matched_tables":0,"unmatched_tables":0,"error":""},"db_analysis_config":{"exclude_schemas":["prediction"],"exclude_tables":[],"max_row_limit":100}},"concept_registry":{"version":1,"taxonomy":"domain-dot","generated_from_tables":10,"concepts":[{"concept_id":"contact.address","column_count":2,"table_count":1,"avg_confidence":0.55,"alias_groups":["address","postal_code"],"sample_columns":["stores.address","stores.postal_code"],"signals":["name","type"]},{"concept_id":"contact.email","column_count":3,"table_count":3,"avg_confidence":1.0,"alias_groups":["email"],"sample_columns":["customers.email","employees.email","suppliers.email"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"contact.person_name","column_count":8,"table_count":5,"avg_confidence":0.56,"alias_groups":["contact_name","first_name","last_name","name"],"sample_columns":["customers.first_name","customers.last_name","employees.first_name","employees.last_name","products.name"],"signals":["name","table_context","type"]},{"concept_id":"contact.phone","column_count":3,"table_count":3,"avg_confidence":1.0,"alias_groups":["phone"],"sample_columns":["customers.phone","stores.phone","suppliers.phone"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"entity.category","column_count":1,"table_count":1,"avg_confidence":0.8,"alias_groups":["category"],"sample_columns":["products.category"],"signals":["name","profile","type"]},{"concept_id":"entity.status","column_count":2,"table_count":2,"avg_confidence":1.0,"alias_groups":["statu"],"sample_columns":["purchase_orders.status","sales_orders.status"],"signals":["name","profile","type","values"]},{"concept_id":"entity.type","column_count":1,"table_count":1,"avg_confidence":0.65,"alias_groups":["role"],"sample_columns":["employees.role"],"signals":["name","profile","type"]},{"concept_id":"finance.currency_amount","column_count":5,"table_count":4,"avg_confidence":1.0,"alias_groups":["amount","price","unit_cost"],"sample_columns":["products.unit_price","products.cost_price","purchase_order_items.unit_cost","sales_order_items.unit_price","sales_orders.total_amount"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"identifier.foreign_key","column_count":26,"table_count":10,"avg_confidence":0.78,"alias_groups":["id"],"sample_columns":["customers.customer_id","employees.employee_id","employees.store_id","inventory.inventory_id","inventory.store_id"],"signals":["cross_table_consensus","name","profile","type"]},{"concept_id":"identifier.product_code","column_count":1,"table_count":1,"avg_confidence":0.7,"alias_groups":["sku"],"sample_columns":["products.sku"],"signals":["name","profile","type"]},{"concept_id":"measure.quantity","column_count":7,"table_count":3,"avg_confidence":1.0,"alias_groups":["ordered_qty","ordered_qty_unit","quantity","quantity_on_hand","sold_qty","sold_qty_unit"],"sample_columns":["inventory.quantity_on_hand","purchase_order_items.quantity","purchase_order_items.ordered_qty_value","purchase_order_items.ordered_qty_unit","sales_order_items.quantity"],"signals":["name","profile","type","values"]},{"concept_id":"temporal.created_at","column_count":10,"table_count":10,"avg_confidence":1.0,"alias_groups":["created_at"],"sample_columns":["customers.created_at","employees.created_at","inventory.created_at","products.created_at","purchase_order_items.created_at"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"temporal.date_only","column_count":4,"table_count":3,"avg_confidence":0.97,"alias_groups":["expected_date","hire_date","order_date"],"sample_columns":["employees.hire_date","purchase_orders.order_date","purchase_orders.expected_date","sales_orders.order_date"],"signals":["cross_table_consensus","name","profile","table_context","type","values"]},{"concept_id":"temporal.event_time","column_count":1,"table_count":1,"avg_confidence":1.0,"alias_groups":["last_restocked_at"],"sample_columns":["inventory.last_restocked_at"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"temporal.updated_at","column_count":10,"table_count":10,"avg_confidence":1.0,"alias_groups":["updated_at"],"sample_columns":["customers.updated_at","employees.updated_at","inventory.updated_at","products.updated_at","purchase_order_items.updated_at"],"signals":["name","profile","table_context","type","values"]}]},"data_quality_summary":{"critical":0,"warning":27,"info":37,"by_check":{"controlled_value_candidate":7,"nullable_but_never_null":13,"missing_primary_key":0,"missing_foreign_key":0,"format_inconsistency":0,"range_violation":0,"timestamp_ordering":10,"delete_management":10,"late_arriving_data":3,"timezone":10,"unit_unknown":11,"unit_noncanonical_but_convertible":0,"unit_mismatch_within_semantic_group":0},"constraints_found":{"check_constraints":0,"enum_columns":0,"unique_constraints":10}},"tables":[{"table":"customers","schema":"dbo","columns":[{"name":"customer_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for each customer in the retail operations system.","glossary_terms":[],"cardinality":100,"null_count":0,"data_range":{"min":"404","max":"503"},"data_category":"discrete","semantic_class":"customer_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"first_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"Stores the given name of a customer as a non-null, case-insensitive Unicode string.","glossary_terms":[],"cardinality":100,"null_count":0,"data_range":{"min":"Customer1","max":"Customer99"},"data_category":"nominal","semantic_class":"given_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.6,"concept_evidence":["name token: first_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","table context: customers"],"concept_sources":["name","table_context","type"],"concept_alias_group":"first_name"},{"name":"last_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"Stores the last name of a customer as a non-null, case-insensitive Unicode string.","glossary_terms":[],"cardinality":100,"null_count":0,"data_range":{"min":"LastName1 (updated)","max":"LastName99"},"data_category":"nominal","semantic_class":"family_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.6,"concept_evidence":["name token: last_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","table context: customers"],"concept_sources":["name","table_context","type"],"concept_alias_group":"last_name"},{"name":"email","type":"nvarchar(450)","nullable":true,"is_incremental":false,"column_description":"Stores the email address of the customer, allowing null values.","glossary_terms":[],"cardinality":100,"null_count":0,"data_range":{"min":"customer1@example.com","max":"customer99@example.com"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.email","concept_confidence":1.0,"concept_evidence":["name token: email","type hint: nvarchar(450)","legacy field classification: contact","value pattern: email","table context: customers","sensitive hint: pii_contact"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"email"},{"name":"phone","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"Stores the customer's phone number as an optional text field for contact purposes.","glossary_terms":[],"cardinality":100,"null_count":0,"data_range":{"min":"555-1001","max":"555-1100"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.phone","concept_confidence":1.0,"concept_evidence":["name token: phone","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: contact","value pattern: phone","table context: customers","sensitive hint: pii_contact"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"phone"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The `created_at` column records the non-nullable timestamp indicating when a customer record was initially created in the system.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":95,"null_count":0,"data_range":{"min":"2021-03-23 15:38:57.201565","max":"2026-02-26 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: customers"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"Tracks the timestamp of the most recent update to a customer's record, ensuring accurate change history.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":95,"null_count":0,"data_range":{"min":"2021-03-23 15:38:57.201565","max":"2026-03-26 08:52:49.252228"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: customers"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"}],"table_description":"The `customers` table stores information about retail customers, including their unique ID, name, contact details, and timestamps for record creation and updates.","glossary_terms":[],"primary_keys":["customer_id"],"foreign_keys":[],"row_count":100,"field_classifications":{"customer_id":"identifier","first_name":"person_name","last_name":"person_name","email":"contact","phone":"contact","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{"email":"pii_contact","phone":"pii_contact"},"incremental_columns":["updated_at"],"join_candidates":[],"unit_summary":{"columns_with_units":0,"columns_without_units":7,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":false,"has_sensitive_fields":true,"row_count_projection_1y":126,"row_count_projection_2y":152,"row_count_projection_5y":232,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.email":1,"contact.person_name":2,"contact.phone":1,"identifier.foreign_key":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"findings":[{"column":"email","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 100 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"phone","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 100 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}},{"table":"employees","schema":"dbo","columns":[{"name":"employee_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for each employee in the retail operations system.","glossary_terms":[],"cardinality":20,"null_count":0,"data_range":{"min":"64","max":"83"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Associates each employee with a specific store, referencing the `store_id` column in the `stores` table.","glossary_terms":[],"cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"first_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"Stores the given name of an employee, represented as a non-null, case-insensitive Unicode string.","glossary_terms":[],"cardinality":20,"null_count":0,"data_range":{"min":"Employee1","max":"Employee9"},"data_category":"nominal","semantic_class":"given_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: first_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"first_name"},{"name":"last_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"The \"last_name\" column in the \"employees\" table stores the non-nullable family name of an employee as a case-insensitive Unicode string.","glossary_terms":[],"cardinality":20,"null_count":0,"data_range":{"min":"LastName1","max":"LastName9"},"data_category":"nominal","semantic_class":"family_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: last_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"last_name"},{"name":"email","type":"nvarchar(450)","nullable":false,"is_incremental":false,"column_description":"Stores the unique email address of each employee for contact purposes, with a maximum length of 450 characters and cannot be null.","glossary_terms":[],"cardinality":20,"null_count":0,"data_range":{"min":"emp1@example.com","max":"emp9@example.com"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.email","concept_confidence":1.0,"concept_evidence":["name token: email","type hint: nvarchar(450)","legacy field classification: contact","value pattern: email","sensitive hint: pii_contact"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"email"},{"name":"role","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"Indicates the job position or function of an employee within the organization, stored as a non-nullable text value.","glossary_terms":[],"cardinality":4,"null_count":0,"data_range":{"min":"Cashier","max":"Stock"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"entity.type","concept_confidence":0.65,"concept_evidence":["name token: role","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","profile heuristic matched"],"concept_sources":["name","profile","type"],"concept_alias_group":"role"},{"name":"hire_date","type":"date","nullable":false,"is_incremental":false,"column_description":"The `hire_date` column in the `employees` table stores the non-nullable date an employee was hired, used for tracking employment start dates.","glossary_terms":[],"cardinality":20,"null_count":0,"data_range":{"min":"2021-05-03","max":"2025-01-26"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.date_only","concept_confidence":1.0,"concept_evidence":["name token: hire_date","type hint: date","legacy field classification: temporal","value pattern: date_only","table context: employees"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"hire_date"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The `created_at` column records the non-nullable timestamp indicating when an employee record was initially created in the system.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":20,"null_count":0,"data_range":{"min":"2021-05-03 15:38:57.201565","max":"2025-01-26 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: employees"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The `updated_at` column stores the non-nullable timestamp of the most recent update to an employee record.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":20,"null_count":0,"data_range":{"min":"2021-05-03 15:38:57.201565","max":"2025-01-26 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: employees"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"}],"table_description":"The `employees` table stores details about retail system employees, including their identifiers, store associations, personal information, roles, hire dates, and record timestamps.","glossary_terms":[],"primary_keys":["employee_id"],"foreign_keys":[{"column":"store_id","references":"stores.store_id"}],"row_count":20,"field_classifications":{"first_name":"person_name","last_name":"person_name","email":"contact","hire_date":"temporal","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{"email":"pii_contact"},"incremental_columns":["updated_at"],"join_candidates":[{"column":"store_id","target_table":"stores","target_column":"store_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":9,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":true,"row_count_projection_1y":35,"row_count_projection_2y":50,"row_count_projection_5y":96,"partition_columns_candidates":["hire_date","created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.email":1,"contact.person_name":2,"entity.type":1,"identifier.foreign_key":2,"temporal.created_at":1,"temporal.date_only":1,"temporal.updated_at":1},"low_confidence_columns":["first_name","last_name"]},"data_quality":{"findings":[{"column":"role","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 4 distinct value(s) ('Cashier', 'Manager', 'Sales', 'Stock') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Cashier","Manager","Sales","Stock"],"cardinality":4},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":"hire_date","check":"late_arriving_data","severity":"info","detail":"Minor arrival delay \u2014 max lag between 'hire_date' and 'created_at' is 15.7h (avg 15.7h, P95 15.7h).","recommendation":"Use 'created_at' as the watermark (preferred). If using 'hire_date', add a 1\u20132 day lookback buffer.","business_date_column":"hire_date","system_ts_column":"created_at","lag_stats":{"total_rows_compared":20,"min_lag_hours":15.65,"avg_lag_hours":15.65,"p95_lag_hours":15.65,"max_lag_hours":15.65,"max_lag_days":0.7,"rows_late_over_1d":0,"rows_late_over_7d":0},"recommended_lookback_days":2},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}},{"table":"inventory","schema":"dbo","columns":[{"name":"inventory_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for each inventory record in the system.","glossary_terms":[],"cardinality":100,"null_count":0,"data_range":{"min":"8","max":"107"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Identifier for the store associated with the inventory record, referencing the `store_id` column in the `stores` table.","glossary_terms":[],"cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"product_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"References the unique identifier of a product from the `products` table to associate inventory records with specific products.","glossary_terms":[],"cardinality":47,"null_count":0,"data_range":{"min":"156","max":"205"},"data_category":"discrete","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"quantity_on_hand","type":"integer","nullable":false,"is_incremental":false,"column_description":"Tracks the current quantity of a product available in inventory, expressed as a non-null integer.","glossary_terms":[],"cardinality":68,"null_count":0,"data_range":{"min":"2","max":"98"},"data_category":"discrete","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: quantity_on_hand","type hint: integer","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"quantity_on_hand"},{"name":"reorder_level","type":"integer","nullable":false,"is_incremental":false,"column_description":"Indicates the minimum quantity of a product in inventory that triggers a reorder, stored as a non-null integer.","glossary_terms":[],"cardinality":20,"null_count":0,"data_range":{"min":"10","max":"29"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: integer","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"last_restocked_at","type":"datetime2","nullable":true,"is_incremental":false,"column_description":"The `last_restocked_at` column records the timestamp of the most recent restocking event for an inventory item, allowing null values if the item has not been restocked.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":89,"null_count":0,"data_range":{"min":"2024-03-14 15:38:57.201565","max":"2026-03-07 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.event_time","concept_confidence":1.0,"concept_evidence":["name token: last_restocked_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: inventory"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"last_restocked_at"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The `created_at` column records the non-nullable timestamp indicating when the inventory record was initially created.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":91,"null_count":0,"data_range":{"min":"2024-03-05 15:38:57.201565","max":"2026-02-23 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: inventory"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"Tracks the timestamp of the most recent update to an inventory record, ensuring accurate change history.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":89,"null_count":0,"data_range":{"min":"2024-03-14 15:38:57.201565","max":"2026-03-07 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"conc</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10336,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>: inventory"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"stock_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"column_description":"Represents the monetary value of stock for an inventory item, stored as a numeric value with up to 10 digits and 2 decimal places, and may be null.","cardinality":0,"null_count":100,"data_category":"continuous","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.0,"concept_evidence":["type hint: numeric(10,2)","ambiguous runner-up concept"],"concept_sources":["type"],"concept_alias_group":null},{"name":"stock_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Current stock unit label.","cardinality":0,"null_count":100,"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.15,"concept_evidence":["value pattern: quantity","ambiguous runner-up concept"],"concept_sources":["values"],"concept_alias_group":null}],"table_description":"Current stock levels with normalized stock unit representation.","primary_keys":["inventory_id"],"foreign_keys":[{"column":"product_id","references":"products.product_id"},{"column":"store_id","references":"stores.store_id"}],"row_count":100,"field_classifications":{"quantity_on_hand":"quantity","last_restocked_at":"temporal","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"product_id","target_table":"products","target_column":"product_id","confidence":"high"},{"column":"store_id","target_table":"stores","target_column":"store_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":10,"mixed_unit_groups":[],"unknown_unit_columns":["quantity_on_hand"]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":146,"row_count_projection_2y":193,"row_count_projection_5y":334,"partition_columns_candidates":["last_restocked_at","created_at","updated_at"],"classification_summary":{"concept_counts":{"identifier.foreign_key":3,"measure.quantity":1,"temporal.created_at":1,"temporal.event_time":1,"temporal.updated_at":1},"low_confidence_columns":["reorder_level","stock_unit"]},"data_quality":{"findings":[{"column":"last_restocked_at","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 100 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 3 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"last_restocked_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":3},{"column":"quantity_on_hand","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."}]}},{"table":"products","schema":"dbo","columns":[{"name":"product_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for each product in the products table.","cardinality":50,"null_count":0,"data_range":{"min":"156","max":"205"},"data_category":"discrete","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"supplier_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"The `supplier_id` column in the `products` table is a non-nullable bigint that serves as a foreign key referencing the `supplier_id` column in the `suppliers` table.","cardinality":10,"null_count":0,"data_range":{"min":"33","max":"42"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"sku","type":"nvarchar(450)","nullable":false,"is_incremental":false,"column_description":"The \"sku\" column stores a unique alphanumeric identifier for each product, with a maximum length of 450 characters, and cannot be null.","cardinality":50,"null_count":0,"data_range":{"min":"SKU-0001","max":"SKU-0050"},"data_category":"nominal","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.product_code","concept_confidence":0.7,"concept_evidence":["name token: sku","type hint: nvarchar(450)","semantic class hint: product_identifier"],"concept_sources":["name","profile","type"],"concept_alias_group":"sku"},{"name":"name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"The \"name\" column in the \"products\" table stores the non-nullable name of the product as a Unicode string.","cardinality":50,"null_count":0,"data_range":{"min":"Product 1","max":"Product 9"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"name"},{"name":"category","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"The \"category\" column stores the product category as a non-null, case-insensitive string (e.g., \"Books\", \"Clothing\", \"Electronics\").","cardinality":5,"null_count":0,"data_range":{"min":"Books","max":"Sports"},"data_category":"nominal","semantic_class":"category","unit_context":null,"concept_id":"entity.category","concept_confidence":0.8,"concept_evidence":["name token: category","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: categorical","profile heuristic matched"],"concept_sources":["name","profile","type"],"concept_alias_group":"category"},{"name":"unit_price","type":"numeric(10,2)","nullable":false,"is_incremental":false,"column_description":"The `unit_price` column stores the non-null numeric value (up to 10 digits with 2 decimal places) representing the selling price of a product in currency.","cardinality":50,"null_count":0,"data_range":{"min":"11.09","max":"490.43"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: price","type hint: numeric(10,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"price"},{"name":"cost_price","type":"numeric(10,2)","nullable":false,"is_incremental":false,"column_description":"The `cost_price` column stores the non-null numeric cost value of a product with up to 10 digits, including 2 decimal places, representing its monetary amount.","cardinality":50,"null_count":0,"data_range":{"min":"5.55","max":"358.59"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: price","type hint: numeric(10,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"price"},{"name":"active","type":"bit","nullable":false,"is_incremental":false,"column_description":"Indicates whether the product is active (True) or inactive (False); cannot be null.","cardinality":1,"null_count":0,"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.0,"concept_evidence":["profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile"],"concept_alias_group":null},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The `created_at` column stores the non-nullable timestamp indicating when a product record was initially created.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":50,"null_count":0,"data_range":{"min":"2021-03-20 15:38:57.201565","max":"2024-12-25 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: products"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The `updated_at` column stores the non-nullable timestamp indicating the last update time of a product record.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":50,"null_count":0,"data_range":{"min":"2021-03-20 15:38:57.201565","max":"2024-12-25 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: products"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"weight_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Source weight unit (kg/lb) used for unit inference testing.","cardinality":0,"null_count":50,"data_category":"nominal","semantic_class":"mass","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":null,"concept_confidence":0.15,"concept_evidence":["value pattern: quantity","ambiguous runner-up concept"],"concept_sources":["values"],"concept_alias_group":null},{"name":"weight_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"column_description":"The `weight_value` column stores the weight of a product as a numeric value with up to 10 digits and 2 decimal places, and it is nullable.","cardinality":0,"null_count":50,"data_category":"continuous","semantic_class":"mass","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":null,"concept_confidence":0.0,"concept_evidence":["type hint: numeric(10,2)","ambiguous runner-up concept"],"concept_sources":["type"],"concept_alias_group":null},{"name":"length_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"column_description":"The `length_value` column stores the numeric length measurement of a product, allowing up to two decimal places, and can be null.","cardinality":0,"null_count":50,"data_category":"continuous","semantic_class":"length","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":null,"concept_confidence":0.0,"concept_evidence":["type hint: numeric(10,2)","ambiguous runner-up concept"],"concept_sources":["type"],"concept_alias_group":null},{"name":"length_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Source length unit (cm/in) used for unit inference testing.","cardinality":0,"null_count":50,"data_category":"nominal","semantic_class":"length","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":null,"concept_confidence":0.15,"concept_evidence":["value pattern: quantity","ambiguous runner-up concept"],"concept_sources":["values"],"concept_alias_group":null},{"name":"product_description","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"Stores an optional textual description of the product.","cardinality":0,"null_count":50,"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"primary_supplier_id","type":"bigint","nullable":true,"is_incremental":false,"column_description":"Primary supplier relationship used for join candidate detection.","cardinality":10,"null_count":0,"data_range":{"min":"33","max":"42"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"}],"table_description":"Master product catalog including physical units for analyzer unit-context testing.","primary_keys":["product_id"],"foreign_keys":[{"column":"primary_supplier_id","references":"suppliers.supplier_id"},{"column":"supplier_id","references":"suppliers.supplier_id"}],"row_count":50,"field_classifications":{"category":"categorical","unit_price":"pricing","cost_price":"pricing","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"primary_supplier_id","target_table":"suppliers","target_column":"supplier_id","confidence":"high"},{"column":"supplier_id","target_table":"suppliers","target_column":"supplier_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":16,"mixed_unit_groups":[],"unknown_unit_columns":["length_unit","length_value","weight_unit","weight_value"]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":68,"row_count_projection_2y":86,"row_count_projection_5y":141,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.person_name":1,"entity.category":1,"finance.currency_amount":2,"identifier.foreign_key":3,"identifier.product_code":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":["length_unit","name","product_description","weight_unit"]},"data_quality":{"findings":[{"column":"category","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 5 distinct value(s) ('Books', 'Clothing', 'Electronics', 'Home', 'Sports') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Books","Clothing","Electronics","Home","Sports"],"cardinality":5},{"column":"primary_supplier_id","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 50 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":"active","check":"delete_management","severity":"info","detail":"Active-flag column 'active' (boolean) detected \u2014 rows with active=false are logically deleted. Current distribution: True=50.","recommendation":"Filter on \"active\" = true for current records during ingestion.","delete_strategy":"soft_delete","soft_delete_column":"active","soft_delete_type":"active_flag","has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2},{"column":"weight_unit","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'mass' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"weight_value","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'mass' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"length_value","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'length' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"length_unit","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'length' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."}]}},{"table":"purchase_order_items","schema":"dbo","columns":[{"name":"po_item_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"The `po_item_id` column is a non-nullable bigint serving as the primary key for uniquely identifying each record in the `purchase_order_items` table.","cardinality":246,"null_count":0,"data_range":{"min":"268","max":"513"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"po_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"References the unique identifier of the associated purchase order in the purchase_orders table.","cardinality":125,"null_count":0,"data_range":{"min":"128","max":"252"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"product_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Represents the unique identifier of a product associated with a purchase order item, referencing the `product_id` column in the `products` table.","cardinality":49,"null_count":0,"data_range":{"min":"156","max":"205"},"data_category":"discrete","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"quantity","type":"integer","nullable":false,"is_incremental":false,"column_description":"The \"quantity\" column in the \"purchase_order_items\" table is a non-null integer representing the number of items in a purchase order.","cardinality":41,"null_count":0,"data_range":{"min":"10","max":"50"},"data_category":"discrete","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: quantity","type hint: integer","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"quantity"},{"name":"unit_cost","type":"numeric(10,2)","nullable":false,"is_incremental":false,"column_description":"Represents the non-null unit cost of a purchase order item, stored as a numeric value with up to 10 digits and 2 decimal places.","cardinality":49,"null_count":0,"data_range":{"min":"5.55","max":"358.59"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: unit_cost","type hint: numeric(10,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount","table context: purchase_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"unit_cost"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The `created_at` column stores the non-nullable timestamp indicating when the purchase order item record was created.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":246,"null_count":0,"data_range":{"min":"2026-03-12 15:44:18.668789","max":"2026-03-12 15:45:45.174099"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: purchase_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The `updated_at` column in the `purchase_order_items` table stores the non-nullable timestamp indicating the last update to a record.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":246,"null_count":0,"data_range":{"min":"2026-03-12 15:44:18.668794","max":"2026-03-12 15:45:45.174104"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: purchase_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"ordered_qty_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"column_description":"Represents the numeric value of the quantity ordered for a purchase order item, allowing up to 10 digits with 2 decimal places, and can be null.","cardinality":0,"null_count":246,"data_category":"continuous","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: ordered_qty","type hint: numeric(10,2)","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"ordered_qty"},{"name":"ordered_qty_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Ordered quantity unit (ea/box).","cardinality":0,"null_count":246,"data_category":"nominal","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: ordered_qty_unit","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity"],"concept_sources":["name","profile","values"],"concept_alias_group":"ordered_qty_unit"}],"table_description":"Line items with order quantities and explicit unit labels.","primary_keys":["po_item_id"],"foreign_keys":[{"column":"po_id","references":"purchase_orders.po_id"},{"column":"product_id","references":"products.product_id"}],"row_count":246,"field_classifications":{"quantity":"quantity","unit_cost":"pricing","created_at":"temporal","updated_at":"temporal","ordered_qty_value":"quantity","ordered_qty_unit":"quantity"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"po_id","target_table":"purchase_orders","target_column":"po_id","confidence":"high"},{"column":"product_id","target_table":"products","target_column":"product_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":9,"mixed_unit_groups":[],"unknown_unit_columns":["ordered_qty_unit","ordered_qty_value","quantity"]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":246,"row_count_projection_2y":246,"row_count_projection_5y":246,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"finance.currency_amount":1,"identifier.foreign_key":3,"measure.quantity":3,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"findings":[{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2},{"column":"quantity","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"ordered_qty_value","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has</t>
+          <t>ept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: inventory"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"stock_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"column_description":"Represents the monetary value of inventory stock, stored as a numeric value with up to 10 digits and 2 decimal places, and may be null.","glossary_terms":[],"cardinality":0,"null_count":100,"data_category":"continuous","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.0,"concept_evidence":["type hint: numeric(10,2)","ambiguous runner-up concept"],"concept_sources":["type"],"concept_alias_group":null},{"name":"stock_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Current stock unit label.","glossary_terms":[],"cardinality":0,"null_count":100,"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.15,"concept_evidence":["value pattern: quantity","ambiguous runner-up concept"],"concept_sources":["values"],"concept_alias_group":null}],"table_description":"Current stock levels with normalized stock unit representation.","glossary_terms":[],"primary_keys":["inventory_id"],"foreign_keys":[{"column":"product_id","references":"products.product_id"},{"column":"store_id","references":"stores.store_id"}],"row_count":100,"field_classifications":{"quantity_on_hand":"quantity","last_restocked_at":"temporal","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"product_id","target_table":"products","target_column":"product_id","confidence":"high"},{"column":"store_id","target_table":"stores","target_column":"store_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":10,"mixed_unit_groups":[],"unknown_unit_columns":["quantity_on_hand"]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":146,"row_count_projection_2y":193,"row_count_projection_5y":334,"partition_columns_candidates":["last_restocked_at","created_at","updated_at"],"classification_summary":{"concept_counts":{"identifier.foreign_key":3,"measure.quantity":1,"temporal.created_at":1,"temporal.event_time":1,"temporal.updated_at":1},"low_confidence_columns":["reorder_level","stock_unit"]},"data_quality":{"findings":[{"column":"last_restocked_at","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 100 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 3 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"last_restocked_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":3},{"column":"quantity_on_hand","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."}]}},{"table":"products","schema":"dbo","columns":[{"name":"product_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for each product in the retail operations system.","glossary_terms":[],"cardinality":50,"null_count":0,"data_range":{"min":"156","max":"205"},"data_category":"discrete","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"supplier_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"The `supplier_id` column in the `products` table is a non-nullable foreign key referencing the `supplier_id` column in the `suppliers` table, identifying the supplier associated with each product.","glossary_terms":[],"cardinality":10,"null_count":0,"data_range":{"min":"33","max":"42"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"sku","type":"nvarchar(450)","nullable":false,"is_incremental":false,"column_description":"Unique alphanumeric identifier for a product used for inventory and sales tracking, stored as a non-null nvarchar(450).","glossary_terms":[],"cardinality":50,"null_count":0,"data_range":{"min":"SKU-0001","max":"SKU-0050"},"data_category":"nominal","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.product_code","concept_confidence":0.7,"concept_evidence":["name token: sku","type hint: nvarchar(450)","semantic class hint: product_identifier"],"concept_sources":["name","profile","type"],"concept_alias_group":"sku"},{"name":"name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"The \"name\" column in the \"products\" table stores the non-nullable name of a product as a case-insensitive Unicode string.","glossary_terms":[],"cardinality":50,"null_count":0,"data_range":{"min":"Product 1","max":"Product 9"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"name"},{"name":"category","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"Indicates the product's category classification, such as \"Books,\" \"Clothing,\" or \"Electronics,\" stored as a non-null, case-insensitive text value.","glossary_terms":[],"cardinality":5,"null_count":0,"data_range":{"min":"Books","max":"Sports"},"data_category":"nominal","semantic_class":"category","unit_context":null,"concept_id":"entity.category","concept_confidence":0.8,"concept_evidence":["name token: category","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: categorical","profile heuristic matched"],"concept_sources":["name","profile","type"],"concept_alias_group":"category"},{"name":"unit_price","type":"numeric(10,2)","nullable":false,"is_incremental":false,"column_description":"Stores the retail price of a product as a non-null numeric value with up to 10 digits and 2 decimal places.","glossary_terms":[],"cardinality":50,"null_count":0,"data_range":{"min":"11.09","max":"490.43"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: price","type hint: numeric(10,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"price"},{"name":"cost_price","type":"numeric(10,2)","nullable":false,"is_incremental":false,"column_description":"Represents the numeric cost price of a product in the retail system, stored as a non-nullable currency amount with up to 10 digits and 2 decimal places.","glossary_terms":[],"cardinality":50,"null_count":0,"data_range":{"min":"5.55","max":"358.59"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: price","type hint: numeric(10,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"price"},{"name":"active","type":"bit","nullable":false,"is_incremental":false,"column_description":"Indicates whether a product is active and available for transactions, stored as a non-nullable boolean value.","glossary_terms":[],"cardinality":1,"null_count":0,"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.0,"concept_evidence":["profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile"],"concept_alias_group":null},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"Indicates the timestamp when the product record was initially created, stored as a non-nullable datetime value.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":50,"null_count":0,"data_range":{"min":"2021-03-20 15:38:57.201565","max":"2024-12-25 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: products"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The `updated_at` column stores the non-nullable timestamp of the most recent update to a product record in the `products` table.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":50,"null_count":0,"data_range":{"min":"2021-03-20 15:38:57.201565","max":"2024-12-25 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: products"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"weight_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Source weight unit (kg/lb) used for unit inference testing.","glossary_terms":[],"cardinality":0,"null_count":50,"data_category":"nominal","semantic_class":"mass","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":null,"concept_confidence":0.15,"concept_evidence":["value pattern: quantity","ambiguous runner-up concept"],"concept_sources":["values"],"concept_alias_group":null},{"name":"weight_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"column_description":"The `weight_value` column stores the weight of a product as a numeric value with up to 10 digits and 2 decimal places, and it is nullable.","glossary_terms":[],"cardinality":0,"null_count":50,"data_category":"continuous","semantic_class":"mass","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":null,"concept_confidence":0.0,"concept_evidence":["type hint: numeric(10,2)","ambiguous runner-up concept"],"concept_sources":["type"],"concept_alias_group":null},{"name":"length_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"column_description":"The \"length_value\" column stores the numeric length measurement of a product, allowing up to 10 digits with 2 decimal places, and is nullable.","glossary_terms":[],"cardinality":0,"null_count":50,"data_category":"continuous","semantic_class":"length","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":null,"concept_confidence":0.0,"concept_evidence":["type hint: numeric(10,2)","ambiguous runner-up concept"],"concept_sources":["type"],"concept_alias_group":null},{"name":"length_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Source length unit (cm/in) used for unit inference testing.","glossary_terms":[],"cardinality":0,"null_count":50,"data_category":"nominal","semantic_class":"length","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":null,"concept_confidence":0.15,"concept_evidence":["value pattern: quantity","ambiguous runner-up concept"],"concept_sources":["values"],"concept_alias_group":null},{"name":"product_description","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"Stores optional textual details about a product, such as features or specifications, with support for Unicode characters.","glossary_terms":[],"cardinality":0,"null_count":50,"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"primary_supplier_id","type":"bigint","nullable":true,"is_incremental":false,"column_description":"Primary supplier relationship used for join candidate detection.","glossary_terms":[],"cardinality":10,"null_count":0,"data_range":{"min":"33","max":"42"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"}],"table_description":"Master product catalog including physical units for analyzer unit-context testing.","glossary_terms":[],"primary_keys":["product_id"],"foreign_keys":[{"column":"primary_supplier_id","references":"suppliers.supplier_id"},{"column":"supplier_id","references":"suppliers.supplier_id"}],"row_count":50,"field_classifications":{"category":"categorical","unit_price":"pricing","cost_price":"pricing","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"primary_supplier_id","target_table":"suppliers","target_column":"supplier_id","confidence":"high"},{"column":"supplier_id","target_table":"suppliers","target_column":"supplier_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":16,"mixed_unit_groups":[],"unknown_unit_columns":["length_unit","length_value","weight_unit","weight_value"]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":68,"row_count_projection_2y":86,"row_count_projection_5y":141,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.person_name":1,"entity.category":1,"finance.currency_amount":2,"identifier.foreign_key":3,"identifier.product_code":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":["length_unit","name","product_description","weight_unit"]},"data_quality":{"findings":[{"column":"category","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 5 distinct value(s) ('Books', 'Clothing', 'Electronics', 'Home', 'Sports') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Books","Clothing","Electronics","Home","Sports"],"cardinality":5},{"column":"primary_supplier_id","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 50 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":"active","check":"delete_management","severity":"info","detail":"Active-flag column 'active' (boolean) detected \u2014 rows with active=false are logically deleted. Current distribution: True=50.","recommendation":"Filter on \"active\" = true for current records during ingestion.","delete_strategy":"soft_delete","soft_delete_column":"active","soft_delete_type":"active_flag","has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2},{"column":"weight_unit","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'mass' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"weight_value","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'mass' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"length_value","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'length' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"length_unit","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'length' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."}]}},{"table":"purchase_order_items","schema":"dbo","columns":[{"name":"po_item_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for each purchase order item record in the `purchase_order_items` table.","glossary_terms":[],"cardinality":246,"null_count":0,"data_range":{"min":"268","max":"513"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"po_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Links each purchase order item to its corresponding purchase order in the `purchase_orders` table via a non-null foreign key.","glossary_terms":[],"cardinality":125,"null_count":0,"data_range":{"min":"128","max":"252"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"product_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Identifier linking each purchase order item to a specific product in the products table.","glossary_terms":[],"cardinality":49,"null_count":0,"data_range":{"min":"156","max":"205"},"data_category":"discrete","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"quantity","type":"integer","nullable":false,"is_incremental":false,"column_description":"The `quantity` column in the `purchase_order_items` table stores the non-null integer value representing the number of units of a product included in a specific purchase order item.","glossary_terms":[],"cardinality":41,"null_count":0,"data_range":{"min":"10","max":"50"},"data_category":"discrete","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: quantity","type hint: integer","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"quantity"},{"name":"unit_cost","type":"numeric(10,2)","nullable":false,"is_incremental":false,"column_description":"The `unit_cost` column in the `purchase_order_items` table stores the non-null numeric cost per unit of a product in a purchase order, represented as a currency amount with up to 10 digits and 2 decimal places.","glossary_terms":[],"cardinality":49,"null_count":0,"data_range":{"min":"5.55","max":"358.59"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: unit_cost","type hint: numeric(10,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount","table context: purchase_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"unit_cost"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"Records the timestamp when a purchase order item entry is created, stored as a non-nullable datetime value.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":246,"null_count":0,"data_range":{"min":"2026-03-12 15:44:18.668789","max":"2026-03-12 15:45:45.174099"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: purchase_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The `updated_at` column in the `purchase_order_items` table stores the non-nullable timestamp of the most recent update to a purchase order item record.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":246,"null_count":0,"data_range":{"min":"2026-03-12 15:44:18.668794","max":"2026-03-12 15:45:45.174104"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: purchase_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"ordered_qty_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"column_description":"The `ordered_qty_value` column stores the numeric quantity value (up to two decimal places) of items ordered in a purchase order, which can be null.","glossary_terms":[],"cardinality":0,"null_count":246,"data_category":"continuous","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: ordered_qty","type hint: numeric(10,2)","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"ordered_qty"},{"name":"ordered_qty_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Ordered quantity unit (ea/box).","glossary_terms":[],"cardinality":0,"null_count":246,"data_category":"nominal","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: ordered_qty_unit","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity"],"concept_sources":["name","profile","values"],"concept_alias_group":"ordered_qty_unit"}],"table_description":"Line items with order quantities and explicit unit labels.","glossary_terms":[],"primary_keys":["po_item_id"],"foreign_keys":[{"column":"po_id","references":"purchase_orders.po_id"},{"column":"product_id","references":"products.product_id"}],"row_count":246,"field_classifications":{"quantity":"quantity","unit_cost":"pricing","created_at":"temporal","updated_at":"temporal","ordered_qty_value":"quantity","ordered_qty_unit":"quantity"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"po_id","target_table":"purchase_orders","target_column":"po_id","confidence":"high"},{"column":"product_id","target_table":"products","target_column":"product_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":9,"mixed_unit_groups":[],"unknown_unit_columns":["ordered_qty_unit","ordered_qty_value","quantity"]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":246,"row_count_projection_2y":246,"row_count_projection_5y":246,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"finance.currency_amount":1,"identifier.foreign_key":3,"measure.quantity":3,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"findings":[{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-</t>
         </is>
       </c>
     </row>
@@ -10215,7 +10346,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"ordered_qty_unit","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."}]}},{"table":"purchase_orders","schema":"dbo","columns":[{"name":"po_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"The `po_id` column is a non-nullable bigint serving as the primary key for uniquely identifying purchase orders in the `dbo.purchase_orders` table.","cardinality":125,"null_count":0,"data_range":{"min":"128","max":"252"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"supplier_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"The `supplier_id` column in the `purchase_orders` table is a non-nullable bigint that references the `supplier_id` column in the `suppliers` table, identifying the supplier associated with each purchase order.","cardinality":10,"null_count":0,"data_range":{"min":"33","max":"42"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"References the unique identifier of the store associated with the purchase order, linking to the `stores.store_id` column.","cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"status","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"Indicates the current state of a purchase order, such as 'Ordered' or 'Received'.","cardinality":3,"null_count":0,"data_range":{"min":"Ordered","max":"Received"},"data_category":"nominal","semantic_class":"category","unit_context":null,"concept_id":"entity.status","concept_confidence":1.0,"concept_evidence":["name token: statu","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: categorical","value pattern: status","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"statu"},{"name":"order_date","type":"date","nullable":false,"is_incremental":false,"column_description":"The `order_date` column stores the non-null date when a purchase order was placed.","cardinality":123,"null_count":0,"data_range":{"min":"2021-04-09","max":"2026-03-12"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.date_only","concept_confidence":1.0,"concept_evidence":["name token: order_date","type hint: date","legacy field classification: temporal","value pattern: date_only","table context: purchase_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"order_date"},{"name":"expected_date","type":"date","nullable":true,"is_incremental":false,"column_description":"The \"expected_date\" column in the \"purchase_orders\" table stores the anticipated delivery date of a purchase order, allowing null values.","cardinality":123,"null_count":0,"data_range":{"min":"2021-04-27","max":"2026-03-31"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.date_only","concept_confidence":1.0,"concept_evidence":["name token: expected_date","type hint: date","legacy field classification: temporal","value pattern: date_only","table context: purchase_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"expected_date"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The `created_at` column stores the non-nullable timestamp indicating when the purchase order record was initially created.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":123,"null_count":0,"data_range":{"min":"2021-04-09 15:38:57.201565","max":"2026-03-12 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: purchase_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The `updated_at` column stores the non-null timestamp indicating the last modification date and time of a purchase order record.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":123,"null_count":0,"data_range":{"min":"2021-04-09 15:38:57.201565","max":"2026-03-12 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: purchase_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"approver_employee_id","type":"bigint","nullable":true,"is_incremental":false,"column_description":"Approver employee foreign key for procurement workflow.","cardinality":0,"null_count":125,"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"}],"table_description":"Procurement headers including approver employee relationship.","primary_keys":["po_id"],"foreign_keys":[{"column":"approver_employee_id","references":"employees.employee_id"},{"column":"store_id","references":"stores.store_id"},{"column":"supplier_id","references":"suppliers.supplier_id"}],"row_count":125,"field_classifications":{"status":"categorical","order_date":"temporal","expected_date":"temporal","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"approver_employee_id","target_table":"employees","target_column":"employee_id","confidence":"high"},{"column":"store_id","target_table":"stores","target_column":"store_id","confidence":"high"},{"column":"supplier_id","target_table":"suppliers","target_column":"supplier_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":9,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":155,"row_count_projection_2y":185,"row_count_projection_5y":276,"partition_columns_candidates":["order_date","expected_date","created_at","updated_at"],"classification_summary":{"concept_counts":{"entity.status":1,"identifier.foreign_key":4,"temporal.created_at":1,"temporal.date_only":2,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"findings":[{"column":"status","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 3 distinct value(s) ('Ordered', 'Pending', 'Received') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Ordered","Pending","Received"],"cardinality":3},{"column":"expected_date","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 125 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":"order_date","check":"late_arriving_data","severity":"info","detail":"Minor arrival delay \u2014 max lag between 'order_date' and 'created_at' is 15.7h (avg 15.7h, P95 15.7h).","recommendation":"Use 'created_at' as the watermark (preferred). If using 'order_date', add a 1\u20132 day lookback buffer.","business_date_column":"order_date","system_ts_column":"created_at","lag_stats":{"total_rows_compared":125,"min_lag_hours":15.65,"avg_lag_hours":15.65,"p95_lag_hours":15.65,"max_lag_hours":15.65,"max_lag_days":0.7,"rows_late_over_1d":0,"rows_late_over_7d":0},"recommended_lookback_days":2},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}},{"table":"sales_order_items","schema":"dbo","columns":[{"name":"sales_order_item_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"The `sales_order_item_id` column is a non-nullable bigint serving as the primary key for uniquely identifying records in the `sales_order_items` table.","cardinality":508,"null_count":0,"data_range":{"min":"497","max":"1004"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"sales_order_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Links each sales order item to its corresponding sales order in the `sales_orders` table via a non-null foreign key.","cardinality":200,"null_count":0,"data_range":{"min":"375","max":"574"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"product_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"References the unique identifier of a product from the products table, establishing a mandatory relationship between sales order items and products.","cardinality":50,"null_count":0,"data_range":{"min":"156","max":"205"},"data_category":"discrete","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"quantity","type":"integer","nullable":false,"is_incremental":false,"column_description":"Represents the non-null integer quantity of a product in a sales order item.","cardinality":5,"null_count":0,"data_range":{"min":"1","max":"5"},"data_category":"discrete","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: quantity","type hint: integer","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"quantity"},{"name":"unit_price","type":"numeric(15,2)","nullable":false,"is_incremental":false,"column_description":"Represents the non-null unit price of a sales order item, stored as a numeric value with up to 15 digits and 2 decimal places.","cardinality":50,"null_count":0,"data_range":{"min":"11.09","max":"490.43"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: price","type hint: numeric(15,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount","table context: sales_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"price"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The `created_at` column records the non-nullable timestamp indicating when the sales order item was created.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":508,"null_count":0,"data_range":{"min":"2026-03-12 15:41:01.155388","max":"2026-03-12 15:43:38.264437"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: sales_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The `updated_at` column in the `sales_order_items` table stores the non-nullable timestamp indicating the last update to a sales order item record.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":508,"null_count":0,"data_range":{"min":"2026-03-12 15:41:01.155390","max":"2026-03-12 15:43:38.264447"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: sales_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"sold_qty_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"column_description":"Represents the numeric value of the sold quantity for a sales order item, allowing up to two decimal places and nullable.","cardinality":0,"null_count":508,"data_category":"continuous","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: sold_qty","type hint: numeric(10,2)","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"sold_qty"},{"name":"sold_qty_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Sold quantity unit (ea/box).","cardinality":0,"null_count":508,"data_category":"nominal","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: sold_qty_unit","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity"],"concept_sources":["name","profile","values"],"concept_alias_group":"sold_qty_unit"}],"table_description":"Sales line items with sold quantity and explicit unit labels.","primary_keys":["sales_order_item_id"],"foreign_keys":[{"column":"product_id","references":"products.product_id"},{"column":"sales_order_id","references":"sales_orders.sales_order_id"}],"row_count":508,"field_classifications":{"quantity":"quantity","unit_price":"pricing","created_at":"temporal","updated_at":"temporal","sold_qty_value":"quantity","sold_qty_unit":"quantity"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"product_id","target_table":"products","target_column":"product_id","confidence":"high"},{"column":"sales_order_id","target_table":"sales_orders","target_column":"sales_order_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":9,"mixed_unit_groups":[],"unknown_unit_columns":["quantity","sold_qty_unit","sold_qty_value"]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":508,"row_count_projection_2y":508,"row_count_projection_5y":508,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"finance.currency_amount":1,"identifier.foreign_key":3,"measure.quantity":3,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"findings":[{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2},{"column":"quantity","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"sold_qty_value","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"sold_qty_unit","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."}]}},{"table":"sales_orders","schema":"dbo","columns":[{"name":"sales_order_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"The `sales_order_id` column is a non-nullable bigint serving as the primary key for uniquely identifying sales orders in the `sales_orders` table.","cardinality":200,"null_count":0,"data_range":{"min":"375","max":"574"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Represents the unique identifier of the store associated with the sales order, referencing the `store_id` column in the `stores` table.","cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"customer_id","type":"bigint","nullable":true,"is_incremental":false,"column_description":"Represents the identifier of the customer associated with the sales order, referencing the `customer_id` column in the `customers` table; nullable.","cardinality":76,"null_count":0,"data_range":{"min":"404","max":"502"},"data_category":"discrete","semantic_class":"customer_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"employee_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Represents the unique identifier of the employee associated with the sales order, referencing the `employees.employee_id` column.","cardinality":20,"null_count":0,"data_range":{"min":"64","max":"83"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"order_date","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The `order_date` column in the `sales_orders` table stores the non-nullable timestamp indicating when the sales order was placed.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":191,"null_count":0,"data_range":{"min":"2021-03-14 15:38:57.201565","max":"2026-03-11 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.date_only","concept_confidence":0.9,"concept_evidence":["name token: order_date","type hint: datetime2","legacy field classification: temporal","table context: sales_orders","cross-table consensus: 2 similar columns"],"concept_sources":["cross_table_consensus","name","profile","table_context","type"],"concept_alias_group":"order_date"},{"name":"status","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"Indicates the current state of a sales order, such as 'Pending' or 'Completed', stored as a non-nullable text category.","cardinality":3,"null_count":0,"data_range":{"min":"Completed","max":"Shipped"},"data_category":"nominal","semantic_class":"category","unit_context":null,"concept_id":"entity.status","concept_confidence":1.0,"concept_evidence":["name token: statu","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: categorical","value pattern: status","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"statu"},{"name":"total_amount","type":"numeric(12,2)","nullable":false,"is_incremental":false,"column_description":"The `total_amount` column stores the total monetary value of a sales order as a non-null numeric value with up to 12 digits, including 2 decimal places.","cardinality":200,"null_count":0,"data_range":{"min":"66.47","max":"998.76"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: amount","type hint: numeric(12,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount","table context: sales_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"amount"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The \"created_at\" column in the \"sales_orders\" table stores the non-nullable timestamp indicating when the sales order record was created.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":191,"null_count":0,"data_range":{"min":"2021-03-14 15:38:57.201565","max":"2026-03-11 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: sales_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The \"updated_at\" column stores the non-nullable timestamp of the most recent update to a sales order record.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":191,"null_count":0,"data_range":{"min":"2021-03-14 15:38:57.201565","max":"2026-03-11 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: sales_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"sales_rep_employee_id","type":"bigint","nullable":true,"is_incremental":false,"column_description":"Sales representative foreign key for order ownership.","cardinality":0,"null_count":200,"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"}],"table_description":"Sales headers including assigned sales representative relationship.","primary_keys":["sales_order_id"],"foreign_keys":[{"column":"customer_id","references":"customers.customer_id"},{"column":"employee_id","references":"employees.employee_id"},{"column":"sales_rep_employee_id","references":"employees.employee_id"},{"column":"store_id","references":"stores.store_id"}],"row_count":200,"field_classifications":{"customer_id":"identifier","order_date":"temporal","status":"categorical","total_amount":"pricing","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"customer_id","target_table":"customers","target_column":"customer_id","confidence":"high"},{"column":"employee_id","target_table":"employees","target_column":"employee_id","confidence":"high"},{"column":"sales_rep_employee_id","target_table":"employees","target_column":"employee_id","confidence":"high"},{"column":"store_id","target_table":"stores","target_column":"store_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":10,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":242,"row_count_projection_2y":284,"row_count_projection_5y":412,"partition_columns_candidates":["order_date","created_at","updated_at"],"classification_summary":{"concept_counts":{"entity.status":1,"finance.currency_amount":1,"identifier.foreign_key":5,"temporal.created_at":1,"temporal.date_only":1,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"f</t>
+          <t>naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2},{"column":"quantity","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"ordered_qty_value","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"ordered_qty_unit","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."}]}},{"table":"purchase_orders","schema":"dbo","columns":[{"name":"po_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for purchase orders in the retail operations system.","glossary_terms":[],"cardinality":125,"null_count":0,"data_range":{"min":"128","max":"252"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"supplier_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"References the unique identifier of the supplier associated with a purchase order, linking to the `suppliers.supplier_id` column.","glossary_terms":[],"cardinality":10,"null_count":0,"data_range":{"min":"33","max":"42"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Identifies the store associated with the purchase order, referencing the `store_id` column in the `stores` table.","glossary_terms":[],"cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"status","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"Indicates the current state of a purchase order, such as 'Ordered' or 'Received', using predefined category values.","glossary_terms":[],"cardinality":3,"null_count":0,"data_range":{"min":"Ordered","max":"Received"},"data_category":"nominal","semantic_class":"category","unit_context":null,"concept_id":"entity.status","concept_confidence":1.0,"concept_evidence":["name token: statu","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: categorical","value pattern: status","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"statu"},{"name":"order_date","type":"date","nullable":false,"is_incremental":false,"column_description":"The `order_date` column in the `purchase_orders` table records the date a purchase order was placed and cannot be null.","glossary_terms":[],"cardinality":123,"null_count":0,"data_range":{"min":"2021-04-09","max":"2026-03-12"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.date_only","concept_confidence":1.0,"concept_evidence":["name token: order_date","type hint: date","legacy field classification: temporal","value pattern: date_only","table context: purchase_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"order_date"},{"name":"expected_date","type":"date","nullable":true,"is_incremental":false,"column_description":"The `expected_date` column in the `purchase_orders` table records the anticipated delivery date for a purchase order, allowing null values.","glossary_terms":[],"cardinality":123,"null_count":0,"data_range":{"min":"2021-04-27","max":"2026-03-31"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.date_only","concept_confidence":1.0,"concept_evidence":["name token: expected_date","type hint: date","legacy field classification: temporal","value pattern: date_only","table context: purchase_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"expected_date"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The `created_at` column records the timestamp when a purchase order record is initially created in the system and cannot be null.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":123,"null_count":0,"data_range":{"min":"2021-04-09 15:38:57.201565","max":"2026-03-12 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: purchase_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The `updated_at` column stores the non-null timestamp indicating the last modification date and time of a purchase order record.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":123,"null_count":0,"data_range":{"min":"2021-04-09 15:38:57.201565","max":"2026-03-12 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: purchase_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"approver_employee_id","type":"bigint","nullable":true,"is_incremental":false,"column_description":"Approver employee foreign key for procurement workflow.","glossary_terms":[],"cardinality":0,"null_count":125,"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"}],"table_description":"Procurement headers including approver employee relationship.","glossary_terms":[],"primary_keys":["po_id"],"foreign_keys":[{"column":"approver_employee_id","references":"employees.employee_id"},{"column":"store_id","references":"stores.store_id"},{"column":"supplier_id","references":"suppliers.supplier_id"}],"row_count":125,"field_classifications":{"status":"categorical","order_date":"temporal","expected_date":"temporal","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"approver_employee_id","target_table":"employees","target_column":"employee_id","confidence":"high"},{"column":"store_id","target_table":"stores","target_column":"store_id","confidence":"high"},{"column":"supplier_id","target_table":"suppliers","target_column":"supplier_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":9,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":155,"row_count_projection_2y":185,"row_count_projection_5y":276,"partition_columns_candidates":["order_date","expected_date","created_at","updated_at"],"classification_summary":{"concept_counts":{"entity.status":1,"identifier.foreign_key":4,"temporal.created_at":1,"temporal.date_only":2,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"findings":[{"column":"status","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 3 distinct value(s) ('Ordered', 'Pending', 'Received') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Ordered","Pending","Received"],"cardinality":3},{"column":"expected_date","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 125 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":"order_date","check":"late_arriving_data","severity":"info","detail":"Minor arrival delay \u2014 max lag between 'order_date' and 'created_at' is 15.7h (avg 15.7h, P95 15.7h).","recommendation":"Use 'created_at' as the watermark (preferred). If using 'order_date', add a 1\u20132 day lookback buffer.","business_date_column":"order_date","system_ts_column":"created_at","lag_stats":{"total_rows_compared":125,"min_lag_hours":15.65,"avg_lag_hours":15.65,"p95_lag_hours":15.65,"max_lag_hours":15.65,"max_lag_days":0.7,"rows_late_over_1d":0,"rows_late_over_7d":0},"recommended_lookback_days":2},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}},{"table":"sales_order_items","schema":"dbo","columns":[{"name":"sales_order_item_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for individual items within a sales order, serving as the primary key for the `sales_order_items` table.","glossary_terms":[],"cardinality":508,"null_count":0,"data_range":{"min":"497","max":"1004"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"sales_order_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Identifier linking each sales order item to its associated sales order in the `sales_orders` table.","glossary_terms":[],"cardinality":200,"null_count":0,"data_range":{"min":"375","max":"574"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"product_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"References the unique identifier of the product associated with a sales order item, linking to the `products.product_id` column.","glossary_terms":[],"cardinality":50,"null_count":0,"data_range":{"min":"156","max":"205"},"data_category":"discrete","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"quantity","type":"integer","nullable":false,"is_incremental":false,"column_description":"The \"quantity\" column in the \"sales_order_items\" table stores the non-null integer value representing the number of units of a product included in a specific sales order item.","glossary_terms":[],"cardinality":5,"null_count":0,"data_range":{"min":"1","max":"5"},"data_category":"discrete","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: quantity","type hint: integer","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"quantity"},{"name":"unit_price","type":"numeric(15,2)","nullable":false,"is_incremental":false,"column_description":"Represents the per-unit price of a product in a sales order item, stored as a non-null numeric value with up to 15 digits and 2 decimal places.","glossary_terms":[],"cardinality":50,"null_count":0,"data_range":{"min":"11.09","max":"490.43"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: price","type hint: numeric(15,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount","table context: sales_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"price"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The `created_at` column in the `sales_order_items` table stores the non-nullable timestamp indicating when a sales order item record was created.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":508,"null_count":0,"data_range":{"min":"2026-03-12 15:41:01.155388","max":"2026-03-12 15:43:38.264437"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: sales_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The `updated_at` column stores the non-nullable timestamp of the most recent update to a sales order item record for tracking modification history.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":508,"null_count":0,"data_range":{"min":"2026-03-12 15:41:01.155390","max":"2026-03-12 15:43:38.264447"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: sales_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"sold_qty_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"column_description":"Represents the numeric value of the quantity sold for a sales order item, allowing up to two decimal places and nullable for cases where the quantity is not recorded.","glossary_terms":[],"cardinality":0,"null_count":508,"data_category":"continuous","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: sold_qty","type hint: numeric(10,2)","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"sold_qty"},{"name":"sold_qty_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Sold quantity unit (ea/box).","glossary_terms":[],"cardinality":0,"null_count":508,"data_category":"nominal","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: sold_qty_unit","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity"],"concept_sources":["name","profile","values"],"concept_alias_group":"sold_qty_unit"}],"table_description":"Sales line items with sold quantity and explicit unit labels.","glossary_terms":[],"primary_keys":["sales_order_item_id"],"foreign_keys":[{"column":"product_id","references":"products.product_id"},{"column":"sales_order_id","references":"sales_orders.sales_order_id"}],"row_count":508,"field_classifications":{"quantity":"quantity","unit_price":"pricing","created_at":"temporal","updated_at":"temporal","sold_qty_value":"quantity","sold_qty_unit":"quantity"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"product_id","target_table":"products","target_column":"product_id","confidence":"high"},{"column":"sales_order_id","target_table":"sales_orders","target_column":"sales_order_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":9,"mixed_unit_groups":[],"unknown_unit_columns":["quantity","sold_qty_unit","sold_qty_value"]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":508,"row_count_projection_2y":508,"row_count_projection_5y":508,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"finance.currency_amount":1,"identifier.foreign_key":3,"measure.quantity":3,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"findings":[{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2},{"column":"quantity","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"sold_qty_value","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"sold_qty_unit","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."}]}},{"table":"sales_orders","schema":"dbo","columns":[{"name":"sales_order_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for each sales order in the system.","glossary_terms":[],"cardinality":200,"null_count":0,"data_range":{"min":"375","max":"574"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Identifies the store associated with a sales order, referencing the `store_id` column in the `stores` table.","glossary_terms":[],"cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"customer_id","type":"bigint","nullable":true,"is_incremental":false,"column_description":"Identifies the customer associated with a sales order, referencing the `customer_id` column in the `customers` table; nullable to accommodate orders without a registered customer.","glossary_terms":[],"cardinality":76,"null_count":0,"data_range":{"min":"404","max":"502"},"data_category":"discrete","semantic_class":"customer_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"employee_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Identifies the employee responsible for processing the sales order, referencing the `employees.employee_id` column.","glossary_terms":[],"cardinality":20,"null_count":0,"data_range":{"min":"64","max":"83"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"order_date","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The `order_date` column records the date and time when a sales order was placed, stored as a non-nullable `datetime2` value.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":191,"null_count":0,"data_range":{"min":"2021-03-14 15:38:57.201565","max":"2026-03-11 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.date_only","concept_confidence":0.9,"concept_evidence":["name token: order_date","type hint: datetime2","legacy field classification: temporal","table context: sales_orders","cross-table consensus: 2 similar columns"],"concept_sources":["cross_table_consensus","name","profile","table_context","type"],"concept_alias_group":"order_date"},{"name":"status","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"Indicates the current state of a sales order, such as 'Pending' or 'Completed', stored as a non-nullable text category.","glossary_terms":[],"cardinality":3,"null_count":0,"data_range":{"min":"Completed","max":"Shipped"},"data_category":"nominal","semantic_class":"category","unit_context":null,"concept_id":"entity.status","concept_confidence":1.0,"concept_evidence":["name token: statu","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: categorical","value pattern: status","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"statu"},{"name":"total_amount","type":"numeric(12,2)","nullable":false,"is_incremental":false,"column_description":"The `total_amount` column in the `sales_orders` table stores the non-nullable total monetary value of a sales order as a numeric value with up to 12 digits and 2 decimal places.","glossary_terms":[],"cardinality":200,"null_count":0,"data_range":{"min":"66.47","max":"998.76"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: amount","type hint: numeric(12,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount","table context: sales_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"amount"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The `created_at` column records the timestamp when a sales order entry was initially created, stored as a non-nullable `datetime2` value.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":191,"null_count":0,"data_range":{"min":"2021-03-14 15:38:57.201565","max":"2026-03-11 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: sales_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The `updated_at` column records the timestamp of the most recent update to a sales order, ensuring accurate tracking of modifications, and it is mandatory.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":191,"null_count":0,"data_range":{"min":"2021-03-14 15:38:57.201565","max":"2026-03-11 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: sales_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"sales_rep_employee_id","type":"bigint","nullable":true,"is_incremental":false,"column_description":"Sales representative foreign key for order ownership.","glossary_terms":[],"cardinality":0,"null_count":200,"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"}],"table_description":"Sales headers including assigned sales representative relationship.","glossary_terms":</t>
         </is>
       </c>
     </row>
@@ -10225,7 +10356,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>indings":[{"column":"status","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 3 distinct value(s) ('Completed', 'Pending', 'Shipped') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Completed","Pending","Shipped"],"cardinality":3},{"column":"customer_id","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 200 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":"order_date","check":"late_arriving_data","severity":"info","detail":"Data arrives promptly \u2014 max lag between 'order_date' and 'created_at' is 0.0h. Standard watermarking on 'created_at' is safe.","recommendation":"Use 'created_at' as the incremental watermark. No special lookback window needed.","business_date_column":"order_date","system_ts_column":"created_at","lag_stats":{"total_rows_compared":200,"min_lag_hours":0.0,"avg_lag_hours":0.0,"p95_lag_hours":0.0,"max_lag_hours":0.0,"max_lag_days":0.0,"rows_late_over_1d":0,"rows_late_over_7d":0},"recommended_lookback_days":1},{"column":null,"check":"timezone","severity":"info","detail":"All 3 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"order_date","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":3}]}},{"table":"stores","schema":"dbo","columns":[{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"The `store_id` column is a non-nullable bigint serving as the primary key for uniquely identifying each store in the `stores` table.","cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"The \"name\" column in the \"stores\" table is a non-nullable nvarchar field intended to store the name of a store, though sample data is unavailable.","cardinality":5,"null_count":0,"data_range":{"min":"Airport Shop","max":"Suburb Store"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"name"},{"name":"code","type":"nvarchar(450)","nullable":false,"is_incremental":false,"column_description":"The \"code\" column in the \"stores\" table is a non-nullable nvarchar(450) field intended to store unique identifiers or short codes for each store.","cardinality":5,"null_count":0,"data_range":{"min":"AIR","max":"SUB"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: nvarchar(450)","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"address","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"Stores.address is an optional nvarchar column storing the physical address of a store, with case-insensitive collation.","cardinality":5,"null_count":0,"data_range":{"min":"1 Main St","max":"5 Main St"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.address","concept_confidence":0.55,"concept_evidence":["name token: address","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"address"},{"name":"city","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"The \"city\" column in the \"stores\" table stores the name of the city where the store is located, allowing null values.","cardinality":3,"null_count":0,"data_range":{"min":"Cork","max":"Limerick"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"state","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"This nullable nvarchar column stores the state or province associated with a store's address.","cardinality":3,"null_count":0,"data_range":{"min":"Connacht","max":"Munster"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"postal_code","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"The \"postal_code\" column in the \"stores\" table stores the postal or ZIP code of a store as a nullable nvarchar string.","cardinality":5,"null_count":0,"data_range":{"min":"10000","max":"10004"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.address","concept_confidence":0.55,"concept_evidence":["name token: postal_code","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"postal_code"},{"name":"phone","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"Stores.phone is an optional nvarchar column storing contact phone numbers for stores, formatted as text.","cardinality":5,"null_count":0,"data_range":{"min":"555-3000","max":"555-3004"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.phone","concept_confidence":1.0,"concept_evidence":["name token: phone","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: contact","value pattern: phone","sensitive hint: pii_contact"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"phone"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The `created_at` column stores the non-nullable timestamp indicating when a store record was created.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":5,"null_count":0,"data_range":{"min":"2021-07-26 15:38:57.201565","max":"2025-01-31 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: stores"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The `updated_at` column in the `stores` table records the non-nullable timestamp of the most recent update to a store's record.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":5,"null_count":0,"data_range":{"min":"2021-07-26 15:38:57.201565","max":"2025-01-31 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: stores"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"}],"table_description":"The `stores` table stores information about retail locations, including unique identifiers, names, contact details, addresses, and timestamps for record creation and updates.","primary_keys":["store_id"],"foreign_keys":[],"row_count":5,"field_classifications":{"phone":"contact","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{"address":"pii_address","postal_code":"pii_address","phone":"pii_contact"},"incremental_columns":["updated_at"],"join_candidates":[],"unit_summary":{"columns_with_units":0,"columns_without_units":10,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":false,"has_sensitive_fields":true,"row_count_projection_1y":17,"row_count_projection_2y":29,"row_count_projection_5y":65,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.address":2,"contact.person_name":1,"contact.phone":1,"identifier.foreign_key":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":["address","city","code","name","postal_code","state"]},"data_quality":{"findings":[{"column":"city","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 3 distinct value(s) ('Cork', 'Galway', 'Limerick') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Cork","Galway","Limerick"],"cardinality":3},{"column":"state","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 3 distinct value(s) ('Connacht', 'Leinster', 'Munster') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Connacht","Leinster","Munster"],"cardinality":3},{"column":"postal_code","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 5 distinct value(s) ('10000', '10001', '10002', '10003', '10004') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["10000","10001","10002","10003","10004"],"cardinality":5},{"column":"address","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"city","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"state","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"postal_code","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"phone","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}},{"table":"suppliers","schema":"dbo","columns":[{"name":"supplier_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for each supplier, serving as the primary key for the suppliers table.","cardinality":10,"null_count":0,"data_range":{"min":"33","max":"42"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"The \"name\" column in the \"suppliers\" table is a non-nullable nvarchar field intended to store supplier names, though sample data indicates it is currently unused.","cardinality":10,"null_count":0,"data_range":{"min":"Supplier 1","max":"Supplier 9"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"name"},{"name":"contact_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"The \"contact_name\" column in the \"suppliers\" table stores the name of a contact person for the supplier, allowing null values.","cardinality":0,"null_count":10,"data_category":"nominal","semantic_class":"person_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: contact_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"contact_name"},{"name":"email","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"The \"email\" column in the \"suppliers\" table stores the email address of a supplier as a nullable nvarchar value, used for contact purposes.","cardinality":10,"null_count":0,"data_range":{"min":"supplier1@example.com","max":"supplier9@example.com"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.email","concept_confidence":1.0,"concept_evidence":["name token: email","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: contact","value pattern: email","sensitive hint: pii_contact"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"email"},{"name":"phone","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"Stores the supplier's phone number as a nullable string, primarily for contact purposes.","cardinality":10,"null_count":0,"data_range":{"min":"555-2001","max":"555-2010"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.phone","concept_confidence":1.0,"concept_evidence":["name token: phone","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: contact","value pattern: phone","sensitive hint: pii_contact"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"phone"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The `created_at` column stores the non-nullable timestamp indicating when a supplier record was created.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":10,"null_count":0,"data_range":{"min":"2021-03-22 15:38:57.201565","max":"2024-02-25 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: suppliers"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The `updated_at` column stores the non-nullable timestamp of the most recent update to a supplier record in the `suppliers` table.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":10,"null_count":0,"data_range":{"min":"2021-03-22 15:38:57.201565","max":"2024-02-25 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: suppliers"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"}],"table_description":"The \"suppliers\" table stores information about suppliers, including their unique identifier, name, contact details, and timestamps for record creation and updates.","primary_keys":["supplier_id"],"foreign_keys":[],"row_count":10,"field_classifications":{"contact_name":"person_name","email":"contact","phone":"contact","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{"email":"pii_contact","phone":"pii_contact"},"incremental_columns":["updated_at"],"join_candidates":[],"unit_summary":{"columns_with_units":0,"columns_without_units":7,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":false,"has_sensitive_fields":true,"row_count_projection_1y":22,"row_count_projection_2y":35,"row_count_projection_5y":74,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.email":1,"contact.person_name":2,"contact.phone":1,"identifier.foreign_key":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":["contact_name","name"]},"data_quality":{"findings":[{"column":"email","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 10 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"phone","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 10 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}}]}</t>
+          <t>[],"primary_keys":["sales_order_id"],"foreign_keys":[{"column":"customer_id","references":"customers.customer_id"},{"column":"employee_id","references":"employees.employee_id"},{"column":"sales_rep_employee_id","references":"employees.employee_id"},{"column":"store_id","references":"stores.store_id"}],"row_count":200,"field_classifications":{"customer_id":"identifier","order_date":"temporal","status":"categorical","total_amount":"pricing","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"customer_id","target_table":"customers","target_column":"customer_id","confidence":"high"},{"column":"employee_id","target_table":"employees","target_column":"employee_id","confidence":"high"},{"column":"sales_rep_employee_id","target_table":"employees","target_column":"employee_id","confidence":"high"},{"column":"store_id","target_table":"stores","target_column":"store_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":10,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":242,"row_count_projection_2y":284,"row_count_projection_5y":412,"partition_columns_candidates":["order_date","created_at","updated_at"],"classification_summary":{"concept_counts":{"entity.status":1,"finance.currency_amount":1,"identifier.foreign_key":5,"temporal.created_at":1,"temporal.date_only":1,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"findings":[{"column":"status","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 3 distinct value(s) ('Completed', 'Pending', 'Shipped') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Completed","Pending","Shipped"],"cardinality":3},{"column":"customer_id","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 200 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":"order_date","check":"late_arriving_data","severity":"info","detail":"Data arrives promptly \u2014 max lag between 'order_date' and 'created_at' is 0.0h. Standard watermarking on 'created_at' is safe.","recommendation":"Use 'created_at' as the incremental watermark. No special lookback window needed.","business_date_column":"order_date","system_ts_column":"created_at","lag_stats":{"total_rows_compared":200,"min_lag_hours":0.0,"avg_lag_hours":0.0,"p95_lag_hours":0.0,"max_lag_hours":0.0,"max_lag_days":0.0,"rows_late_over_1d":0,"rows_late_over_7d":0},"recommended_lookback_days":1},{"column":null,"check":"timezone","severity":"info","detail":"All 3 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"order_date","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":3}]}},{"table":"stores","schema":"dbo","columns":[{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for each store in the retail operations system.","glossary_terms":[],"cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"The \"name\" column in the \"stores\" table is a non-nullable nvarchar field storing the name of each retail store.","glossary_terms":[],"cardinality":5,"null_count":0,"data_range":{"min":"Airport Shop","max":"Suburb Store"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"name"},{"name":"code","type":"nvarchar(450)","nullable":false,"is_incremental":false,"column_description":"Unique identifier for a store, typically represented as an alphanumeric code.","glossary_terms":[],"cardinality":5,"null_count":0,"data_range":{"min":"AIR","max":"SUB"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: nvarchar(450)","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"address","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"The \"address\" column in the \"stores\" table stores the street address of a retail store location as a nullable Unicode string.","glossary_terms":[],"cardinality":5,"null_count":0,"data_range":{"min":"1 Main St","max":"5 Main St"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.address","concept_confidence":0.55,"concept_evidence":["name token: address","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"address"},{"name":"city","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"The \"city\" column in the \"stores\" table stores the name of the city where a store is located, allowing null values.","glossary_terms":[],"cardinality":3,"null_count":0,"data_range":{"min":"Cork","max":"Limerick"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"state","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"Indicates the state or province where the store is located, stored as a nullable text field.","glossary_terms":[],"cardinality":3,"null_count":0,"data_range":{"min":"Connacht","max":"Munster"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"postal_code","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"The \"postal_code\" column in the \"stores\" table stores the postal or ZIP code of a store location as a nullable, case-insensitive string.","glossary_terms":[],"cardinality":5,"null_count":0,"data_range":{"min":"10000","max":"10004"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.address","concept_confidence":0.55,"concept_evidence":["name token: postal_code","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"postal_code"},{"name":"phone","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"Stores.phone is an optional nvarchar column storing the contact phone number for a store location.","glossary_terms":[],"cardinality":5,"null_count":0,"data_range":{"min":"555-3000","max":"555-3004"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.phone","concept_confidence":1.0,"concept_evidence":["name token: phone","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: contact","value pattern: phone","sensitive hint: pii_contact"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"phone"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The `created_at` column records the non-nullable timestamp indicating when a store record was initially created in the system.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":5,"null_count":0,"data_range":{"min":"2021-07-26 15:38:57.201565","max":"2025-01-31 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: stores"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The `updated_at` column records the timestamp of the most recent update to a store's record and cannot be null.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":5,"null_count":0,"data_range":{"min":"2021-07-26 15:38:57.201565","max":"2025-01-31 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: stores"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"}],"table_description":"The \"stores\" table contains details about retail store locations, including unique identifiers, names, addresses, contact information, and timestamps for record creation and updates.","glossary_terms":[],"primary_keys":["store_id"],"foreign_keys":[],"row_count":5,"field_classifications":{"phone":"contact","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{"address":"pii_address","postal_code":"pii_address","phone":"pii_contact"},"incremental_columns":["updated_at"],"join_candidates":[],"unit_summary":{"columns_with_units":0,"columns_without_units":10,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":false,"has_sensitive_fields":true,"row_count_projection_1y":17,"row_count_projection_2y":29,"row_count_projection_5y":65,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.address":2,"contact.person_name":1,"contact.phone":1,"identifier.foreign_key":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":["address","city","code","name","postal_code","state"]},"data_quality":{"findings":[{"column":"city","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 3 distinct value(s) ('Cork', 'Galway', 'Limerick') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Cork","Galway","Limerick"],"cardinality":3},{"column":"state","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 3 distinct value(s) ('Connacht', 'Leinster', 'Munster') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Connacht","Leinster","Munster"],"cardinality":3},{"column":"postal_code","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 5 distinct value(s) ('10000', '10001', '10002', '10003', '10004') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["10000","10001","10002","10003","10004"],"cardinality":5},{"column":"address","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"city","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"state","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"postal_code","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"phone","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}},{"table":"suppliers","schema":"dbo","columns":[{"name":"supplier_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for each supplier, serving as the primary key in the suppliers table.","glossary_terms":[],"cardinality":10,"null_count":0,"data_range":{"min":"33","max":"42"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"The \"name\" column in the \"suppliers\" table is a non-nullable nvarchar field intended to store the name of the supplier, though sample data indicates it is currently unused.","glossary_terms":[],"cardinality":10,"null_count":0,"data_range":{"min":"Supplier 1","max":"Supplier 9"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"name"},{"name":"contact_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"The `contact_name` column in the `suppliers` table stores the name of the primary contact person for a supplier, allowing null values.","glossary_terms":[],"cardinality":0,"null_count":10,"data_category":"nominal","semantic_class":"person_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: contact_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"contact_name"},{"name":"email","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"The \"email\" column in the \"suppliers\" table stores the email address of a supplier as a nullable nvarchar value for contact purposes.","glossary_terms":[],"cardinality":10,"null_count":0,"data_range":{"min":"supplier1@example.com","max":"supplier9@example.com"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.email","concept_confidence":1.0,"concept_evidence":["name token: email","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: contact","value pattern: email","sensitive hint: pii_contact"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"email"},{"name":"phone","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"The \"phone\" column in the \"suppliers\" table stores the supplier's contact phone number as a nullable string.","glossary_terms":[],"cardinality":10,"null_count":0,"data_range":{"min":"555-2001","max":"555-2010"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.phone","concept_confidence":1.0,"concept_evidence":["name token: phone","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: contact","value pattern: phone","sensitive hint: pii_contact"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"phone"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The `created_at` column records the non-nullable timestamp indicating when a supplier record was initially created in the system.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":10,"null_count":0,"data_range":{"min":"2021-03-22 15:38:57.201565","max":"2024-02-25 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: suppliers"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The `updated_at` column stores the non-nullable timestamp of the most recent update to a supplier record.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":10,"null_count":0,"data_range":{"min":"2021-03-22 15:38:57.201565","max":"2024-02-25 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: suppliers"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"}],"table_description":"The \"suppliers\" table stores information about suppliers, including their unique identifier, name, contact details, and timestamps for record creation and updates.","glossary_terms":[],"primary_keys":["supplier_id"],"foreign_keys":[],"row_count":10,"field_classifications":{"contact_name":"person_name","email":"contact","phone":"contact","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{"email":"pii_contact","phone":"pii_contact"},"incremental_columns":["updated_at"],"join_candidates":[],"unit_summary":{"columns_with_units":0,"columns_without_units":7,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":false,"has_sensitive_fields":true,"row_count_projection_1y":22,"row_count_projection_2y":35,"row_count_projection_5y":74,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.email":1,"contact.person_name":2,"contact.phone":1,"identifier.foreign_key":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":["contact_name","name"]},"data_quality":{"findings":[{"column":"email","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 10 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"phone","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 10 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}}]}</t>
         </is>
       </c>
     </row>
@@ -10285,7 +10416,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-04-01T10:39:15.579372+00:00</t>
+          <t>2026-04-03T12:09:52.790221+00:00</t>
         </is>
       </c>
       <c r="C3" s="4" t="n"/>
@@ -15170,7 +15301,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -15192,185 +15323,197 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>semantic_class</t>
+          <t>glossary_terms</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Specific meaning inferred for the column, such as email, timestamp, given_name, or customer_identifier.</t>
+          <t>Comma-separated OpenMetadata glossary term FQNs assigned to the table or column.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>concept_id</t>
+          <t>semantic_class</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Normalized business concept assigned to the column, used to group similar fields across tables.</t>
+          <t>Specific meaning inferred for the column, such as email, timestamp, given_name, or customer_identifier.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>concept_confidence</t>
+          <t>concept_id</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Confidence score for the selected concept_id, typically between 0 and 1.</t>
+          <t>Normalized business concept assigned to the column, used to group similar fields across tables.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>concept_alias_group</t>
+          <t>concept_confidence</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Normalized alias bucket used to compare similar column names across tables.</t>
+          <t>Confidence score for the selected concept_id, typically between 0 and 1.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>concept_evidence_json</t>
+          <t>concept_alias_group</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Serialized JSON showing the signals that supported the chosen concept.</t>
+          <t>Normalized alias bucket used to compare similar column names across tables.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>concept_sources_json</t>
+          <t>concept_evidence_json</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Serialized JSON list of source types used during concept inference, such as name, values, or profile.</t>
+          <t>Serialized JSON showing the signals that supported the chosen concept.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>concept_sources_json</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Detected source unit for the column, usually taken from the name or stored unit metadata.</t>
+          <t>Serialized JSON list of source types used during concept inference, such as name, values, or profile.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>unit_source</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Where the unit came from, for example name-based detection or manually provided metadata.</t>
+          <t>Detected source unit for the column, usually taken from the name or stored unit metadata.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>canonical_unit</t>
+          <t>unit_source</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Normalized target unit used for consistent comparisons and conversions.</t>
+          <t>Where the unit came from, for example name-based detection or manually provided metadata.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>unit_system</t>
+          <t>canonical_unit</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Measurement system associated with the unit, such as metric or imperial.</t>
+          <t>Normalized target unit used for consistent comparisons and conversions.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>unit_confidence</t>
+          <t>unit_system</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Confidence level for the detected unit assignment.</t>
+          <t>Measurement system associated with the unit, such as metric or imperial.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>unit_notes</t>
+          <t>unit_confidence</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Additional notes about unit detection or normalization behavior.</t>
+          <t>Confidence level for the detected unit assignment.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>factor_to_canonical</t>
+          <t>unit_notes</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Multiplication factor used to convert the source unit into the canonical unit.</t>
+          <t>Additional notes about unit detection or normalization behavior.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>offset_to_canonical</t>
+          <t>factor_to_canonical</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Additive offset used during conversion to the canonical unit.</t>
+          <t>Multiplication factor used to convert the source unit into the canonical unit.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>offset_to_canonical</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Additive offset used during conversion to the canonical unit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>conversion_formula</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Human-readable formula showing how to convert the source unit to the canonical unit.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B16"/>
+  <autoFilter ref="A1:B17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15381,7 +15524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z34"/>
+  <dimension ref="A1:AA34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -15392,24 +15535,25 @@
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="80" customWidth="1" min="7" max="7"/>
     <col width="80" customWidth="1" min="8" max="8"/>
-    <col width="80" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
     <col width="80" customWidth="1" min="10" max="10"/>
-    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="80" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
     <col width="25" customWidth="1" min="13" max="13"/>
-    <col width="80" customWidth="1" min="14" max="14"/>
-    <col width="52" customWidth="1" min="15" max="15"/>
-    <col width="17" customWidth="1" min="16" max="16"/>
+    <col width="25" customWidth="1" min="14" max="14"/>
+    <col width="80" customWidth="1" min="15" max="15"/>
+    <col width="52" customWidth="1" min="16" max="16"/>
     <col width="22" customWidth="1" min="17" max="17"/>
     <col width="18" customWidth="1" min="18" max="18"/>
     <col width="34" customWidth="1" min="19" max="19"/>
     <col width="80" customWidth="1" min="20" max="20"/>
     <col width="34" customWidth="1" min="21" max="21"/>
-    <col width="21" customWidth="1" min="22" max="22"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
     <col width="21" customWidth="1" min="23" max="23"/>
-    <col width="20" customWidth="1" min="24" max="24"/>
-    <col width="28" customWidth="1" min="25" max="25"/>
+    <col width="21" customWidth="1" min="24" max="24"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
     <col width="63" customWidth="1" min="26" max="26"/>
+    <col width="28" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15462,25 +15606,30 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
+          <t>glossary_terms</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
           <t>classification_summary_json</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>unit_summary_json</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>row_count_projection_1y</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>row_count_projection_2y</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>row_count_projection_5y</t>
         </is>
@@ -15522,26 +15671,27 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>The `customers` table stores information about customers, including their unique identifier, name, contact details, and timestamps for record creation and updates.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
+          <t>The `customers` table stores information about retail customers, including their unique ID, name, contact details, and timestamps for record creation and updates.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
         <is>
           <t>{"concept_counts":{"contact.email":1,"contact.person_name":2,"contact.phone":1,"identifier.foreign_key":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":[]}</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>{"columns_with_units":0,"columns_without_units":7,"mixed_unit_groups":[],"unknown_unit_columns":[]}</t>
         </is>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>126</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>152</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>232</v>
       </c>
     </row>
@@ -15575,6 +15725,7 @@
       <c r="K6" s="2" t="n"/>
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
+      <c r="N6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -15616,6 +15767,7 @@
       <c r="K10" s="2" t="n"/>
       <c r="L10" s="2" t="n"/>
       <c r="M10" s="2" t="n"/>
+      <c r="N10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -15657,6 +15809,7 @@
       <c r="K14" s="2" t="n"/>
       <c r="L14" s="2" t="n"/>
       <c r="M14" s="2" t="n"/>
+      <c r="N14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -15739,80 +15892,85 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
+          <t>glossary_terms</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
           <t>concept_id</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>concept_confidence</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>concept_alias_group</t>
         </is>
       </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>concept_evidence_json</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
         <is>
           <t>concept_sources_json</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="Q19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>unit_source</t>
         </is>
       </c>
-      <c r="R19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>canonical_unit</t>
         </is>
       </c>
-      <c r="S19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
         <is>
           <t>unit_system</t>
         </is>
       </c>
-      <c r="T19" s="2" t="inlineStr">
+      <c r="U19" s="2" t="inlineStr">
         <is>
           <t>unit_confidence</t>
         </is>
       </c>
-      <c r="U19" s="2" t="inlineStr">
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>unit_notes</t>
         </is>
       </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="W19" s="2" t="inlineStr">
         <is>
           <t>factor_to_canonical</t>
         </is>
       </c>
-      <c r="W19" s="2" t="inlineStr">
+      <c r="X19" s="2" t="inlineStr">
         <is>
           <t>offset_to_canonical</t>
         </is>
       </c>
-      <c r="X19" s="2" t="inlineStr">
+      <c r="Y19" s="2" t="inlineStr">
         <is>
           <t>conversion_formula</t>
         </is>
       </c>
-      <c r="Y19" s="2" t="inlineStr">
+      <c r="Z19" s="2" t="inlineStr">
         <is>
           <t>range_min</t>
         </is>
       </c>
-      <c r="Z19" s="2" t="inlineStr">
+      <c r="AA19" s="2" t="inlineStr">
         <is>
           <t>range_max</t>
         </is>
@@ -15858,33 +16016,33 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>The `customer_id` column is a non-nullable bigint serving as the primary key and unique identifier for each customer in the `customers` table.</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
+          <t>Unique identifier for each customer in the retail operations system.</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
         </is>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>0.6</v>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"]</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>["cross_table_consensus","name","type"]</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr"/>
@@ -15893,12 +16051,13 @@
       <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr">
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr">
         <is>
           <t>404</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
+      <c r="AA20" t="inlineStr">
         <is>
           <t>503</t>
         </is>
@@ -15944,33 +16103,33 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>The "first_name" column in the "customers" table stores non-nullable given names as nvarchar strings using the "sql_latin1_general_cp1_ci_as" collation.</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
+          <t>Stores the given name of a customer as a non-null, case-insensitive Unicode string.</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
         <is>
           <t>contact.person_name</t>
         </is>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>0.6</v>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>first_name</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>["name token: first_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","table context: customers"]</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>["name","table_context","type"]</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr"/>
@@ -15979,12 +16138,13 @@
       <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr">
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr">
         <is>
           <t>Customer1</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
+      <c r="AA21" t="inlineStr">
         <is>
           <t>Customer99</t>
         </is>
@@ -16030,33 +16190,33 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>The "last_name" column in the "customers" table stores the non-nullable family name of a customer as a case-insensitive Unicode string.</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
+          <t>Stores the last name of a customer as a non-null, case-insensitive Unicode string.</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
         <is>
           <t>contact.person_name</t>
         </is>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>0.6</v>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>last_name</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>["name token: last_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","table context: customers"]</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>["name","table_context","type"]</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr"/>
@@ -16065,12 +16225,13 @@
       <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="inlineStr">
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr">
         <is>
           <t>LastName1 (updated)</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
+      <c r="AA22" t="inlineStr">
         <is>
           <t>LastName99</t>
         </is>
@@ -16120,33 +16281,33 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Stores the customer's email address, allowing null values, with a maximum length of 450 characters.</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
+          <t>Stores the email address of the customer, allowing null values.</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
         <is>
           <t>contact.email</t>
         </is>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>1</v>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>["name token: email","type hint: nvarchar(450)","legacy field classification: contact","value pattern: email","table context: customers","sensitive hint: pii_contact"]</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>["name","profile","table_context","type","values"]</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr"/>
@@ -16155,12 +16316,13 @@
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr">
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr">
         <is>
           <t>customer1@example.com</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
+      <c r="AA23" t="inlineStr">
         <is>
           <t>customer99@example.com</t>
         </is>
@@ -16210,33 +16372,33 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Stores the customer's phone number as a nullable text field with case-insensitive collation.</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
+          <t>Stores the customer's phone number as an optional text field for contact purposes.</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
         <is>
           <t>contact.phone</t>
         </is>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>1</v>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>phone</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>["name token: phone","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: contact","value pattern: phone","table context: customers","sensitive hint: pii_contact"]</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>["name","profile","table_context","type","values"]</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr"/>
@@ -16245,12 +16407,13 @@
       <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr"/>
       <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr">
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr">
         <is>
           <t>555-1001</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
+      <c r="AA24" t="inlineStr">
         <is>
           <t>555-1100</t>
         </is>
@@ -16296,33 +16459,33 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>The `created_at` column stores the non-nullable timestamp indicating when a customer record was initially created.</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
+          <t>The `created_at` column records the non-nullable timestamp indicating when a customer record was initially created in the system.</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
         <is>
           <t>temporal.created_at</t>
         </is>
       </c>
-      <c r="L25" t="n">
+      <c r="M25" t="n">
         <v>1</v>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: customers"]</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>["name","profile","table_context","type","values"]</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr"/>
@@ -16331,12 +16494,13 @@
       <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr"/>
       <c r="X25" t="inlineStr"/>
-      <c r="Y25" t="inlineStr">
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr">
         <is>
           <t>2021-03-23 15:38:57.201565</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
+      <c r="AA25" t="inlineStr">
         <is>
           <t>2026-02-26 15:38:57.201565</t>
         </is>
@@ -16382,33 +16546,33 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>The `updated_at` column stores the non-nullable timestamp of the most recent update to a customer's record.</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
+          <t>Tracks the timestamp of the most recent update to a customer's record, ensuring accurate change history.</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
         <is>
           <t>temporal.updated_at</t>
         </is>
       </c>
-      <c r="L26" t="n">
+      <c r="M26" t="n">
         <v>1</v>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: customers"]</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>["name","profile","table_context","type","values"]</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr"/>
@@ -16417,12 +16581,13 @@
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr"/>
       <c r="X26" t="inlineStr"/>
-      <c r="Y26" t="inlineStr">
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr">
         <is>
           <t>2021-03-23 15:38:57.201565</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
+      <c r="AA26" t="inlineStr">
         <is>
           <t>2026-03-26 08:52:49.252228</t>
         </is>
@@ -16567,6 +16732,7 @@
           <t>extra_json</t>
         </is>
       </c>
+      <c r="AA29" s="2" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -16885,7 +17051,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z45"/>
+  <dimension ref="A1:AA45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -16896,24 +17062,25 @@
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="80" customWidth="1" min="7" max="7"/>
     <col width="80" customWidth="1" min="8" max="8"/>
-    <col width="80" customWidth="1" min="9" max="9"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
     <col width="80" customWidth="1" min="10" max="10"/>
-    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="80" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
     <col width="25" customWidth="1" min="13" max="13"/>
-    <col width="80" customWidth="1" min="14" max="14"/>
-    <col width="52" customWidth="1" min="15" max="15"/>
-    <col width="17" customWidth="1" min="16" max="16"/>
+    <col width="25" customWidth="1" min="14" max="14"/>
+    <col width="80" customWidth="1" min="15" max="15"/>
+    <col width="52" customWidth="1" min="16" max="16"/>
     <col width="22" customWidth="1" min="17" max="17"/>
     <col width="18" customWidth="1" min="18" max="18"/>
     <col width="34" customWidth="1" min="19" max="19"/>
     <col width="80" customWidth="1" min="20" max="20"/>
     <col width="34" customWidth="1" min="21" max="21"/>
-    <col width="21" customWidth="1" min="22" max="22"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
     <col width="21" customWidth="1" min="23" max="23"/>
-    <col width="20" customWidth="1" min="24" max="24"/>
-    <col width="28" customWidth="1" min="25" max="25"/>
+    <col width="21" customWidth="1" min="24" max="24"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
     <col width="63" customWidth="1" min="26" max="26"/>
+    <col width="28" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16966,25 +17133,30 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
+          <t>glossary_terms</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
           <t>classification_summary_json</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>unit_summary_json</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>row_count_projection_1y</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>row_count_projection_2y</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>row_count_projection_5y</t>
         </is>
@@ -17026,26 +17198,27 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>The `employees` table stores information about employees, including their unique ID, associated store, personal details, role, hire date, and record timestamps.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
+          <t>The `employees` table stores details about retail system employees, including their identifiers, store associations, personal information, roles, hire dates, and record timestamps.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
         <is>
           <t>{"concept_counts":{"contact.email":1,"contact.person_name":2,"entity.type":1,"identifier.foreign_key":2,"temporal.created_at":1,"temporal.date_only":1,"temporal.updated_at":1},"low_confidence_columns":["first_name","last_name"]}</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>{"columns_with_units":0,"columns_without_units":9,"mixed_unit_groups":[],"unknown_unit_columns":[]}</t>
         </is>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>35</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>50</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>96</v>
       </c>
     </row>
@@ -17079,6 +17252,7 @@
       <c r="K6" s="2" t="n"/>
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
+      <c r="N6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -17120,6 +17294,7 @@
       <c r="K10" s="2" t="n"/>
       <c r="L10" s="2" t="n"/>
       <c r="M10" s="2" t="n"/>
+      <c r="N10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -17163,6 +17338,7 @@
       <c r="K14" s="2" t="n"/>
       <c r="L14" s="2" t="n"/>
       <c r="M14" s="2" t="n"/>
+      <c r="N14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -17204,6 +17380,7 @@
       <c r="K18" s="2" t="n"/>
       <c r="L18" s="2" t="n"/>
       <c r="M18" s="2" t="n"/>
+      <c r="N18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -17273,6 +17450,7 @@
       <c r="K24" s="2" t="n"/>
       <c r="L24" s="2" t="n"/>
       <c r="M24" s="2" t="n"/>
+      <c r="N24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -17357,80 +17535,85 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
+          <t>glossary_terms</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
           <t>concept_id</t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr">
+      <c r="M28" s="2" t="inlineStr">
         <is>
           <t>concept_confidence</t>
         </is>
       </c>
-      <c r="M28" s="2" t="inlineStr">
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>concept_alias_group</t>
         </is>
       </c>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>concept_evidence_json</t>
         </is>
       </c>
-      <c r="O28" s="2" t="inlineStr">
+      <c r="P28" s="2" t="inlineStr">
         <is>
           <t>concept_sources_json</t>
         </is>
       </c>
-      <c r="P28" s="2" t="inlineStr">
+      <c r="Q28" s="2" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="Q28" s="2" t="inlineStr">
+      <c r="R28" s="2" t="inlineStr">
         <is>
           <t>unit_source</t>
         </is>
       </c>
-      <c r="R28" s="2" t="inlineStr">
+      <c r="S28" s="2" t="inlineStr">
         <is>
           <t>canonical_unit</t>
         </is>
       </c>
-      <c r="S28" s="2" t="inlineStr">
+      <c r="T28" s="2" t="inlineStr">
         <is>
           <t>unit_system</t>
         </is>
       </c>
-      <c r="T28" s="2" t="inlineStr">
+      <c r="U28" s="2" t="inlineStr">
         <is>
           <t>unit_confidence</t>
         </is>
       </c>
-      <c r="U28" s="2" t="inlineStr">
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>unit_notes</t>
         </is>
       </c>
-      <c r="V28" s="2" t="inlineStr">
+      <c r="W28" s="2" t="inlineStr">
         <is>
           <t>factor_to_canonical</t>
         </is>
       </c>
-      <c r="W28" s="2" t="inlineStr">
+      <c r="X28" s="2" t="inlineStr">
         <is>
           <t>offset_to_canonical</t>
         </is>
       </c>
-      <c r="X28" s="2" t="inlineStr">
+      <c r="Y28" s="2" t="inlineStr">
         <is>
           <t>conversion_formula</t>
         </is>
       </c>
-      <c r="Y28" s="2" t="inlineStr">
+      <c r="Z28" s="2" t="inlineStr">
         <is>
           <t>range_min</t>
         </is>
       </c>
-      <c r="Z28" s="2" t="inlineStr">
+      <c r="AA28" s="2" t="inlineStr">
         <is>
           <t>range_max</t>
         </is>
@@ -17468,33 +17651,33 @@
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>The `employee_id` column is a non-nullable bigint serving as the primary key for uniquely identifying employees in the `employees` table.</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
+          <t>Unique identifier for each employee in the retail operations system.</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
         </is>
       </c>
-      <c r="L29" t="n">
+      <c r="M29" t="n">
         <v>0.6</v>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"]</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>["cross_table_consensus","name","type"]</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr"/>
@@ -17503,12 +17686,13 @@
       <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr"/>
       <c r="X29" t="inlineStr"/>
-      <c r="Y29" t="inlineStr">
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr">
         <is>
           <t>64</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
+      <c r="AA29" t="inlineStr">
         <is>
           <t>83</t>
         </is>
@@ -17546,33 +17730,33 @@
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>The `store_id` column in the `employees` table is a non-nullable bigint that serves as a foreign key referencing the `store_id` column in the `stores` table.</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
+          <t>Associates each employee with a specific store, referencing the `store_id` column in the `stores` table.</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
         </is>
       </c>
-      <c r="L30" t="n">
+      <c r="M30" t="n">
         <v>0.9</v>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>["name token: id","type hint: bigint","structural hint: join candidate"]</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>["name","profile","type"]</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr"/>
@@ -17581,12 +17765,13 @@
       <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr"/>
-      <c r="Y30" t="inlineStr">
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
+      <c r="AA30" t="inlineStr">
         <is>
           <t>23</t>
         </is>
@@ -17632,33 +17817,33 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>The "first_name" column in the "employees" table stores the given name of an employee as a non-null, case-insensitive Unicode string.</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
+          <t>Stores the given name of an employee, represented as a non-null, case-insensitive Unicode string.</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
         <is>
           <t>contact.person_name</t>
         </is>
       </c>
-      <c r="L31" t="n">
+      <c r="M31" t="n">
         <v>0.55</v>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>first_name</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>["name token: first_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""]</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>["name","type"]</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr"/>
@@ -17667,12 +17852,13 @@
       <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr"/>
-      <c r="Y31" t="inlineStr">
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr">
         <is>
           <t>Employee1</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
+      <c r="AA31" t="inlineStr">
         <is>
           <t>Employee9</t>
         </is>
@@ -17721,30 +17907,30 @@
           <t>The "last_name" column in the "employees" table stores the non-nullable family name of an employee as a case-insensitive Unicode string.</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
         <is>
           <t>contact.person_name</t>
         </is>
       </c>
-      <c r="L32" t="n">
+      <c r="M32" t="n">
         <v>0.55</v>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>last_name</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>["name token: last_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""]</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>["name","type"]</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
@@ -17753,12 +17939,13 @@
       <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr"/>
-      <c r="Y32" t="inlineStr">
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr">
         <is>
           <t>LastName1</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
+      <c r="AA32" t="inlineStr">
         <is>
           <t>LastName9</t>
         </is>
@@ -17808,33 +17995,33 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>The "email" column stores the unique email address of each employee as a non-null nvarchar string with a maximum length of 450 characters.</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
+          <t>Stores the unique email address of each employee for contact purposes, with a maximum length of 450 characters and cannot be null.</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
         <is>
           <t>contact.email</t>
         </is>
       </c>
-      <c r="L33" t="n">
+      <c r="M33" t="n">
         <v>1</v>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>["name token: email","type hint: nvarchar(450)","legacy field classification: contact","value pattern: email","sensitive hint: pii_contact"]</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>["name","profile","type","values"]</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
@@ -17843,12 +18030,13 @@
       <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr"/>
-      <c r="Y33" t="inlineStr">
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr">
         <is>
           <t>emp1@example.com</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
+      <c r="AA33" t="inlineStr">
         <is>
           <t>emp9@example.com</t>
         </is>
@@ -17886,33 +18074,33 @@
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>The "role" column in the "employees" table stores the job title or position of an employee as a non-null nvarchar string.</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
+          <t>Indicates the job position or function of an employee within the organization, stored as a non-nullable text value.</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
         <is>
           <t>entity.type</t>
         </is>
       </c>
-      <c r="L34" t="n">
+      <c r="M34" t="n">
         <v>0.65</v>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>role</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>["name token: role","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","profile heuristic matched"]</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>["name","profile","type"]</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
@@ -17921,12 +18109,13 @@
       <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr"/>
       <c r="X34" t="inlineStr"/>
-      <c r="Y34" t="inlineStr">
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr">
         <is>
           <t>Cashier</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
+      <c r="AA34" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
@@ -17972,33 +18161,33 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>The `hire_date` column stores the non-null date an employee was hired.</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
+          <t>The `hire_date` column in the `employees` table stores the non-nullable date an employee was hired, used for tracking employment start dates.</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
         <is>
           <t>temporal.date_only</t>
         </is>
       </c>
-      <c r="L35" t="n">
+      <c r="M35" t="n">
         <v>1</v>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>hire_date</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>["name token: hire_date","type hint: date","legacy field classification: temporal","value pattern: date_only","table context: employees"]</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>["name","profile","table_context","type","values"]</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr"/>
@@ -18007,12 +18196,13 @@
       <c r="V35" t="inlineStr"/>
       <c r="W35" t="inlineStr"/>
       <c r="X35" t="inlineStr"/>
-      <c r="Y35" t="inlineStr">
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr">
         <is>
           <t>2021-05-03</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
+      <c r="AA35" t="inlineStr">
         <is>
           <t>2025-01-26</t>
         </is>
@@ -18058,33 +18248,33 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>The "created_at" column stores the non-nullable timestamp indicating when the employee record was initially created.</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
+          <t>The `created_at` column records the non-nullable timestamp indicating when an employee record was initially created in the system.</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
         <is>
           <t>temporal.created_at</t>
         </is>
       </c>
-      <c r="L36" t="n">
+      <c r="M36" t="n">
         <v>1</v>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: employees"]</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>["name","profile","table_context","type","values"]</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr"/>
@@ -18093,12 +18283,13 @@
       <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr"/>
-      <c r="Y36" t="inlineStr">
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr">
         <is>
           <t>2021-05-03 15:38:57.201565</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
+      <c r="AA36" t="inlineStr">
         <is>
           <t>2025-01-26 15:38:57.201565</t>
         </is>
@@ -18144,33 +18335,33 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>The `updated_at` column stores the non-nullable timestamp indicating the last update time for an employee record.</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
+          <t>The `updated_at` column stores the non-nullable timestamp of the most recent update to an employee record.</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
         <is>
           <t>temporal.updated_at</t>
         </is>
       </c>
-      <c r="L37" t="n">
+      <c r="M37" t="n">
         <v>1</v>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: employees"]</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>["name","profile","table_context","type","values"]</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr"/>
@@ -18179,12 +18370,13 @@
       <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr"/>
       <c r="X37" t="inlineStr"/>
-      <c r="Y37" t="inlineStr">
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr">
         <is>
           <t>2021-05-03 15:38:57.201565</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
+      <c r="AA37" t="inlineStr">
         <is>
           <t>2025-01-26 15:38:57.201565</t>
         </is>
@@ -18329,6 +18521,7 @@
           <t>extra_json</t>
         </is>
       </c>
+      <c r="AA40" s="2" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -18661,7 +18854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z48"/>
+  <dimension ref="A1:AA48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -18672,24 +18865,25 @@
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="80" customWidth="1" min="7" max="7"/>
     <col width="80" customWidth="1" min="8" max="8"/>
-    <col width="80" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
     <col width="80" customWidth="1" min="10" max="10"/>
-    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="80" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
     <col width="25" customWidth="1" min="13" max="13"/>
-    <col width="80" customWidth="1" min="14" max="14"/>
-    <col width="52" customWidth="1" min="15" max="15"/>
-    <col width="17" customWidth="1" min="16" max="16"/>
+    <col width="25" customWidth="1" min="14" max="14"/>
+    <col width="80" customWidth="1" min="15" max="15"/>
+    <col width="52" customWidth="1" min="16" max="16"/>
     <col width="22" customWidth="1" min="17" max="17"/>
     <col width="18" customWidth="1" min="18" max="18"/>
     <col width="34" customWidth="1" min="19" max="19"/>
     <col width="80" customWidth="1" min="20" max="20"/>
-    <col width="80" customWidth="1" min="21" max="21"/>
-    <col width="21" customWidth="1" min="22" max="22"/>
+    <col width="34" customWidth="1" min="21" max="21"/>
+    <col width="80" customWidth="1" min="22" max="22"/>
     <col width="21" customWidth="1" min="23" max="23"/>
-    <col width="20" customWidth="1" min="24" max="24"/>
-    <col width="28" customWidth="1" min="25" max="25"/>
+    <col width="21" customWidth="1" min="24" max="24"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
     <col width="63" customWidth="1" min="26" max="26"/>
+    <col width="28" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18742,25 +18936,30 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
+          <t>glossary_terms</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
           <t>classification_summary_json</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>unit_summary_json</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>row_count_projection_1y</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>row_count_projection_2y</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>row_count_projection_5y</t>
         </is>
@@ -18805,23 +19004,24 @@
           <t>Current stock levels with normalized stock unit representation.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
         <is>
           <t>{"concept_counts":{"identifier.foreign_key":3,"measure.quantity":1,"temporal.created_at":1,"temporal.event_time":1,"temporal.updated_at":1},"low_confidence_columns":["reorder_level","stock_unit"]}</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>{"columns_with_units":0,"columns_without_units":10,"mixed_unit_groups":[],"unknown_unit_columns":["quantity_on_hand"]}</t>
         </is>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>146</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>193</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>334</v>
       </c>
     </row>
@@ -18855,6 +19055,7 @@
       <c r="K6" s="2" t="n"/>
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
+      <c r="N6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -18896,6 +19097,7 @@
       <c r="K10" s="2" t="n"/>
       <c r="L10" s="2" t="n"/>
       <c r="M10" s="2" t="n"/>
+      <c r="N10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -18951,6 +19153,7 @@
       <c r="K15" s="2" t="n"/>
       <c r="L15" s="2" t="n"/>
       <c r="M15" s="2" t="n"/>
+      <c r="N15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -18992,6 +19195,7 @@
       <c r="K19" s="2" t="n"/>
       <c r="L19" s="2" t="n"/>
       <c r="M19" s="2" t="n"/>
+      <c r="N19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -19061,6 +19265,7 @@
       <c r="K25" s="2" t="n"/>
       <c r="L25" s="2" t="n"/>
       <c r="M25" s="2" t="n"/>
+      <c r="N25" s="2" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -19167,80 +19372,85 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
+          <t>glossary_terms</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
           <t>concept_id</t>
         </is>
       </c>
-      <c r="L30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>concept_confidence</t>
         </is>
       </c>
-      <c r="M30" s="2" t="inlineStr">
+      <c r="N30" s="2" t="inlineStr">
         <is>
           <t>concept_alias_group</t>
         </is>
       </c>
-      <c r="N30" s="2" t="inlineStr">
+      <c r="O30" s="2" t="inlineStr">
         <is>
           <t>concept_evidence_json</t>
         </is>
       </c>
-      <c r="O30" s="2" t="inlineStr">
+      <c r="P30" s="2" t="inlineStr">
         <is>
           <t>concept_sources_json</t>
         </is>
       </c>
-      <c r="P30" s="2" t="inlineStr">
+      <c r="Q30" s="2" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="Q30" s="2" t="inlineStr">
+      <c r="R30" s="2" t="inlineStr">
         <is>
           <t>unit_source</t>
         </is>
       </c>
-      <c r="R30" s="2" t="inlineStr">
+      <c r="S30" s="2" t="inlineStr">
         <is>
           <t>canonical_unit</t>
         </is>
       </c>
-      <c r="S30" s="2" t="inlineStr">
+      <c r="T30" s="2" t="inlineStr">
         <is>
           <t>unit_system</t>
         </is>
       </c>
-      <c r="T30" s="2" t="inlineStr">
+      <c r="U30" s="2" t="inlineStr">
         <is>
           <t>unit_confidence</t>
         </is>
       </c>
-      <c r="U30" s="2" t="inlineStr">
+      <c r="V30" s="2" t="inlineStr">
         <is>
           <t>unit_notes</t>
         </is>
       </c>
-      <c r="V30" s="2" t="inlineStr">
+      <c r="W30" s="2" t="inlineStr">
         <is>
           <t>factor_to_canonical</t>
         </is>
       </c>
-      <c r="W30" s="2" t="inlineStr">
+      <c r="X30" s="2" t="inlineStr">
         <is>
           <t>offset_to_canonical</t>
         </is>
       </c>
-      <c r="X30" s="2" t="inlineStr">
+      <c r="Y30" s="2" t="inlineStr">
         <is>
           <t>conversion_formula</t>
         </is>
       </c>
-      <c r="Y30" s="2" t="inlineStr">
+      <c r="Z30" s="2" t="inlineStr">
         <is>
           <t>range_min</t>
         </is>
       </c>
-      <c r="Z30" s="2" t="inlineStr">
+      <c r="AA30" s="2" t="inlineStr">
         <is>
           <t>range_max</t>
         </is>
@@ -19278,33 +19488,33 @@
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>The `inventory_id` column is a non-nullable bigint serving as the primary key for uniquely identifying records in the `inventory` table.</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
+          <t>Unique identifier for each inventory record in the system.</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
         </is>
       </c>
-      <c r="L31" t="n">
+      <c r="M31" t="n">
         <v>0.6</v>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"]</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>["cross_table_consensus","name","type"]</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr"/>
@@ -19313,12 +19523,13 @@
       <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr"/>
-      <c r="Y31" t="inlineStr">
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
+      <c r="AA31" t="inlineStr">
         <is>
           <t>107</t>
         </is>
@@ -19356,33 +19567,33 @@
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>The `store_id` column in the `inventory` table is a non-nullable bigint that references the `store_id` column in the `stores` table, establishing a foreign key relationship.</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
+          <t>Identifier for the store associated with the inventory record, referencing the `store_id` column in the `stores` table.</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
         </is>
       </c>
-      <c r="L32" t="n">
+      <c r="M32" t="n">
         <v>0.9</v>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>["name token: id","type hint: bigint","structural hint: join candidate"]</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>["name","profile","type"]</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
@@ -19391,12 +19602,13 @@
       <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr"/>
-      <c r="Y32" t="inlineStr">
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
+      <c r="AA32" t="inlineStr">
         <is>
           <t>23</t>
         </is>
@@ -19438,33 +19650,33 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>References the unique identifier of a product from the products table, establishing a foreign key relationship.</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
+          <t>References the unique identifier of a product from the `products` table to associate inventory records with specific products.</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
         </is>
       </c>
-      <c r="L33" t="n">
+      <c r="M33" t="n">
         <v>0.9</v>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>["name token: id","type hint: bigint","structural hint: join candidate"]</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>["name","profile","type"]</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
@@ -19473,12 +19685,13 @@
       <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr"/>
-      <c r="Y33" t="inlineStr">
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr">
         <is>
           <t>156</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
+      <c r="AA33" t="inlineStr">
         <is>
           <t>205</t>
         </is>
@@ -19524,63 +19737,64 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Tracks the current stock quantity of an item in inventory, stored as a non-null integer.</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
+          <t>Tracks the current quantity of a product available in inventory, expressed as a non-null integer.</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
         <is>
           <t>measure.quantity</t>
         </is>
       </c>
-      <c r="L34" t="n">
+      <c r="M34" t="n">
         <v>1</v>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>quantity_on_hand</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>["name token: quantity_on_hand","type hint: integer","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity","profile heuristic matched"]</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>["name","profile","type","values"]</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr">
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr">
         <is>
           <t>combined</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr">
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr">
+      <c r="U34" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
+      <c r="V34" t="inlineStr">
         <is>
           <t>Semantic class suggests units, but no explicit source unit token was detected.</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr"/>
       <c r="X34" t="inlineStr"/>
-      <c r="Y34" t="inlineStr">
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
+      <c r="AA34" t="inlineStr">
         <is>
           <t>98</t>
         </is>
@@ -19618,25 +19832,25 @@
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>The `reorder_level` column in the `inventory` table stores a non-null integer indicating the threshold quantity at which stock should be reordered.</t>
+          <t>Indicates the minimum quantity of a product in inventory that triggers a reorder, stored as a non-null integer.</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="n">
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="n">
         <v>0.1</v>
       </c>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr">
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr">
         <is>
           <t>["type hint: integer","profile heuristic matched","ambiguous runner-up concept"]</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>["profile","type"]</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr"/>
@@ -19645,12 +19859,13 @@
       <c r="V35" t="inlineStr"/>
       <c r="W35" t="inlineStr"/>
       <c r="X35" t="inlineStr"/>
-      <c r="Y35" t="inlineStr">
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
+      <c r="AA35" t="inlineStr">
         <is>
           <t>29</t>
         </is>
@@ -19696,33 +19911,33 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>The `last_restocked_at` column records the timestamp of the most recent inventory restocking event and allows null values.</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
+          <t>The `last_restocked_at` column records the timestamp of the most recent restocking event for an inventory item, allowing null values if the item has not been restocked.</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
         <is>
           <t>temporal.event_time</t>
         </is>
       </c>
-      <c r="L36" t="n">
+      <c r="M36" t="n">
         <v>1</v>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>last_restocked_at</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>["name token: last_restocked_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: inventory"]</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>["name","profile","table_context","type","values"]</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr"/>
@@ -19731,12 +19946,13 @@
       <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr"/>
-      <c r="Y36" t="inlineStr">
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr">
         <is>
           <t>2024-03-14 15:38:57.201565</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
+      <c r="AA36" t="inlineStr">
         <is>
           <t>2026-03-07 15:38:57.201565</t>
         </is>
@@ -19782,33 +19998,33 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>The "created_at" column stores the non-nullable timestamp indicating when the inventory record was initially created.</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
+          <t>The `created_at` column records the non-nullable timestamp indicating when the inventory record was initially created.</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
         <is>
           <t>temporal.created_at</t>
         </is>
       </c>
-      <c r="L37" t="n">
+      <c r="M37" t="n">
         <v>1</v>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: inventory"]</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>["name","profile","table_context","type","values"]</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr"/>
@@ -19817,12 +20033,13 @@
       <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr"/>
       <c r="X37" t="inlineStr"/>
-      <c r="Y37" t="inlineStr">
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr">
         <is>
           <t>2024-03-05 15:38:57.201565</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
+      <c r="AA37" t="inlineStr">
         <is>
           <t>2026-02-23 15:38:57.201565</t>
         </is>
@@ -19868,33 +20085,33 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>The `updated_at` column in the `inventory` table stores the non-null timestamp of the most recent update to a record, using the `datetime2` data type.</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
+          <t>Tracks the timestamp of the most recent update to an inventory record, ensuring accurate change history.</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
         <is>
           <t>temporal.updated_at</t>
         </is>
       </c>
-      <c r="L38" t="n">
+      <c r="M38" t="n">
         <v>1</v>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: inventory"]</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
+      <c r="P38" t="inlineStr">
         <is>
           <t>["name","profile","table_context","type","values"]</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
@@ -19903,12 +20120,13 @@
       <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr"/>
       <c r="X38" t="inlineStr"/>
-      <c r="Y38" t="inlineStr">
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr">
         <is>
           <t>2024-03-14 15:38:57.201565</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
+      <c r="AA38" t="inlineStr">
         <is>
           <t>2026-03-07 15:38:57.201565</t>
         </is>
@@ -19946,25 +20164,25 @@
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Represents the monetary value of stock for an inventory item, stored as a numeric value with up to 10 digits and 2 decimal places, and may be null.</t>
+          <t>Represents the monetary value of inventory stock, stored as a numeric value with up to 10 digits and 2 decimal places, and may be null.</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="n">
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="n">
         <v>0</v>
       </c>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr">
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr">
         <is>
           <t>["type hint: numeric(10,2)","ambiguous runner-up concept"]</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="P39" t="inlineStr">
         <is>
           <t>["type"]</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr"/>
@@ -19975,6 +20193,7 @@
       <c r="X39" t="inlineStr"/>
       <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -20012,21 +20231,21 @@
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="n">
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="n">
         <v>0.15</v>
       </c>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr">
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr">
         <is>
           <t>["value pattern: quantity","ambiguous runner-up concept"]</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
+      <c r="P40" t="inlineStr">
         <is>
           <t>["values"]</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr"/>
@@ -20037,6 +20256,7 @@
       <c r="X40" t="inlineStr"/>
       <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr"/>
     </row>
     <row r="41"/>
     <row r="42">
@@ -20177,6 +20397,7 @@
           <t>extra_json</t>
         </is>
       </c>
+      <c r="AA43" s="2" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -20495,7 +20716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z57"/>
+  <dimension ref="A1:AA57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -20506,24 +20727,25 @@
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="80" customWidth="1" min="7" max="7"/>
     <col width="80" customWidth="1" min="8" max="8"/>
-    <col width="80" customWidth="1" min="9" max="9"/>
+    <col width="44" customWidth="1" min="9" max="9"/>
     <col width="80" customWidth="1" min="10" max="10"/>
-    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="80" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
     <col width="25" customWidth="1" min="13" max="13"/>
-    <col width="80" customWidth="1" min="14" max="14"/>
-    <col width="52" customWidth="1" min="15" max="15"/>
-    <col width="17" customWidth="1" min="16" max="16"/>
+    <col width="25" customWidth="1" min="14" max="14"/>
+    <col width="80" customWidth="1" min="15" max="15"/>
+    <col width="52" customWidth="1" min="16" max="16"/>
     <col width="22" customWidth="1" min="17" max="17"/>
     <col width="18" customWidth="1" min="18" max="18"/>
     <col width="34" customWidth="1" min="19" max="19"/>
     <col width="80" customWidth="1" min="20" max="20"/>
-    <col width="80" customWidth="1" min="21" max="21"/>
-    <col width="21" customWidth="1" min="22" max="22"/>
+    <col width="34" customWidth="1" min="21" max="21"/>
+    <col width="80" customWidth="1" min="22" max="22"/>
     <col width="21" customWidth="1" min="23" max="23"/>
-    <col width="20" customWidth="1" min="24" max="24"/>
-    <col width="28" customWidth="1" min="25" max="25"/>
+    <col width="21" customWidth="1" min="24" max="24"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
     <col width="63" customWidth="1" min="26" max="26"/>
+    <col width="28" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -20576,25 +20798,30 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
+          <t>glossary_terms</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
           <t>classification_summary_json</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>unit_summary_json</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>row_count_projection_1y</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>row_count_projection_2y</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>row_count_projection_5y</t>
         </is>
@@ -20639,23 +20866,24 @@
           <t>Master product catalog including physical units for analyzer unit-context testing.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
         <is>
           <t>{"concept_counts":{"contact.person_name":1,"entity.category":1,"finance.currency_amount":2,"identifier.foreign_key":3,"identifier.product_code":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":["length_unit","name","product_description","weight_unit"]}</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>{"columns_with_units":0,"columns_without_units":16,"mixed_unit_groups":[],"unknown_unit_columns":["length_unit","length_value","weight_unit","weight_value"]}</t>
         </is>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>68</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>86</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>141</v>
       </c>
     </row>
@@ -20689,6 +20917,7 @@
       <c r="K6" s="2" t="n"/>
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
+      <c r="N6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -20730,6 +20959,7 @@
       <c r="K10" s="2" t="n"/>
       <c r="L10" s="2" t="n"/>
       <c r="M10" s="2" t="n"/>
+      <c r="N10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -20785,6 +21015,7 @@
       <c r="K15" s="2" t="n"/>
       <c r="L15" s="2" t="n"/>
       <c r="M15" s="2" t="n"/>
+      <c r="N15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -20826,6 +21057,7 @@
       <c r="K19" s="2" t="n"/>
       <c r="L19" s="2" t="n"/>
       <c r="M19" s="2" t="n"/>
+      <c r="N19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -20885,6 +21117,7 @@
       <c r="K24" s="2" t="n"/>
       <c r="L24" s="2" t="n"/>
       <c r="M24" s="2" t="n"/>
+      <c r="N24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -20991,80 +21224,85 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
+          <t>glossary_terms</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
           <t>concept_id</t>
         </is>
       </c>
-      <c r="L29" s="2" t="inlineStr">
+      <c r="M29" s="2" t="inlineStr">
         <is>
           <t>concept_confidence</t>
         </is>
       </c>
-      <c r="M29" s="2" t="inlineStr">
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>concept_alias_group</t>
         </is>
       </c>
-      <c r="N29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
         <is>
           <t>concept_evidence_json</t>
         </is>
       </c>
-      <c r="O29" s="2" t="inlineStr">
+      <c r="P29" s="2" t="inlineStr">
         <is>
           <t>concept_sources_json</t>
         </is>
       </c>
-      <c r="P29" s="2" t="inlineStr">
+      <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="Q29" s="2" t="inlineStr">
+      <c r="R29" s="2" t="inlineStr">
         <is>
           <t>unit_source</t>
         </is>
       </c>
-      <c r="R29" s="2" t="inlineStr">
+      <c r="S29" s="2" t="inlineStr">
         <is>
           <t>canonical_unit</t>
         </is>
       </c>
-      <c r="S29" s="2" t="inlineStr">
+      <c r="T29" s="2" t="inlineStr">
         <is>
           <t>unit_system</t>
         </is>
       </c>
-      <c r="T29" s="2" t="inlineStr">
+      <c r="U29" s="2" t="inlineStr">
         <is>
           <t>unit_confidence</t>
         </is>
       </c>
-      <c r="U29" s="2" t="inlineStr">
+      <c r="V29" s="2" t="inlineStr">
         <is>
           <t>unit_notes</t>
         </is>
       </c>
-      <c r="V29" s="2" t="inlineStr">
+      <c r="W29" s="2" t="inlineStr">
         <is>
           <t>factor_to_canonical</t>
         </is>
       </c>
-      <c r="W29" s="2" t="inlineStr">
+      <c r="X29" s="2" t="inlineStr">
         <is>
           <t>offset_to_canonical</t>
         </is>
       </c>
-      <c r="X29" s="2" t="inlineStr">
+      <c r="Y29" s="2" t="inlineStr">
         <is>
           <t>conversion_formula</t>
         </is>
       </c>
-      <c r="Y29" s="2" t="inlineStr">
+      <c r="Z29" s="2" t="inlineStr">
         <is>
           <t>range_min</t>
         </is>
       </c>
-      <c r="Z29" s="2" t="inlineStr">
+      <c r="AA29" s="2" t="inlineStr">
         <is>
           <t>range_max</t>
         </is>
@@ -21106,33 +21344,33 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Unique identifier for each product in the products table.</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
+          <t>Unique identifier for each product in the retail operations system.</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
         </is>
       </c>
-      <c r="L30" t="n">
+      <c r="M30" t="n">
         <v>0.6</v>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"]</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>["cross_table_consensus","name","type"]</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr"/>
@@ -21141,12 +21379,13 @@
       <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr"/>
-      <c r="Y30" t="inlineStr">
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr">
         <is>
           <t>156</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
+      <c r="AA30" t="inlineStr">
         <is>
           <t>205</t>
         </is>
@@ -21184,33 +21423,33 @@
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>The `supplier_id` column in the `products` table is a non-nullable bigint that serves as a foreign key referencing the `supplier_id` column in the `suppliers` table.</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
+          <t>The `supplier_id` column in the `products` table is a non-nullable foreign key referencing the `supplier_id` column in the `suppliers` table, identifying the supplier associated with each product.</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
         </is>
       </c>
-      <c r="L31" t="n">
+      <c r="M31" t="n">
         <v>0.9</v>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>["name token: id","type hint: bigint","structural hint: join candidate"]</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>["name","profile","type"]</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr"/>
@@ -21219,12 +21458,13 @@
       <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr"/>
-      <c r="Y31" t="inlineStr">
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
+      <c r="AA31" t="inlineStr">
         <is>
           <t>42</t>
         </is>
@@ -21266,33 +21506,33 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>The "sku" column stores a unique alphanumeric identifier for each product, with a maximum length of 450 characters, and cannot be null.</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
+          <t>Unique alphanumeric identifier for a product used for inventory and sales tracking, stored as a non-null nvarchar(450).</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
         <is>
           <t>identifier.product_code</t>
         </is>
       </c>
-      <c r="L32" t="n">
+      <c r="M32" t="n">
         <v>0.7</v>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>sku</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>["name token: sku","type hint: nvarchar(450)","semantic class hint: product_identifier"]</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>["name","profile","type"]</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
@@ -21301,12 +21541,13 @@
       <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr"/>
-      <c r="Y32" t="inlineStr">
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr">
         <is>
           <t>SKU-0001</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
+      <c r="AA32" t="inlineStr">
         <is>
           <t>SKU-0050</t>
         </is>
@@ -21344,33 +21585,33 @@
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>The "name" column in the "products" table stores the non-nullable name of the product as a Unicode string.</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
+          <t>The "name" column in the "products" table stores the non-nullable name of a product as a case-insensitive Unicode string.</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
         <is>
           <t>contact.person_name</t>
         </is>
       </c>
-      <c r="L33" t="n">
+      <c r="M33" t="n">
         <v>0.55</v>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>["name token: name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""]</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>["name","type"]</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
@@ -21379,12 +21620,13 @@
       <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr"/>
-      <c r="Y33" t="inlineStr">
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr">
         <is>
           <t>Product 1</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
+      <c r="AA33" t="inlineStr">
         <is>
           <t>Product 9</t>
         </is>
@@ -21430,33 +21672,33 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>The "category" column stores the product category as a non-null, case-insensitive string (e.g., "Books", "Clothing", "Electronics").</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
+          <t>Indicates the product's category classification, such as "Books," "Clothing," or "Electronics," stored as a non-null, case-insensitive text value.</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
         <is>
           <t>entity.category</t>
         </is>
       </c>
-      <c r="L34" t="n">
+      <c r="M34" t="n">
         <v>0.8</v>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>["name token: category","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: categorical","profile heuristic matched"]</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>["name","profile","type"]</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
@@ -21465,12 +21707,13 @@
       <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr"/>
       <c r="X34" t="inlineStr"/>
-      <c r="Y34" t="inlineStr">
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr">
         <is>
           <t>Books</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
+      <c r="AA34" t="inlineStr">
         <is>
           <t>Sports</t>
         </is>
@@ -21516,33 +21759,33 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>The `unit_price` column stores the non-null numeric value (up to 10 digits with 2 decimal places) representing the selling price of a product in currency.</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
+          <t>Stores the retail price of a product as a non-null numeric value with up to 10 digits and 2 decimal places.</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
         <is>
           <t>finance.currency_amount</t>
         </is>
       </c>
-      <c r="L35" t="n">
+      <c r="M35" t="n">
         <v>1</v>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>["name token: price","type hint: numeric(10,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount"]</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>["name","profile","type","values"]</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr"/>
@@ -21551,12 +21794,13 @@
       <c r="V35" t="inlineStr"/>
       <c r="W35" t="inlineStr"/>
       <c r="X35" t="inlineStr"/>
-      <c r="Y35" t="inlineStr">
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr">
         <is>
           <t>11.09</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
+      <c r="AA35" t="inlineStr">
         <is>
           <t>490.43</t>
         </is>
@@ -21602,33 +21846,33 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>The `cost_price` column stores the non-null numeric cost value of a product with up to 10 digits, including 2 decimal places, representing its monetary amount.</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
+          <t>Represents the numeric cost price of a product in the retail system, stored as a non-nullable currency amount with up to 10 digits and 2 decimal places.</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
         <is>
           <t>finance.currency_amount</t>
         </is>
       </c>
-      <c r="L36" t="n">
+      <c r="M36" t="n">
         <v>1</v>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>["name token: price","type hint: numeric(10,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount"]</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>["name","profile","type","values"]</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr"/>
@@ -21637,12 +21881,13 @@
       <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr"/>
-      <c r="Y36" t="inlineStr">
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr">
         <is>
           <t>5.55</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
+      <c r="AA36" t="inlineStr">
         <is>
           <t>358.59</t>
         </is>
@@ -21680,25 +21925,25 @@
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Indicates whether the product is active (True) or inactive (False); cannot be null.</t>
+          <t>Indicates whether a product is active and available for transactions, stored as a non-nullable boolean value.</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="n">
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="n">
         <v>0</v>
       </c>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr">
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr">
         <is>
           <t>["profile heuristic matched","ambiguous runner-up concept"]</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>["profile"]</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr"/>
@@ -21709,6 +21954,7 @@
       <c r="X37" t="inlineStr"/>
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -21750,33 +21996,33 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>The `created_at` column stores the non-nullable timestamp indicating when a product record was initially created.</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
+          <t>Indicates the timestamp when the product record was initially created, stored as a non-nullable datetime value.</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
         <is>
           <t>temporal.created_at</t>
         </is>
       </c>
-      <c r="L38" t="n">
+      <c r="M38" t="n">
         <v>1</v>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: products"]</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
+      <c r="P38" t="inlineStr">
         <is>
           <t>["name","profile","table_context","type","values"]</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
@@ -21785,12 +22031,13 @@
       <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr"/>
       <c r="X38" t="inlineStr"/>
-      <c r="Y38" t="inlineStr">
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr">
         <is>
           <t>2021-03-20 15:38:57.201565</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
+      <c r="AA38" t="inlineStr">
         <is>
           <t>2024-12-25 15:38:57.201565</t>
         </is>
@@ -21836,33 +22083,33 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>The `updated_at` column stores the non-nullable timestamp indicating the last update time of a product record.</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
+          <t>The `updated_at` column stores the non-nullable timestamp of the most recent update to a product record in the `products` table.</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
         <is>
           <t>temporal.updated_at</t>
         </is>
       </c>
-      <c r="L39" t="n">
+      <c r="M39" t="n">
         <v>1</v>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: products"]</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="P39" t="inlineStr">
         <is>
           <t>["name","profile","table_context","type","values"]</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr"/>
@@ -21871,12 +22118,13 @@
       <c r="V39" t="inlineStr"/>
       <c r="W39" t="inlineStr"/>
       <c r="X39" t="inlineStr"/>
-      <c r="Y39" t="inlineStr">
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr">
         <is>
           <t>2021-03-20 15:38:57.201565</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
+      <c r="AA39" t="inlineStr">
         <is>
           <t>2024-12-25 15:38:57.201565</t>
         </is>
@@ -21922,47 +22170,48 @@
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="n">
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="n">
         <v>0.15</v>
       </c>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr">
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr">
         <is>
           <t>["value pattern: quantity","ambiguous runner-up concept"]</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
+      <c r="P40" t="inlineStr">
         <is>
           <t>["values"]</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr">
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr">
         <is>
           <t>combined</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr">
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="T40" t="inlineStr">
+      <c r="U40" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="U40" t="inlineStr">
+      <c r="V40" t="inlineStr">
         <is>
           <t>Semantic class suggests units, but no explicit source unit token was detected.</t>
         </is>
       </c>
-      <c r="V40" t="inlineStr"/>
       <c r="W40" t="inlineStr"/>
       <c r="X40" t="inlineStr"/>
       <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -22004,47 +22253,48 @@
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="n">
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="n">
         <v>0</v>
       </c>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr">
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr">
         <is>
           <t>["type hint: numeric(10,2)","ambiguous runner-up concept"]</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="P41" t="inlineStr">
         <is>
           <t>["type"]</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr">
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr">
         <is>
           <t>combined</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr"/>
-      <c r="S41" t="inlineStr">
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="T41" t="inlineStr">
+      <c r="U41" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="U41" t="inlineStr">
+      <c r="V41" t="inlineStr">
         <is>
           <t>Semantic class suggests units, but no explicit source unit token was detected.</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr"/>
       <c r="X41" t="inlineStr"/>
       <c r="Y41" t="inlineStr"/>
       <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -22082,51 +22332,52 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>The `length_value` column stores the numeric length measurement of a product, allowing up to two decimal places, and can be null.</t>
+          <t>The "length_value" column stores the numeric length measurement of a product, allowing up to 10 digits with 2 decimal places, and is nullable.</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="n">
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="n">
         <v>0</v>
       </c>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr">
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr">
         <is>
           <t>["type hint: numeric(10,2)","ambiguous runner-up concept"]</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="P42" t="inlineStr">
         <is>
           <t>["type"]</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr">
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr">
         <is>
           <t>combined</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr"/>
-      <c r="S42" t="inlineStr">
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr">
+      <c r="U42" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr">
+      <c r="V42" t="inlineStr">
         <is>
           <t>Semantic class suggests units, but no explicit source unit token was detected.</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr"/>
       <c r="W42" t="inlineStr"/>
       <c r="X42" t="inlineStr"/>
       <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -22168,47 +22419,48 @@
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="n">
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="n">
         <v>0.15</v>
       </c>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr">
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr">
         <is>
           <t>["value pattern: quantity","ambiguous runner-up concept"]</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="P43" t="inlineStr">
         <is>
           <t>["values"]</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr">
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr">
         <is>
           <t>combined</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr"/>
-      <c r="S43" t="inlineStr">
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="T43" t="inlineStr">
+      <c r="U43" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr">
+      <c r="V43" t="inlineStr">
         <is>
           <t>Semantic class suggests units, but no explicit source unit token was detected.</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr"/>
       <c r="W43" t="inlineStr"/>
       <c r="X43" t="inlineStr"/>
       <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -22242,25 +22494,25 @@
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Stores an optional textual description of the product.</t>
+          <t>Stores optional textual details about a product, such as features or specifications, with support for Unicode characters.</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="n">
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="n">
         <v>0.1</v>
       </c>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr">
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr">
         <is>
           <t>["type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","profile heuristic matched","ambiguous runner-up concept"]</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
+      <c r="P44" t="inlineStr">
         <is>
           <t>["profile","type"]</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr"/>
@@ -22271,6 +22523,7 @@
       <c r="X44" t="inlineStr"/>
       <c r="Y44" t="inlineStr"/>
       <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -22307,30 +22560,30 @@
           <t>Primary supplier relationship used for join candidate detection.</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
         </is>
       </c>
-      <c r="L45" t="n">
+      <c r="M45" t="n">
         <v>0.9</v>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>["name token: id","type hint: bigint","structural hint: join candidate"]</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
+      <c r="P45" t="inlineStr">
         <is>
           <t>["name","profile","type"]</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr"/>
@@ -22339,12 +22592,13 @@
       <c r="V45" t="inlineStr"/>
       <c r="W45" t="inlineStr"/>
       <c r="X45" t="inlineStr"/>
-      <c r="Y45" t="inlineStr">
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
+      <c r="AA45" t="inlineStr">
         <is>
           <t>42</t>
         </is>
@@ -22489,6 +22743,7 @@
           <t>extra_json</t>
         </is>
       </c>
+      <c r="AA48" s="2" t="n"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -23057,7 +23312,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z47"/>
+  <dimension ref="A1:AA47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -23068,24 +23323,25 @@
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="80" customWidth="1" min="7" max="7"/>
     <col width="80" customWidth="1" min="8" max="8"/>
-    <col width="80" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
     <col width="80" customWidth="1" min="10" max="10"/>
-    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="80" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
     <col width="25" customWidth="1" min="13" max="13"/>
-    <col width="80" customWidth="1" min="14" max="14"/>
-    <col width="52" customWidth="1" min="15" max="15"/>
-    <col width="17" customWidth="1" min="16" max="16"/>
+    <col width="25" customWidth="1" min="14" max="14"/>
+    <col width="80" customWidth="1" min="15" max="15"/>
+    <col width="52" customWidth="1" min="16" max="16"/>
     <col width="22" customWidth="1" min="17" max="17"/>
     <col width="18" customWidth="1" min="18" max="18"/>
     <col width="34" customWidth="1" min="19" max="19"/>
     <col width="80" customWidth="1" min="20" max="20"/>
-    <col width="80" customWidth="1" min="21" max="21"/>
-    <col width="21" customWidth="1" min="22" max="22"/>
+    <col width="34" customWidth="1" min="21" max="21"/>
+    <col width="80" customWidth="1" min="22" max="22"/>
     <col width="21" customWidth="1" min="23" max="23"/>
-    <col width="20" customWidth="1" min="24" max="24"/>
-    <col width="28" customWidth="1" min="25" max="25"/>
+    <col width="21" customWidth="1" min="24" max="24"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
     <col width="63" customWidth="1" min="26" max="26"/>
+    <col width="28" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -23138,25 +23394,30 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
+          <t>glossary_terms</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
           <t>classification_summary_json</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>unit_summary_json</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>row_count_projection_1y</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>row_count_projection_2y</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>row_count_projection_5y</t>
         </is>
@@ -23201,23 +23462,24 @@
           <t>Line items with order quantities and explicit unit labels.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
         <is>
           <t>{"concept_counts":{"finance.currency_amount":1,"identifier.foreign_key":3,"measure.quantity":3,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":[]}</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>{"columns_with_units":0,"columns_without_units":9,"mixed_unit_groups":[],"unknown_unit_columns":["ordered_qty_unit","ordered_qty_value","quantity"]}</t>
         </is>
-      </c>
-      <c r="K3" t="n">
-        <v>246</v>
       </c>
       <c r="L3" t="n">
         <v>246</v>
       </c>
       <c r="M3" t="n">
+        <v>246</v>
+      </c>
+      <c r="N3" t="n">
         <v>246</v>
       </c>
     </row>
@@ -23251,6 +23513,7 @@
       <c r="K6" s="2" t="n"/>
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
+      <c r="N6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -23292,6 +23555,7 @@
       <c r="K10" s="2" t="n"/>
       <c r="L10" s="2" t="n"/>
       <c r="M10" s="2" t="n"/>
+      <c r="N10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -23347,6 +23611,7 @@
       <c r="K15" s="2" t="n"/>
       <c r="L15" s="2" t="n"/>
       <c r="M15" s="2" t="n"/>
+      <c r="N15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -23388,6 +23653,7 @@
       <c r="K19" s="2" t="n"/>
       <c r="L19" s="2" t="n"/>
       <c r="M19" s="2" t="n"/>
+      <c r="N19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -23447,6 +23713,7 @@
       <c r="K24" s="2" t="n"/>
       <c r="L24" s="2" t="n"/>
       <c r="M24" s="2" t="n"/>
+      <c r="N24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -23553,80 +23820,85 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
+          <t>glossary_terms</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
           <t>concept_id</t>
         </is>
       </c>
-      <c r="L29" s="2" t="inlineStr">
+      <c r="M29" s="2" t="inlineStr">
         <is>
           <t>concept_confidence</t>
         </is>
       </c>
-      <c r="M29" s="2" t="inlineStr">
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>concept_alias_group</t>
         </is>
       </c>
-      <c r="N29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
         <is>
           <t>concept_evidence_json</t>
         </is>
       </c>
-      <c r="O29" s="2" t="inlineStr">
+      <c r="P29" s="2" t="inlineStr">
         <is>
           <t>concept_sources_json</t>
         </is>
       </c>
-      <c r="P29" s="2" t="inlineStr">
+      <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="Q29" s="2" t="inlineStr">
+      <c r="R29" s="2" t="inlineStr">
         <is>
           <t>unit_source</t>
         </is>
       </c>
-      <c r="R29" s="2" t="inlineStr">
+      <c r="S29" s="2" t="inlineStr">
         <is>
           <t>canonical_unit</t>
         </is>
       </c>
-      <c r="S29" s="2" t="inlineStr">
+      <c r="T29" s="2" t="inlineStr">
         <is>
           <t>unit_system</t>
         </is>
       </c>
-      <c r="T29" s="2" t="inlineStr">
+      <c r="U29" s="2" t="inlineStr">
         <is>
           <t>unit_confidence</t>
         </is>
       </c>
-      <c r="U29" s="2" t="inlineStr">
+      <c r="V29" s="2" t="inlineStr">
         <is>
           <t>unit_notes</t>
         </is>
       </c>
-      <c r="V29" s="2" t="inlineStr">
+      <c r="W29" s="2" t="inlineStr">
         <is>
           <t>factor_to_canonical</t>
         </is>
       </c>
-      <c r="W29" s="2" t="inlineStr">
+      <c r="X29" s="2" t="inlineStr">
         <is>
           <t>offset_to_canonical</t>
         </is>
       </c>
-      <c r="X29" s="2" t="inlineStr">
+      <c r="Y29" s="2" t="inlineStr">
         <is>
           <t>conversion_formula</t>
         </is>
       </c>
-      <c r="Y29" s="2" t="inlineStr">
+      <c r="Z29" s="2" t="inlineStr">
         <is>
           <t>range_min</t>
         </is>
       </c>
-      <c r="Z29" s="2" t="inlineStr">
+      <c r="AA29" s="2" t="inlineStr">
         <is>
           <t>range_max</t>
         </is>
@@ -23664,33 +23936,33 @@
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>The `po_item_id` column is a non-nullable bigint serving as the primary key for uniquely identifying each record in the `purchase_order_items` table.</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
+          <t>Unique identifier for each purchase order item record in the `purchase_order_items` table.</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
         </is>
       </c>
-      <c r="L30" t="n">
+      <c r="M30" t="n">
         <v>0.6</v>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"]</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>["cross_table_consensus","name","type"]</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr"/>
@@ -23699,12 +23971,13 @@
       <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr"/>
-      <c r="Y30" t="inlineStr">
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr">
         <is>
           <t>268</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
+      <c r="AA30" t="inlineStr">
         <is>
           <t>513</t>
         </is>
@@ -23742,33 +24015,33 @@
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>References the unique identifier of the associated purchase order in the purchase_orders table.</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
+          <t>Links each purchase order item to its corresponding purchase order in the `purchase_orders` table via a non-null foreign key.</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
         </is>
       </c>
-      <c r="L31" t="n">
+      <c r="M31" t="n">
         <v>0.9</v>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>["name token: id","type hint: bigint","structural hint: join candidate"]</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>["name","profile","type"]</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr"/>
@@ -23777,12 +24050,13 @@
       <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr"/>
-      <c r="Y31" t="inlineStr">
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr">
         <is>
           <t>128</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
+      <c r="AA31" t="inlineStr">
         <is>
           <t>252</t>
         </is>
@@ -23824,33 +24098,33 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Represents the unique identifier of a product associated with a purchase order item, referencing the `product_id` column in the `products` table.</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
+          <t>Identifier linking each purchase order item to a specific product in the products table.</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
         </is>
       </c>
-      <c r="L32" t="n">
+      <c r="M32" t="n">
         <v>0.9</v>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>["name token: id","type hint: bigint","structural hint: join candidate"]</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>["name","profile","type"]</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
@@ -23859,12 +24133,13 @@
       <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr"/>
-      <c r="Y32" t="inlineStr">
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr">
         <is>
           <t>156</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
+      <c r="AA32" t="inlineStr">
         <is>
           <t>205</t>
         </is>
@@ -23910,63 +24185,64 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>The "quantity" column in the "purchase_order_items" table is a non-null integer representing the number of items in a purchase order.</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
+          <t>The `quantity` column in the `purchase_order_items` table stores the non-null integer value representing the number of units of a product included in a specific purchase order item.</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
         <is>
           <t>measure.quantity</t>
         </is>
       </c>
-      <c r="L33" t="n">
+      <c r="M33" t="n">
         <v>1</v>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>quantity</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>["name token: quantity","type hint: integer","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity","profile heuristic matched"]</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>["name","profile","type","values"]</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr">
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr">
         <is>
           <t>combined</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr">
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
+      <c r="U33" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
+      <c r="V33" t="inlineStr">
         <is>
           <t>Semantic class suggests units, but no explicit source unit token was detected.</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr"/>
-      <c r="Y33" t="inlineStr">
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
+      <c r="AA33" t="inlineStr">
         <is>
           <t>50</t>
         </is>
@@ -24012,33 +24288,33 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Represents the non-null unit cost of a purchase order item, stored as a numeric value with up to 10 digits and 2 decimal places.</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
+          <t>The `unit_cost` column in the `purchase_order_items` table stores the non-null numeric cost per unit of a product in a purchase order, represented as a currency amount with up to 10 digits and 2 decimal places.</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
         <is>
           <t>finance.currency_amount</t>
         </is>
       </c>
-      <c r="L34" t="n">
+      <c r="M34" t="n">
         <v>1</v>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>unit_cost</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>["name token: unit_cost","type hint: numeric(10,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount","table context: purchase_order_items"]</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>["name","profile","table_context","type","values"]</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
@@ -24047,12 +24323,13 @@
       <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr"/>
       <c r="X34" t="inlineStr"/>
-      <c r="Y34" t="inlineStr">
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr">
         <is>
           <t>5.55</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
+      <c r="AA34" t="inlineStr">
         <is>
           <t>358.59</t>
         </is>
@@ -24098,33 +24375,33 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>The `created_at` column stores the non-nullable timestamp indicating when the purchase order item record was created.</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
+          <t>Records the timestamp when a purchase order item entry is created, stored as a non-nullable datetime value.</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
         <is>
           <t>temporal.created_at</t>
         </is>
       </c>
-      <c r="L35" t="n">
+      <c r="M35" t="n">
         <v>1</v>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: purchase_order_items"]</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>["name","profile","table_context","type","values"]</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr"/>
@@ -24133,12 +24410,13 @@
       <c r="V35" t="inlineStr"/>
       <c r="W35" t="inlineStr"/>
       <c r="X35" t="inlineStr"/>
-      <c r="Y35" t="inlineStr">
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr">
         <is>
           <t>2026-03-12 15:44:18.668789</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
+      <c r="AA35" t="inlineStr">
         <is>
           <t>2026-03-12 15:45:45.174099</t>
         </is>
@@ -24184,33 +24462,33 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>The `updated_at` column in the `purchase_order_items` table stores the non-nullable timestamp indicating the last update to a record.</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
+          <t>The `updated_at` column in the `purchase_order_items` table stores the non-nullable timestamp of the most recent update to a purchase order item record.</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
         <is>
           <t>temporal.updated_at</t>
         </is>
       </c>
-      <c r="L36" t="n">
+      <c r="M36" t="n">
         <v>1</v>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: purchase_order_items"]</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>["name","profile","table_context","type","values"]</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr"/>
@@ -24219,12 +24497,13 @@
       <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr"/>
-      <c r="Y36" t="inlineStr">
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr">
         <is>
           <t>2026-03-12 15:44:18.668794</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
+      <c r="AA36" t="inlineStr">
         <is>
           <t>2026-03-12 15:45:45.174104</t>
         </is>
@@ -24270,59 +24549,60 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Represents the numeric value of the quantity ordered for a purchase order item, allowing up to 10 digits with 2 decimal places, and can be null.</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
+          <t>The `ordered_qty_value` column stores the numeric quantity value (up to two decimal places) of items ordered in a purchase order, which can be null.</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
         <is>
           <t>measure.quantity</t>
         </is>
       </c>
-      <c r="L37" t="n">
+      <c r="M37" t="n">
         <v>1</v>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>ordered_qty</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>["name token: ordered_qty","type hint: numeric(10,2)","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity"]</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>["name","profile","type","values"]</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr">
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr">
         <is>
           <t>combined</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr">
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr">
+      <c r="U37" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr">
+      <c r="V37" t="inlineStr">
         <is>
           <t>Semantic class suggests units, but no explicit source unit token was detected.</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr"/>
       <c r="X37" t="inlineStr"/>
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -24367,56 +24647,57 @@
           <t>Ordered quantity unit (ea/box).</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
         <is>
           <t>measure.quantity</t>
         </is>
       </c>
-      <c r="L38" t="n">
+      <c r="M38" t="n">
         <v>1</v>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>ordered_qty_unit</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>["name token: ordered_qty_unit","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity"]</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
+      <c r="P38" t="inlineStr">
         <is>
           <t>["name","profile","values"]</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr">
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr">
         <is>
           <t>combined</t>
         </is>
       </c>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr">
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="T38" t="inlineStr">
+      <c r="U38" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr">
+      <c r="V38" t="inlineStr">
         <is>
           <t>Semantic class suggests units, but no explicit source unit token was detected.</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr"/>
       <c r="X38" t="inlineStr"/>
       <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr"/>
     </row>
     <row r="39"/>
     <row r="40">
@@ -24557,6 +24838,7 @@
           <t>extra_json</t>
         </is>
       </c>
+      <c r="AA41" s="2" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">

--- a/LATEST_SCHEMA/schema_azure_mssql_dbo.xlsx
+++ b/LATEST_SCHEMA/schema_azure_mssql_dbo.xlsx
@@ -826,7 +826,7 @@
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="80" customWidth="1" min="7" max="7"/>
     <col width="80" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="70" customWidth="1" min="9" max="9"/>
     <col width="80" customWidth="1" min="10" max="10"/>
     <col width="80" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
@@ -965,7 +965,11 @@
           <t>Procurement headers including approver employee relationship.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>RetailDomainGlossary.PurchaseOrder, RetailDomainGlossary.OrderStatus</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>{"concept_counts":{"entity.status":1,"identifier.foreign_key":4,"temporal.created_at":1,"temporal.date_only":2,"temporal.updated_at":1},"low_confidence_columns":[]}</t>
@@ -1493,10 +1497,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Unique identifier for purchase orders in the retail operations system.</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
+          <t>Unique identifier for purchase orders in the system.</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>RetailDomainGlossary.PurchaseOrder</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
@@ -1572,10 +1580,14 @@
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>References the unique identifier of the supplier associated with a purchase order, linking to the `suppliers.supplier_id` column.</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
+          <t>Identifies the supplier associated with a purchase order, referencing the `supplier_id` column in the `suppliers` table.</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>RetailDomainGlossary.SupplierCode</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
@@ -1738,10 +1750,14 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Indicates the current state of a purchase order, such as 'Ordered' or 'Received', using predefined category values.</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
+          <t>Indicates the current state of a purchase order (e.g., "Ordered," "Received") as a non-null categorical value.</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>RetailDomainGlossary.OrderStatus</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>entity.status</t>
@@ -1825,7 +1841,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>The `order_date` column in the `purchase_orders` table records the date a purchase order was placed and cannot be null.</t>
+          <t>The `order_date` column in the `purchase_orders` table records the date a purchase order was placed, is mandatory, and uses the `date` data type.</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -1915,7 +1931,11 @@
           <t>The `expected_date` column in the `purchase_orders` table records the anticipated delivery date for a purchase order, allowing null values.</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>RetailDomainGlossary.OrderDeliveryRelationship</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>temporal.date_only</t>
@@ -1999,7 +2019,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>The `created_at` column records the timestamp when a purchase order record is initially created in the system and cannot be null.</t>
+          <t>The `created_at` column stores the non-nullable timestamp indicating when a purchase order record was initially created in the system.</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2086,7 +2106,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>The `updated_at` column stores the non-null timestamp indicating the last modification date and time of a purchase order record.</t>
+          <t>The `updated_at` column stores the non-nullable timestamp of the most recent update to a purchase order record.</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2745,7 +2765,7 @@
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="80" customWidth="1" min="7" max="7"/>
     <col width="80" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="80" customWidth="1" min="9" max="9"/>
     <col width="80" customWidth="1" min="10" max="10"/>
     <col width="80" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
@@ -2884,7 +2904,11 @@
           <t>Sales line items with sold quantity and explicit unit labels.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>RetailDomainGlossary.OrderLine, RetailDomainGlossary.SalesOrder, RetailDomainGlossary.UnitOfMeasure</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>{"concept_counts":{"finance.currency_amount":1,"identifier.foreign_key":3,"measure.quantity":3,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":[]}</t>
@@ -3358,10 +3382,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Unique identifier for individual items within a sales order, serving as the primary key for the `sales_order_items` table.</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
+          <t>Unique identifier for each sales order item in the sales_order_items table.</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>RetailDomainGlossary.OrderLine</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
@@ -3440,7 +3468,11 @@
           <t>Identifier linking each sales order item to its associated sales order in the `sales_orders` table.</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>RetailDomainGlossary.SalesOrder</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
@@ -3520,10 +3552,14 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>References the unique identifier of the product associated with a sales order item, linking to the `products.product_id` column.</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
+          <t>Identifier for the product associated with the sales order item, referencing the primary key in the products table.</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>RetailDomainGlossary.ProductCategory</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
@@ -3607,10 +3643,14 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>The "quantity" column in the "sales_order_items" table stores the non-null integer value representing the number of units of a product included in a specific sales order item.</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
+          <t>The "quantity" column in the "sales_order_items" table stores the number of units of a product included in a sales order item, represented as a non-null integer.</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>RetailDomainGlossary.OrderLine</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>measure.quantity</t>
@@ -3710,10 +3750,14 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Represents the per-unit price of a product in a sales order item, stored as a non-null numeric value with up to 15 digits and 2 decimal places.</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
+          <t>The `unit_price` column in the `sales_order_items` table stores the per-unit selling price of a product in the sales order as a non-null numeric value with two decimal places.</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>RetailDomainGlossary.SellingPrice</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>finance.currency_amount</t>
@@ -3797,7 +3841,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>The `created_at` column in the `sales_order_items` table stores the non-nullable timestamp indicating when a sales order item record was created.</t>
+          <t>Records the timestamp when a sales order item entry is created, ensuring accurate tracking of creation events.</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -3884,7 +3928,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>The `updated_at` column stores the non-nullable timestamp of the most recent update to a sales order item record for tracking modification history.</t>
+          <t>The `updated_at` column in the `sales_order_items` table stores the non-nullable timestamp of the most recent update to a sales order item record.</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -3971,10 +4015,14 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Represents the numeric value of the quantity sold for a sales order item, allowing up to two decimal places and nullable for cases where the quantity is not recorded.</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
+          <t>The `sold_qty_value` column stores the numeric value representing the quantity of a product sold in a sales order item, allowing up to two decimal places, and can be null.</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>RetailDomainGlossary.OrderLine</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>measure.quantity</t>
@@ -4069,7 +4117,11 @@
           <t>Sold quantity unit (ea/box).</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>RetailDomainGlossary.UnitOfMeasure</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>measure.quantity</t>
@@ -4648,7 +4700,7 @@
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="80" customWidth="1" min="7" max="7"/>
     <col width="80" customWidth="1" min="8" max="8"/>
-    <col width="29" customWidth="1" min="9" max="9"/>
+    <col width="80" customWidth="1" min="9" max="9"/>
     <col width="80" customWidth="1" min="10" max="10"/>
     <col width="80" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
@@ -4787,7 +4839,11 @@
           <t>Sales headers including assigned sales representative relationship.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>RetailDomainGlossary.SalesOrder, RetailDomainGlossary.CustomerIdentifier, RetailDomainGlossary.OrderStatus</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>{"concept_counts":{"entity.status":1,"finance.currency_amount":1,"identifier.foreign_key":5,"temporal.created_at":1,"temporal.date_only":1,"temporal.updated_at":1},"low_confidence_columns":[]}</t>
@@ -5339,10 +5395,14 @@
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Unique identifier for each sales order in the system.</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
+          <t>Unique identifier for each sales order in the system, serving as the primary key for the sales_orders table.</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>RetailDomainGlossary.SalesOrder</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
@@ -5421,7 +5481,11 @@
           <t>Identifies the store associated with a sales order, referencing the `store_id` column in the `stores` table.</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>RetailDomainGlossary.SalesChannel</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
@@ -5505,10 +5569,14 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Identifies the customer associated with a sales order, referencing the `customer_id` column in the `customers` table; nullable to accommodate orders without a registered customer.</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
+          <t>Represents the identifier of the customer associated with a sales order, referencing the `customer_id` column in the `customers` table, and may be null if no customer is linked.</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>RetailDomainGlossary.CustomerIdentifier</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
@@ -5584,7 +5652,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Identifies the employee responsible for processing the sales order, referencing the `employees.employee_id` column.</t>
+          <t>Represents the unique identifier of the employee associated with the sales order, referencing the `employees.employee_id` column.</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -5761,7 +5829,11 @@
           <t>Indicates the current state of a sales order, such as 'Pending' or 'Completed', stored as a non-nullable text category.</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>RetailDomainGlossary.OrderStatus</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>entity.status</t>
@@ -5848,7 +5920,11 @@
           <t>The `total_amount` column in the `sales_orders` table stores the non-nullable total monetary value of a sales order as a numeric value with up to 12 digits and 2 decimal places.</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>RetailDomainGlossary.SalesOrder</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>finance.currency_amount</t>
@@ -5932,7 +6008,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>The `created_at` column records the timestamp when a sales order entry was initially created, stored as a non-nullable `datetime2` value.</t>
+          <t>The `created_at` column records the timestamp when a sales order record is initially created, stored as a non-nullable `datetime2` value.</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -6019,7 +6095,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>The `updated_at` column records the timestamp of the most recent update to a sales order, ensuring accurate tracking of modifications, and it is mandatory.</t>
+          <t>The `updated_at` column records the timestamp of the most recent update to a sales order, stored as a non-nullable datetime2 value.</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -6814,10 +6890,14 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>The "stores" table contains details about retail store locations, including unique identifiers, names, addresses, contact information, and timestamps for record creation and updates.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>The "stores" table stores information about retail store locations, including unique identifiers, names, codes, addresses, contact details, and timestamps for record creation and updates.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>RetailDomainGlossary.StoreCode</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>{"concept_counts":{"contact.address":2,"contact.person_name":1,"contact.phone":1,"identifier.foreign_key":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":["address","city","code","name","postal_code","state"]}</t>
@@ -7154,7 +7234,11 @@
           <t>Unique identifier for each store in the retail operations system.</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>RetailDomainGlossary.StoreCode</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
@@ -7230,7 +7314,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>The "name" column in the "stores" table is a non-nullable nvarchar field storing the name of each retail store.</t>
+          <t>The "name" column in the "stores" table is a non-nullable nvarchar field storing the name of a retail store.</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -7309,10 +7393,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Unique identifier for a store, typically represented as an alphanumeric code.</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
+          <t>Unique alphanumeric identifier for a store, used for internal reference and operations.</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>RetailDomainGlossary.StoreCode</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="n">
         <v>0.1</v>
@@ -7534,7 +7622,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Indicates the state or province where the store is located, stored as a nullable text field.</t>
+          <t>The "state" column in the "stores" table stores the name of the state or province where a store is located, allowing null values.</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -7609,7 +7697,7 @@
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>The "postal_code" column in the "stores" table stores the postal or ZIP code of a store location as a nullable, case-insensitive string.</t>
+          <t>The "postal_code" column in the "stores" table stores the postal or ZIP code of a store location as a nullable string.</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -7700,7 +7788,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Stores.phone is an optional nvarchar column storing the contact phone number for a store location.</t>
+          <t>The "phone" column in the "stores" table stores the contact phone number of a store as a nullable nvarchar value.</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -7787,7 +7875,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>The `created_at` column records the non-nullable timestamp indicating when a store record was initially created in the system.</t>
+          <t>The `created_at` column stores the non-nullable timestamp indicating when a store record was initially created in the system.</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -8756,7 +8844,7 @@
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="80" customWidth="1" min="7" max="7"/>
     <col width="80" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="35" customWidth="1" min="9" max="9"/>
     <col width="80" customWidth="1" min="10" max="10"/>
     <col width="80" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
@@ -8895,7 +8983,11 @@
           <t>The "suppliers" table stores information about suppliers, including their unique identifier, name, contact details, and timestamps for record creation and updates.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>RetailDomainGlossary.SupplierCode</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>{"concept_counts":{"contact.email":1,"contact.person_name":2,"contact.phone":1,"identifier.foreign_key":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":["contact_name","name"]}</t>
@@ -9232,7 +9324,11 @@
           <t>Unique identifier for each supplier, serving as the primary key in the suppliers table.</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>RetailDomainGlossary.SupplierCode</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
@@ -9395,7 +9491,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>The `contact_name` column in the `suppliers` table stores the name of the primary contact person for a supplier, allowing null values.</t>
+          <t>Stores the name of the primary contact person for a supplier, allowing null values.</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -9569,7 +9665,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>The "phone" column in the "suppliers" table stores the supplier's contact phone number as a nullable string.</t>
+          <t>The "phone" column in the "suppliers" table stores the contact phone number of a supplier as a nullable string.</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -9656,7 +9752,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>The `created_at` column records the non-nullable timestamp indicating when a supplier record was initially created in the system.</t>
+          <t>Records the timestamp when a supplier entry is initially created in the system, stored as a non-nullable datetime value.</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -9743,7 +9839,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>The `updated_at` column stores the non-nullable timestamp of the most recent update to a supplier record.</t>
+          <t>The `updated_at` column stores the non-nullable timestamp of the most recent update to a supplier record in the `suppliers` table.</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -10326,7 +10422,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{"metadata":{"generated_at":"2026-04-03T12:09:52.790221+00:00","database_url":"pioneertest.database.windows.net:1433/free-sql-db-3300567?driver=ODBC+Driver+18+for+SQL+Server&amp;TrustServerCertificate=yes","schema_filter":"dbo","total_tables":10,"total_rows":1364,"total_findings":64},"connection":{"host":"pioneertest.database.windows.net","port":"1433","database":"free-sql-db-3300567","driver":"mssql","timezone":"(UTC) Coordinated Universal Time"},"source_system_context":{"contacts":[],"delete_management_instruction":"","restrictions":"","late_arriving_data_manual":"","volume_size_projection_manual":"","system_description":"Retail operations source system covering customers, stores, employees, suppliers, products, inventory, purchase orders, and sales orders used for day-to-day store, procurement, and sales transaction management.","openmetadata_enrichment":{"enabled":false,"configured":false,"database_service_name":"","schema":"dbo","matched_tables":0,"unmatched_tables":0,"error":""},"db_analysis_config":{"exclude_schemas":["prediction"],"exclude_tables":[],"max_row_limit":100}},"concept_registry":{"version":1,"taxonomy":"domain-dot","generated_from_tables":10,"concepts":[{"concept_id":"contact.address","column_count":2,"table_count":1,"avg_confidence":0.55,"alias_groups":["address","postal_code"],"sample_columns":["stores.address","stores.postal_code"],"signals":["name","type"]},{"concept_id":"contact.email","column_count":3,"table_count":3,"avg_confidence":1.0,"alias_groups":["email"],"sample_columns":["customers.email","employees.email","suppliers.email"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"contact.person_name","column_count":8,"table_count":5,"avg_confidence":0.56,"alias_groups":["contact_name","first_name","last_name","name"],"sample_columns":["customers.first_name","customers.last_name","employees.first_name","employees.last_name","products.name"],"signals":["name","table_context","type"]},{"concept_id":"contact.phone","column_count":3,"table_count":3,"avg_confidence":1.0,"alias_groups":["phone"],"sample_columns":["customers.phone","stores.phone","suppliers.phone"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"entity.category","column_count":1,"table_count":1,"avg_confidence":0.8,"alias_groups":["category"],"sample_columns":["products.category"],"signals":["name","profile","type"]},{"concept_id":"entity.status","column_count":2,"table_count":2,"avg_confidence":1.0,"alias_groups":["statu"],"sample_columns":["purchase_orders.status","sales_orders.status"],"signals":["name","profile","type","values"]},{"concept_id":"entity.type","column_count":1,"table_count":1,"avg_confidence":0.65,"alias_groups":["role"],"sample_columns":["employees.role"],"signals":["name","profile","type"]},{"concept_id":"finance.currency_amount","column_count":5,"table_count":4,"avg_confidence":1.0,"alias_groups":["amount","price","unit_cost"],"sample_columns":["products.unit_price","products.cost_price","purchase_order_items.unit_cost","sales_order_items.unit_price","sales_orders.total_amount"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"identifier.foreign_key","column_count":26,"table_count":10,"avg_confidence":0.78,"alias_groups":["id"],"sample_columns":["customers.customer_id","employees.employee_id","employees.store_id","inventory.inventory_id","inventory.store_id"],"signals":["cross_table_consensus","name","profile","type"]},{"concept_id":"identifier.product_code","column_count":1,"table_count":1,"avg_confidence":0.7,"alias_groups":["sku"],"sample_columns":["products.sku"],"signals":["name","profile","type"]},{"concept_id":"measure.quantity","column_count":7,"table_count":3,"avg_confidence":1.0,"alias_groups":["ordered_qty","ordered_qty_unit","quantity","quantity_on_hand","sold_qty","sold_qty_unit"],"sample_columns":["inventory.quantity_on_hand","purchase_order_items.quantity","purchase_order_items.ordered_qty_value","purchase_order_items.ordered_qty_unit","sales_order_items.quantity"],"signals":["name","profile","type","values"]},{"concept_id":"temporal.created_at","column_count":10,"table_count":10,"avg_confidence":1.0,"alias_groups":["created_at"],"sample_columns":["customers.created_at","employees.created_at","inventory.created_at","products.created_at","purchase_order_items.created_at"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"temporal.date_only","column_count":4,"table_count":3,"avg_confidence":0.97,"alias_groups":["expected_date","hire_date","order_date"],"sample_columns":["employees.hire_date","purchase_orders.order_date","purchase_orders.expected_date","sales_orders.order_date"],"signals":["cross_table_consensus","name","profile","table_context","type","values"]},{"concept_id":"temporal.event_time","column_count":1,"table_count":1,"avg_confidence":1.0,"alias_groups":["last_restocked_at"],"sample_columns":["inventory.last_restocked_at"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"temporal.updated_at","column_count":10,"table_count":10,"avg_confidence":1.0,"alias_groups":["updated_at"],"sample_columns":["customers.updated_at","employees.updated_at","inventory.updated_at","products.updated_at","purchase_order_items.updated_at"],"signals":["name","profile","table_context","type","values"]}]},"data_quality_summary":{"critical":0,"warning":27,"info":37,"by_check":{"controlled_value_candidate":7,"nullable_but_never_null":13,"missing_primary_key":0,"missing_foreign_key":0,"format_inconsistency":0,"range_violation":0,"timestamp_ordering":10,"delete_management":10,"late_arriving_data":3,"timezone":10,"unit_unknown":11,"unit_noncanonical_but_convertible":0,"unit_mismatch_within_semantic_group":0},"constraints_found":{"check_constraints":0,"enum_columns":0,"unique_constraints":10}},"tables":[{"table":"customers","schema":"dbo","columns":[{"name":"customer_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for each customer in the retail operations system.","glossary_terms":[],"cardinality":100,"null_count":0,"data_range":{"min":"404","max":"503"},"data_category":"discrete","semantic_class":"customer_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"first_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"Stores the given name of a customer as a non-null, case-insensitive Unicode string.","glossary_terms":[],"cardinality":100,"null_count":0,"data_range":{"min":"Customer1","max":"Customer99"},"data_category":"nominal","semantic_class":"given_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.6,"concept_evidence":["name token: first_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","table context: customers"],"concept_sources":["name","table_context","type"],"concept_alias_group":"first_name"},{"name":"last_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"Stores the last name of a customer as a non-null, case-insensitive Unicode string.","glossary_terms":[],"cardinality":100,"null_count":0,"data_range":{"min":"LastName1 (updated)","max":"LastName99"},"data_category":"nominal","semantic_class":"family_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.6,"concept_evidence":["name token: last_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","table context: customers"],"concept_sources":["name","table_context","type"],"concept_alias_group":"last_name"},{"name":"email","type":"nvarchar(450)","nullable":true,"is_incremental":false,"column_description":"Stores the email address of the customer, allowing null values.","glossary_terms":[],"cardinality":100,"null_count":0,"data_range":{"min":"customer1@example.com","max":"customer99@example.com"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.email","concept_confidence":1.0,"concept_evidence":["name token: email","type hint: nvarchar(450)","legacy field classification: contact","value pattern: email","table context: customers","sensitive hint: pii_contact"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"email"},{"name":"phone","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"Stores the customer's phone number as an optional text field for contact purposes.","glossary_terms":[],"cardinality":100,"null_count":0,"data_range":{"min":"555-1001","max":"555-1100"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.phone","concept_confidence":1.0,"concept_evidence":["name token: phone","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: contact","value pattern: phone","table context: customers","sensitive hint: pii_contact"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"phone"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The `created_at` column records the non-nullable timestamp indicating when a customer record was initially created in the system.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":95,"null_count":0,"data_range":{"min":"2021-03-23 15:38:57.201565","max":"2026-02-26 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: customers"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"Tracks the timestamp of the most recent update to a customer's record, ensuring accurate change history.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":95,"null_count":0,"data_range":{"min":"2021-03-23 15:38:57.201565","max":"2026-03-26 08:52:49.252228"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: customers"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"}],"table_description":"The `customers` table stores information about retail customers, including their unique ID, name, contact details, and timestamps for record creation and updates.","glossary_terms":[],"primary_keys":["customer_id"],"foreign_keys":[],"row_count":100,"field_classifications":{"customer_id":"identifier","first_name":"person_name","last_name":"person_name","email":"contact","phone":"contact","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{"email":"pii_contact","phone":"pii_contact"},"incremental_columns":["updated_at"],"join_candidates":[],"unit_summary":{"columns_with_units":0,"columns_without_units":7,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":false,"has_sensitive_fields":true,"row_count_projection_1y":126,"row_count_projection_2y":152,"row_count_projection_5y":232,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.email":1,"contact.person_name":2,"contact.phone":1,"identifier.foreign_key":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"findings":[{"column":"email","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 100 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"phone","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 100 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}},{"table":"employees","schema":"dbo","columns":[{"name":"employee_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for each employee in the retail operations system.","glossary_terms":[],"cardinality":20,"null_count":0,"data_range":{"min":"64","max":"83"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Associates each employee with a specific store, referencing the `store_id` column in the `stores` table.","glossary_terms":[],"cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"first_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"Stores the given name of an employee, represented as a non-null, case-insensitive Unicode string.","glossary_terms":[],"cardinality":20,"null_count":0,"data_range":{"min":"Employee1","max":"Employee9"},"data_category":"nominal","semantic_class":"given_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: first_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"first_name"},{"name":"last_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"The \"last_name\" column in the \"employees\" table stores the non-nullable family name of an employee as a case-insensitive Unicode string.","glossary_terms":[],"cardinality":20,"null_count":0,"data_range":{"min":"LastName1","max":"LastName9"},"data_category":"nominal","semantic_class":"family_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: last_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"last_name"},{"name":"email","type":"nvarchar(450)","nullable":false,"is_incremental":false,"column_description":"Stores the unique email address of each employee for contact purposes, with a maximum length of 450 characters and cannot be null.","glossary_terms":[],"cardinality":20,"null_count":0,"data_range":{"min":"emp1@example.com","max":"emp9@example.com"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.email","concept_confidence":1.0,"concept_evidence":["name token: email","type hint: nvarchar(450)","legacy field classification: contact","value pattern: email","sensitive hint: pii_contact"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"email"},{"name":"role","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"Indicates the job position or function of an employee within the organization, stored as a non-nullable text value.","glossary_terms":[],"cardinality":4,"null_count":0,"data_range":{"min":"Cashier","max":"Stock"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"entity.type","concept_confidence":0.65,"concept_evidence":["name token: role","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","profile heuristic matched"],"concept_sources":["name","profile","type"],"concept_alias_group":"role"},{"name":"hire_date","type":"date","nullable":false,"is_incremental":false,"column_description":"The `hire_date` column in the `employees` table stores the non-nullable date an employee was hired, used for tracking employment start dates.","glossary_terms":[],"cardinality":20,"null_count":0,"data_range":{"min":"2021-05-03","max":"2025-01-26"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.date_only","concept_confidence":1.0,"concept_evidence":["name token: hire_date","type hint: date","legacy field classification: temporal","value pattern: date_only","table context: employees"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"hire_date"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The `created_at` column records the non-nullable timestamp indicating when an employee record was initially created in the system.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":20,"null_count":0,"data_range":{"min":"2021-05-03 15:38:57.201565","max":"2025-01-26 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: employees"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The `updated_at` column stores the non-nullable timestamp of the most recent update to an employee record.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":20,"null_count":0,"data_range":{"min":"2021-05-03 15:38:57.201565","max":"2025-01-26 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: employees"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"}],"table_description":"The `employees` table stores details about retail system employees, including their identifiers, store associations, personal information, roles, hire dates, and record timestamps.","glossary_terms":[],"primary_keys":["employee_id"],"foreign_keys":[{"column":"store_id","references":"stores.store_id"}],"row_count":20,"field_classifications":{"first_name":"person_name","last_name":"person_name","email":"contact","hire_date":"temporal","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{"email":"pii_contact"},"incremental_columns":["updated_at"],"join_candidates":[{"column":"store_id","target_table":"stores","target_column":"store_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":9,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":true,"row_count_projection_1y":35,"row_count_projection_2y":50,"row_count_projection_5y":96,"partition_columns_candidates":["hire_date","created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.email":1,"contact.person_name":2,"entity.type":1,"identifier.foreign_key":2,"temporal.created_at":1,"temporal.date_only":1,"temporal.updated_at":1},"low_confidence_columns":["first_name","last_name"]},"data_quality":{"findings":[{"column":"role","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 4 distinct value(s) ('Cashier', 'Manager', 'Sales', 'Stock') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Cashier","Manager","Sales","Stock"],"cardinality":4},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":"hire_date","check":"late_arriving_data","severity":"info","detail":"Minor arrival delay \u2014 max lag between 'hire_date' and 'created_at' is 15.7h (avg 15.7h, P95 15.7h).","recommendation":"Use 'created_at' as the watermark (preferred). If using 'hire_date', add a 1\u20132 day lookback buffer.","business_date_column":"hire_date","system_ts_column":"created_at","lag_stats":{"total_rows_compared":20,"min_lag_hours":15.65,"avg_lag_hours":15.65,"p95_lag_hours":15.65,"max_lag_hours":15.65,"max_lag_days":0.7,"rows_late_over_1d":0,"rows_late_over_7d":0},"recommended_lookback_days":2},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}},{"table":"inventory","schema":"dbo","columns":[{"name":"inventory_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for each inventory record in the system.","glossary_terms":[],"cardinality":100,"null_count":0,"data_range":{"min":"8","max":"107"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Identifier for the store associated with the inventory record, referencing the `store_id` column in the `stores` table.","glossary_terms":[],"cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"product_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"References the unique identifier of a product from the `products` table to associate inventory records with specific products.","glossary_terms":[],"cardinality":47,"null_count":0,"data_range":{"min":"156","max":"205"},"data_category":"discrete","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"quantity_on_hand","type":"integer","nullable":false,"is_incremental":false,"column_description":"Tracks the current quantity of a product available in inventory, expressed as a non-null integer.","glossary_terms":[],"cardinality":68,"null_count":0,"data_range":{"min":"2","max":"98"},"data_category":"discrete","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: quantity_on_hand","type hint: integer","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"quantity_on_hand"},{"name":"reorder_level","type":"integer","nullable":false,"is_incremental":false,"column_description":"Indicates the minimum quantity of a product in inventory that triggers a reorder, stored as a non-null integer.","glossary_terms":[],"cardinality":20,"null_count":0,"data_range":{"min":"10","max":"29"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: integer","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"last_restocked_at","type":"datetime2","nullable":true,"is_incremental":false,"column_description":"The `last_restocked_at` column records the timestamp of the most recent restocking event for an inventory item, allowing null values if the item has not been restocked.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":89,"null_count":0,"data_range":{"min":"2024-03-14 15:38:57.201565","max":"2026-03-07 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.event_time","concept_confidence":1.0,"concept_evidence":["name token: last_restocked_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: inventory"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"last_restocked_at"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The `created_at` column records the non-nullable timestamp indicating when the inventory record was initially created.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":91,"null_count":0,"data_range":{"min":"2024-03-05 15:38:57.201565","max":"2026-02-23 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: inventory"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"Tracks the timestamp of the most recent update to an inventory record, ensuring accurate change history.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":89,"null_count":0,"data_range":{"min":"2024-03-14 15:38:57.201565","max":"2026-03-07 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"conc</t>
+          <t>{"metadata":{"generated_at":"2026-04-07T08:55:59.245988+00:00","database_url":"pioneertest.database.windows.net:1433/free-sql-db-3300567?driver=ODBC+Driver+18+for+SQL+Server&amp;TrustServerCertificate=yes","schema_filter":"dbo","total_tables":10,"total_rows":1364,"total_findings":64},"connection":{"host":"pioneertest.database.windows.net","port":"1433","database":"free-sql-db-3300567","driver":"mssql","timezone":"(UTC) Coordinated Universal Time"},"source_system_context":{"contacts":[],"delete_management_instruction":"","restrictions":"","late_arriving_data_manual":"","volume_size_projection_manual":"","system_description":"Retail operations source system covering customers, stores, employees, suppliers, products, inventory, purchase orders, and sales orders used for day-to-day store, procurement, and sales transaction management.","openmetadata_enrichment":{"enabled":true,"configured":true,"database_service_name":"","schema":"dbo","match_strategy":"table_name","matched_tables":0,"unmatched_tables":10,"error":""},"db_analysis_config":{"exclude_schemas":["prediction"],"exclude_tables":[],"max_row_limit":100}},"concept_registry":{"version":1,"taxonomy":"domain-dot","generated_from_tables":10,"concepts":[{"concept_id":"contact.address","column_count":2,"table_count":1,"avg_confidence":0.55,"alias_groups":["address","postal_code"],"sample_columns":["stores.address","stores.postal_code"],"signals":["name","type"]},{"concept_id":"contact.email","column_count":3,"table_count":3,"avg_confidence":1.0,"alias_groups":["email"],"sample_columns":["customers.email","employees.email","suppliers.email"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"contact.person_name","column_count":8,"table_count":5,"avg_confidence":0.56,"alias_groups":["contact_name","first_name","last_name","name"],"sample_columns":["customers.first_name","customers.last_name","employees.first_name","employees.last_name","products.name"],"signals":["name","table_context","type"]},{"concept_id":"contact.phone","column_count":3,"table_count":3,"avg_confidence":1.0,"alias_groups":["phone"],"sample_columns":["customers.phone","stores.phone","suppliers.phone"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"entity.category","column_count":1,"table_count":1,"avg_confidence":0.8,"alias_groups":["category"],"sample_columns":["products.category"],"signals":["name","profile","type"]},{"concept_id":"entity.status","column_count":2,"table_count":2,"avg_confidence":1.0,"alias_groups":["statu"],"sample_columns":["purchase_orders.status","sales_orders.status"],"signals":["name","profile","type","values"]},{"concept_id":"entity.type","column_count":1,"table_count":1,"avg_confidence":0.65,"alias_groups":["role"],"sample_columns":["employees.role"],"signals":["name","profile","type"]},{"concept_id":"finance.currency_amount","column_count":5,"table_count":4,"avg_confidence":1.0,"alias_groups":["amount","price","unit_cost"],"sample_columns":["products.unit_price","products.cost_price","purchase_order_items.unit_cost","sales_order_items.unit_price","sales_orders.total_amount"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"identifier.foreign_key","column_count":26,"table_count":10,"avg_confidence":0.78,"alias_groups":["id"],"sample_columns":["customers.customer_id","employees.employee_id","employees.store_id","inventory.inventory_id","inventory.store_id"],"signals":["cross_table_consensus","name","profile","type"]},{"concept_id":"identifier.product_code","column_count":1,"table_count":1,"avg_confidence":0.7,"alias_groups":["sku"],"sample_columns":["products.sku"],"signals":["name","profile","type"]},{"concept_id":"measure.quantity","column_count":7,"table_count":3,"avg_confidence":1.0,"alias_groups":["ordered_qty","ordered_qty_unit","quantity","quantity_on_hand","sold_qty","sold_qty_unit"],"sample_columns":["inventory.quantity_on_hand","purchase_order_items.quantity","purchase_order_items.ordered_qty_value","purchase_order_items.ordered_qty_unit","sales_order_items.quantity"],"signals":["name","profile","type","values"]},{"concept_id":"temporal.created_at","column_count":10,"table_count":10,"avg_confidence":1.0,"alias_groups":["created_at"],"sample_columns":["customers.created_at","employees.created_at","inventory.created_at","products.created_at","purchase_order_items.created_at"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"temporal.date_only","column_count":4,"table_count":3,"avg_confidence":0.97,"alias_groups":["expected_date","hire_date","order_date"],"sample_columns":["employees.hire_date","purchase_orders.order_date","purchase_orders.expected_date","sales_orders.order_date"],"signals":["cross_table_consensus","name","profile","table_context","type","values"]},{"concept_id":"temporal.event_time","column_count":1,"table_count":1,"avg_confidence":1.0,"alias_groups":["last_restocked_at"],"sample_columns":["inventory.last_restocked_at"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"temporal.updated_at","column_count":10,"table_count":10,"avg_confidence":1.0,"alias_groups":["updated_at"],"sample_columns":["customers.updated_at","employees.updated_at","inventory.updated_at","products.updated_at","purchase_order_items.updated_at"],"signals":["name","profile","table_context","type","values"]}]},"data_quality_summary":{"critical":0,"warning":27,"info":37,"by_check":{"controlled_value_candidate":7,"nullable_but_never_null":13,"missing_primary_key":0,"missing_foreign_key":0,"format_inconsistency":0,"range_violation":0,"timestamp_ordering":10,"delete_management":10,"late_arriving_data":3,"timezone":10,"unit_unknown":11,"unit_noncanonical_but_convertible":0,"unit_mismatch_within_semantic_group":0},"constraints_found":{"check_constraints":0,"enum_columns":0,"unique_constraints":10}},"tables":[{"table":"customers","schema":"dbo","columns":[{"name":"customer_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for each customer in the retail operations system.","glossary_terms":["RetailDomainGlossary.CustomerIdentifier"],"cardinality":100,"null_count":0,"data_range":{"min":"404","max":"503"},"data_category":"discrete","semantic_class":"customer_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"first_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"Stores the given name of a customer as a non-null Unicode string.","glossary_terms":[],"cardinality":100,"null_count":0,"data_range":{"min":"Customer1","max":"Customer99"},"data_category":"nominal","semantic_class":"given_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.6,"concept_evidence":["name token: first_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","table context: customers"],"concept_sources":["name","table_context","type"],"concept_alias_group":"first_name"},{"name":"last_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"The \"last_name\" column in the \"customers\" table stores the non-nullable family name of a customer as a case-insensitive Unicode string.","glossary_terms":["RetailDomainGlossary.Customer"],"cardinality":100,"null_count":0,"data_range":{"min":"LastName1 (updated)","max":"LastName99"},"data_category":"nominal","semantic_class":"family_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.6,"concept_evidence":["name token: last_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","table context: customers"],"concept_sources":["name","table_context","type"],"concept_alias_group":"last_name"},{"name":"email","type":"nvarchar(450)","nullable":true,"is_incremental":false,"column_description":"Stores the email address of the customer, allowing null values for cases where an email is not provided.","glossary_terms":[],"cardinality":100,"null_count":0,"data_range":{"min":"customer1@example.com","max":"customer99@example.com"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.email","concept_confidence":1.0,"concept_evidence":["name token: email","type hint: nvarchar(450)","legacy field classification: contact","value pattern: email","table context: customers","sensitive hint: pii_contact"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"email"},{"name":"phone","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"Stores the customer's phone number as an optional text field for contact purposes.","glossary_terms":[],"cardinality":100,"null_count":0,"data_range":{"min":"555-1001","max":"555-1100"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.phone","concept_confidence":1.0,"concept_evidence":["name token: phone","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: contact","value pattern: phone","table context: customers","sensitive hint: pii_contact"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"phone"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The `created_at` column records the non-nullable timestamp indicating when a customer record was initially created in the system.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":95,"null_count":0,"data_range":{"min":"2021-03-23 15:38:57.201565","max":"2026-02-26 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: customers"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"Tracks the timestamp of the most recent update to a customer record, ensuring accurate audit and change history.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":95,"null_count":0,"data_range":{"min":"2021-03-23 15:38:57.201565","max":"2026-03-26 08:52:49.252228"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: customers"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"}],"table_description":"The \"customers\" table stores information about retail customers, including their unique ID, name, contact details, and timestamps for record creation and updates.","glossary_terms":["RetailDomainGlossary.CustomerIdentifier"],"primary_keys":["customer_id"],"foreign_keys":[],"row_count":100,"field_classifications":{"customer_id":"identifier","first_name":"person_name","last_name":"person_name","email":"contact","phone":"contact","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{"email":"pii_contact","phone":"pii_contact"},"incremental_columns":["updated_at"],"join_candidates":[],"unit_summary":{"columns_with_units":0,"columns_without_units":7,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":false,"has_sensitive_fields":true,"row_count_projection_1y":126,"row_count_projection_2y":152,"row_count_projection_5y":232,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.email":1,"contact.person_name":2,"contact.phone":1,"identifier.foreign_key":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"findings":[{"column":"email","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 100 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"phone","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 100 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}},{"table":"employees","schema":"dbo","columns":[{"name":"employee_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for employees in the retail operations system.","glossary_terms":[],"cardinality":20,"null_count":0,"data_range":{"min":"64","max":"83"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Identifies the store where the employee is assigned, referencing the `store_id` column in the `stores` table.","glossary_terms":[],"cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"first_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"Stores the given name of an employee, represented as a non-null Unicode string.","glossary_terms":[],"cardinality":20,"null_count":0,"data_range":{"min":"Employee1","max":"Employee9"},"data_category":"nominal","semantic_class":"given_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: first_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"first_name"},{"name":"last_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"The \"last_name\" column in the \"employees\" table stores the non-nullable family name of each employee as a case-insensitive Unicode string.","glossary_terms":[],"cardinality":20,"null_count":0,"data_range":{"min":"LastName1","max":"LastName9"},"data_category":"nominal","semantic_class":"family_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: last_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"last_name"},{"name":"email","type":"nvarchar(450)","nullable":false,"is_incremental":false,"column_description":"The \"email\" column in the \"employees\" table stores the unique, non-null email address of each employee for contact purposes.","glossary_terms":[],"cardinality":20,"null_count":0,"data_range":{"min":"emp1@example.com","max":"emp9@example.com"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.email","concept_confidence":1.0,"concept_evidence":["name token: email","type hint: nvarchar(450)","legacy field classification: contact","value pattern: email","sensitive hint: pii_contact"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"email"},{"name":"role","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"Stores the job role or position of an employee within the organization, such as \"Cashier\" or \"Sales,\" as a non-null text value.","glossary_terms":[],"cardinality":4,"null_count":0,"data_range":{"min":"Cashier","max":"Stock"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"entity.type","concept_confidence":0.65,"concept_evidence":["name token: role","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","profile heuristic matched"],"concept_sources":["name","profile","type"],"concept_alias_group":"role"},{"name":"hire_date","type":"date","nullable":false,"is_incremental":false,"column_description":"The `hire_date` column in the `employees` table stores the non-nullable date an employee was hired, used for tracking employment start dates.","glossary_terms":[],"cardinality":20,"null_count":0,"data_range":{"min":"2021-05-03","max":"2025-01-26"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.date_only","concept_confidence":1.0,"concept_evidence":["name token: hire_date","type hint: date","legacy field classification: temporal","value pattern: date_only","table context: employees"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"hire_date"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The `created_at` column records the non-nullable timestamp indicating when an employee record was initially created in the system.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":20,"null_count":0,"data_range":{"min":"2021-05-03 15:38:57.201565","max":"2025-01-26 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: employees"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The `updated_at` column in the `employees` table stores the non-nullable timestamp of the most recent update to an employee record.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":20,"null_count":0,"data_range":{"min":"2021-05-03 15:38:57.201565","max":"2025-01-26 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: employees"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"}],"table_description":"The `employees` table stores detailed information about retail system employees, including their unique identifiers, store assignments, personal details, job roles, hire dates, and record timestamps.","glossary_terms":[],"primary_keys":["employee_id"],"foreign_keys":[{"column":"store_id","references":"stores.store_id"}],"row_count":20,"field_classifications":{"first_name":"person_name","last_name":"person_name","email":"contact","hire_date":"temporal","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{"email":"pii_contact"},"incremental_columns":["updated_at"],"join_candidates":[{"column":"store_id","target_table":"stores","target_column":"store_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":9,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":true,"row_count_projection_1y":35,"row_count_projection_2y":50,"row_count_projection_5y":96,"partition_columns_candidates":["hire_date","created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.email":1,"contact.person_name":2,"entity.type":1,"identifier.foreign_key":2,"temporal.created_at":1,"temporal.date_only":1,"temporal.updated_at":1},"low_confidence_columns":["first_name","last_name"]},"data_quality":{"findings":[{"column":"role","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 4 distinct value(s) ('Cashier', 'Manager', 'Sales', 'Stock') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Cashier","Manager","Sales","Stock"],"cardinality":4},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":"hire_date","check":"late_arriving_data","severity":"info","detail":"Minor arrival delay \u2014 max lag between 'hire_date' and 'created_at' is 15.7h (avg 15.7h, P95 15.7h).","recommendation":"Use 'created_at' as the watermark (preferred). If using 'hire_date', add a 1\u20132 day lookback buffer.","business_date_column":"hire_date","system_ts_column":"created_at","lag_stats":{"total_rows_compared":20,"min_lag_hours":15.65,"avg_lag_hours":15.65,"p95_lag_hours":15.65,"max_lag_hours":15.65,"max_lag_days":0.7,"rows_late_over_1d":0,"rows_late_over_7d":0},"recommended_lookback_days":2},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}},{"table":"inventory","schema":"dbo","columns":[{"name":"inventory_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for each inventory record in the system.","glossary_terms":[],"cardinality":100,"null_count":0,"data_range":{"min":"8","max":"107"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Represents the unique identifier of the store associated with the inventory record, referencing the `store_id` column in the `stores` table.","glossary_terms":[],"cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"product_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"References the unique identifier of a product from the products table, linking inventory records to specific products.","glossary_terms":[],"cardinality":47,"null_count":0,"data_range":{"min":"156","max":"205"},"data_category":"discrete","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"quantity_on_hand","type":"integer","nullable":false,"is_incremental":false,"column_description":"The `quantity_on_hand` column in the `inventory` table stores the current stock level of a product as a non-null integer.","glossary_terms":["RetailDomainGlossary.Inventory"],"cardinality":68,"null_count":0,"data_range":{"min":"2","max":"98"},"data_category":"discrete","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: quantity_on_hand","type hint: integer","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"quantity_on_hand"},{"name":"reorder_level","type":"integer","nullable":false,"is_incremental":false,"column_description":"Indicates the minimum quantity of a product in inventory that triggers a reorder, stored as a non-null integer.","glossary_terms":["RetailDomainGlossary.ReorderPoint"],"cardinality":20,"null_count":0,"data_range":{"min":"10","max":"29"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: integer","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"last_restocked_at","type":"datetime2","nullable":true,"is_incremental":false,"column_description":"The `last_restocked_at` column records the timestamp of the most recent restocking event for an inventory item, allowing null values if the item has not been restocked.","glossary_terms":["RetailDomainGlossary.Replenishment"],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":89,"null_count":0,"data_range":{"min":"2024-03-14 15:38:57.201565","max":"2026-03-07 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.event_time","concept_confidence":1.0,"concept_evidence":["name token: last_restocked_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: inventory"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"last_restocked_at"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The `created_at` column records the non-nullable timestamp indicating when the inventory record was initially created.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":91,"null_count":0,"data_range":{"min":"2024-03-05 15:38:57.201565","max":"2026-02-23 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: inventory"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incr</t>
         </is>
       </c>
     </row>
@@ -10336,7 +10432,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: inventory"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"stock_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"column_description":"Represents the monetary value of inventory stock, stored as a numeric value with up to 10 digits and 2 decimal places, and may be null.","glossary_terms":[],"cardinality":0,"null_count":100,"data_category":"continuous","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.0,"concept_evidence":["type hint: numeric(10,2)","ambiguous runner-up concept"],"concept_sources":["type"],"concept_alias_group":null},{"name":"stock_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Current stock unit label.","glossary_terms":[],"cardinality":0,"null_count":100,"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.15,"concept_evidence":["value pattern: quantity","ambiguous runner-up concept"],"concept_sources":["values"],"concept_alias_group":null}],"table_description":"Current stock levels with normalized stock unit representation.","glossary_terms":[],"primary_keys":["inventory_id"],"foreign_keys":[{"column":"product_id","references":"products.product_id"},{"column":"store_id","references":"stores.store_id"}],"row_count":100,"field_classifications":{"quantity_on_hand":"quantity","last_restocked_at":"temporal","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"product_id","target_table":"products","target_column":"product_id","confidence":"high"},{"column":"store_id","target_table":"stores","target_column":"store_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":10,"mixed_unit_groups":[],"unknown_unit_columns":["quantity_on_hand"]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":146,"row_count_projection_2y":193,"row_count_projection_5y":334,"partition_columns_candidates":["last_restocked_at","created_at","updated_at"],"classification_summary":{"concept_counts":{"identifier.foreign_key":3,"measure.quantity":1,"temporal.created_at":1,"temporal.event_time":1,"temporal.updated_at":1},"low_confidence_columns":["reorder_level","stock_unit"]},"data_quality":{"findings":[{"column":"last_restocked_at","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 100 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 3 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"last_restocked_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":3},{"column":"quantity_on_hand","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."}]}},{"table":"products","schema":"dbo","columns":[{"name":"product_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for each product in the retail operations system.","glossary_terms":[],"cardinality":50,"null_count":0,"data_range":{"min":"156","max":"205"},"data_category":"discrete","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"supplier_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"The `supplier_id` column in the `products` table is a non-nullable foreign key referencing the `supplier_id` column in the `suppliers` table, identifying the supplier associated with each product.","glossary_terms":[],"cardinality":10,"null_count":0,"data_range":{"min":"33","max":"42"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"sku","type":"nvarchar(450)","nullable":false,"is_incremental":false,"column_description":"Unique alphanumeric identifier for a product used for inventory and sales tracking, stored as a non-null nvarchar(450).","glossary_terms":[],"cardinality":50,"null_count":0,"data_range":{"min":"SKU-0001","max":"SKU-0050"},"data_category":"nominal","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.product_code","concept_confidence":0.7,"concept_evidence":["name token: sku","type hint: nvarchar(450)","semantic class hint: product_identifier"],"concept_sources":["name","profile","type"],"concept_alias_group":"sku"},{"name":"name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"The \"name\" column in the \"products\" table stores the non-nullable name of a product as a case-insensitive Unicode string.","glossary_terms":[],"cardinality":50,"null_count":0,"data_range":{"min":"Product 1","max":"Product 9"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"name"},{"name":"category","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"Indicates the product's category classification, such as \"Books,\" \"Clothing,\" or \"Electronics,\" stored as a non-null, case-insensitive text value.","glossary_terms":[],"cardinality":5,"null_count":0,"data_range":{"min":"Books","max":"Sports"},"data_category":"nominal","semantic_class":"category","unit_context":null,"concept_id":"entity.category","concept_confidence":0.8,"concept_evidence":["name token: category","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: categorical","profile heuristic matched"],"concept_sources":["name","profile","type"],"concept_alias_group":"category"},{"name":"unit_price","type":"numeric(10,2)","nullable":false,"is_incremental":false,"column_description":"Stores the retail price of a product as a non-null numeric value with up to 10 digits and 2 decimal places.","glossary_terms":[],"cardinality":50,"null_count":0,"data_range":{"min":"11.09","max":"490.43"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: price","type hint: numeric(10,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"price"},{"name":"cost_price","type":"numeric(10,2)","nullable":false,"is_incremental":false,"column_description":"Represents the numeric cost price of a product in the retail system, stored as a non-nullable currency amount with up to 10 digits and 2 decimal places.","glossary_terms":[],"cardinality":50,"null_count":0,"data_range":{"min":"5.55","max":"358.59"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: price","type hint: numeric(10,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"price"},{"name":"active","type":"bit","nullable":false,"is_incremental":false,"column_description":"Indicates whether a product is active and available for transactions, stored as a non-nullable boolean value.","glossary_terms":[],"cardinality":1,"null_count":0,"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.0,"concept_evidence":["profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile"],"concept_alias_group":null},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"Indicates the timestamp when the product record was initially created, stored as a non-nullable datetime value.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":50,"null_count":0,"data_range":{"min":"2021-03-20 15:38:57.201565","max":"2024-12-25 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: products"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The `updated_at` column stores the non-nullable timestamp of the most recent update to a product record in the `products` table.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":50,"null_count":0,"data_range":{"min":"2021-03-20 15:38:57.201565","max":"2024-12-25 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: products"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"weight_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Source weight unit (kg/lb) used for unit inference testing.","glossary_terms":[],"cardinality":0,"null_count":50,"data_category":"nominal","semantic_class":"mass","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":null,"concept_confidence":0.15,"concept_evidence":["value pattern: quantity","ambiguous runner-up concept"],"concept_sources":["values"],"concept_alias_group":null},{"name":"weight_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"column_description":"The `weight_value` column stores the weight of a product as a numeric value with up to 10 digits and 2 decimal places, and it is nullable.","glossary_terms":[],"cardinality":0,"null_count":50,"data_category":"continuous","semantic_class":"mass","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":null,"concept_confidence":0.0,"concept_evidence":["type hint: numeric(10,2)","ambiguous runner-up concept"],"concept_sources":["type"],"concept_alias_group":null},{"name":"length_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"column_description":"The \"length_value\" column stores the numeric length measurement of a product, allowing up to 10 digits with 2 decimal places, and is nullable.","glossary_terms":[],"cardinality":0,"null_count":50,"data_category":"continuous","semantic_class":"length","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":null,"concept_confidence":0.0,"concept_evidence":["type hint: numeric(10,2)","ambiguous runner-up concept"],"concept_sources":["type"],"concept_alias_group":null},{"name":"length_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Source length unit (cm/in) used for unit inference testing.","glossary_terms":[],"cardinality":0,"null_count":50,"data_category":"nominal","semantic_class":"length","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":null,"concept_confidence":0.15,"concept_evidence":["value pattern: quantity","ambiguous runner-up concept"],"concept_sources":["values"],"concept_alias_group":null},{"name":"product_description","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"Stores optional textual details about a product, such as features or specifications, with support for Unicode characters.","glossary_terms":[],"cardinality":0,"null_count":50,"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"primary_supplier_id","type":"bigint","nullable":true,"is_incremental":false,"column_description":"Primary supplier relationship used for join candidate detection.","glossary_terms":[],"cardinality":10,"null_count":0,"data_range":{"min":"33","max":"42"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"}],"table_description":"Master product catalog including physical units for analyzer unit-context testing.","glossary_terms":[],"primary_keys":["product_id"],"foreign_keys":[{"column":"primary_supplier_id","references":"suppliers.supplier_id"},{"column":"supplier_id","references":"suppliers.supplier_id"}],"row_count":50,"field_classifications":{"category":"categorical","unit_price":"pricing","cost_price":"pricing","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"primary_supplier_id","target_table":"suppliers","target_column":"supplier_id","confidence":"high"},{"column":"supplier_id","target_table":"suppliers","target_column":"supplier_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":16,"mixed_unit_groups":[],"unknown_unit_columns":["length_unit","length_value","weight_unit","weight_value"]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":68,"row_count_projection_2y":86,"row_count_projection_5y":141,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.person_name":1,"entity.category":1,"finance.currency_amount":2,"identifier.foreign_key":3,"identifier.product_code":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":["length_unit","name","product_description","weight_unit"]},"data_quality":{"findings":[{"column":"category","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 5 distinct value(s) ('Books', 'Clothing', 'Electronics', 'Home', 'Sports') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Books","Clothing","Electronics","Home","Sports"],"cardinality":5},{"column":"primary_supplier_id","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 50 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":"active","check":"delete_management","severity":"info","detail":"Active-flag column 'active' (boolean) detected \u2014 rows with active=false are logically deleted. Current distribution: True=50.","recommendation":"Filter on \"active\" = true for current records during ingestion.","delete_strategy":"soft_delete","soft_delete_column":"active","soft_delete_type":"active_flag","has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2},{"column":"weight_unit","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'mass' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"weight_value","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'mass' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"length_value","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'length' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"length_unit","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'length' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."}]}},{"table":"purchase_order_items","schema":"dbo","columns":[{"name":"po_item_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for each purchase order item record in the `purchase_order_items` table.","glossary_terms":[],"cardinality":246,"null_count":0,"data_range":{"min":"268","max":"513"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"po_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Links each purchase order item to its corresponding purchase order in the `purchase_orders` table via a non-null foreign key.","glossary_terms":[],"cardinality":125,"null_count":0,"data_range":{"min":"128","max":"252"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"product_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Identifier linking each purchase order item to a specific product in the products table.","glossary_terms":[],"cardinality":49,"null_count":0,"data_range":{"min":"156","max":"205"},"data_category":"discrete","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"quantity","type":"integer","nullable":false,"is_incremental":false,"column_description":"The `quantity` column in the `purchase_order_items` table stores the non-null integer value representing the number of units of a product included in a specific purchase order item.","glossary_terms":[],"cardinality":41,"null_count":0,"data_range":{"min":"10","max":"50"},"data_category":"discrete","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: quantity","type hint: integer","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"quantity"},{"name":"unit_cost","type":"numeric(10,2)","nullable":false,"is_incremental":false,"column_description":"The `unit_cost` column in the `purchase_order_items` table stores the non-null numeric cost per unit of a product in a purchase order, represented as a currency amount with up to 10 digits and 2 decimal places.","glossary_terms":[],"cardinality":49,"null_count":0,"data_range":{"min":"5.55","max":"358.59"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: unit_cost","type hint: numeric(10,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount","table context: purchase_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"unit_cost"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"Records the timestamp when a purchase order item entry is created, stored as a non-nullable datetime value.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":246,"null_count":0,"data_range":{"min":"2026-03-12 15:44:18.668789","max":"2026-03-12 15:45:45.174099"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: purchase_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The `updated_at` column in the `purchase_order_items` table stores the non-nullable timestamp of the most recent update to a purchase order item record.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":246,"null_count":0,"data_range":{"min":"2026-03-12 15:44:18.668794","max":"2026-03-12 15:45:45.174104"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: purchase_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"ordered_qty_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"column_description":"The `ordered_qty_value` column stores the numeric quantity value (up to two decimal places) of items ordered in a purchase order, which can be null.","glossary_terms":[],"cardinality":0,"null_count":246,"data_category":"continuous","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: ordered_qty","type hint: numeric(10,2)","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"ordered_qty"},{"name":"ordered_qty_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Ordered quantity unit (ea/box).","glossary_terms":[],"cardinality":0,"null_count":246,"data_category":"nominal","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: ordered_qty_unit","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity"],"concept_sources":["name","profile","values"],"concept_alias_group":"ordered_qty_unit"}],"table_description":"Line items with order quantities and explicit unit labels.","glossary_terms":[],"primary_keys":["po_item_id"],"foreign_keys":[{"column":"po_id","references":"purchase_orders.po_id"},{"column":"product_id","references":"products.product_id"}],"row_count":246,"field_classifications":{"quantity":"quantity","unit_cost":"pricing","created_at":"temporal","updated_at":"temporal","ordered_qty_value":"quantity","ordered_qty_unit":"quantity"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"po_id","target_table":"purchase_orders","target_column":"po_id","confidence":"high"},{"column":"product_id","target_table":"products","target_column":"product_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":9,"mixed_unit_groups":[],"unknown_unit_columns":["ordered_qty_unit","ordered_qty_value","quantity"]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":246,"row_count_projection_2y":246,"row_count_projection_5y":246,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"finance.currency_amount":1,"identifier.foreign_key":3,"measure.quantity":3,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"findings":[{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-</t>
+          <t>emental":true,"column_description":"Tracks the timestamp of the most recent update to an inventory record, ensuring accurate change history.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":89,"null_count":0,"data_range":{"min":"2024-03-14 15:38:57.201565","max":"2026-03-07 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: inventory"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"stock_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"column_description":"Represents the monetary value of inventory stock, stored as a numeric value with two decimal places, and may be null.","glossary_terms":["RetailDomainGlossary.Inventory"],"cardinality":0,"null_count":100,"data_category":"continuous","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.0,"concept_evidence":["type hint: numeric(10,2)","ambiguous runner-up concept"],"concept_sources":["type"],"concept_alias_group":null},{"name":"stock_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Current stock unit label.","glossary_terms":["RetailDomainGlossary.UnitOfMeasure"],"cardinality":0,"null_count":100,"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.15,"concept_evidence":["value pattern: quantity","ambiguous runner-up concept"],"concept_sources":["values"],"concept_alias_group":null}],"table_description":"Current stock levels with normalized stock unit representation.","glossary_terms":["RetailDomainGlossary.Inventory","RetailDomainGlossary.InventoryByProductAndLocation"],"primary_keys":["inventory_id"],"foreign_keys":[{"column":"product_id","references":"products.product_id"},{"column":"store_id","references":"stores.store_id"}],"row_count":100,"field_classifications":{"quantity_on_hand":"quantity","last_restocked_at":"temporal","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"product_id","target_table":"products","target_column":"product_id","confidence":"high"},{"column":"store_id","target_table":"stores","target_column":"store_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":10,"mixed_unit_groups":[],"unknown_unit_columns":["quantity_on_hand"]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":146,"row_count_projection_2y":193,"row_count_projection_5y":334,"partition_columns_candidates":["last_restocked_at","created_at","updated_at"],"classification_summary":{"concept_counts":{"identifier.foreign_key":3,"measure.quantity":1,"temporal.created_at":1,"temporal.event_time":1,"temporal.updated_at":1},"low_confidence_columns":["reorder_level","stock_unit"]},"data_quality":{"findings":[{"column":"last_restocked_at","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 100 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 3 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"last_restocked_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":3},{"column":"quantity_on_hand","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."}]}},{"table":"products","schema":"dbo","columns":[{"name":"product_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for each product in the retail system, serving as the primary key for the products table.","glossary_terms":["RetailDomainGlossary.Barcode"],"cardinality":50,"null_count":0,"data_range":{"min":"156","max":"205"},"data_category":"discrete","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"supplier_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"The `supplier_id` column in the `products` table is a non-nullable foreign key referencing the `supplier_id` column in the `suppliers` table, identifying the supplier associated with each product.","glossary_terms":["RetailDomainGlossary.SupplierCode"],"cardinality":10,"null_count":0,"data_range":{"min":"33","max":"42"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"sku","type":"nvarchar(450)","nullable":false,"is_incremental":false,"column_description":"Unique alphanumeric identifier for a product used for inventory and sales tracking.","glossary_terms":["RetailDomainGlossary.Product"],"cardinality":50,"null_count":0,"data_range":{"min":"SKU-0001","max":"SKU-0050"},"data_category":"nominal","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.product_code","concept_confidence":0.7,"concept_evidence":["name token: sku","type hint: nvarchar(450)","semantic class hint: product_identifier"],"concept_sources":["name","profile","type"],"concept_alias_group":"sku"},{"name":"name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"Stores the name of the product as a non-null, case-insensitive Unicode string.","glossary_terms":[],"cardinality":50,"null_count":0,"data_range":{"min":"Product 1","max":"Product 9"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"name"},{"name":"category","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"Indicates the product's category classification, such as \"Books,\" \"Clothing,\" or \"Electronics,\" stored as a non-nullable nvarchar value.","glossary_terms":["RetailDomainGlossary.ProductCategory"],"cardinality":5,"null_count":0,"data_range":{"min":"Books","max":"Sports"},"data_category":"nominal","semantic_class":"category","unit_context":null,"concept_id":"entity.category","concept_confidence":0.8,"concept_evidence":["name token: category","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: categorical","profile heuristic matched"],"concept_sources":["name","profile","type"],"concept_alias_group":"category"},{"name":"unit_price","type":"numeric(10,2)","nullable":false,"is_incremental":false,"column_description":"The `unit_price` column stores the non-null selling price of a product as a numeric value with up to 10 digits and 2 decimal places, representing a currency amount.","glossary_terms":["RetailDomainGlossary.SellingPrice"],"cardinality":50,"null_count":0,"data_range":{"min":"11.09","max":"490.43"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: price","type hint: numeric(10,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"price"},{"name":"cost_price","type":"numeric(10,2)","nullable":false,"is_incremental":false,"column_description":"The `cost_price` column stores the non-null numeric cost amount (up to 10 digits with 2 decimal places) representing the purchase price of a product in the retail system.","glossary_terms":["RetailDomainGlossary.CostPrice"],"cardinality":50,"null_count":0,"data_range":{"min":"5.55","max":"358.59"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: price","type hint: numeric(10,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"price"},{"name":"active","type":"bit","nullable":false,"is_incremental":false,"column_description":"Indicates whether a product is active and available for transactions, stored as a non-nullable boolean value.","glossary_terms":[],"cardinality":1,"null_count":0,"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.0,"concept_evidence":["profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile"],"concept_alias_group":null},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The `created_at` column stores the non-nullable timestamp indicating when a product record was initially created in the system.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":50,"null_count":0,"data_range":{"min":"2021-03-20 15:38:57.201565","max":"2024-12-25 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: products"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The `updated_at` column stores the non-nullable timestamp of the most recent update to a product record in the `products` table.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":50,"null_count":0,"data_range":{"min":"2021-03-20 15:38:57.201565","max":"2024-12-25 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: products"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"weight_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Source weight unit (kg/lb) used for unit inference testing.","glossary_terms":["RetailDomainGlossary.UnitOfMeasure"],"cardinality":0,"null_count":50,"data_category":"nominal","semantic_class":"mass","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":null,"concept_confidence":0.15,"concept_evidence":["value pattern: quantity","ambiguous runner-up concept"],"concept_sources":["values"],"concept_alias_group":null},{"name":"weight_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"column_description":"The `weight_value` column stores the weight of a product as a numeric value with up to 10 digits and 2 decimal places, and it is nullable.","glossary_terms":["RetailDomainGlossary.UnitOfMeasure"],"cardinality":0,"null_count":50,"data_category":"continuous","semantic_class":"mass","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":null,"concept_confidence":0.0,"concept_evidence":["type hint: numeric(10,2)","ambiguous runner-up concept"],"concept_sources":["type"],"concept_alias_group":null},{"name":"length_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"column_description":"Represents the length measurement of a product in numeric format, allowing null values.","glossary_terms":[],"cardinality":0,"null_count":50,"data_category":"continuous","semantic_class":"length","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":null,"concept_confidence":0.0,"concept_evidence":["type hint: numeric(10,2)","ambiguous runner-up concept"],"concept_sources":["type"],"concept_alias_group":null},{"name":"length_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Source length unit (cm/in) used for unit inference testing.","glossary_terms":["RetailDomainGlossary.UnitOfMeasure"],"cardinality":0,"null_count":50,"data_category":"nominal","semantic_class":"length","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":null,"concept_confidence":0.15,"concept_evidence":["value pattern: quantity","ambiguous runner-up concept"],"concept_sources":["values"],"concept_alias_group":null},{"name":"product_description","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"Stores optional textual details about a product, such as features or specifications.","glossary_terms":["RetailDomainGlossary.Product"],"cardinality":0,"null_count":50,"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"primary_supplier_id","type":"bigint","nullable":true,"is_incremental":false,"column_description":"Primary supplier relationship used for join candidate detection.","glossary_terms":["RetailDomainGlossary.SupplierPurchaseRelationship"],"cardinality":10,"null_count":0,"data_range":{"min":"33","max":"42"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"}],"table_description":"Master product catalog including physical units for analyzer unit-context testing.","glossary_terms":["RetailDomainGlossary.Inventory","RetailDomainGlossary.SupplierCode"],"primary_keys":["product_id"],"foreign_keys":[{"column":"primary_supplier_id","references":"suppliers.supplier_id"},{"column":"supplier_id","references":"suppliers.supplier_id"}],"row_count":50,"field_classifications":{"category":"categorical","unit_price":"pricing","cost_price":"pricing","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"primary_supplier_id","target_table":"suppliers","target_column":"supplier_id","confidence":"high"},{"column":"supplier_id","target_table":"suppliers","target_column":"supplier_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":16,"mixed_unit_groups":[],"unknown_unit_columns":["length_unit","length_value","weight_unit","weight_value"]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":68,"row_count_projection_2y":86,"row_count_projection_5y":141,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.person_name":1,"entity.category":1,"finance.currency_amount":2,"identifier.foreign_key":3,"identifier.product_code":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":["length_unit","name","product_description","weight_unit"]},"data_quality":{"findings":[{"column":"category","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 5 distinct value(s) ('Books', 'Clothing', 'Electronics', 'Home', 'Sports') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Books","Clothing","Electronics","Home","Sports"],"cardinality":5},{"column":"primary_supplier_id","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 50 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":"active","check":"delete_management","severity":"info","detail":"Active-flag column 'active' (boolean) detected \u2014 rows with active=false are logically deleted. Current distribution: True=50.","recommendation":"Filter on \"active\" = true for current records during ingestion.","delete_strategy":"soft_delete","soft_delete_column":"active","soft_delete_type":"active_flag","has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2},{"column":"weight_unit","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'mass' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"weight_value","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'mass' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"length_value","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'length' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"length_unit","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'length' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."}]}},{"table":"purchase_order_items","schema":"dbo","columns":[{"name":"po_item_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for each purchase order item record in the `purchase_order_items` table.","glossary_terms":["RetailDomainGlossary.OrderLine"],"cardinality":246,"null_count":0,"data_range":{"min":"268","max":"513"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"po_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Represents the unique identifier of the associated purchase order, linking purchase order items to their parent purchase order in the `purchase_orders` table.","glossary_terms":["RetailDomainGlossary.PurchaseOrder"],"cardinality":125,"null_count":0,"data_range":{"min":"128","max":"252"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"product_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Identifier linking each purchase order item to a specific product in the products table.","glossary_terms":["RetailDomainGlossary.ProductCategory"],"cardinality":49,"null_count":0,"data_range":{"min":"156","max":"205"},"data_category":"discrete","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"quantity","type":"integer","nullable":false,"is_incremental":false,"column_description":"The `quantity` column in the `purchase_order_items` table stores the non-null integer value representing the number of units of a product included in a specific purchase order item.","glossary_terms":["RetailDomainGlossary.UnitOfMeasure"],"cardinality":41,"null_count":0,"data_range":{"min":"10","max":"50"},"data_category":"discrete","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: quantity","type hint: integer","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"quantity"},{"name":"unit_cost","type":"numeric(10,2)","nullable":false,"is_incremental":false,"column_description":"Represents the per-unit cost of a product in a purchase order, stored as a non-null numeric value with up to 10 digits and 2 decimal places.","glossary_terms":["RetailDomainGlossary.CostPrice"],"cardinality":49,"null_count":0,"data_range":{"min":"5.55","max":"358.59"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: unit_cost","type hint: numeric(10,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount","table context: purchase_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"unit_cost"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The `created_at` column records the non-nullable timestamp indicating when each purchase order item record was created.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":246,"null_count":0,"data_range":{"min":"2026-03-12 15:44:18.668789","max":"2026-03-12 15:45:45.174099"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: purchase_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"Records the timestamp of the most recent update to a purchase order item, ensuring accurate tracking of modifications.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":246,"null_count":0,"data_range":{"min":"2026-03-12 15:44:18.668794","max":"2026-03-12 15:45:45.174104"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: purchase_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"ordered_qty_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"column_description":"The `ordered_qty_value` column stores the numeric quantity value (up to two decimal places) of items ordered in a purchase order, which can be null.","glossary_terms":["RetailDomainGlossary.PurchaseOrder"],"cardinality":0,"null_count":246,"data_category":"continuous","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: ordered_qty","type hint: numeric(10,2)","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"ordered_qty"},{"name":"ordered_qty_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Ordered quantity unit (ea/box).","glossary_terms":["RetailDomainGlossary.UnitOfMeasure"],"cardinality":0,"null_count":246,"data_category":"nominal","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: ordered_qty_unit","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity"],"concept_sources":["name","profile","values"],"concept_alias_group":"ordered_qty_unit"}],"table_description":"Line items with order quantities and explicit unit labels.","glossary_terms":["RetailDomainGlossary.OrderLine","RetailDomainGlossary.UnitOfMeasure","RetailDomainGlossary.CostPrice","RetailDomainGlossary.PurchaseOrder"],"primary_keys":["po_item_id"],"foreign_keys":[{"column":"po_id","references":"purchase_orders.po_id"},{"column":"product_id","references":"products.product_id"}],"row_count":246,"field_classifications":{"quantity":"quantity","unit_cost":"pricing","created_at":"temporal","updated_at":"temporal","ordered_qty_value":"quantity","ordered_qty_unit":"quantity"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"po_id","target_table":"purchase_orders","target_column":"po_id","confidence":"high"},{"column":"product_id","target_table":"products","target_column":"product_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":9,"mixed_unit_groups":[],"unknown_unit_columns":["ordered_qty_unit","ordered_qty_value","quantity"]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitiv</t>
         </is>
       </c>
     </row>
@@ -10346,7 +10442,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2},{"column":"quantity","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"ordered_qty_value","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"ordered_qty_unit","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."}]}},{"table":"purchase_orders","schema":"dbo","columns":[{"name":"po_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for purchase orders in the retail operations system.","glossary_terms":[],"cardinality":125,"null_count":0,"data_range":{"min":"128","max":"252"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"supplier_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"References the unique identifier of the supplier associated with a purchase order, linking to the `suppliers.supplier_id` column.","glossary_terms":[],"cardinality":10,"null_count":0,"data_range":{"min":"33","max":"42"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Identifies the store associated with the purchase order, referencing the `store_id` column in the `stores` table.","glossary_terms":[],"cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"status","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"Indicates the current state of a purchase order, such as 'Ordered' or 'Received', using predefined category values.","glossary_terms":[],"cardinality":3,"null_count":0,"data_range":{"min":"Ordered","max":"Received"},"data_category":"nominal","semantic_class":"category","unit_context":null,"concept_id":"entity.status","concept_confidence":1.0,"concept_evidence":["name token: statu","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: categorical","value pattern: status","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"statu"},{"name":"order_date","type":"date","nullable":false,"is_incremental":false,"column_description":"The `order_date` column in the `purchase_orders` table records the date a purchase order was placed and cannot be null.","glossary_terms":[],"cardinality":123,"null_count":0,"data_range":{"min":"2021-04-09","max":"2026-03-12"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.date_only","concept_confidence":1.0,"concept_evidence":["name token: order_date","type hint: date","legacy field classification: temporal","value pattern: date_only","table context: purchase_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"order_date"},{"name":"expected_date","type":"date","nullable":true,"is_incremental":false,"column_description":"The `expected_date` column in the `purchase_orders` table records the anticipated delivery date for a purchase order, allowing null values.","glossary_terms":[],"cardinality":123,"null_count":0,"data_range":{"min":"2021-04-27","max":"2026-03-31"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.date_only","concept_confidence":1.0,"concept_evidence":["name token: expected_date","type hint: date","legacy field classification: temporal","value pattern: date_only","table context: purchase_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"expected_date"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The `created_at` column records the timestamp when a purchase order record is initially created in the system and cannot be null.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":123,"null_count":0,"data_range":{"min":"2021-04-09 15:38:57.201565","max":"2026-03-12 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: purchase_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The `updated_at` column stores the non-null timestamp indicating the last modification date and time of a purchase order record.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":123,"null_count":0,"data_range":{"min":"2021-04-09 15:38:57.201565","max":"2026-03-12 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: purchase_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"approver_employee_id","type":"bigint","nullable":true,"is_incremental":false,"column_description":"Approver employee foreign key for procurement workflow.","glossary_terms":[],"cardinality":0,"null_count":125,"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"}],"table_description":"Procurement headers including approver employee relationship.","glossary_terms":[],"primary_keys":["po_id"],"foreign_keys":[{"column":"approver_employee_id","references":"employees.employee_id"},{"column":"store_id","references":"stores.store_id"},{"column":"supplier_id","references":"suppliers.supplier_id"}],"row_count":125,"field_classifications":{"status":"categorical","order_date":"temporal","expected_date":"temporal","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"approver_employee_id","target_table":"employees","target_column":"employee_id","confidence":"high"},{"column":"store_id","target_table":"stores","target_column":"store_id","confidence":"high"},{"column":"supplier_id","target_table":"suppliers","target_column":"supplier_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":9,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":155,"row_count_projection_2y":185,"row_count_projection_5y":276,"partition_columns_candidates":["order_date","expected_date","created_at","updated_at"],"classification_summary":{"concept_counts":{"entity.status":1,"identifier.foreign_key":4,"temporal.created_at":1,"temporal.date_only":2,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"findings":[{"column":"status","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 3 distinct value(s) ('Ordered', 'Pending', 'Received') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Ordered","Pending","Received"],"cardinality":3},{"column":"expected_date","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 125 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":"order_date","check":"late_arriving_data","severity":"info","detail":"Minor arrival delay \u2014 max lag between 'order_date' and 'created_at' is 15.7h (avg 15.7h, P95 15.7h).","recommendation":"Use 'created_at' as the watermark (preferred). If using 'order_date', add a 1\u20132 day lookback buffer.","business_date_column":"order_date","system_ts_column":"created_at","lag_stats":{"total_rows_compared":125,"min_lag_hours":15.65,"avg_lag_hours":15.65,"p95_lag_hours":15.65,"max_lag_hours":15.65,"max_lag_days":0.7,"rows_late_over_1d":0,"rows_late_over_7d":0},"recommended_lookback_days":2},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}},{"table":"sales_order_items","schema":"dbo","columns":[{"name":"sales_order_item_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for individual items within a sales order, serving as the primary key for the `sales_order_items` table.","glossary_terms":[],"cardinality":508,"null_count":0,"data_range":{"min":"497","max":"1004"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"sales_order_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Identifier linking each sales order item to its associated sales order in the `sales_orders` table.","glossary_terms":[],"cardinality":200,"null_count":0,"data_range":{"min":"375","max":"574"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"product_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"References the unique identifier of the product associated with a sales order item, linking to the `products.product_id` column.","glossary_terms":[],"cardinality":50,"null_count":0,"data_range":{"min":"156","max":"205"},"data_category":"discrete","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"quantity","type":"integer","nullable":false,"is_incremental":false,"column_description":"The \"quantity\" column in the \"sales_order_items\" table stores the non-null integer value representing the number of units of a product included in a specific sales order item.","glossary_terms":[],"cardinality":5,"null_count":0,"data_range":{"min":"1","max":"5"},"data_category":"discrete","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: quantity","type hint: integer","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"quantity"},{"name":"unit_price","type":"numeric(15,2)","nullable":false,"is_incremental":false,"column_description":"Represents the per-unit price of a product in a sales order item, stored as a non-null numeric value with up to 15 digits and 2 decimal places.","glossary_terms":[],"cardinality":50,"null_count":0,"data_range":{"min":"11.09","max":"490.43"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: price","type hint: numeric(15,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount","table context: sales_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"price"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The `created_at` column in the `sales_order_items` table stores the non-nullable timestamp indicating when a sales order item record was created.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":508,"null_count":0,"data_range":{"min":"2026-03-12 15:41:01.155388","max":"2026-03-12 15:43:38.264437"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: sales_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The `updated_at` column stores the non-nullable timestamp of the most recent update to a sales order item record for tracking modification history.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":508,"null_count":0,"data_range":{"min":"2026-03-12 15:41:01.155390","max":"2026-03-12 15:43:38.264447"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: sales_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"sold_qty_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"column_description":"Represents the numeric value of the quantity sold for a sales order item, allowing up to two decimal places and nullable for cases where the quantity is not recorded.","glossary_terms":[],"cardinality":0,"null_count":508,"data_category":"continuous","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: sold_qty","type hint: numeric(10,2)","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"sold_qty"},{"name":"sold_qty_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Sold quantity unit (ea/box).","glossary_terms":[],"cardinality":0,"null_count":508,"data_category":"nominal","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: sold_qty_unit","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity"],"concept_sources":["name","profile","values"],"concept_alias_group":"sold_qty_unit"}],"table_description":"Sales line items with sold quantity and explicit unit labels.","glossary_terms":[],"primary_keys":["sales_order_item_id"],"foreign_keys":[{"column":"product_id","references":"products.product_id"},{"column":"sales_order_id","references":"sales_orders.sales_order_id"}],"row_count":508,"field_classifications":{"quantity":"quantity","unit_price":"pricing","created_at":"temporal","updated_at":"temporal","sold_qty_value":"quantity","sold_qty_unit":"quantity"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"product_id","target_table":"products","target_column":"product_id","confidence":"high"},{"column":"sales_order_id","target_table":"sales_orders","target_column":"sales_order_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":9,"mixed_unit_groups":[],"unknown_unit_columns":["quantity","sold_qty_unit","sold_qty_value"]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":508,"row_count_projection_2y":508,"row_count_projection_5y":508,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"finance.currency_amount":1,"identifier.foreign_key":3,"measure.quantity":3,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"findings":[{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2},{"column":"quantity","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"sold_qty_value","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"sold_qty_unit","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."}]}},{"table":"sales_orders","schema":"dbo","columns":[{"name":"sales_order_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for each sales order in the system.","glossary_terms":[],"cardinality":200,"null_count":0,"data_range":{"min":"375","max":"574"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Identifies the store associated with a sales order, referencing the `store_id` column in the `stores` table.","glossary_terms":[],"cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"customer_id","type":"bigint","nullable":true,"is_incremental":false,"column_description":"Identifies the customer associated with a sales order, referencing the `customer_id` column in the `customers` table; nullable to accommodate orders without a registered customer.","glossary_terms":[],"cardinality":76,"null_count":0,"data_range":{"min":"404","max":"502"},"data_category":"discrete","semantic_class":"customer_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"employee_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Identifies the employee responsible for processing the sales order, referencing the `employees.employee_id` column.","glossary_terms":[],"cardinality":20,"null_count":0,"data_range":{"min":"64","max":"83"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"order_date","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The `order_date` column records the date and time when a sales order was placed, stored as a non-nullable `datetime2` value.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":191,"null_count":0,"data_range":{"min":"2021-03-14 15:38:57.201565","max":"2026-03-11 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.date_only","concept_confidence":0.9,"concept_evidence":["name token: order_date","type hint: datetime2","legacy field classification: temporal","table context: sales_orders","cross-table consensus: 2 similar columns"],"concept_sources":["cross_table_consensus","name","profile","table_context","type"],"concept_alias_group":"order_date"},{"name":"status","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"Indicates the current state of a sales order, such as 'Pending' or 'Completed', stored as a non-nullable text category.","glossary_terms":[],"cardinality":3,"null_count":0,"data_range":{"min":"Completed","max":"Shipped"},"data_category":"nominal","semantic_class":"category","unit_context":null,"concept_id":"entity.status","concept_confidence":1.0,"concept_evidence":["name token: statu","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: categorical","value pattern: status","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"statu"},{"name":"total_amount","type":"numeric(12,2)","nullable":false,"is_incremental":false,"column_description":"The `total_amount` column in the `sales_orders` table stores the non-nullable total monetary value of a sales order as a numeric value with up to 12 digits and 2 decimal places.","glossary_terms":[],"cardinality":200,"null_count":0,"data_range":{"min":"66.47","max":"998.76"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: amount","type hint: numeric(12,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount","table context: sales_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"amount"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The `created_at` column records the timestamp when a sales order entry was initially created, stored as a non-nullable `datetime2` value.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":191,"null_count":0,"data_range":{"min":"2021-03-14 15:38:57.201565","max":"2026-03-11 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: sales_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The `updated_at` column records the timestamp of the most recent update to a sales order, ensuring accurate tracking of modifications, and it is mandatory.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":191,"null_count":0,"data_range":{"min":"2021-03-14 15:38:57.201565","max":"2026-03-11 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: sales_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"sales_rep_employee_id","type":"bigint","nullable":true,"is_incremental":false,"column_description":"Sales representative foreign key for order ownership.","glossary_terms":[],"cardinality":0,"null_count":200,"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"}],"table_description":"Sales headers including assigned sales representative relationship.","glossary_terms":</t>
+          <t>e_fields":false,"row_count_projection_1y":246,"row_count_projection_2y":246,"row_count_projection_5y":246,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"finance.currency_amount":1,"identifier.foreign_key":3,"measure.quantity":3,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"findings":[{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2},{"column":"quantity","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"ordered_qty_value","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"ordered_qty_unit","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."}]}},{"table":"purchase_orders","schema":"dbo","columns":[{"name":"po_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for purchase orders in the system.","glossary_terms":["RetailDomainGlossary.PurchaseOrder"],"cardinality":125,"null_count":0,"data_range":{"min":"128","max":"252"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"supplier_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Identifies the supplier associated with a purchase order, referencing the `supplier_id` column in the `suppliers` table.","glossary_terms":["RetailDomainGlossary.SupplierCode"],"cardinality":10,"null_count":0,"data_range":{"min":"33","max":"42"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Identifies the store associated with the purchase order, referencing the `store_id` column in the `stores` table.","glossary_terms":[],"cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"status","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"Indicates the current state of a purchase order (e.g., \"Ordered,\" \"Received\") as a non-null categorical value.","glossary_terms":["RetailDomainGlossary.OrderStatus"],"cardinality":3,"null_count":0,"data_range":{"min":"Ordered","max":"Received"},"data_category":"nominal","semantic_class":"category","unit_context":null,"concept_id":"entity.status","concept_confidence":1.0,"concept_evidence":["name token: statu","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: categorical","value pattern: status","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"statu"},{"name":"order_date","type":"date","nullable":false,"is_incremental":false,"column_description":"The `order_date` column in the `purchase_orders` table records the date a purchase order was placed, is mandatory, and uses the `date` data type.","glossary_terms":[],"cardinality":123,"null_count":0,"data_range":{"min":"2021-04-09","max":"2026-03-12"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.date_only","concept_confidence":1.0,"concept_evidence":["name token: order_date","type hint: date","legacy field classification: temporal","value pattern: date_only","table context: purchase_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"order_date"},{"name":"expected_date","type":"date","nullable":true,"is_incremental":false,"column_description":"The `expected_date` column in the `purchase_orders` table records the anticipated delivery date for a purchase order, allowing null values.","glossary_terms":["RetailDomainGlossary.OrderDeliveryRelationship"],"cardinality":123,"null_count":0,"data_range":{"min":"2021-04-27","max":"2026-03-31"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.date_only","concept_confidence":1.0,"concept_evidence":["name token: expected_date","type hint: date","legacy field classification: temporal","value pattern: date_only","table context: purchase_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"expected_date"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The `created_at` column stores the non-nullable timestamp indicating when a purchase order record was initially created in the system.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":123,"null_count":0,"data_range":{"min":"2021-04-09 15:38:57.201565","max":"2026-03-12 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: purchase_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The `updated_at` column stores the non-nullable timestamp of the most recent update to a purchase order record.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":123,"null_count":0,"data_range":{"min":"2021-04-09 15:38:57.201565","max":"2026-03-12 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: purchase_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"approver_employee_id","type":"bigint","nullable":true,"is_incremental":false,"column_description":"Approver employee foreign key for procurement workflow.","glossary_terms":[],"cardinality":0,"null_count":125,"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"}],"table_description":"Procurement headers including approver employee relationship.","glossary_terms":["RetailDomainGlossary.PurchaseOrder","RetailDomainGlossary.OrderStatus"],"primary_keys":["po_id"],"foreign_keys":[{"column":"approver_employee_id","references":"employees.employee_id"},{"column":"store_id","references":"stores.store_id"},{"column":"supplier_id","references":"suppliers.supplier_id"}],"row_count":125,"field_classifications":{"status":"categorical","order_date":"temporal","expected_date":"temporal","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"approver_employee_id","target_table":"employees","target_column":"employee_id","confidence":"high"},{"column":"store_id","target_table":"stores","target_column":"store_id","confidence":"high"},{"column":"supplier_id","target_table":"suppliers","target_column":"supplier_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":9,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":155,"row_count_projection_2y":185,"row_count_projection_5y":276,"partition_columns_candidates":["order_date","expected_date","created_at","updated_at"],"classification_summary":{"concept_counts":{"entity.status":1,"identifier.foreign_key":4,"temporal.created_at":1,"temporal.date_only":2,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"findings":[{"column":"status","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 3 distinct value(s) ('Ordered', 'Pending', 'Received') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Ordered","Pending","Received"],"cardinality":3},{"column":"expected_date","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 125 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":"order_date","check":"late_arriving_data","severity":"info","detail":"Minor arrival delay \u2014 max lag between 'order_date' and 'created_at' is 15.7h (avg 15.7h, P95 15.7h).","recommendation":"Use 'created_at' as the watermark (preferred). If using 'order_date', add a 1\u20132 day lookback buffer.","business_date_column":"order_date","system_ts_column":"created_at","lag_stats":{"total_rows_compared":125,"min_lag_hours":15.65,"avg_lag_hours":15.65,"p95_lag_hours":15.65,"max_lag_hours":15.65,"max_lag_days":0.7,"rows_late_over_1d":0,"rows_late_over_7d":0},"recommended_lookback_days":2},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}},{"table":"sales_order_items","schema":"dbo","columns":[{"name":"sales_order_item_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for each sales order item in the sales_order_items table.","glossary_terms":["RetailDomainGlossary.OrderLine"],"cardinality":508,"null_count":0,"data_range":{"min":"497","max":"1004"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"sales_order_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Identifier linking each sales order item to its associated sales order in the `sales_orders` table.","glossary_terms":["RetailDomainGlossary.SalesOrder"],"cardinality":200,"null_count":0,"data_range":{"min":"375","max":"574"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"product_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Identifier for the product associated with the sales order item, referencing the primary key in the products table.","glossary_terms":["RetailDomainGlossary.ProductCategory"],"cardinality":50,"null_count":0,"data_range":{"min":"156","max":"205"},"data_category":"discrete","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"quantity","type":"integer","nullable":false,"is_incremental":false,"column_description":"The \"quantity\" column in the \"sales_order_items\" table stores the number of units of a product included in a sales order item, represented as a non-null integer.","glossary_terms":["RetailDomainGlossary.OrderLine"],"cardinality":5,"null_count":0,"data_range":{"min":"1","max":"5"},"data_category":"discrete","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: quantity","type hint: integer","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"quantity"},{"name":"unit_price","type":"numeric(15,2)","nullable":false,"is_incremental":false,"column_description":"The `unit_price` column in the `sales_order_items` table stores the per-unit selling price of a product in the sales order as a non-null numeric value with two decimal places.","glossary_terms":["RetailDomainGlossary.SellingPrice"],"cardinality":50,"null_count":0,"data_range":{"min":"11.09","max":"490.43"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: price","type hint: numeric(15,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount","table context: sales_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"price"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"Records the timestamp when a sales order item entry is created, ensuring accurate tracking of creation events.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":508,"null_count":0,"data_range":{"min":"2026-03-12 15:41:01.155388","max":"2026-03-12 15:43:38.264437"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: sales_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The `updated_at` column in the `sales_order_items` table stores the non-nullable timestamp of the most recent update to a sales order item record.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":508,"null_count":0,"data_range":{"min":"2026-03-12 15:41:01.155390","max":"2026-03-12 15:43:38.264447"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: sales_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"sold_qty_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"column_description":"The `sold_qty_value` column stores the numeric value representing the quantity of a product sold in a sales order item, allowing up to two decimal places, and can be null.","glossary_terms":["RetailDomainGlossary.OrderLine"],"cardinality":0,"null_count":508,"data_category":"continuous","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: sold_qty","type hint: numeric(10,2)","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"sold_qty"},{"name":"sold_qty_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Sold quantity unit (ea/box).","glossary_terms":["RetailDomainGlossary.UnitOfMeasure"],"cardinality":0,"null_count":508,"data_category":"nominal","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: sold_qty_unit","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity"],"concept_sources":["name","profile","values"],"concept_alias_group":"sold_qty_unit"}],"table_description":"Sales line items with sold quantity and explicit unit labels.","glossary_terms":["RetailDomainGlossary.OrderLine","RetailDomainGlossary.SalesOrder","RetailDomainGlossary.UnitOfMeasure"],"primary_keys":["sales_order_item_id"],"foreign_keys":[{"column":"product_id","references":"products.product_id"},{"column":"sales_order_id","references":"sales_orders.sales_order_id"}],"row_count":508,"field_classifications":{"quantity":"quantity","unit_price":"pricing","created_at":"temporal","updated_at":"temporal","sold_qty_value":"quantity","sold_qty_unit":"quantity"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"product_id","target_table":"products","target_column":"product_id","confidence":"high"},{"column":"sales_order_id","target_table":"sales_orders","target_column":"sales_order_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":9,"mixed_unit_groups":[],"unknown_unit_columns":["quantity","sold_qty_unit","sold_qty_value"]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":508,"row_count_projection_2y":508,"row_count_projection_5y":508,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"finance.currency_amount":1,"identifier.foreign_key":3,"measure.quantity":3,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"findings":[{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2},{"column":"quantity","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"sold_qty_value","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"sold_qty_unit","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."}]}},{"table":"sales_orders","schema":"dbo","columns":[{"name":"sales_order_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for each sales order in the system, serving as the primary key for the sales_orders table.","glossary_terms":["RetailDomainGlossary.SalesOrder"],"cardinality":200,"null_count":0,"data_range":{"min":"375","max":"574"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Identifies the store associated with a sales order, referencing the `store_id` column in the `stores` table.","glossary_terms":["RetailDomainGlossary.SalesChannel"],"cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"customer_id","type":"bigint","nullable":true,"is_incremental":false,"column_description":"Represents the identifier of the customer associated with a sales order, referencing the `customer_id` column in the `customers` table, and may be null if no customer is linked.","glossary_terms":["RetailDomainGlossary.CustomerIdentifier"],"cardinality":76,"null_count":0,"data_range":{"min":"404","max":"502"},"data_category":"discrete","semantic_class":"customer_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"employee_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Represents the unique identifier of the employee associated with the sales order, referencing the `employees.employee_id` column.","glossary_terms":[],"cardinality":20,"null_count":0,"data_range":{"min":"64","max":"83"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"order_date","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The `order_date` column records the date and time when a sales order was placed, stored as a non-nullable `datetime2` value.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":191,"null_count":0,"data_range":{"min":"2021-03-14 15:38:57.201565","max":"2026-03-11 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.date_only","concept_confidence":0.9,"concept_evidence":["name token: order_date","type hint: datetime2","legacy field classification: temporal","table context: sales_orders","cross-table consensus: 2 similar columns"],"concept_sources":["cross_table_consensus","name","profile","table_context","type"],"concept_alias_group":"order_date"},{"name":"status","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"Indicates the current state of a sales order, such as 'Pending' or 'Completed', stored as a non-nullable text category.","glossary_terms":["RetailDomainGlossary.OrderStatus"],"cardinality":3,"null_count":0,"data_range":{"min":"Completed","max":"Shipped"},"data_category":"nominal","semantic_class":"category","unit_context":null,"concept_id":"entity.status","concept_confidence":1.0,"concept_evidence":["name token: statu","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: categorical","value pattern: status","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"statu"},{"name":"total_amount","type":"numeric(12,2)","nullable":false,"is_incremental":false,"column_description":"The `total_amount` column in the `sales_orders` table stores the non-nullable total monetary value of a sales order as a numeric value with up to 12 digits and 2 decimal places.","glossary_terms":["RetailDomainGlossary.SalesOrder"],"cardinality":200,"null_count":0,"data_range":{"min":"66.47","max":"998.76"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: amount","type hint: numeric(12,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount","table context: sales_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"amount"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The `created_at` column records the timestamp when a sales order record is initially created, stored as a non-nullable `datetime2` value.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardina</t>
         </is>
       </c>
     </row>
@@ -10356,7 +10452,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[],"primary_keys":["sales_order_id"],"foreign_keys":[{"column":"customer_id","references":"customers.customer_id"},{"column":"employee_id","references":"employees.employee_id"},{"column":"sales_rep_employee_id","references":"employees.employee_id"},{"column":"store_id","references":"stores.store_id"}],"row_count":200,"field_classifications":{"customer_id":"identifier","order_date":"temporal","status":"categorical","total_amount":"pricing","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"customer_id","target_table":"customers","target_column":"customer_id","confidence":"high"},{"column":"employee_id","target_table":"employees","target_column":"employee_id","confidence":"high"},{"column":"sales_rep_employee_id","target_table":"employees","target_column":"employee_id","confidence":"high"},{"column":"store_id","target_table":"stores","target_column":"store_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":10,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":242,"row_count_projection_2y":284,"row_count_projection_5y":412,"partition_columns_candidates":["order_date","created_at","updated_at"],"classification_summary":{"concept_counts":{"entity.status":1,"finance.currency_amount":1,"identifier.foreign_key":5,"temporal.created_at":1,"temporal.date_only":1,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"findings":[{"column":"status","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 3 distinct value(s) ('Completed', 'Pending', 'Shipped') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Completed","Pending","Shipped"],"cardinality":3},{"column":"customer_id","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 200 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":"order_date","check":"late_arriving_data","severity":"info","detail":"Data arrives promptly \u2014 max lag between 'order_date' and 'created_at' is 0.0h. Standard watermarking on 'created_at' is safe.","recommendation":"Use 'created_at' as the incremental watermark. No special lookback window needed.","business_date_column":"order_date","system_ts_column":"created_at","lag_stats":{"total_rows_compared":200,"min_lag_hours":0.0,"avg_lag_hours":0.0,"p95_lag_hours":0.0,"max_lag_hours":0.0,"max_lag_days":0.0,"rows_late_over_1d":0,"rows_late_over_7d":0},"recommended_lookback_days":1},{"column":null,"check":"timezone","severity":"info","detail":"All 3 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"order_date","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":3}]}},{"table":"stores","schema":"dbo","columns":[{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for each store in the retail operations system.","glossary_terms":[],"cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"The \"name\" column in the \"stores\" table is a non-nullable nvarchar field storing the name of each retail store.","glossary_terms":[],"cardinality":5,"null_count":0,"data_range":{"min":"Airport Shop","max":"Suburb Store"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"name"},{"name":"code","type":"nvarchar(450)","nullable":false,"is_incremental":false,"column_description":"Unique identifier for a store, typically represented as an alphanumeric code.","glossary_terms":[],"cardinality":5,"null_count":0,"data_range":{"min":"AIR","max":"SUB"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: nvarchar(450)","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"address","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"The \"address\" column in the \"stores\" table stores the street address of a retail store location as a nullable Unicode string.","glossary_terms":[],"cardinality":5,"null_count":0,"data_range":{"min":"1 Main St","max":"5 Main St"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.address","concept_confidence":0.55,"concept_evidence":["name token: address","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"address"},{"name":"city","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"The \"city\" column in the \"stores\" table stores the name of the city where a store is located, allowing null values.","glossary_terms":[],"cardinality":3,"null_count":0,"data_range":{"min":"Cork","max":"Limerick"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"state","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"Indicates the state or province where the store is located, stored as a nullable text field.","glossary_terms":[],"cardinality":3,"null_count":0,"data_range":{"min":"Connacht","max":"Munster"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"postal_code","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"The \"postal_code\" column in the \"stores\" table stores the postal or ZIP code of a store location as a nullable, case-insensitive string.","glossary_terms":[],"cardinality":5,"null_count":0,"data_range":{"min":"10000","max":"10004"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.address","concept_confidence":0.55,"concept_evidence":["name token: postal_code","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"postal_code"},{"name":"phone","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"Stores.phone is an optional nvarchar column storing the contact phone number for a store location.","glossary_terms":[],"cardinality":5,"null_count":0,"data_range":{"min":"555-3000","max":"555-3004"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.phone","concept_confidence":1.0,"concept_evidence":["name token: phone","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: contact","value pattern: phone","sensitive hint: pii_contact"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"phone"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The `created_at` column records the non-nullable timestamp indicating when a store record was initially created in the system.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":5,"null_count":0,"data_range":{"min":"2021-07-26 15:38:57.201565","max":"2025-01-31 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: stores"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The `updated_at` column records the timestamp of the most recent update to a store's record and cannot be null.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":5,"null_count":0,"data_range":{"min":"2021-07-26 15:38:57.201565","max":"2025-01-31 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: stores"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"}],"table_description":"The \"stores\" table contains details about retail store locations, including unique identifiers, names, addresses, contact information, and timestamps for record creation and updates.","glossary_terms":[],"primary_keys":["store_id"],"foreign_keys":[],"row_count":5,"field_classifications":{"phone":"contact","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{"address":"pii_address","postal_code":"pii_address","phone":"pii_contact"},"incremental_columns":["updated_at"],"join_candidates":[],"unit_summary":{"columns_with_units":0,"columns_without_units":10,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":false,"has_sensitive_fields":true,"row_count_projection_1y":17,"row_count_projection_2y":29,"row_count_projection_5y":65,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.address":2,"contact.person_name":1,"contact.phone":1,"identifier.foreign_key":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":["address","city","code","name","postal_code","state"]},"data_quality":{"findings":[{"column":"city","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 3 distinct value(s) ('Cork', 'Galway', 'Limerick') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Cork","Galway","Limerick"],"cardinality":3},{"column":"state","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 3 distinct value(s) ('Connacht', 'Leinster', 'Munster') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Connacht","Leinster","Munster"],"cardinality":3},{"column":"postal_code","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 5 distinct value(s) ('10000', '10001', '10002', '10003', '10004') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["10000","10001","10002","10003","10004"],"cardinality":5},{"column":"address","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"city","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"state","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"postal_code","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"phone","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}},{"table":"suppliers","schema":"dbo","columns":[{"name":"supplier_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for each supplier, serving as the primary key in the suppliers table.","glossary_terms":[],"cardinality":10,"null_count":0,"data_range":{"min":"33","max":"42"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"The \"name\" column in the \"suppliers\" table is a non-nullable nvarchar field intended to store the name of the supplier, though sample data indicates it is currently unused.","glossary_terms":[],"cardinality":10,"null_count":0,"data_range":{"min":"Supplier 1","max":"Supplier 9"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"name"},{"name":"contact_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"The `contact_name` column in the `suppliers` table stores the name of the primary contact person for a supplier, allowing null values.","glossary_terms":[],"cardinality":0,"null_count":10,"data_category":"nominal","semantic_class":"person_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: contact_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"contact_name"},{"name":"email","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"The \"email\" column in the \"suppliers\" table stores the email address of a supplier as a nullable nvarchar value for contact purposes.","glossary_terms":[],"cardinality":10,"null_count":0,"data_range":{"min":"supplier1@example.com","max":"supplier9@example.com"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.email","concept_confidence":1.0,"concept_evidence":["name token: email","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: contact","value pattern: email","sensitive hint: pii_contact"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"email"},{"name":"phone","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"The \"phone\" column in the \"suppliers\" table stores the supplier's contact phone number as a nullable string.","glossary_terms":[],"cardinality":10,"null_count":0,"data_range":{"min":"555-2001","max":"555-2010"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.phone","concept_confidence":1.0,"concept_evidence":["name token: phone","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: contact","value pattern: phone","sensitive hint: pii_contact"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"phone"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The `created_at` column records the non-nullable timestamp indicating when a supplier record was initially created in the system.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":10,"null_count":0,"data_range":{"min":"2021-03-22 15:38:57.201565","max":"2024-02-25 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: suppliers"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The `updated_at` column stores the non-nullable timestamp of the most recent update to a supplier record.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":10,"null_count":0,"data_range":{"min":"2021-03-22 15:38:57.201565","max":"2024-02-25 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: suppliers"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"}],"table_description":"The \"suppliers\" table stores information about suppliers, including their unique identifier, name, contact details, and timestamps for record creation and updates.","glossary_terms":[],"primary_keys":["supplier_id"],"foreign_keys":[],"row_count":10,"field_classifications":{"contact_name":"person_name","email":"contact","phone":"contact","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{"email":"pii_contact","phone":"pii_contact"},"incremental_columns":["updated_at"],"join_candidates":[],"unit_summary":{"columns_with_units":0,"columns_without_units":7,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":false,"has_sensitive_fields":true,"row_count_projection_1y":22,"row_count_projection_2y":35,"row_count_projection_5y":74,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.email":1,"contact.person_name":2,"contact.phone":1,"identifier.foreign_key":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":["contact_name","name"]},"data_quality":{"findings":[{"column":"email","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 10 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"phone","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 10 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}}]}</t>
+          <t>lity":191,"null_count":0,"data_range":{"min":"2021-03-14 15:38:57.201565","max":"2026-03-11 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: sales_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The `updated_at` column records the timestamp of the most recent update to a sales order, stored as a non-nullable datetime2 value.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":191,"null_count":0,"data_range":{"min":"2021-03-14 15:38:57.201565","max":"2026-03-11 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: sales_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"sales_rep_employee_id","type":"bigint","nullable":true,"is_incremental":false,"column_description":"Sales representative foreign key for order ownership.","glossary_terms":[],"cardinality":0,"null_count":200,"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"}],"table_description":"Sales headers including assigned sales representative relationship.","glossary_terms":["RetailDomainGlossary.SalesOrder","RetailDomainGlossary.CustomerIdentifier","RetailDomainGlossary.OrderStatus"],"primary_keys":["sales_order_id"],"foreign_keys":[{"column":"customer_id","references":"customers.customer_id"},{"column":"employee_id","references":"employees.employee_id"},{"column":"sales_rep_employee_id","references":"employees.employee_id"},{"column":"store_id","references":"stores.store_id"}],"row_count":200,"field_classifications":{"customer_id":"identifier","order_date":"temporal","status":"categorical","total_amount":"pricing","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"customer_id","target_table":"customers","target_column":"customer_id","confidence":"high"},{"column":"employee_id","target_table":"employees","target_column":"employee_id","confidence":"high"},{"column":"sales_rep_employee_id","target_table":"employees","target_column":"employee_id","confidence":"high"},{"column":"store_id","target_table":"stores","target_column":"store_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":10,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":242,"row_count_projection_2y":284,"row_count_projection_5y":412,"partition_columns_candidates":["order_date","created_at","updated_at"],"classification_summary":{"concept_counts":{"entity.status":1,"finance.currency_amount":1,"identifier.foreign_key":5,"temporal.created_at":1,"temporal.date_only":1,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"findings":[{"column":"status","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 3 distinct value(s) ('Completed', 'Pending', 'Shipped') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Completed","Pending","Shipped"],"cardinality":3},{"column":"customer_id","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 200 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":"order_date","check":"late_arriving_data","severity":"info","detail":"Data arrives promptly \u2014 max lag between 'order_date' and 'created_at' is 0.0h. Standard watermarking on 'created_at' is safe.","recommendation":"Use 'created_at' as the incremental watermark. No special lookback window needed.","business_date_column":"order_date","system_ts_column":"created_at","lag_stats":{"total_rows_compared":200,"min_lag_hours":0.0,"avg_lag_hours":0.0,"p95_lag_hours":0.0,"max_lag_hours":0.0,"max_lag_days":0.0,"rows_late_over_1d":0,"rows_late_over_7d":0},"recommended_lookback_days":1},{"column":null,"check":"timezone","severity":"info","detail":"All 3 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"order_date","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":3}]}},{"table":"stores","schema":"dbo","columns":[{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for each store in the retail operations system.","glossary_terms":["RetailDomainGlossary.StoreCode"],"cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"The \"name\" column in the \"stores\" table is a non-nullable nvarchar field storing the name of a retail store.","glossary_terms":[],"cardinality":5,"null_count":0,"data_range":{"min":"Airport Shop","max":"Suburb Store"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"name"},{"name":"code","type":"nvarchar(450)","nullable":false,"is_incremental":false,"column_description":"Unique alphanumeric identifier for a store, used for internal reference and operations.","glossary_terms":["RetailDomainGlossary.StoreCode"],"cardinality":5,"null_count":0,"data_range":{"min":"AIR","max":"SUB"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: nvarchar(450)","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"address","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"The \"address\" column in the \"stores\" table stores the street address of a retail store location as a nullable Unicode string.","glossary_terms":[],"cardinality":5,"null_count":0,"data_range":{"min":"1 Main St","max":"5 Main St"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.address","concept_confidence":0.55,"concept_evidence":["name token: address","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"address"},{"name":"city","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"The \"city\" column in the \"stores\" table stores the name of the city where a store is located, allowing null values.","glossary_terms":[],"cardinality":3,"null_count":0,"data_range":{"min":"Cork","max":"Limerick"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"state","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"The \"state\" column in the \"stores\" table stores the name of the state or province where a store is located, allowing null values.","glossary_terms":[],"cardinality":3,"null_count":0,"data_range":{"min":"Connacht","max":"Munster"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"postal_code","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"The \"postal_code\" column in the \"stores\" table stores the postal or ZIP code of a store location as a nullable string.","glossary_terms":[],"cardinality":5,"null_count":0,"data_range":{"min":"10000","max":"10004"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.address","concept_confidence":0.55,"concept_evidence":["name token: postal_code","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"postal_code"},{"name":"phone","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"The \"phone\" column in the \"stores\" table stores the contact phone number of a store as a nullable nvarchar value.","glossary_terms":[],"cardinality":5,"null_count":0,"data_range":{"min":"555-3000","max":"555-3004"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.phone","concept_confidence":1.0,"concept_evidence":["name token: phone","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: contact","value pattern: phone","sensitive hint: pii_contact"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"phone"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The `created_at` column stores the non-nullable timestamp indicating when a store record was initially created in the system.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":5,"null_count":0,"data_range":{"min":"2021-07-26 15:38:57.201565","max":"2025-01-31 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: stores"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The `updated_at` column records the timestamp of the most recent update to a store's record and cannot be null.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":5,"null_count":0,"data_range":{"min":"2021-07-26 15:38:57.201565","max":"2025-01-31 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: stores"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"}],"table_description":"The \"stores\" table stores information about retail store locations, including unique identifiers, names, codes, addresses, contact details, and timestamps for record creation and updates.","glossary_terms":["RetailDomainGlossary.StoreCode"],"primary_keys":["store_id"],"foreign_keys":[],"row_count":5,"field_classifications":{"phone":"contact","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{"address":"pii_address","postal_code":"pii_address","phone":"pii_contact"},"incremental_columns":["updated_at"],"join_candidates":[],"unit_summary":{"columns_with_units":0,"columns_without_units":10,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":false,"has_sensitive_fields":true,"row_count_projection_1y":17,"row_count_projection_2y":29,"row_count_projection_5y":65,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.address":2,"contact.person_name":1,"contact.phone":1,"identifier.foreign_key":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":["address","city","code","name","postal_code","state"]},"data_quality":{"findings":[{"column":"city","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 3 distinct value(s) ('Cork', 'Galway', 'Limerick') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Cork","Galway","Limerick"],"cardinality":3},{"column":"state","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 3 distinct value(s) ('Connacht', 'Leinster', 'Munster') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Connacht","Leinster","Munster"],"cardinality":3},{"column":"postal_code","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 5 distinct value(s) ('10000', '10001', '10002', '10003', '10004') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["10000","10001","10002","10003","10004"],"cardinality":5},{"column":"address","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"city","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"state","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"postal_code","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"phone","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}},{"table":"suppliers","schema":"dbo","columns":[{"name":"supplier_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for each supplier, serving as the primary key in the suppliers table.","glossary_terms":["RetailDomainGlossary.SupplierCode"],"cardinality":10,"null_count":0,"data_range":{"min":"33","max":"42"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"The \"name\" column in the \"suppliers\" table is a non-nullable nvarchar field intended to store the name of the supplier, though sample data indicates it is currently unused.","glossary_terms":[],"cardinality":10,"null_count":0,"data_range":{"min":"Supplier 1","max":"Supplier 9"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"name"},{"name":"contact_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"Stores the name of the primary contact person for a supplier, allowing null values.","glossary_terms":[],"cardinality":0,"null_count":10,"data_category":"nominal","semantic_class":"person_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: contact_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"contact_name"},{"name":"email","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"The \"email\" column in the \"suppliers\" table stores the email address of a supplier as a nullable nvarchar value for contact purposes.","glossary_terms":[],"cardinality":10,"null_count":0,"data_range":{"min":"supplier1@example.com","max":"supplier9@example.com"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.email","concept_confidence":1.0,"concept_evidence":["name token: email","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: contact","value pattern: email","sensitive hint: pii_contact"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"email"},{"name":"phone","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"The \"phone\" column in the \"suppliers\" table stores the contact phone number of a supplier as a nullable string.","glossary_terms":[],"cardinality":10,"null_count":0,"data_range":{"min":"555-2001","max":"555-2010"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.phone","concept_confidence":1.0,"concept_evidence":["name token: phone","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: contact","value pattern: phone","sensitive hint: pii_contact"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"phone"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"Records the timestamp when a supplier entry is initially created in the system, stored as a non-nullable datetime value.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":10,"null_count":0,"data_range":{"min":"2021-03-22 15:38:57.201565","max":"2024-02-25 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: suppliers"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The `updated_at` column stores the non-nullable timestamp of the most recent update to a supplier record in the `suppliers` table.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":10,"null_count":0,"data_range":{"min":"2021-03-22 15:38:57.201565","max":"2024-02-25 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: suppliers"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"}],"table_description":"The \"suppliers\" table stores information about suppliers, including their unique identifier, name, contact details, and timestamps for record creation and updates.","glossary_terms":["RetailDomainGlossary.SupplierCode"],"primary_keys":["supplier_id"],"foreign_keys":[],"row_count":10,"field_classifications":{"contact_name":"person_name","email":"contact","phone":"contact","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{"email":"pii_contact","phone":"pii_contact"},"incremental_columns":["updated_at"],"join_candidates":[],"unit_summary":{"columns_with_units":0,"columns_without_units":7,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":false,"has_sensitive_fields":true,"row_count_projection_1y":22,"row_count_projection_2y":35,"row_count_projection_5y":74,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.email":1,"contact.person_name":2,"contact.phone":1,"identifier.foreign_key":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":["contact_name","name"]},"data_quality":{"findings":[{"column":"email","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 10 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"phone","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 10 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}}]}</t>
         </is>
       </c>
     </row>
@@ -10416,7 +10512,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-04-03T12:09:52.790221+00:00</t>
+          <t>2026-04-07T08:55:59.245988+00:00</t>
         </is>
       </c>
       <c r="C3" s="4" t="n"/>
@@ -15535,7 +15631,7 @@
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="80" customWidth="1" min="7" max="7"/>
     <col width="80" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="41" customWidth="1" min="9" max="9"/>
     <col width="80" customWidth="1" min="10" max="10"/>
     <col width="80" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
@@ -15671,10 +15767,14 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>The `customers` table stores information about retail customers, including their unique ID, name, contact details, and timestamps for record creation and updates.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>The "customers" table stores information about retail customers, including their unique ID, name, contact details, and timestamps for record creation and updates.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>RetailDomainGlossary.CustomerIdentifier</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>{"concept_counts":{"contact.email":1,"contact.person_name":2,"contact.phone":1,"identifier.foreign_key":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":[]}</t>
@@ -16019,7 +16119,11 @@
           <t>Unique identifier for each customer in the retail operations system.</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>RetailDomainGlossary.CustomerIdentifier</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
@@ -16103,7 +16207,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Stores the given name of a customer as a non-null, case-insensitive Unicode string.</t>
+          <t>Stores the given name of a customer as a non-null Unicode string.</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -16190,10 +16294,14 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Stores the last name of a customer as a non-null, case-insensitive Unicode string.</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
+          <t>The "last_name" column in the "customers" table stores the non-nullable family name of a customer as a case-insensitive Unicode string.</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>RetailDomainGlossary.Customer</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>contact.person_name</t>
@@ -16281,7 +16389,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Stores the email address of the customer, allowing null values.</t>
+          <t>Stores the email address of the customer, allowing null values for cases where an email is not provided.</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -16546,7 +16654,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Tracks the timestamp of the most recent update to a customer's record, ensuring accurate change history.</t>
+          <t>Tracks the timestamp of the most recent update to a customer record, ensuring accurate audit and change history.</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -17198,7 +17306,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>The `employees` table stores details about retail system employees, including their identifiers, store associations, personal information, roles, hire dates, and record timestamps.</t>
+          <t>The `employees` table stores detailed information about retail system employees, including their unique identifiers, store assignments, personal details, job roles, hire dates, and record timestamps.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -17651,7 +17759,7 @@
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Unique identifier for each employee in the retail operations system.</t>
+          <t>Unique identifier for employees in the retail operations system.</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -17730,7 +17838,7 @@
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Associates each employee with a specific store, referencing the `store_id` column in the `stores` table.</t>
+          <t>Identifies the store where the employee is assigned, referencing the `store_id` column in the `stores` table.</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -17817,7 +17925,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Stores the given name of an employee, represented as a non-null, case-insensitive Unicode string.</t>
+          <t>Stores the given name of an employee, represented as a non-null Unicode string.</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -17904,7 +18012,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>The "last_name" column in the "employees" table stores the non-nullable family name of an employee as a case-insensitive Unicode string.</t>
+          <t>The "last_name" column in the "employees" table stores the non-nullable family name of each employee as a case-insensitive Unicode string.</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -17995,7 +18103,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Stores the unique email address of each employee for contact purposes, with a maximum length of 450 characters and cannot be null.</t>
+          <t>The "email" column in the "employees" table stores the unique, non-null email address of each employee for contact purposes.</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -18074,7 +18182,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Indicates the job position or function of an employee within the organization, stored as a non-nullable text value.</t>
+          <t>Stores the job role or position of an employee within the organization, such as "Cashier" or "Sales," as a non-null text value.</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -18335,7 +18443,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>The `updated_at` column stores the non-nullable timestamp of the most recent update to an employee record.</t>
+          <t>The `updated_at` column in the `employees` table stores the non-nullable timestamp of the most recent update to an employee record.</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -18865,7 +18973,7 @@
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="80" customWidth="1" min="7" max="7"/>
     <col width="80" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="80" customWidth="1" min="9" max="9"/>
     <col width="80" customWidth="1" min="10" max="10"/>
     <col width="80" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
@@ -19004,7 +19112,11 @@
           <t>Current stock levels with normalized stock unit representation.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>RetailDomainGlossary.Inventory, RetailDomainGlossary.InventoryByProductAndLocation</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>{"concept_counts":{"identifier.foreign_key":3,"measure.quantity":1,"temporal.created_at":1,"temporal.event_time":1,"temporal.updated_at":1},"low_confidence_columns":["reorder_level","stock_unit"]}</t>
@@ -19567,7 +19679,7 @@
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Identifier for the store associated with the inventory record, referencing the `store_id` column in the `stores` table.</t>
+          <t>Represents the unique identifier of the store associated with the inventory record, referencing the `store_id` column in the `stores` table.</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -19650,7 +19762,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>References the unique identifier of a product from the `products` table to associate inventory records with specific products.</t>
+          <t>References the unique identifier of a product from the products table, linking inventory records to specific products.</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -19737,10 +19849,14 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Tracks the current quantity of a product available in inventory, expressed as a non-null integer.</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
+          <t>The `quantity_on_hand` column in the `inventory` table stores the current stock level of a product as a non-null integer.</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>RetailDomainGlossary.Inventory</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>measure.quantity</t>
@@ -19835,7 +19951,11 @@
           <t>Indicates the minimum quantity of a product in inventory that triggers a reorder, stored as a non-null integer.</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>RetailDomainGlossary.ReorderPoint</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="n">
         <v>0.1</v>
@@ -19914,7 +20034,11 @@
           <t>The `last_restocked_at` column records the timestamp of the most recent restocking event for an inventory item, allowing null values if the item has not been restocked.</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>RetailDomainGlossary.Replenishment</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>temporal.event_time</t>
@@ -20164,10 +20288,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Represents the monetary value of inventory stock, stored as a numeric value with up to 10 digits and 2 decimal places, and may be null.</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
+          <t>Represents the monetary value of inventory stock, stored as a numeric value with two decimal places, and may be null.</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>RetailDomainGlossary.Inventory</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="n">
         <v>0</v>
@@ -20230,7 +20358,11 @@
           <t>Current stock unit label.</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>RetailDomainGlossary.UnitOfMeasure</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="n">
         <v>0.15</v>
@@ -20727,7 +20859,7 @@
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="80" customWidth="1" min="7" max="7"/>
     <col width="80" customWidth="1" min="8" max="8"/>
-    <col width="44" customWidth="1" min="9" max="9"/>
+    <col width="67" customWidth="1" min="9" max="9"/>
     <col width="80" customWidth="1" min="10" max="10"/>
     <col width="80" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
@@ -20866,7 +20998,11 @@
           <t>Master product catalog including physical units for analyzer unit-context testing.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>RetailDomainGlossary.Inventory, RetailDomainGlossary.SupplierCode</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>{"concept_counts":{"contact.person_name":1,"entity.category":1,"finance.currency_amount":2,"identifier.foreign_key":3,"identifier.product_code":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":["length_unit","name","product_description","weight_unit"]}</t>
@@ -21344,10 +21480,14 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Unique identifier for each product in the retail operations system.</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
+          <t>Unique identifier for each product in the retail system, serving as the primary key for the products table.</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>RetailDomainGlossary.Barcode</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
@@ -21426,7 +21566,11 @@
           <t>The `supplier_id` column in the `products` table is a non-nullable foreign key referencing the `supplier_id` column in the `suppliers` table, identifying the supplier associated with each product.</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>RetailDomainGlossary.SupplierCode</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
@@ -21506,10 +21650,14 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Unique alphanumeric identifier for a product used for inventory and sales tracking, stored as a non-null nvarchar(450).</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
+          <t>Unique alphanumeric identifier for a product used for inventory and sales tracking.</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>RetailDomainGlossary.Product</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>identifier.product_code</t>
@@ -21585,7 +21733,7 @@
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>The "name" column in the "products" table stores the non-nullable name of a product as a case-insensitive Unicode string.</t>
+          <t>Stores the name of the product as a non-null, case-insensitive Unicode string.</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -21672,10 +21820,14 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Indicates the product's category classification, such as "Books," "Clothing," or "Electronics," stored as a non-null, case-insensitive text value.</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
+          <t>Indicates the product's category classification, such as "Books," "Clothing," or "Electronics," stored as a non-nullable nvarchar value.</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>RetailDomainGlossary.ProductCategory</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>entity.category</t>
@@ -21759,10 +21911,14 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Stores the retail price of a product as a non-null numeric value with up to 10 digits and 2 decimal places.</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
+          <t>The `unit_price` column stores the non-null selling price of a product as a numeric value with up to 10 digits and 2 decimal places, representing a currency amount.</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>RetailDomainGlossary.SellingPrice</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>finance.currency_amount</t>
@@ -21846,10 +22002,14 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Represents the numeric cost price of a product in the retail system, stored as a non-nullable currency amount with up to 10 digits and 2 decimal places.</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
+          <t>The `cost_price` column stores the non-null numeric cost amount (up to 10 digits with 2 decimal places) representing the purchase price of a product in the retail system.</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>RetailDomainGlossary.CostPrice</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>finance.currency_amount</t>
@@ -21996,7 +22156,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Indicates the timestamp when the product record was initially created, stored as a non-nullable datetime value.</t>
+          <t>The `created_at` column stores the non-nullable timestamp indicating when a product record was initially created in the system.</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -22169,7 +22329,11 @@
           <t>Source weight unit (kg/lb) used for unit inference testing.</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>RetailDomainGlossary.UnitOfMeasure</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="n">
         <v>0.15</v>
@@ -22252,7 +22416,11 @@
           <t>The `weight_value` column stores the weight of a product as a numeric value with up to 10 digits and 2 decimal places, and it is nullable.</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>RetailDomainGlossary.UnitOfMeasure</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="n">
         <v>0</v>
@@ -22332,7 +22500,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>The "length_value" column stores the numeric length measurement of a product, allowing up to 10 digits with 2 decimal places, and is nullable.</t>
+          <t>Represents the length measurement of a product in numeric format, allowing null values.</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -22418,7 +22586,11 @@
           <t>Source length unit (cm/in) used for unit inference testing.</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>RetailDomainGlossary.UnitOfMeasure</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="n">
         <v>0.15</v>
@@ -22494,10 +22666,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Stores optional textual details about a product, such as features or specifications, with support for Unicode characters.</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
+          <t>Stores optional textual details about a product, such as features or specifications.</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>RetailDomainGlossary.Product</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="n">
         <v>0.1</v>
@@ -22560,7 +22736,11 @@
           <t>Primary supplier relationship used for join candidate detection.</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>RetailDomainGlossary.SupplierPurchaseRelationship</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
@@ -23323,7 +23503,7 @@
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="80" customWidth="1" min="7" max="7"/>
     <col width="80" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="80" customWidth="1" min="9" max="9"/>
     <col width="80" customWidth="1" min="10" max="10"/>
     <col width="80" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
@@ -23462,7 +23642,11 @@
           <t>Line items with order quantities and explicit unit labels.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>RetailDomainGlossary.OrderLine, RetailDomainGlossary.UnitOfMeasure, RetailDomainGlossary.CostPrice, RetailDomainGlossary.PurchaseOrder</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>{"concept_counts":{"finance.currency_amount":1,"identifier.foreign_key":3,"measure.quantity":3,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":[]}</t>
@@ -23939,7 +24123,11 @@
           <t>Unique identifier for each purchase order item record in the `purchase_order_items` table.</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>RetailDomainGlossary.OrderLine</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
@@ -24015,10 +24203,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Links each purchase order item to its corresponding purchase order in the `purchase_orders` table via a non-null foreign key.</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
+          <t>Represents the unique identifier of the associated purchase order, linking purchase order items to their parent purchase order in the `purchase_orders` table.</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>RetailDomainGlossary.PurchaseOrder</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
@@ -24101,7 +24293,11 @@
           <t>Identifier linking each purchase order item to a specific product in the products table.</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>RetailDomainGlossary.ProductCategory</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
@@ -24188,7 +24384,11 @@
           <t>The `quantity` column in the `purchase_order_items` table stores the non-null integer value representing the number of units of a product included in a specific purchase order item.</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>RetailDomainGlossary.UnitOfMeasure</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>measure.quantity</t>
@@ -24288,10 +24488,14 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>The `unit_cost` column in the `purchase_order_items` table stores the non-null numeric cost per unit of a product in a purchase order, represented as a currency amount with up to 10 digits and 2 decimal places.</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
+          <t>Represents the per-unit cost of a product in a purchase order, stored as a non-null numeric value with up to 10 digits and 2 decimal places.</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>RetailDomainGlossary.CostPrice</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>finance.currency_amount</t>
@@ -24375,7 +24579,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Records the timestamp when a purchase order item entry is created, stored as a non-nullable datetime value.</t>
+          <t>The `created_at` column records the non-nullable timestamp indicating when each purchase order item record was created.</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -24462,7 +24666,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>The `updated_at` column in the `purchase_order_items` table stores the non-nullable timestamp of the most recent update to a purchase order item record.</t>
+          <t>Records the timestamp of the most recent update to a purchase order item, ensuring accurate tracking of modifications.</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -24552,7 +24756,11 @@
           <t>The `ordered_qty_value` column stores the numeric quantity value (up to two decimal places) of items ordered in a purchase order, which can be null.</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>RetailDomainGlossary.PurchaseOrder</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>measure.quantity</t>
@@ -24647,7 +24855,11 @@
           <t>Ordered quantity unit (ea/box).</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>RetailDomainGlossary.UnitOfMeasure</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>measure.quantity</t>

--- a/LATEST_SCHEMA/schema_azure_mssql_dbo.xlsx
+++ b/LATEST_SCHEMA/schema_azure_mssql_dbo.xlsx
@@ -826,7 +826,7 @@
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="80" customWidth="1" min="7" max="7"/>
     <col width="80" customWidth="1" min="8" max="8"/>
-    <col width="70" customWidth="1" min="9" max="9"/>
+    <col width="80" customWidth="1" min="9" max="9"/>
     <col width="80" customWidth="1" min="10" max="10"/>
     <col width="80" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
@@ -967,7 +967,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>RetailDomainGlossary.PurchaseOrder, RetailDomainGlossary.OrderStatus</t>
+          <t>RetailDomainGlossary.PurchaseOrder, RetailDomainGlossary.Supplier, RetailDomainGlossary.StoreLocation, RetailDomainGlossary.OrderStatus</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>RetailDomainGlossary.SupplierCode</t>
+          <t>RetailDomainGlossary.Supplier</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -1663,10 +1663,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Identifies the store associated with the purchase order, referencing the `store_id` column in the `stores` table.</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
+          <t>Identifier for the store associated with the purchase order, referencing the `store_id` column in the `stores` table.</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>RetailDomainGlossary.StoreLocation</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
@@ -1750,7 +1754,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Indicates the current state of a purchase order (e.g., "Ordered," "Received") as a non-null categorical value.</t>
+          <t>Indicates the current state of a purchase order (e.g., "Ordered", "Received"), stored as a non-nullable text category.</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -1841,7 +1845,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>The `order_date` column in the `purchase_orders` table records the date a purchase order was placed, is mandatory, and uses the `date` data type.</t>
+          <t>The `order_date` column in the `purchase_orders` table records the date a purchase order was placed and cannot be null.</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -1931,11 +1935,7 @@
           <t>The `expected_date` column in the `purchase_orders` table records the anticipated delivery date for a purchase order, allowing null values.</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>RetailDomainGlossary.OrderDeliveryRelationship</t>
-        </is>
-      </c>
+      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
           <t>temporal.date_only</t>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>The `created_at` column stores the non-nullable timestamp indicating when a purchase order record was initially created in the system.</t>
+          <t>The `created_at` column records the timestamp when a purchase order record was initially created, using a non-nullable `datetime2` data type.</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>The `updated_at` column stores the non-nullable timestamp of the most recent update to a purchase order record.</t>
+          <t>The `updated_at` column stores the non-null timestamp indicating the last modification date and time of a purchase order record.</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>RetailDomainGlossary.OrderLine, RetailDomainGlossary.SalesOrder, RetailDomainGlossary.UnitOfMeasure</t>
+          <t>RetailDomainGlossary.OrderLine, RetailDomainGlossary.Quantity, RetailDomainGlossary.UnitOfMeasure, RetailDomainGlossary.Sale</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -3382,14 +3382,10 @@
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Unique identifier for each sales order item in the sales_order_items table.</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>RetailDomainGlossary.OrderLine</t>
-        </is>
-      </c>
+          <t>Unique identifier for each item in a sales order, serving as the primary key for the `sales_order_items` table.</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
@@ -3552,12 +3548,12 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Identifier for the product associated with the sales order item, referencing the primary key in the products table.</t>
+          <t>Identifies the product associated with a sales order item, referencing the `products.product_id` column.</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>RetailDomainGlossary.ProductCategory</t>
+          <t>RetailDomainGlossary.Product</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3643,12 +3639,12 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>The "quantity" column in the "sales_order_items" table stores the number of units of a product included in a sales order item, represented as a non-null integer.</t>
+          <t>The "quantity" column in the "sales_order_items" table stores the non-null integer value representing the number of units of a product included in a specific sales order item.</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>RetailDomainGlossary.OrderLine</t>
+          <t>RetailDomainGlossary.Quantity</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3750,7 +3746,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>The `unit_price` column in the `sales_order_items` table stores the per-unit selling price of a product in the sales order as a non-null numeric value with two decimal places.</t>
+          <t>The "unit_price" column stores the non-null numeric price per unit of a product in a sales order item, represented as a currency amount with up to 15 digits and 2 decimal places.</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -3841,7 +3837,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Records the timestamp when a sales order item entry is created, ensuring accurate tracking of creation events.</t>
+          <t>The `created_at` column records the timestamp when a sales order item was created, stored as a non-nullable `datetime2` value.</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -3928,7 +3924,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>The `updated_at` column in the `sales_order_items` table stores the non-nullable timestamp of the most recent update to a sales order item record.</t>
+          <t>The `updated_at` column stores the non-nullable timestamp of the most recent update to a sales order item record in the `sales_order_items` table.</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -4020,7 +4016,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>RetailDomainGlossary.OrderLine</t>
+          <t>RetailDomainGlossary.Quantity</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -4700,7 +4696,7 @@
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="80" customWidth="1" min="7" max="7"/>
     <col width="80" customWidth="1" min="8" max="8"/>
-    <col width="80" customWidth="1" min="9" max="9"/>
+    <col width="33" customWidth="1" min="9" max="9"/>
     <col width="80" customWidth="1" min="10" max="10"/>
     <col width="80" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
@@ -4841,7 +4837,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>RetailDomainGlossary.SalesOrder, RetailDomainGlossary.CustomerIdentifier, RetailDomainGlossary.OrderStatus</t>
+          <t>RetailDomainGlossary.SalesOrder</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -5395,7 +5391,7 @@
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Unique identifier for each sales order in the system, serving as the primary key for the sales_orders table.</t>
+          <t>Unique identifier for each sales order in the system.</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -5483,7 +5479,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>RetailDomainGlossary.SalesChannel</t>
+          <t>RetailDomainGlossary.StoreLocation</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -5569,12 +5565,12 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Represents the identifier of the customer associated with a sales order, referencing the `customer_id` column in the `customers` table, and may be null if no customer is linked.</t>
+          <t>Identifies the customer associated with a sales order, referencing the `customer_id` column in the `customers` table; nullable to accommodate orders without a registered customer.</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>RetailDomainGlossary.CustomerIdentifier</t>
+          <t>RetailDomainGlossary.Customer, RetailDomainGlossary.CustomerIdentifier</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -5917,12 +5913,12 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>The `total_amount` column in the `sales_orders` table stores the non-nullable total monetary value of a sales order as a numeric value with up to 12 digits and 2 decimal places.</t>
+          <t>The `total_amount` column in the `sales_orders` table stores the non-null total monetary value of a sales order as a numeric value with up to 12 digits and 2 decimal places.</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>RetailDomainGlossary.SalesOrder</t>
+          <t>RetailDomainGlossary.NetSales</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -6008,7 +6004,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>The `created_at` column records the timestamp when a sales order record is initially created, stored as a non-nullable `datetime2` value.</t>
+          <t>The `created_at` column in the `sales_orders` table stores the non-nullable timestamp indicating when the sales order record was initially created.</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -6754,7 +6750,7 @@
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="80" customWidth="1" min="7" max="7"/>
     <col width="80" customWidth="1" min="8" max="8"/>
-    <col width="35" customWidth="1" min="9" max="9"/>
+    <col width="80" customWidth="1" min="9" max="9"/>
     <col width="80" customWidth="1" min="10" max="10"/>
     <col width="80" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
@@ -6890,12 +6886,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>The "stores" table stores information about retail store locations, including unique identifiers, names, codes, addresses, contact details, and timestamps for record creation and updates.</t>
+          <t>The "stores" table stores information about retail store locations, including unique identifiers, names, addresses, contact details, and timestamps for record creation and updates.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>RetailDomainGlossary.StoreCode</t>
+          <t>RetailDomainGlossary.PhysicalStore, RetailDomainGlossary.StoreLocation, RetailDomainGlossary.StoreCode</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -7236,7 +7232,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>RetailDomainGlossary.StoreCode</t>
+          <t>RetailDomainGlossary.StoreLocation</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -7314,10 +7310,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>The "name" column in the "stores" table is a non-nullable nvarchar field storing the name of a retail store.</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
+          <t>The "name" column in the "stores" table is a non-nullable nvarchar field that stores the name of a retail store.</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>RetailDomainGlossary.PhysicalStore</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>contact.person_name</t>
@@ -7393,7 +7393,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Unique alphanumeric identifier for a store, used for internal reference and operations.</t>
+          <t>Unique alphanumeric identifier for a store, used to distinguish stores within the retail system.</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -7625,7 +7625,11 @@
           <t>The "state" column in the "stores" table stores the name of the state or province where a store is located, allowing null values.</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>RetailDomainGlossary.StoreLocation</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="n">
         <v>0.1</v>
@@ -7697,7 +7701,7 @@
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>The "postal_code" column in the "stores" table stores the postal or ZIP code of a store location as a nullable string.</t>
+          <t>The "postal_code" column in the "stores" table stores the postal or ZIP code of a store location as a nullable nvarchar value.</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -7788,7 +7792,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>The "phone" column in the "stores" table stores the contact phone number of a store as a nullable nvarchar value.</t>
+          <t>Stores.phone is an optional nvarchar column storing the contact phone number for a store location.</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -7875,7 +7879,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>The `created_at` column stores the non-nullable timestamp indicating when a store record was initially created in the system.</t>
+          <t>The `created_at` column in the `stores` table records the non-nullable timestamp indicating when a store record was initially created.</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -8844,7 +8848,7 @@
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="80" customWidth="1" min="7" max="7"/>
     <col width="80" customWidth="1" min="8" max="8"/>
-    <col width="35" customWidth="1" min="9" max="9"/>
+    <col width="80" customWidth="1" min="9" max="9"/>
     <col width="80" customWidth="1" min="10" max="10"/>
     <col width="80" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
@@ -8985,7 +8989,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>RetailDomainGlossary.SupplierCode</t>
+          <t>RetailDomainGlossary.Supplier, RetailDomainGlossary.SupplierCode, RetailDomainGlossary.SupplierPurchaseRelationship</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -9324,11 +9328,7 @@
           <t>Unique identifier for each supplier, serving as the primary key in the suppliers table.</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>RetailDomainGlossary.SupplierCode</t>
-        </is>
-      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
@@ -9574,7 +9574,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>The "email" column in the "suppliers" table stores the email address of a supplier as a nullable nvarchar value for contact purposes.</t>
+          <t>Stores the email address of the supplier, allowing null values for cases where no email is provided.</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -10422,7 +10422,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{"metadata":{"generated_at":"2026-04-07T08:55:59.245988+00:00","database_url":"pioneertest.database.windows.net:1433/free-sql-db-3300567?driver=ODBC+Driver+18+for+SQL+Server&amp;TrustServerCertificate=yes","schema_filter":"dbo","total_tables":10,"total_rows":1364,"total_findings":64},"connection":{"host":"pioneertest.database.windows.net","port":"1433","database":"free-sql-db-3300567","driver":"mssql","timezone":"(UTC) Coordinated Universal Time"},"source_system_context":{"contacts":[],"delete_management_instruction":"","restrictions":"","late_arriving_data_manual":"","volume_size_projection_manual":"","system_description":"Retail operations source system covering customers, stores, employees, suppliers, products, inventory, purchase orders, and sales orders used for day-to-day store, procurement, and sales transaction management.","openmetadata_enrichment":{"enabled":true,"configured":true,"database_service_name":"","schema":"dbo","match_strategy":"table_name","matched_tables":0,"unmatched_tables":10,"error":""},"db_analysis_config":{"exclude_schemas":["prediction"],"exclude_tables":[],"max_row_limit":100}},"concept_registry":{"version":1,"taxonomy":"domain-dot","generated_from_tables":10,"concepts":[{"concept_id":"contact.address","column_count":2,"table_count":1,"avg_confidence":0.55,"alias_groups":["address","postal_code"],"sample_columns":["stores.address","stores.postal_code"],"signals":["name","type"]},{"concept_id":"contact.email","column_count":3,"table_count":3,"avg_confidence":1.0,"alias_groups":["email"],"sample_columns":["customers.email","employees.email","suppliers.email"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"contact.person_name","column_count":8,"table_count":5,"avg_confidence":0.56,"alias_groups":["contact_name","first_name","last_name","name"],"sample_columns":["customers.first_name","customers.last_name","employees.first_name","employees.last_name","products.name"],"signals":["name","table_context","type"]},{"concept_id":"contact.phone","column_count":3,"table_count":3,"avg_confidence":1.0,"alias_groups":["phone"],"sample_columns":["customers.phone","stores.phone","suppliers.phone"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"entity.category","column_count":1,"table_count":1,"avg_confidence":0.8,"alias_groups":["category"],"sample_columns":["products.category"],"signals":["name","profile","type"]},{"concept_id":"entity.status","column_count":2,"table_count":2,"avg_confidence":1.0,"alias_groups":["statu"],"sample_columns":["purchase_orders.status","sales_orders.status"],"signals":["name","profile","type","values"]},{"concept_id":"entity.type","column_count":1,"table_count":1,"avg_confidence":0.65,"alias_groups":["role"],"sample_columns":["employees.role"],"signals":["name","profile","type"]},{"concept_id":"finance.currency_amount","column_count":5,"table_count":4,"avg_confidence":1.0,"alias_groups":["amount","price","unit_cost"],"sample_columns":["products.unit_price","products.cost_price","purchase_order_items.unit_cost","sales_order_items.unit_price","sales_orders.total_amount"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"identifier.foreign_key","column_count":26,"table_count":10,"avg_confidence":0.78,"alias_groups":["id"],"sample_columns":["customers.customer_id","employees.employee_id","employees.store_id","inventory.inventory_id","inventory.store_id"],"signals":["cross_table_consensus","name","profile","type"]},{"concept_id":"identifier.product_code","column_count":1,"table_count":1,"avg_confidence":0.7,"alias_groups":["sku"],"sample_columns":["products.sku"],"signals":["name","profile","type"]},{"concept_id":"measure.quantity","column_count":7,"table_count":3,"avg_confidence":1.0,"alias_groups":["ordered_qty","ordered_qty_unit","quantity","quantity_on_hand","sold_qty","sold_qty_unit"],"sample_columns":["inventory.quantity_on_hand","purchase_order_items.quantity","purchase_order_items.ordered_qty_value","purchase_order_items.ordered_qty_unit","sales_order_items.quantity"],"signals":["name","profile","type","values"]},{"concept_id":"temporal.created_at","column_count":10,"table_count":10,"avg_confidence":1.0,"alias_groups":["created_at"],"sample_columns":["customers.created_at","employees.created_at","inventory.created_at","products.created_at","purchase_order_items.created_at"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"temporal.date_only","column_count":4,"table_count":3,"avg_confidence":0.97,"alias_groups":["expected_date","hire_date","order_date"],"sample_columns":["employees.hire_date","purchase_orders.order_date","purchase_orders.expected_date","sales_orders.order_date"],"signals":["cross_table_consensus","name","profile","table_context","type","values"]},{"concept_id":"temporal.event_time","column_count":1,"table_count":1,"avg_confidence":1.0,"alias_groups":["last_restocked_at"],"sample_columns":["inventory.last_restocked_at"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"temporal.updated_at","column_count":10,"table_count":10,"avg_confidence":1.0,"alias_groups":["updated_at"],"sample_columns":["customers.updated_at","employees.updated_at","inventory.updated_at","products.updated_at","purchase_order_items.updated_at"],"signals":["name","profile","table_context","type","values"]}]},"data_quality_summary":{"critical":0,"warning":27,"info":37,"by_check":{"controlled_value_candidate":7,"nullable_but_never_null":13,"missing_primary_key":0,"missing_foreign_key":0,"format_inconsistency":0,"range_violation":0,"timestamp_ordering":10,"delete_management":10,"late_arriving_data":3,"timezone":10,"unit_unknown":11,"unit_noncanonical_but_convertible":0,"unit_mismatch_within_semantic_group":0},"constraints_found":{"check_constraints":0,"enum_columns":0,"unique_constraints":10}},"tables":[{"table":"customers","schema":"dbo","columns":[{"name":"customer_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for each customer in the retail operations system.","glossary_terms":["RetailDomainGlossary.CustomerIdentifier"],"cardinality":100,"null_count":0,"data_range":{"min":"404","max":"503"},"data_category":"discrete","semantic_class":"customer_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"first_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"Stores the given name of a customer as a non-null Unicode string.","glossary_terms":[],"cardinality":100,"null_count":0,"data_range":{"min":"Customer1","max":"Customer99"},"data_category":"nominal","semantic_class":"given_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.6,"concept_evidence":["name token: first_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","table context: customers"],"concept_sources":["name","table_context","type"],"concept_alias_group":"first_name"},{"name":"last_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"The \"last_name\" column in the \"customers\" table stores the non-nullable family name of a customer as a case-insensitive Unicode string.","glossary_terms":["RetailDomainGlossary.Customer"],"cardinality":100,"null_count":0,"data_range":{"min":"LastName1 (updated)","max":"LastName99"},"data_category":"nominal","semantic_class":"family_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.6,"concept_evidence":["name token: last_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","table context: customers"],"concept_sources":["name","table_context","type"],"concept_alias_group":"last_name"},{"name":"email","type":"nvarchar(450)","nullable":true,"is_incremental":false,"column_description":"Stores the email address of the customer, allowing null values for cases where an email is not provided.","glossary_terms":[],"cardinality":100,"null_count":0,"data_range":{"min":"customer1@example.com","max":"customer99@example.com"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.email","concept_confidence":1.0,"concept_evidence":["name token: email","type hint: nvarchar(450)","legacy field classification: contact","value pattern: email","table context: customers","sensitive hint: pii_contact"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"email"},{"name":"phone","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"Stores the customer's phone number as an optional text field for contact purposes.","glossary_terms":[],"cardinality":100,"null_count":0,"data_range":{"min":"555-1001","max":"555-1100"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.phone","concept_confidence":1.0,"concept_evidence":["name token: phone","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: contact","value pattern: phone","table context: customers","sensitive hint: pii_contact"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"phone"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The `created_at` column records the non-nullable timestamp indicating when a customer record was initially created in the system.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":95,"null_count":0,"data_range":{"min":"2021-03-23 15:38:57.201565","max":"2026-02-26 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: customers"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"Tracks the timestamp of the most recent update to a customer record, ensuring accurate audit and change history.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":95,"null_count":0,"data_range":{"min":"2021-03-23 15:38:57.201565","max":"2026-03-26 08:52:49.252228"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: customers"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"}],"table_description":"The \"customers\" table stores information about retail customers, including their unique ID, name, contact details, and timestamps for record creation and updates.","glossary_terms":["RetailDomainGlossary.CustomerIdentifier"],"primary_keys":["customer_id"],"foreign_keys":[],"row_count":100,"field_classifications":{"customer_id":"identifier","first_name":"person_name","last_name":"person_name","email":"contact","phone":"contact","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{"email":"pii_contact","phone":"pii_contact"},"incremental_columns":["updated_at"],"join_candidates":[],"unit_summary":{"columns_with_units":0,"columns_without_units":7,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":false,"has_sensitive_fields":true,"row_count_projection_1y":126,"row_count_projection_2y":152,"row_count_projection_5y":232,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.email":1,"contact.person_name":2,"contact.phone":1,"identifier.foreign_key":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"findings":[{"column":"email","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 100 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"phone","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 100 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}},{"table":"employees","schema":"dbo","columns":[{"name":"employee_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for employees in the retail operations system.","glossary_terms":[],"cardinality":20,"null_count":0,"data_range":{"min":"64","max":"83"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Identifies the store where the employee is assigned, referencing the `store_id` column in the `stores` table.","glossary_terms":[],"cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"first_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"Stores the given name of an employee, represented as a non-null Unicode string.","glossary_terms":[],"cardinality":20,"null_count":0,"data_range":{"min":"Employee1","max":"Employee9"},"data_category":"nominal","semantic_class":"given_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: first_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"first_name"},{"name":"last_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"The \"last_name\" column in the \"employees\" table stores the non-nullable family name of each employee as a case-insensitive Unicode string.","glossary_terms":[],"cardinality":20,"null_count":0,"data_range":{"min":"LastName1","max":"LastName9"},"data_category":"nominal","semantic_class":"family_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: last_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"last_name"},{"name":"email","type":"nvarchar(450)","nullable":false,"is_incremental":false,"column_description":"The \"email\" column in the \"employees\" table stores the unique, non-null email address of each employee for contact purposes.","glossary_terms":[],"cardinality":20,"null_count":0,"data_range":{"min":"emp1@example.com","max":"emp9@example.com"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.email","concept_confidence":1.0,"concept_evidence":["name token: email","type hint: nvarchar(450)","legacy field classification: contact","value pattern: email","sensitive hint: pii_contact"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"email"},{"name":"role","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"Stores the job role or position of an employee within the organization, such as \"Cashier\" or \"Sales,\" as a non-null text value.","glossary_terms":[],"cardinality":4,"null_count":0,"data_range":{"min":"Cashier","max":"Stock"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"entity.type","concept_confidence":0.65,"concept_evidence":["name token: role","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","profile heuristic matched"],"concept_sources":["name","profile","type"],"concept_alias_group":"role"},{"name":"hire_date","type":"date","nullable":false,"is_incremental":false,"column_description":"The `hire_date` column in the `employees` table stores the non-nullable date an employee was hired, used for tracking employment start dates.","glossary_terms":[],"cardinality":20,"null_count":0,"data_range":{"min":"2021-05-03","max":"2025-01-26"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.date_only","concept_confidence":1.0,"concept_evidence":["name token: hire_date","type hint: date","legacy field classification: temporal","value pattern: date_only","table context: employees"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"hire_date"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The `created_at` column records the non-nullable timestamp indicating when an employee record was initially created in the system.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":20,"null_count":0,"data_range":{"min":"2021-05-03 15:38:57.201565","max":"2025-01-26 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: employees"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The `updated_at` column in the `employees` table stores the non-nullable timestamp of the most recent update to an employee record.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":20,"null_count":0,"data_range":{"min":"2021-05-03 15:38:57.201565","max":"2025-01-26 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: employees"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"}],"table_description":"The `employees` table stores detailed information about retail system employees, including their unique identifiers, store assignments, personal details, job roles, hire dates, and record timestamps.","glossary_terms":[],"primary_keys":["employee_id"],"foreign_keys":[{"column":"store_id","references":"stores.store_id"}],"row_count":20,"field_classifications":{"first_name":"person_name","last_name":"person_name","email":"contact","hire_date":"temporal","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{"email":"pii_contact"},"incremental_columns":["updated_at"],"join_candidates":[{"column":"store_id","target_table":"stores","target_column":"store_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":9,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":true,"row_count_projection_1y":35,"row_count_projection_2y":50,"row_count_projection_5y":96,"partition_columns_candidates":["hire_date","created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.email":1,"contact.person_name":2,"entity.type":1,"identifier.foreign_key":2,"temporal.created_at":1,"temporal.date_only":1,"temporal.updated_at":1},"low_confidence_columns":["first_name","last_name"]},"data_quality":{"findings":[{"column":"role","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 4 distinct value(s) ('Cashier', 'Manager', 'Sales', 'Stock') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Cashier","Manager","Sales","Stock"],"cardinality":4},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":"hire_date","check":"late_arriving_data","severity":"info","detail":"Minor arrival delay \u2014 max lag between 'hire_date' and 'created_at' is 15.7h (avg 15.7h, P95 15.7h).","recommendation":"Use 'created_at' as the watermark (preferred). If using 'hire_date', add a 1\u20132 day lookback buffer.","business_date_column":"hire_date","system_ts_column":"created_at","lag_stats":{"total_rows_compared":20,"min_lag_hours":15.65,"avg_lag_hours":15.65,"p95_lag_hours":15.65,"max_lag_hours":15.65,"max_lag_days":0.7,"rows_late_over_1d":0,"rows_late_over_7d":0},"recommended_lookback_days":2},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}},{"table":"inventory","schema":"dbo","columns":[{"name":"inventory_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for each inventory record in the system.","glossary_terms":[],"cardinality":100,"null_count":0,"data_range":{"min":"8","max":"107"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Represents the unique identifier of the store associated with the inventory record, referencing the `store_id` column in the `stores` table.","glossary_terms":[],"cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"product_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"References the unique identifier of a product from the products table, linking inventory records to specific products.","glossary_terms":[],"cardinality":47,"null_count":0,"data_range":{"min":"156","max":"205"},"data_category":"discrete","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"quantity_on_hand","type":"integer","nullable":false,"is_incremental":false,"column_description":"The `quantity_on_hand` column in the `inventory` table stores the current stock level of a product as a non-null integer.","glossary_terms":["RetailDomainGlossary.Inventory"],"cardinality":68,"null_count":0,"data_range":{"min":"2","max":"98"},"data_category":"discrete","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: quantity_on_hand","type hint: integer","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"quantity_on_hand"},{"name":"reorder_level","type":"integer","nullable":false,"is_incremental":false,"column_description":"Indicates the minimum quantity of a product in inventory that triggers a reorder, stored as a non-null integer.","glossary_terms":["RetailDomainGlossary.ReorderPoint"],"cardinality":20,"null_count":0,"data_range":{"min":"10","max":"29"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: integer","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"last_restocked_at","type":"datetime2","nullable":true,"is_incremental":false,"column_description":"The `last_restocked_at` column records the timestamp of the most recent restocking event for an inventory item, allowing null values if the item has not been restocked.","glossary_terms":["RetailDomainGlossary.Replenishment"],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":89,"null_count":0,"data_range":{"min":"2024-03-14 15:38:57.201565","max":"2026-03-07 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.event_time","concept_confidence":1.0,"concept_evidence":["name token: last_restocked_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: inventory"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"last_restocked_at"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The `created_at` column records the non-nullable timestamp indicating when the inventory record was initially created.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":91,"null_count":0,"data_range":{"min":"2024-03-05 15:38:57.201565","max":"2026-02-23 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: inventory"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incr</t>
+          <t>{"metadata":{"generated_at":"2026-04-07T10:07:13.375975+00:00","database_url":"pioneertest.database.windows.net:1433/free-sql-db-3300567?driver=ODBC+Driver+18+for+SQL+Server&amp;TrustServerCertificate=yes","schema_filter":"dbo","total_tables":10,"total_rows":1364,"total_findings":64},"connection":{"host":"pioneertest.database.windows.net","port":"1433","database":"free-sql-db-3300567","driver":"mssql","timezone":"(UTC) Coordinated Universal Time"},"source_system_context":{"contacts":[],"delete_management_instruction":"","restrictions":"","late_arriving_data_manual":"","volume_size_projection_manual":"","system_description":"Retail operations source system covering customers, stores, employees, suppliers, products, inventory, purchase orders, and sales orders used for day-to-day store, procurement, and sales transaction management.","openmetadata_enrichment":{"enabled":true,"configured":true,"database_service_name":"","schema":"dbo","match_strategy":"table_name","matched_tables":0,"unmatched_tables":10,"error":""},"db_analysis_config":{"exclude_schemas":["prediction"],"exclude_tables":[],"max_row_limit":100}},"concept_registry":{"version":1,"taxonomy":"domain-dot","generated_from_tables":10,"concepts":[{"concept_id":"contact.address","column_count":2,"table_count":1,"avg_confidence":0.55,"alias_groups":["address","postal_code"],"sample_columns":["stores.address","stores.postal_code"],"signals":["name","type"]},{"concept_id":"contact.email","column_count":3,"table_count":3,"avg_confidence":1.0,"alias_groups":["email"],"sample_columns":["customers.email","employees.email","suppliers.email"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"contact.person_name","column_count":8,"table_count":5,"avg_confidence":0.56,"alias_groups":["contact_name","first_name","last_name","name"],"sample_columns":["customers.first_name","customers.last_name","employees.first_name","employees.last_name","products.name"],"signals":["name","table_context","type"]},{"concept_id":"contact.phone","column_count":3,"table_count":3,"avg_confidence":1.0,"alias_groups":["phone"],"sample_columns":["customers.phone","stores.phone","suppliers.phone"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"entity.category","column_count":1,"table_count":1,"avg_confidence":0.8,"alias_groups":["category"],"sample_columns":["products.category"],"signals":["name","profile","type"]},{"concept_id":"entity.status","column_count":2,"table_count":2,"avg_confidence":1.0,"alias_groups":["statu"],"sample_columns":["purchase_orders.status","sales_orders.status"],"signals":["name","profile","type","values"]},{"concept_id":"entity.type","column_count":1,"table_count":1,"avg_confidence":0.65,"alias_groups":["role"],"sample_columns":["employees.role"],"signals":["name","profile","type"]},{"concept_id":"finance.currency_amount","column_count":5,"table_count":4,"avg_confidence":1.0,"alias_groups":["amount","price","unit_cost"],"sample_columns":["products.unit_price","products.cost_price","purchase_order_items.unit_cost","sales_order_items.unit_price","sales_orders.total_amount"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"identifier.foreign_key","column_count":26,"table_count":10,"avg_confidence":0.78,"alias_groups":["id"],"sample_columns":["customers.customer_id","employees.employee_id","employees.store_id","inventory.inventory_id","inventory.store_id"],"signals":["cross_table_consensus","name","profile","type"]},{"concept_id":"identifier.product_code","column_count":1,"table_count":1,"avg_confidence":0.7,"alias_groups":["sku"],"sample_columns":["products.sku"],"signals":["name","profile","type"]},{"concept_id":"measure.quantity","column_count":7,"table_count":3,"avg_confidence":1.0,"alias_groups":["ordered_qty","ordered_qty_unit","quantity","quantity_on_hand","sold_qty","sold_qty_unit"],"sample_columns":["inventory.quantity_on_hand","purchase_order_items.quantity","purchase_order_items.ordered_qty_value","purchase_order_items.ordered_qty_unit","sales_order_items.quantity"],"signals":["name","profile","type","values"]},{"concept_id":"temporal.created_at","column_count":10,"table_count":10,"avg_confidence":1.0,"alias_groups":["created_at"],"sample_columns":["customers.created_at","employees.created_at","inventory.created_at","products.created_at","purchase_order_items.created_at"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"temporal.date_only","column_count":4,"table_count":3,"avg_confidence":0.97,"alias_groups":["expected_date","hire_date","order_date"],"sample_columns":["employees.hire_date","purchase_orders.order_date","purchase_orders.expected_date","sales_orders.order_date"],"signals":["cross_table_consensus","name","profile","table_context","type","values"]},{"concept_id":"temporal.event_time","column_count":1,"table_count":1,"avg_confidence":1.0,"alias_groups":["last_restocked_at"],"sample_columns":["inventory.last_restocked_at"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"temporal.updated_at","column_count":10,"table_count":10,"avg_confidence":1.0,"alias_groups":["updated_at"],"sample_columns":["customers.updated_at","employees.updated_at","inventory.updated_at","products.updated_at","purchase_order_items.updated_at"],"signals":["name","profile","table_context","type","values"]}]},"data_quality_summary":{"critical":0,"warning":27,"info":37,"by_check":{"controlled_value_candidate":7,"nullable_but_never_null":13,"missing_primary_key":0,"missing_foreign_key":0,"format_inconsistency":0,"range_violation":0,"timestamp_ordering":10,"delete_management":10,"late_arriving_data":3,"timezone":10,"unit_unknown":11,"unit_noncanonical_but_convertible":0,"unit_mismatch_within_semantic_group":0},"constraints_found":{"check_constraints":0,"enum_columns":0,"unique_constraints":10}},"tables":[{"table":"customers","schema":"dbo","columns":[{"name":"customer_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for each customer in the retail operations system, serving as the primary key for the customers table.","glossary_terms":["RetailDomainGlossary.CustomerIdentifier"],"cardinality":100,"null_count":0,"data_range":{"min":"404","max":"503"},"data_category":"discrete","semantic_class":"customer_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"first_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"Stores the given name of a customer as a non-null, case-insensitive Unicode string.","glossary_terms":[],"cardinality":100,"null_count":0,"data_range":{"min":"Customer1","max":"Customer99"},"data_category":"nominal","semantic_class":"given_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.6,"concept_evidence":["name token: first_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","table context: customers"],"concept_sources":["name","table_context","type"],"concept_alias_group":"first_name"},{"name":"last_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"The \"last_name\" column in the \"customers\" table stores the non-nullable family name of a customer as a case-insensitive Unicode string.","glossary_terms":[],"cardinality":100,"null_count":0,"data_range":{"min":"LastName1 (updated)","max":"LastName99"},"data_category":"nominal","semantic_class":"family_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.6,"concept_evidence":["name token: last_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","table context: customers"],"concept_sources":["name","table_context","type"],"concept_alias_group":"last_name"},{"name":"email","type":"nvarchar(450)","nullable":true,"is_incremental":false,"column_description":"Stores the email address of the customer, allowing null values, with a maximum length of 450 characters.","glossary_terms":[],"cardinality":100,"null_count":0,"data_range":{"min":"customer1@example.com","max":"customer99@example.com"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.email","concept_confidence":1.0,"concept_evidence":["name token: email","type hint: nvarchar(450)","legacy field classification: contact","value pattern: email","table context: customers","sensitive hint: pii_contact"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"email"},{"name":"phone","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"Stores the customer's phone number as an optional text field for contact purposes.","glossary_terms":[],"cardinality":100,"null_count":0,"data_range":{"min":"555-1001","max":"555-1100"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.phone","concept_confidence":1.0,"concept_evidence":["name token: phone","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: contact","value pattern: phone","table context: customers","sensitive hint: pii_contact"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"phone"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The `created_at` column records the non-nullable timestamp indicating when a customer record was initially created in the system.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":95,"null_count":0,"data_range":{"min":"2021-03-23 15:38:57.201565","max":"2026-02-26 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: customers"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The `updated_at` column in the `customers` table stores the non-nullable timestamp of the most recent update to a customer's record.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":95,"null_count":0,"data_range":{"min":"2021-03-23 15:38:57.201565","max":"2026-03-26 08:52:49.252228"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: customers"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"}],"table_description":"The \"customers\" table stores information about retail system customers, including unique identifiers, names, contact details, and timestamps for record creation and updates.","glossary_terms":["RetailDomainGlossary.Customer","RetailDomainGlossary.CustomerIdentifier"],"primary_keys":["customer_id"],"foreign_keys":[],"row_count":100,"field_classifications":{"customer_id":"identifier","first_name":"person_name","last_name":"person_name","email":"contact","phone":"contact","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{"email":"pii_contact","phone":"pii_contact"},"incremental_columns":["updated_at"],"join_candidates":[],"unit_summary":{"columns_with_units":0,"columns_without_units":7,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":false,"has_sensitive_fields":true,"row_count_projection_1y":126,"row_count_projection_2y":152,"row_count_projection_5y":232,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.email":1,"contact.person_name":2,"contact.phone":1,"identifier.foreign_key":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"findings":[{"column":"email","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 100 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"phone","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 100 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}},{"table":"employees","schema":"dbo","columns":[{"name":"employee_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for employees in the retail operations system.","glossary_terms":[],"cardinality":20,"null_count":0,"data_range":{"min":"64","max":"83"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Associates each employee with a specific store, referencing the unique identifier in the `stores.store_id` column.","glossary_terms":["RetailDomainGlossary.StoreLocation"],"cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"first_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"Stores the given name of an employee as a non-null Unicode string.","glossary_terms":[],"cardinality":20,"null_count":0,"data_range":{"min":"Employee1","max":"Employee9"},"data_category":"nominal","semantic_class":"given_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: first_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"first_name"},{"name":"last_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"The \"last_name\" column in the \"employees\" table stores the non-nullable family name of an employee as a case-insensitive Unicode string.","glossary_terms":[],"cardinality":20,"null_count":0,"data_range":{"min":"LastName1","max":"LastName9"},"data_category":"nominal","semantic_class":"family_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: last_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"last_name"},{"name":"email","type":"nvarchar(450)","nullable":false,"is_incremental":false,"column_description":"The \"email\" column in the \"employees\" table stores the unique, non-null email address of each employee for contact purposes.","glossary_terms":[],"cardinality":20,"null_count":0,"data_range":{"min":"emp1@example.com","max":"emp9@example.com"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.email","concept_confidence":1.0,"concept_evidence":["name token: email","type hint: nvarchar(450)","legacy field classification: contact","value pattern: email","sensitive hint: pii_contact"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"email"},{"name":"role","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"Stores the job role or position of an employee within the organization, represented as a non-nullable text value.","glossary_terms":[],"cardinality":4,"null_count":0,"data_range":{"min":"Cashier","max":"Stock"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"entity.type","concept_confidence":0.65,"concept_evidence":["name token: role","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","profile heuristic matched"],"concept_sources":["name","profile","type"],"concept_alias_group":"role"},{"name":"hire_date","type":"date","nullable":false,"is_incremental":false,"column_description":"The `hire_date` column in the `employees` table records the date an employee was hired, is mandatory, and uses the `date` data type.","glossary_terms":[],"cardinality":20,"null_count":0,"data_range":{"min":"2021-05-03","max":"2025-01-26"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.date_only","concept_confidence":1.0,"concept_evidence":["name token: hire_date","type hint: date","legacy field classification: temporal","value pattern: date_only","table context: employees"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"hire_date"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The `created_at` column records the non-nullable timestamp indicating when an employee record was initially created in the system.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":20,"null_count":0,"data_range":{"min":"2021-05-03 15:38:57.201565","max":"2025-01-26 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: employees"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"Tracks the timestamp of the most recent update to an employee record, ensuring accurate audit trails for changes.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":20,"null_count":0,"data_range":{"min":"2021-05-03 15:38:57.201565","max":"2025-01-26 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: employees"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"}],"table_description":"The `employees` table stores detailed information about retail system employees, including their unique identifiers, store associations, personal details, roles, hire dates, and record timestamps for creation and updates.","glossary_terms":["RetailDomainGlossary.Customer","RetailDomainGlossary.PhysicalStore","RetailDomainGlossary.Role","RetailDomainGlossary.Timestamp"],"primary_keys":["employee_id"],"foreign_keys":[{"column":"store_id","references":"stores.store_id"}],"row_count":20,"field_classifications":{"first_name":"person_name","last_name":"person_name","email":"contact","hire_date":"temporal","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{"email":"pii_contact"},"incremental_columns":["updated_at"],"join_candidates":[{"column":"store_id","target_table":"stores","target_column":"store_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":9,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":true,"row_count_projection_1y":35,"row_count_projection_2y":50,"row_count_projection_5y":96,"partition_columns_candidates":["hire_date","created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.email":1,"contact.person_name":2,"entity.type":1,"identifier.foreign_key":2,"temporal.created_at":1,"temporal.date_only":1,"temporal.updated_at":1},"low_confidence_columns":["first_name","last_name"]},"data_quality":{"findings":[{"column":"role","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 4 distinct value(s) ('Cashier', 'Manager', 'Sales', 'Stock') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Cashier","Manager","Sales","Stock"],"cardinality":4},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":"hire_date","check":"late_arriving_data","severity":"info","detail":"Minor arrival delay \u2014 max lag between 'hire_date' and 'created_at' is 15.7h (avg 15.7h, P95 15.7h).","recommendation":"Use 'created_at' as the watermark (preferred). If using 'hire_date', add a 1\u20132 day lookback buffer.","business_date_column":"hire_date","system_ts_column":"created_at","lag_stats":{"total_rows_compared":20,"min_lag_hours":15.65,"avg_lag_hours":15.65,"p95_lag_hours":15.65,"max_lag_hours":15.65,"max_lag_days":0.7,"rows_late_over_1d":0,"rows_late_over_7d":0},"recommended_lookback_days":2},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}},{"table":"inventory","schema":"dbo","columns":[{"name":"inventory_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for each inventory record in the system.","glossary_terms":[],"cardinality":100,"null_count":0,"data_range":{"min":"8","max":"107"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Identifier linking inventory records to the associated store, referencing the `stores.store_id` column.","glossary_terms":["RetailDomainGlossary.StoreLocation"],"cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"product_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"References the unique identifier of a product from the products table, linking inventory records to specific products.","glossary_terms":["RetailDomainGlossary.Product"],"cardinality":47,"null_count":0,"data_range":{"min":"156","max":"205"},"data_category":"discrete","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"quantity_on_hand","type":"integer","nullable":false,"is_incremental":false,"column_description":"Tracks the current quantity of a product available in inventory, expressed as a non-null integer.","glossary_terms":["RetailDomainGlossary.Inventory","RetailDomainGlossary.LocationLevelInventory"],"cardinality":68,"null_count":0,"data_range":{"min":"2","max":"98"},"data_category":"discrete","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: quantity_on_hand","type hint: integer","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"quantity_on_hand"},{"name":"reorder_level","type":"integer","nullable":false,"is_incremental":false,"column_description":"Indicates the minimum quantity of a product in inventory that triggers a reorder, stored as a non-null integer.","glossary_terms":["RetailDomainGlossary.ReorderPoint"],"cardinality":20,"null_count":0,"data_range":{"min":"10","max":"29"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: integer","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"last_restocked_at","type":"datetime2","nullable":true,"is_incremental":false,"column_description":"The `last_restocked_at` column records the timestamp of the most recent restocking event for an inventory item, allowing null values if the item has not been restocked.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":89,"null_count":0,"data_range":{"min":"2024-03-14 15:38:57.201565","max":"2026-03-07 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.event_time","concept_confidence":1.0,"concept_evidence":["name token: last_restocked_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: inventory"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"last_restocked_at"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The `created_at` column records the non-nullable timestamp indicating when the inventory record was initially created.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":91,"null_count":0,"data_range":{"min":"2024-03-05 15:38:57.201565","max":"2026-02-23 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field cl</t>
         </is>
       </c>
     </row>
@@ -10432,7 +10432,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>emental":true,"column_description":"Tracks the timestamp of the most recent update to an inventory record, ensuring accurate change history.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":89,"null_count":0,"data_range":{"min":"2024-03-14 15:38:57.201565","max":"2026-03-07 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: inventory"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"stock_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"column_description":"Represents the monetary value of inventory stock, stored as a numeric value with two decimal places, and may be null.","glossary_terms":["RetailDomainGlossary.Inventory"],"cardinality":0,"null_count":100,"data_category":"continuous","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.0,"concept_evidence":["type hint: numeric(10,2)","ambiguous runner-up concept"],"concept_sources":["type"],"concept_alias_group":null},{"name":"stock_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Current stock unit label.","glossary_terms":["RetailDomainGlossary.UnitOfMeasure"],"cardinality":0,"null_count":100,"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.15,"concept_evidence":["value pattern: quantity","ambiguous runner-up concept"],"concept_sources":["values"],"concept_alias_group":null}],"table_description":"Current stock levels with normalized stock unit representation.","glossary_terms":["RetailDomainGlossary.Inventory","RetailDomainGlossary.InventoryByProductAndLocation"],"primary_keys":["inventory_id"],"foreign_keys":[{"column":"product_id","references":"products.product_id"},{"column":"store_id","references":"stores.store_id"}],"row_count":100,"field_classifications":{"quantity_on_hand":"quantity","last_restocked_at":"temporal","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"product_id","target_table":"products","target_column":"product_id","confidence":"high"},{"column":"store_id","target_table":"stores","target_column":"store_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":10,"mixed_unit_groups":[],"unknown_unit_columns":["quantity_on_hand"]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":146,"row_count_projection_2y":193,"row_count_projection_5y":334,"partition_columns_candidates":["last_restocked_at","created_at","updated_at"],"classification_summary":{"concept_counts":{"identifier.foreign_key":3,"measure.quantity":1,"temporal.created_at":1,"temporal.event_time":1,"temporal.updated_at":1},"low_confidence_columns":["reorder_level","stock_unit"]},"data_quality":{"findings":[{"column":"last_restocked_at","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 100 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 3 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"last_restocked_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":3},{"column":"quantity_on_hand","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."}]}},{"table":"products","schema":"dbo","columns":[{"name":"product_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for each product in the retail system, serving as the primary key for the products table.","glossary_terms":["RetailDomainGlossary.Barcode"],"cardinality":50,"null_count":0,"data_range":{"min":"156","max":"205"},"data_category":"discrete","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"supplier_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"The `supplier_id` column in the `products` table is a non-nullable foreign key referencing the `supplier_id` column in the `suppliers` table, identifying the supplier associated with each product.","glossary_terms":["RetailDomainGlossary.SupplierCode"],"cardinality":10,"null_count":0,"data_range":{"min":"33","max":"42"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"sku","type":"nvarchar(450)","nullable":false,"is_incremental":false,"column_description":"Unique alphanumeric identifier for a product used for inventory and sales tracking.","glossary_terms":["RetailDomainGlossary.Product"],"cardinality":50,"null_count":0,"data_range":{"min":"SKU-0001","max":"SKU-0050"},"data_category":"nominal","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.product_code","concept_confidence":0.7,"concept_evidence":["name token: sku","type hint: nvarchar(450)","semantic class hint: product_identifier"],"concept_sources":["name","profile","type"],"concept_alias_group":"sku"},{"name":"name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"Stores the name of the product as a non-null, case-insensitive Unicode string.","glossary_terms":[],"cardinality":50,"null_count":0,"data_range":{"min":"Product 1","max":"Product 9"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"name"},{"name":"category","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"Indicates the product's category classification, such as \"Books,\" \"Clothing,\" or \"Electronics,\" stored as a non-nullable nvarchar value.","glossary_terms":["RetailDomainGlossary.ProductCategory"],"cardinality":5,"null_count":0,"data_range":{"min":"Books","max":"Sports"},"data_category":"nominal","semantic_class":"category","unit_context":null,"concept_id":"entity.category","concept_confidence":0.8,"concept_evidence":["name token: category","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: categorical","profile heuristic matched"],"concept_sources":["name","profile","type"],"concept_alias_group":"category"},{"name":"unit_price","type":"numeric(10,2)","nullable":false,"is_incremental":false,"column_description":"The `unit_price` column stores the non-null selling price of a product as a numeric value with up to 10 digits and 2 decimal places, representing a currency amount.","glossary_terms":["RetailDomainGlossary.SellingPrice"],"cardinality":50,"null_count":0,"data_range":{"min":"11.09","max":"490.43"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: price","type hint: numeric(10,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"price"},{"name":"cost_price","type":"numeric(10,2)","nullable":false,"is_incremental":false,"column_description":"The `cost_price` column stores the non-null numeric cost amount (up to 10 digits with 2 decimal places) representing the purchase price of a product in the retail system.","glossary_terms":["RetailDomainGlossary.CostPrice"],"cardinality":50,"null_count":0,"data_range":{"min":"5.55","max":"358.59"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: price","type hint: numeric(10,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"price"},{"name":"active","type":"bit","nullable":false,"is_incremental":false,"column_description":"Indicates whether a product is active and available for transactions, stored as a non-nullable boolean value.","glossary_terms":[],"cardinality":1,"null_count":0,"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.0,"concept_evidence":["profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile"],"concept_alias_group":null},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The `created_at` column stores the non-nullable timestamp indicating when a product record was initially created in the system.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":50,"null_count":0,"data_range":{"min":"2021-03-20 15:38:57.201565","max":"2024-12-25 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: products"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The `updated_at` column stores the non-nullable timestamp of the most recent update to a product record in the `products` table.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":50,"null_count":0,"data_range":{"min":"2021-03-20 15:38:57.201565","max":"2024-12-25 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: products"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"weight_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Source weight unit (kg/lb) used for unit inference testing.","glossary_terms":["RetailDomainGlossary.UnitOfMeasure"],"cardinality":0,"null_count":50,"data_category":"nominal","semantic_class":"mass","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":null,"concept_confidence":0.15,"concept_evidence":["value pattern: quantity","ambiguous runner-up concept"],"concept_sources":["values"],"concept_alias_group":null},{"name":"weight_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"column_description":"The `weight_value` column stores the weight of a product as a numeric value with up to 10 digits and 2 decimal places, and it is nullable.","glossary_terms":["RetailDomainGlossary.UnitOfMeasure"],"cardinality":0,"null_count":50,"data_category":"continuous","semantic_class":"mass","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":null,"concept_confidence":0.0,"concept_evidence":["type hint: numeric(10,2)","ambiguous runner-up concept"],"concept_sources":["type"],"concept_alias_group":null},{"name":"length_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"column_description":"Represents the length measurement of a product in numeric format, allowing null values.","glossary_terms":[],"cardinality":0,"null_count":50,"data_category":"continuous","semantic_class":"length","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":null,"concept_confidence":0.0,"concept_evidence":["type hint: numeric(10,2)","ambiguous runner-up concept"],"concept_sources":["type"],"concept_alias_group":null},{"name":"length_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Source length unit (cm/in) used for unit inference testing.","glossary_terms":["RetailDomainGlossary.UnitOfMeasure"],"cardinality":0,"null_count":50,"data_category":"nominal","semantic_class":"length","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":null,"concept_confidence":0.15,"concept_evidence":["value pattern: quantity","ambiguous runner-up concept"],"concept_sources":["values"],"concept_alias_group":null},{"name":"product_description","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"Stores optional textual details about a product, such as features or specifications.","glossary_terms":["RetailDomainGlossary.Product"],"cardinality":0,"null_count":50,"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"primary_supplier_id","type":"bigint","nullable":true,"is_incremental":false,"column_description":"Primary supplier relationship used for join candidate detection.","glossary_terms":["RetailDomainGlossary.SupplierPurchaseRelationship"],"cardinality":10,"null_count":0,"data_range":{"min":"33","max":"42"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"}],"table_description":"Master product catalog including physical units for analyzer unit-context testing.","glossary_terms":["RetailDomainGlossary.Inventory","RetailDomainGlossary.SupplierCode"],"primary_keys":["product_id"],"foreign_keys":[{"column":"primary_supplier_id","references":"suppliers.supplier_id"},{"column":"supplier_id","references":"suppliers.supplier_id"}],"row_count":50,"field_classifications":{"category":"categorical","unit_price":"pricing","cost_price":"pricing","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"primary_supplier_id","target_table":"suppliers","target_column":"supplier_id","confidence":"high"},{"column":"supplier_id","target_table":"suppliers","target_column":"supplier_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":16,"mixed_unit_groups":[],"unknown_unit_columns":["length_unit","length_value","weight_unit","weight_value"]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":68,"row_count_projection_2y":86,"row_count_projection_5y":141,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.person_name":1,"entity.category":1,"finance.currency_amount":2,"identifier.foreign_key":3,"identifier.product_code":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":["length_unit","name","product_description","weight_unit"]},"data_quality":{"findings":[{"column":"category","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 5 distinct value(s) ('Books', 'Clothing', 'Electronics', 'Home', 'Sports') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Books","Clothing","Electronics","Home","Sports"],"cardinality":5},{"column":"primary_supplier_id","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 50 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":"active","check":"delete_management","severity":"info","detail":"Active-flag column 'active' (boolean) detected \u2014 rows with active=false are logically deleted. Current distribution: True=50.","recommendation":"Filter on \"active\" = true for current records during ingestion.","delete_strategy":"soft_delete","soft_delete_column":"active","soft_delete_type":"active_flag","has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2},{"column":"weight_unit","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'mass' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"weight_value","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'mass' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"length_value","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'length' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"length_unit","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'length' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."}]}},{"table":"purchase_order_items","schema":"dbo","columns":[{"name":"po_item_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for each purchase order item record in the `purchase_order_items` table.","glossary_terms":["RetailDomainGlossary.OrderLine"],"cardinality":246,"null_count":0,"data_range":{"min":"268","max":"513"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"po_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Represents the unique identifier of the associated purchase order, linking purchase order items to their parent purchase order in the `purchase_orders` table.","glossary_terms":["RetailDomainGlossary.PurchaseOrder"],"cardinality":125,"null_count":0,"data_range":{"min":"128","max":"252"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"product_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Identifier linking each purchase order item to a specific product in the products table.","glossary_terms":["RetailDomainGlossary.ProductCategory"],"cardinality":49,"null_count":0,"data_range":{"min":"156","max":"205"},"data_category":"discrete","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"quantity","type":"integer","nullable":false,"is_incremental":false,"column_description":"The `quantity` column in the `purchase_order_items` table stores the non-null integer value representing the number of units of a product included in a specific purchase order item.","glossary_terms":["RetailDomainGlossary.UnitOfMeasure"],"cardinality":41,"null_count":0,"data_range":{"min":"10","max":"50"},"data_category":"discrete","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: quantity","type hint: integer","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"quantity"},{"name":"unit_cost","type":"numeric(10,2)","nullable":false,"is_incremental":false,"column_description":"Represents the per-unit cost of a product in a purchase order, stored as a non-null numeric value with up to 10 digits and 2 decimal places.","glossary_terms":["RetailDomainGlossary.CostPrice"],"cardinality":49,"null_count":0,"data_range":{"min":"5.55","max":"358.59"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: unit_cost","type hint: numeric(10,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount","table context: purchase_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"unit_cost"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The `created_at` column records the non-nullable timestamp indicating when each purchase order item record was created.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":246,"null_count":0,"data_range":{"min":"2026-03-12 15:44:18.668789","max":"2026-03-12 15:45:45.174099"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: purchase_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"Records the timestamp of the most recent update to a purchase order item, ensuring accurate tracking of modifications.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":246,"null_count":0,"data_range":{"min":"2026-03-12 15:44:18.668794","max":"2026-03-12 15:45:45.174104"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: purchase_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"ordered_qty_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"column_description":"The `ordered_qty_value` column stores the numeric quantity value (up to two decimal places) of items ordered in a purchase order, which can be null.","glossary_terms":["RetailDomainGlossary.PurchaseOrder"],"cardinality":0,"null_count":246,"data_category":"continuous","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: ordered_qty","type hint: numeric(10,2)","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"ordered_qty"},{"name":"ordered_qty_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Ordered quantity unit (ea/box).","glossary_terms":["RetailDomainGlossary.UnitOfMeasure"],"cardinality":0,"null_count":246,"data_category":"nominal","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: ordered_qty_unit","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity"],"concept_sources":["name","profile","values"],"concept_alias_group":"ordered_qty_unit"}],"table_description":"Line items with order quantities and explicit unit labels.","glossary_terms":["RetailDomainGlossary.OrderLine","RetailDomainGlossary.UnitOfMeasure","RetailDomainGlossary.CostPrice","RetailDomainGlossary.PurchaseOrder"],"primary_keys":["po_item_id"],"foreign_keys":[{"column":"po_id","references":"purchase_orders.po_id"},{"column":"product_id","references":"products.product_id"}],"row_count":246,"field_classifications":{"quantity":"quantity","unit_cost":"pricing","created_at":"temporal","updated_at":"temporal","ordered_qty_value":"quantity","ordered_qty_unit":"quantity"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"po_id","target_table":"purchase_orders","target_column":"po_id","confidence":"high"},{"column":"product_id","target_table":"products","target_column":"product_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":9,"mixed_unit_groups":[],"unknown_unit_columns":["ordered_qty_unit","ordered_qty_value","quantity"]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitiv</t>
+          <t>assification: temporal","value pattern: timestamp","table context: inventory"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"Tracks the timestamp of the most recent update to an inventory record, ensuring accurate change history.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":89,"null_count":0,"data_range":{"min":"2024-03-14 15:38:57.201565","max":"2026-03-07 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: inventory"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"stock_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"column_description":"Represents the monetary value of inventory stock, stored as a numeric value with up to 10 digits and 2 decimal places, and may be null.","glossary_terms":["RetailDomainGlossary.Inventory"],"cardinality":0,"null_count":100,"data_category":"continuous","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.0,"concept_evidence":["type hint: numeric(10,2)","ambiguous runner-up concept"],"concept_sources":["type"],"concept_alias_group":null},{"name":"stock_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Current stock unit label.","glossary_terms":["RetailDomainGlossary.UnitOfMeasure"],"cardinality":0,"null_count":100,"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.15,"concept_evidence":["value pattern: quantity","ambiguous runner-up concept"],"concept_sources":["values"],"concept_alias_group":null}],"table_description":"Current stock levels with normalized stock unit representation.","glossary_terms":["RetailDomainGlossary.Inventory","RetailDomainGlossary.InventoryTracking","RetailDomainGlossary.UnitOfMeasure"],"primary_keys":["inventory_id"],"foreign_keys":[{"column":"product_id","references":"products.product_id"},{"column":"store_id","references":"stores.store_id"}],"row_count":100,"field_classifications":{"quantity_on_hand":"quantity","last_restocked_at":"temporal","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"product_id","target_table":"products","target_column":"product_id","confidence":"high"},{"column":"store_id","target_table":"stores","target_column":"store_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":10,"mixed_unit_groups":[],"unknown_unit_columns":["quantity_on_hand"]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":146,"row_count_projection_2y":193,"row_count_projection_5y":334,"partition_columns_candidates":["last_restocked_at","created_at","updated_at"],"classification_summary":{"concept_counts":{"identifier.foreign_key":3,"measure.quantity":1,"temporal.created_at":1,"temporal.event_time":1,"temporal.updated_at":1},"low_confidence_columns":["reorder_level","stock_unit"]},"data_quality":{"findings":[{"column":"last_restocked_at","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 100 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 3 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"last_restocked_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":3},{"column":"quantity_on_hand","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."}]}},{"table":"products","schema":"dbo","columns":[{"name":"product_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for each product in the retail system, serving as the primary key for the products table.","glossary_terms":["RetailDomainGlossary.Product"],"cardinality":50,"null_count":0,"data_range":{"min":"156","max":"205"},"data_category":"discrete","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"supplier_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"The `supplier_id` column in the `products` table is a non-nullable foreign key referencing the `supplier_id` column in the `suppliers` table, identifying the supplier associated with each product.","glossary_terms":["RetailDomainGlossary.Supplier"],"cardinality":10,"null_count":0,"data_range":{"min":"33","max":"42"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"sku","type":"nvarchar(450)","nullable":false,"is_incremental":false,"column_description":"Unique alphanumeric identifier for a product used for inventory and sales tracking.","glossary_terms":["RetailDomainGlossary.Product"],"cardinality":50,"null_count":0,"data_range":{"min":"SKU-0001","max":"SKU-0050"},"data_category":"nominal","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.product_code","concept_confidence":0.7,"concept_evidence":["name token: sku","type hint: nvarchar(450)","semantic class hint: product_identifier"],"concept_sources":["name","profile","type"],"concept_alias_group":"sku"},{"name":"name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"The \"name\" column in the \"products\" table stores the non-nullable name of each product as a Unicode string.","glossary_terms":["RetailDomainGlossary.Product"],"cardinality":50,"null_count":0,"data_range":{"min":"Product 1","max":"Product 9"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"name"},{"name":"category","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"Indicates the product's category classification, such as \"Books,\" \"Clothing,\" or \"Electronics,\" stored as a non-null, case-insensitive text value.","glossary_terms":["RetailDomainGlossary.ProductCategory"],"cardinality":5,"null_count":0,"data_range":{"min":"Books","max":"Sports"},"data_category":"nominal","semantic_class":"category","unit_context":null,"concept_id":"entity.category","concept_confidence":0.8,"concept_evidence":["name token: category","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: categorical","profile heuristic matched"],"concept_sources":["name","profile","type"],"concept_alias_group":"category"},{"name":"unit_price","type":"numeric(10,2)","nullable":false,"is_incremental":false,"column_description":"The `unit_price` column stores the selling price of a product as a non-null numeric value with up to 10 digits and 2 decimal places, representing a currency amount.","glossary_terms":["RetailDomainGlossary.SellingPrice"],"cardinality":50,"null_count":0,"data_range":{"min":"11.09","max":"490.43"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: price","type hint: numeric(10,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"price"},{"name":"cost_price","type":"numeric(10,2)","nullable":false,"is_incremental":false,"column_description":"The `cost_price` column in the `products` table stores the non-null numeric value representing the purchase cost of a product in currency format with up to 10 digits and 2 decimal places.","glossary_terms":["RetailDomainGlossary.CostPrice"],"cardinality":50,"null_count":0,"data_range":{"min":"5.55","max":"358.59"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: price","type hint: numeric(10,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"price"},{"name":"active","type":"bit","nullable":false,"is_incremental":false,"column_description":"Indicates whether a product is active and available for transactions, stored as a non-nullable boolean value.","glossary_terms":[],"cardinality":1,"null_count":0,"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.0,"concept_evidence":["profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile"],"concept_alias_group":null},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The `created_at` column stores the non-nullable timestamp indicating when a product record was initially created in the system.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":50,"null_count":0,"data_range":{"min":"2021-03-20 15:38:57.201565","max":"2024-12-25 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: products"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The `updated_at` column stores the non-nullable timestamp of the most recent update to a product record in the `products` table.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":50,"null_count":0,"data_range":{"min":"2021-03-20 15:38:57.201565","max":"2024-12-25 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: products"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"weight_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Source weight unit (kg/lb) used for unit inference testing.","glossary_terms":["RetailDomainGlossary.UnitOfMeasure"],"cardinality":0,"null_count":50,"data_category":"nominal","semantic_class":"mass","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":null,"concept_confidence":0.15,"concept_evidence":["value pattern: quantity","ambiguous runner-up concept"],"concept_sources":["values"],"concept_alias_group":null},{"name":"weight_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"column_description":"The `weight_value` column stores the weight of a product as a numeric value with up to 10 digits and 2 decimal places, and it is nullable.","glossary_terms":["RetailDomainGlossary.UnitOfMeasure"],"cardinality":0,"null_count":50,"data_category":"continuous","semantic_class":"mass","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":null,"concept_confidence":0.0,"concept_evidence":["type hint: numeric(10,2)","ambiguous runner-up concept"],"concept_sources":["type"],"concept_alias_group":null},{"name":"length_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"column_description":"Represents the length measurement of a product, stored as a numeric value with up to two decimal places, and may be null if not applicable.","glossary_terms":["RetailDomainGlossary.UnitOfMeasure"],"cardinality":0,"null_count":50,"data_category":"continuous","semantic_class":"length","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":null,"concept_confidence":0.0,"concept_evidence":["type hint: numeric(10,2)","ambiguous runner-up concept"],"concept_sources":["type"],"concept_alias_group":null},{"name":"length_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Source length unit (cm/in) used for unit inference testing.","glossary_terms":["RetailDomainGlossary.UnitOfMeasure"],"cardinality":0,"null_count":50,"data_category":"nominal","semantic_class":"length","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":null,"concept_confidence":0.15,"concept_evidence":["value pattern: quantity","ambiguous runner-up concept"],"concept_sources":["values"],"concept_alias_group":null},{"name":"product_description","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"Stores optional textual details about a product, such as features or specifications.","glossary_terms":[],"cardinality":0,"null_count":50,"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"primary_supplier_id","type":"bigint","nullable":true,"is_incremental":false,"column_description":"Primary supplier relationship used for join candidate detection.","glossary_terms":["RetailDomainGlossary.Supplier"],"cardinality":10,"null_count":0,"data_range":{"min":"33","max":"42"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"}],"table_description":"Master product catalog including physical units for analyzer unit-context testing.","glossary_terms":["RetailDomainGlossary.Product","RetailDomainGlossary.ProductCategory","RetailDomainGlossary.CostPrice","RetailDomainGlossary.UnitOfMeasure"],"primary_keys":["product_id"],"foreign_keys":[{"column":"primary_supplier_id","references":"suppliers.supplier_id"},{"column":"supplier_id","references":"suppliers.supplier_id"}],"row_count":50,"field_classifications":{"category":"categorical","unit_price":"pricing","cost_price":"pricing","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"primary_supplier_id","target_table":"suppliers","target_column":"supplier_id","confidence":"high"},{"column":"supplier_id","target_table":"suppliers","target_column":"supplier_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":16,"mixed_unit_groups":[],"unknown_unit_columns":["length_unit","length_value","weight_unit","weight_value"]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":68,"row_count_projection_2y":86,"row_count_projection_5y":141,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.person_name":1,"entity.category":1,"finance.currency_amount":2,"identifier.foreign_key":3,"identifier.product_code":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":["length_unit","name","product_description","weight_unit"]},"data_quality":{"findings":[{"column":"category","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 5 distinct value(s) ('Books', 'Clothing', 'Electronics', 'Home', 'Sports') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Books","Clothing","Electronics","Home","Sports"],"cardinality":5},{"column":"primary_supplier_id","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 50 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":"active","check":"delete_management","severity":"info","detail":"Active-flag column 'active' (boolean) detected \u2014 rows with active=false are logically deleted. Current distribution: True=50.","recommendation":"Filter on \"active\" = true for current records during ingestion.","delete_strategy":"soft_delete","soft_delete_column":"active","soft_delete_type":"active_flag","has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2},{"column":"weight_unit","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'mass' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"weight_value","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'mass' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"length_value","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'length' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"length_unit","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'length' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."}]}},{"table":"purchase_order_items","schema":"dbo","columns":[{"name":"po_item_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for each purchase order item record in the `purchase_order_items` table.","glossary_terms":[],"cardinality":246,"null_count":0,"data_range":{"min":"268","max":"513"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"po_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Identifier linking each purchase order item to its associated purchase order in the `purchase_orders` table.","glossary_terms":["RetailDomainGlossary.PurchaseOrder"],"cardinality":125,"null_count":0,"data_range":{"min":"128","max":"252"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"product_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Identifier linking each purchase order item to a specific product in the products table.","glossary_terms":["RetailDomainGlossary.Product"],"cardinality":49,"null_count":0,"data_range":{"min":"156","max":"205"},"data_category":"discrete","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"quantity","type":"integer","nullable":false,"is_incremental":false,"column_description":"The \"quantity\" column in the \"purchase_order_items\" table stores the non-null integer value representing the number of units of a product included in a specific purchase order item.","glossary_terms":[],"cardinality":41,"null_count":0,"data_range":{"min":"10","max":"50"},"data_category":"discrete","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: quantity","type hint: integer","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"quantity"},{"name":"unit_cost","type":"numeric(10,2)","nullable":false,"is_incremental":false,"column_description":"Represents the per-unit cost of a product in a purchase order, stored as a non-null numeric value with up to 10 digits and 2 decimal places.","glossary_terms":["RetailDomainGlossary.CostPrice"],"cardinality":49,"null_count":0,"data_range":{"min":"5.55","max":"358.59"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: unit_cost","type hint: numeric(10,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount","table context: purchase_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"unit_cost"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"Records the timestamp when a purchase order item entry is created, stored as a non-nullable datetime value.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":246,"null_count":0,"data_range":{"min":"2026-03-12 15:44:18.668789","max":"2026-03-12 15:45:45.174099"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: purchase_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"Records the timestamp of the most recent update to a purchase order item, ensuring accurate tracking of modifications.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":246,"null_count":0,"data_range":{"min":"2026-03-12 15:44:18.668794","max":"2026-03-12 15:45:45.174104"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: purchase_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"ordered_qty_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"column_description":"The `ordered_qty_value` column stores the numeric quantity value (up to two decimal places) of items ordered in a purchase order, which can be null.","glossary_terms":["RetailDomainGlossary.Quantity"],"cardinality":0,"null_count":246,"data_category":"continuous","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: ordered_qty","type hint: numeric(10,2)","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"ordered_qty"},{"name":"ordered_qty_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Ordered quantity unit (ea/box).","glossary_terms":["RetailDomainGlossary.UnitOfMeasure"],"cardinality":0,"null_count":246,"data_category":"nominal","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: ordered_qty_unit","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity"],"concept_sources":["name","profile","values"],"concept_alias_group":"ordered_qty_unit"}],"table_description":"Line items with order quantities and explicit unit labels.","glossary_terms":["RetailDomainGlossary.OrderLine","RetailDomainGlossary.Quantity","RetailDomainGlossary.UnitOfMeasure","RetailDomainGlossary.PurchaseOrder"],"primary_keys":["po_item_id"],"foreign_keys":[{"column":"po_id","references":"purchase_orders.po_id"},{"column":"product_id","references":"products.product_id"}],"row_count":246,"field_classifications":{"quantity":"quantity","unit_cost":"pricing","created_at":"temporal","updated_at":"temporal","ordered_qty_value":"quantity","ordered_qty_unit":"quantity"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"po_id","target_table":"purchase_orders","target_column":"po_id","confidence":"high</t>
         </is>
       </c>
     </row>
@@ -10442,7 +10442,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>e_fields":false,"row_count_projection_1y":246,"row_count_projection_2y":246,"row_count_projection_5y":246,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"finance.currency_amount":1,"identifier.foreign_key":3,"measure.quantity":3,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"findings":[{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2},{"column":"quantity","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"ordered_qty_value","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"ordered_qty_unit","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."}]}},{"table":"purchase_orders","schema":"dbo","columns":[{"name":"po_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for purchase orders in the system.","glossary_terms":["RetailDomainGlossary.PurchaseOrder"],"cardinality":125,"null_count":0,"data_range":{"min":"128","max":"252"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"supplier_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Identifies the supplier associated with a purchase order, referencing the `supplier_id` column in the `suppliers` table.","glossary_terms":["RetailDomainGlossary.SupplierCode"],"cardinality":10,"null_count":0,"data_range":{"min":"33","max":"42"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Identifies the store associated with the purchase order, referencing the `store_id` column in the `stores` table.","glossary_terms":[],"cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"status","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"Indicates the current state of a purchase order (e.g., \"Ordered,\" \"Received\") as a non-null categorical value.","glossary_terms":["RetailDomainGlossary.OrderStatus"],"cardinality":3,"null_count":0,"data_range":{"min":"Ordered","max":"Received"},"data_category":"nominal","semantic_class":"category","unit_context":null,"concept_id":"entity.status","concept_confidence":1.0,"concept_evidence":["name token: statu","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: categorical","value pattern: status","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"statu"},{"name":"order_date","type":"date","nullable":false,"is_incremental":false,"column_description":"The `order_date` column in the `purchase_orders` table records the date a purchase order was placed, is mandatory, and uses the `date` data type.","glossary_terms":[],"cardinality":123,"null_count":0,"data_range":{"min":"2021-04-09","max":"2026-03-12"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.date_only","concept_confidence":1.0,"concept_evidence":["name token: order_date","type hint: date","legacy field classification: temporal","value pattern: date_only","table context: purchase_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"order_date"},{"name":"expected_date","type":"date","nullable":true,"is_incremental":false,"column_description":"The `expected_date` column in the `purchase_orders` table records the anticipated delivery date for a purchase order, allowing null values.","glossary_terms":["RetailDomainGlossary.OrderDeliveryRelationship"],"cardinality":123,"null_count":0,"data_range":{"min":"2021-04-27","max":"2026-03-31"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.date_only","concept_confidence":1.0,"concept_evidence":["name token: expected_date","type hint: date","legacy field classification: temporal","value pattern: date_only","table context: purchase_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"expected_date"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The `created_at` column stores the non-nullable timestamp indicating when a purchase order record was initially created in the system.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":123,"null_count":0,"data_range":{"min":"2021-04-09 15:38:57.201565","max":"2026-03-12 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: purchase_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The `updated_at` column stores the non-nullable timestamp of the most recent update to a purchase order record.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":123,"null_count":0,"data_range":{"min":"2021-04-09 15:38:57.201565","max":"2026-03-12 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: purchase_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"approver_employee_id","type":"bigint","nullable":true,"is_incremental":false,"column_description":"Approver employee foreign key for procurement workflow.","glossary_terms":[],"cardinality":0,"null_count":125,"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"}],"table_description":"Procurement headers including approver employee relationship.","glossary_terms":["RetailDomainGlossary.PurchaseOrder","RetailDomainGlossary.OrderStatus"],"primary_keys":["po_id"],"foreign_keys":[{"column":"approver_employee_id","references":"employees.employee_id"},{"column":"store_id","references":"stores.store_id"},{"column":"supplier_id","references":"suppliers.supplier_id"}],"row_count":125,"field_classifications":{"status":"categorical","order_date":"temporal","expected_date":"temporal","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"approver_employee_id","target_table":"employees","target_column":"employee_id","confidence":"high"},{"column":"store_id","target_table":"stores","target_column":"store_id","confidence":"high"},{"column":"supplier_id","target_table":"suppliers","target_column":"supplier_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":9,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":155,"row_count_projection_2y":185,"row_count_projection_5y":276,"partition_columns_candidates":["order_date","expected_date","created_at","updated_at"],"classification_summary":{"concept_counts":{"entity.status":1,"identifier.foreign_key":4,"temporal.created_at":1,"temporal.date_only":2,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"findings":[{"column":"status","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 3 distinct value(s) ('Ordered', 'Pending', 'Received') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Ordered","Pending","Received"],"cardinality":3},{"column":"expected_date","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 125 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":"order_date","check":"late_arriving_data","severity":"info","detail":"Minor arrival delay \u2014 max lag between 'order_date' and 'created_at' is 15.7h (avg 15.7h, P95 15.7h).","recommendation":"Use 'created_at' as the watermark (preferred). If using 'order_date', add a 1\u20132 day lookback buffer.","business_date_column":"order_date","system_ts_column":"created_at","lag_stats":{"total_rows_compared":125,"min_lag_hours":15.65,"avg_lag_hours":15.65,"p95_lag_hours":15.65,"max_lag_hours":15.65,"max_lag_days":0.7,"rows_late_over_1d":0,"rows_late_over_7d":0},"recommended_lookback_days":2},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}},{"table":"sales_order_items","schema":"dbo","columns":[{"name":"sales_order_item_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for each sales order item in the sales_order_items table.","glossary_terms":["RetailDomainGlossary.OrderLine"],"cardinality":508,"null_count":0,"data_range":{"min":"497","max":"1004"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"sales_order_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Identifier linking each sales order item to its associated sales order in the `sales_orders` table.","glossary_terms":["RetailDomainGlossary.SalesOrder"],"cardinality":200,"null_count":0,"data_range":{"min":"375","max":"574"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"product_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Identifier for the product associated with the sales order item, referencing the primary key in the products table.","glossary_terms":["RetailDomainGlossary.ProductCategory"],"cardinality":50,"null_count":0,"data_range":{"min":"156","max":"205"},"data_category":"discrete","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"quantity","type":"integer","nullable":false,"is_incremental":false,"column_description":"The \"quantity\" column in the \"sales_order_items\" table stores the number of units of a product included in a sales order item, represented as a non-null integer.","glossary_terms":["RetailDomainGlossary.OrderLine"],"cardinality":5,"null_count":0,"data_range":{"min":"1","max":"5"},"data_category":"discrete","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: quantity","type hint: integer","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"quantity"},{"name":"unit_price","type":"numeric(15,2)","nullable":false,"is_incremental":false,"column_description":"The `unit_price` column in the `sales_order_items` table stores the per-unit selling price of a product in the sales order as a non-null numeric value with two decimal places.","glossary_terms":["RetailDomainGlossary.SellingPrice"],"cardinality":50,"null_count":0,"data_range":{"min":"11.09","max":"490.43"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: price","type hint: numeric(15,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount","table context: sales_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"price"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"Records the timestamp when a sales order item entry is created, ensuring accurate tracking of creation events.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":508,"null_count":0,"data_range":{"min":"2026-03-12 15:41:01.155388","max":"2026-03-12 15:43:38.264437"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: sales_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The `updated_at` column in the `sales_order_items` table stores the non-nullable timestamp of the most recent update to a sales order item record.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":508,"null_count":0,"data_range":{"min":"2026-03-12 15:41:01.155390","max":"2026-03-12 15:43:38.264447"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: sales_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"sold_qty_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"column_description":"The `sold_qty_value` column stores the numeric value representing the quantity of a product sold in a sales order item, allowing up to two decimal places, and can be null.","glossary_terms":["RetailDomainGlossary.OrderLine"],"cardinality":0,"null_count":508,"data_category":"continuous","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: sold_qty","type hint: numeric(10,2)","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"sold_qty"},{"name":"sold_qty_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Sold quantity unit (ea/box).","glossary_terms":["RetailDomainGlossary.UnitOfMeasure"],"cardinality":0,"null_count":508,"data_category":"nominal","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: sold_qty_unit","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity"],"concept_sources":["name","profile","values"],"concept_alias_group":"sold_qty_unit"}],"table_description":"Sales line items with sold quantity and explicit unit labels.","glossary_terms":["RetailDomainGlossary.OrderLine","RetailDomainGlossary.SalesOrder","RetailDomainGlossary.UnitOfMeasure"],"primary_keys":["sales_order_item_id"],"foreign_keys":[{"column":"product_id","references":"products.product_id"},{"column":"sales_order_id","references":"sales_orders.sales_order_id"}],"row_count":508,"field_classifications":{"quantity":"quantity","unit_price":"pricing","created_at":"temporal","updated_at":"temporal","sold_qty_value":"quantity","sold_qty_unit":"quantity"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"product_id","target_table":"products","target_column":"product_id","confidence":"high"},{"column":"sales_order_id","target_table":"sales_orders","target_column":"sales_order_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":9,"mixed_unit_groups":[],"unknown_unit_columns":["quantity","sold_qty_unit","sold_qty_value"]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":508,"row_count_projection_2y":508,"row_count_projection_5y":508,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"finance.currency_amount":1,"identifier.foreign_key":3,"measure.quantity":3,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"findings":[{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2},{"column":"quantity","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"sold_qty_value","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"sold_qty_unit","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."}]}},{"table":"sales_orders","schema":"dbo","columns":[{"name":"sales_order_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for each sales order in the system, serving as the primary key for the sales_orders table.","glossary_terms":["RetailDomainGlossary.SalesOrder"],"cardinality":200,"null_count":0,"data_range":{"min":"375","max":"574"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Identifies the store associated with a sales order, referencing the `store_id` column in the `stores` table.","glossary_terms":["RetailDomainGlossary.SalesChannel"],"cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"customer_id","type":"bigint","nullable":true,"is_incremental":false,"column_description":"Represents the identifier of the customer associated with a sales order, referencing the `customer_id` column in the `customers` table, and may be null if no customer is linked.","glossary_terms":["RetailDomainGlossary.CustomerIdentifier"],"cardinality":76,"null_count":0,"data_range":{"min":"404","max":"502"},"data_category":"discrete","semantic_class":"customer_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"employee_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Represents the unique identifier of the employee associated with the sales order, referencing the `employees.employee_id` column.","glossary_terms":[],"cardinality":20,"null_count":0,"data_range":{"min":"64","max":"83"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"order_date","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The `order_date` column records the date and time when a sales order was placed, stored as a non-nullable `datetime2` value.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":191,"null_count":0,"data_range":{"min":"2021-03-14 15:38:57.201565","max":"2026-03-11 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.date_only","concept_confidence":0.9,"concept_evidence":["name token: order_date","type hint: datetime2","legacy field classification: temporal","table context: sales_orders","cross-table consensus: 2 similar columns"],"concept_sources":["cross_table_consensus","name","profile","table_context","type"],"concept_alias_group":"order_date"},{"name":"status","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"Indicates the current state of a sales order, such as 'Pending' or 'Completed', stored as a non-nullable text category.","glossary_terms":["RetailDomainGlossary.OrderStatus"],"cardinality":3,"null_count":0,"data_range":{"min":"Completed","max":"Shipped"},"data_category":"nominal","semantic_class":"category","unit_context":null,"concept_id":"entity.status","concept_confidence":1.0,"concept_evidence":["name token: statu","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: categorical","value pattern: status","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"statu"},{"name":"total_amount","type":"numeric(12,2)","nullable":false,"is_incremental":false,"column_description":"The `total_amount` column in the `sales_orders` table stores the non-nullable total monetary value of a sales order as a numeric value with up to 12 digits and 2 decimal places.","glossary_terms":["RetailDomainGlossary.SalesOrder"],"cardinality":200,"null_count":0,"data_range":{"min":"66.47","max":"998.76"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: amount","type hint: numeric(12,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount","table context: sales_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"amount"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The `created_at` column records the timestamp when a sales order record is initially created, stored as a non-nullable `datetime2` value.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardina</t>
+          <t>"},{"column":"product_id","target_table":"products","target_column":"product_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":9,"mixed_unit_groups":[],"unknown_unit_columns":["ordered_qty_unit","ordered_qty_value","quantity"]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":246,"row_count_projection_2y":246,"row_count_projection_5y":246,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"finance.currency_amount":1,"identifier.foreign_key":3,"measure.quantity":3,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"findings":[{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2},{"column":"quantity","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"ordered_qty_value","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"ordered_qty_unit","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."}]}},{"table":"purchase_orders","schema":"dbo","columns":[{"name":"po_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for purchase orders in the system.","glossary_terms":["RetailDomainGlossary.PurchaseOrder"],"cardinality":125,"null_count":0,"data_range":{"min":"128","max":"252"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"supplier_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Identifies the supplier associated with a purchase order, referencing the `supplier_id` column in the `suppliers` table.","glossary_terms":["RetailDomainGlossary.Supplier"],"cardinality":10,"null_count":0,"data_range":{"min":"33","max":"42"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Identifier for the store associated with the purchase order, referencing the `store_id` column in the `stores` table.","glossary_terms":["RetailDomainGlossary.StoreLocation"],"cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"status","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"Indicates the current state of a purchase order (e.g., \"Ordered\", \"Received\"), stored as a non-nullable text category.","glossary_terms":["RetailDomainGlossary.OrderStatus"],"cardinality":3,"null_count":0,"data_range":{"min":"Ordered","max":"Received"},"data_category":"nominal","semantic_class":"category","unit_context":null,"concept_id":"entity.status","concept_confidence":1.0,"concept_evidence":["name token: statu","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: categorical","value pattern: status","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"statu"},{"name":"order_date","type":"date","nullable":false,"is_incremental":false,"column_description":"The `order_date` column in the `purchase_orders` table records the date a purchase order was placed and cannot be null.","glossary_terms":[],"cardinality":123,"null_count":0,"data_range":{"min":"2021-04-09","max":"2026-03-12"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.date_only","concept_confidence":1.0,"concept_evidence":["name token: order_date","type hint: date","legacy field classification: temporal","value pattern: date_only","table context: purchase_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"order_date"},{"name":"expected_date","type":"date","nullable":true,"is_incremental":false,"column_description":"The `expected_date` column in the `purchase_orders` table records the anticipated delivery date for a purchase order, allowing null values.","glossary_terms":[],"cardinality":123,"null_count":0,"data_range":{"min":"2021-04-27","max":"2026-03-31"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.date_only","concept_confidence":1.0,"concept_evidence":["name token: expected_date","type hint: date","legacy field classification: temporal","value pattern: date_only","table context: purchase_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"expected_date"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The `created_at` column records the timestamp when a purchase order record was initially created, using a non-nullable `datetime2` data type.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":123,"null_count":0,"data_range":{"min":"2021-04-09 15:38:57.201565","max":"2026-03-12 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: purchase_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The `updated_at` column stores the non-null timestamp indicating the last modification date and time of a purchase order record.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":123,"null_count":0,"data_range":{"min":"2021-04-09 15:38:57.201565","max":"2026-03-12 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: purchase_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"approver_employee_id","type":"bigint","nullable":true,"is_incremental":false,"column_description":"Approver employee foreign key for procurement workflow.","glossary_terms":[],"cardinality":0,"null_count":125,"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"}],"table_description":"Procurement headers including approver employee relationship.","glossary_terms":["RetailDomainGlossary.PurchaseOrder","RetailDomainGlossary.Supplier","RetailDomainGlossary.StoreLocation","RetailDomainGlossary.OrderStatus"],"primary_keys":["po_id"],"foreign_keys":[{"column":"approver_employee_id","references":"employees.employee_id"},{"column":"store_id","references":"stores.store_id"},{"column":"supplier_id","references":"suppliers.supplier_id"}],"row_count":125,"field_classifications":{"status":"categorical","order_date":"temporal","expected_date":"temporal","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"approver_employee_id","target_table":"employees","target_column":"employee_id","confidence":"high"},{"column":"store_id","target_table":"stores","target_column":"store_id","confidence":"high"},{"column":"supplier_id","target_table":"suppliers","target_column":"supplier_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":9,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":155,"row_count_projection_2y":185,"row_count_projection_5y":276,"partition_columns_candidates":["order_date","expected_date","created_at","updated_at"],"classification_summary":{"concept_counts":{"entity.status":1,"identifier.foreign_key":4,"temporal.created_at":1,"temporal.date_only":2,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"findings":[{"column":"status","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 3 distinct value(s) ('Ordered', 'Pending', 'Received') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Ordered","Pending","Received"],"cardinality":3},{"column":"expected_date","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 125 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":"order_date","check":"late_arriving_data","severity":"info","detail":"Minor arrival delay \u2014 max lag between 'order_date' and 'created_at' is 15.7h (avg 15.7h, P95 15.7h).","recommendation":"Use 'created_at' as the watermark (preferred). If using 'order_date', add a 1\u20132 day lookback buffer.","business_date_column":"order_date","system_ts_column":"created_at","lag_stats":{"total_rows_compared":125,"min_lag_hours":15.65,"avg_lag_hours":15.65,"p95_lag_hours":15.65,"max_lag_hours":15.65,"max_lag_days":0.7,"rows_late_over_1d":0,"rows_late_over_7d":0},"recommended_lookback_days":2},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}},{"table":"sales_order_items","schema":"dbo","columns":[{"name":"sales_order_item_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for each item in a sales order, serving as the primary key for the `sales_order_items` table.","glossary_terms":[],"cardinality":508,"null_count":0,"data_range":{"min":"497","max":"1004"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"sales_order_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Identifier linking each sales order item to its associated sales order in the `sales_orders` table.","glossary_terms":["RetailDomainGlossary.SalesOrder"],"cardinality":200,"null_count":0,"data_range":{"min":"375","max":"574"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"product_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Identifies the product associated with a sales order item, referencing the `products.product_id` column.","glossary_terms":["RetailDomainGlossary.Product"],"cardinality":50,"null_count":0,"data_range":{"min":"156","max":"205"},"data_category":"discrete","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"quantity","type":"integer","nullable":false,"is_incremental":false,"column_description":"The \"quantity\" column in the \"sales_order_items\" table stores the non-null integer value representing the number of units of a product included in a specific sales order item.","glossary_terms":["RetailDomainGlossary.Quantity"],"cardinality":5,"null_count":0,"data_range":{"min":"1","max":"5"},"data_category":"discrete","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: quantity","type hint: integer","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"quantity"},{"name":"unit_price","type":"numeric(15,2)","nullable":false,"is_incremental":false,"column_description":"The \"unit_price\" column stores the non-null numeric price per unit of a product in a sales order item, represented as a currency amount with up to 15 digits and 2 decimal places.","glossary_terms":["RetailDomainGlossary.SellingPrice"],"cardinality":50,"null_count":0,"data_range":{"min":"11.09","max":"490.43"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: price","type hint: numeric(15,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount","table context: sales_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"price"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The `created_at` column records the timestamp when a sales order item was created, stored as a non-nullable `datetime2` value.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":508,"null_count":0,"data_range":{"min":"2026-03-12 15:41:01.155388","max":"2026-03-12 15:43:38.264437"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: sales_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The `updated_at` column stores the non-nullable timestamp of the most recent update to a sales order item record in the `sales_order_items` table.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":508,"null_count":0,"data_range":{"min":"2026-03-12 15:41:01.155390","max":"2026-03-12 15:43:38.264447"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: sales_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"sold_qty_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"column_description":"The `sold_qty_value` column stores the numeric value representing the quantity of a product sold in a sales order item, allowing up to two decimal places, and can be null.","glossary_terms":["RetailDomainGlossary.Quantity"],"cardinality":0,"null_count":508,"data_category":"continuous","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: sold_qty","type hint: numeric(10,2)","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"sold_qty"},{"name":"sold_qty_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Sold quantity unit (ea/box).","glossary_terms":["RetailDomainGlossary.UnitOfMeasure"],"cardinality":0,"null_count":508,"data_category":"nominal","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: sold_qty_unit","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity"],"concept_sources":["name","profile","values"],"concept_alias_group":"sold_qty_unit"}],"table_description":"Sales line items with sold quantity and explicit unit labels.","glossary_terms":["RetailDomainGlossary.OrderLine","RetailDomainGlossary.Quantity","RetailDomainGlossary.UnitOfMeasure","RetailDomainGlossary.Sale"],"primary_keys":["sales_order_item_id"],"foreign_keys":[{"column":"product_id","references":"products.product_id"},{"column":"sales_order_id","references":"sales_orders.sales_order_id"}],"row_count":508,"field_classifications":{"quantity":"quantity","unit_price":"pricing","created_at":"temporal","updated_at":"temporal","sold_qty_value":"quantity","sold_qty_unit":"quantity"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"product_id","target_table":"products","target_column":"product_id","confidence":"high"},{"column":"sales_order_id","target_table":"sales_orders","target_column":"sales_order_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":9,"mixed_unit_groups":[],"unknown_unit_columns":["quantity","sold_qty_unit","sold_qty_value"]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":508,"row_count_projection_2y":508,"row_count_projection_5y":508,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"finance.currency_amount":1,"identifier.foreign_key":3,"measure.quantity":3,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"findings":[{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2},{"column":"quantity","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"sold_qty_value","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"sold_qty_unit","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."}]}},{"table":"sales_orders","schema":"dbo","columns":[{"name":"sales_order_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for each sales order in the system.","glossary_terms":["RetailDomainGlossary.SalesOrder"],"cardinality":200,"null_count":0,"data_range":{"min":"375","max":"574"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Identifies the store associated with a sales order, referencing the `store_id` column in the `stores` table.","glossary_terms":["RetailDomainGlossary.StoreLocation"],"cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"customer_id","type":"bigint","nullable":true,"is_incremental":false,"column_description":"Identifies the customer associated with a sales order, referencing the `customer_id` column in the `customers` table; nullable to accommodate orders without a registered customer.","glossary_terms":["RetailDomainGlossary.Customer","RetailDomainGlossary.CustomerIdentifier"],"cardinality":76,"null_count":0,"data_range":{"min":"404","max":"502"},"data_category":"discrete","semantic_class":"customer_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"employee_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Represents the unique identifier of the employee associated with the sales order, referencing the `employees.employee_id` column.","glossary_terms":[],"cardinality":20,"null_count":0,"data_range":{"min":"64","max":"83"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"order_date","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The `order_date` column records the date and time when a sales order was placed, stored as a non-nullable `datetime2` value.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":191,"null_count":0,"data_range":{"min":"2021-03-14 15:38:57.201565","max":"2026-03-11 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.date_only","concept_confidence":0.9,"concept_evidence":["name token: order_date","type hint: datetime2","legacy field classification: temporal","table context: sales_orders","cross-table consensus: 2 similar columns"],"concept_sources":["cross_table_consensus","name","profile","table_context","type"],"concept_alias_group":"order_date"},{"name":"status","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"Indicates the current state of a sales order, such as 'Pending' or 'Completed', stored as a non-nullable text category.","glossary_terms":["RetailDomainGlossary.OrderStatus"],"cardinality":3,"null_count":0,"data_range":{"min":"Completed","max":"Shipped"},"data_category":"nominal","semantic_class":"category","unit_context":null,"concept_id":"entity.status","concept_confidence":1.0,"concept_evidence":["name token: statu","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: categorical","value pattern: status","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"statu"},{"name":"total_amount","type":"numeric(12,2)","nullable":false,"is_incremental":false,"column_description":"The `total_amount` column in the `sales_orders` table stores the non-null total monetary value of a sales order as a numeric value with up to 12 digits and 2 decimal places.","glossary_terms":["RetailDomainGlossary.NetSales"],"cardinality":200,"null_count":0,"data_range":{"min":"66.47","max":"998.76"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: amount","type hint: numeric(12,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount","table context: sales_orde</t>
         </is>
       </c>
     </row>
@@ -10452,7 +10452,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>lity":191,"null_count":0,"data_range":{"min":"2021-03-14 15:38:57.201565","max":"2026-03-11 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: sales_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The `updated_at` column records the timestamp of the most recent update to a sales order, stored as a non-nullable datetime2 value.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":191,"null_count":0,"data_range":{"min":"2021-03-14 15:38:57.201565","max":"2026-03-11 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: sales_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"sales_rep_employee_id","type":"bigint","nullable":true,"is_incremental":false,"column_description":"Sales representative foreign key for order ownership.","glossary_terms":[],"cardinality":0,"null_count":200,"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"}],"table_description":"Sales headers including assigned sales representative relationship.","glossary_terms":["RetailDomainGlossary.SalesOrder","RetailDomainGlossary.CustomerIdentifier","RetailDomainGlossary.OrderStatus"],"primary_keys":["sales_order_id"],"foreign_keys":[{"column":"customer_id","references":"customers.customer_id"},{"column":"employee_id","references":"employees.employee_id"},{"column":"sales_rep_employee_id","references":"employees.employee_id"},{"column":"store_id","references":"stores.store_id"}],"row_count":200,"field_classifications":{"customer_id":"identifier","order_date":"temporal","status":"categorical","total_amount":"pricing","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"customer_id","target_table":"customers","target_column":"customer_id","confidence":"high"},{"column":"employee_id","target_table":"employees","target_column":"employee_id","confidence":"high"},{"column":"sales_rep_employee_id","target_table":"employees","target_column":"employee_id","confidence":"high"},{"column":"store_id","target_table":"stores","target_column":"store_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":10,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":242,"row_count_projection_2y":284,"row_count_projection_5y":412,"partition_columns_candidates":["order_date","created_at","updated_at"],"classification_summary":{"concept_counts":{"entity.status":1,"finance.currency_amount":1,"identifier.foreign_key":5,"temporal.created_at":1,"temporal.date_only":1,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"findings":[{"column":"status","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 3 distinct value(s) ('Completed', 'Pending', 'Shipped') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Completed","Pending","Shipped"],"cardinality":3},{"column":"customer_id","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 200 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":"order_date","check":"late_arriving_data","severity":"info","detail":"Data arrives promptly \u2014 max lag between 'order_date' and 'created_at' is 0.0h. Standard watermarking on 'created_at' is safe.","recommendation":"Use 'created_at' as the incremental watermark. No special lookback window needed.","business_date_column":"order_date","system_ts_column":"created_at","lag_stats":{"total_rows_compared":200,"min_lag_hours":0.0,"avg_lag_hours":0.0,"p95_lag_hours":0.0,"max_lag_hours":0.0,"max_lag_days":0.0,"rows_late_over_1d":0,"rows_late_over_7d":0},"recommended_lookback_days":1},{"column":null,"check":"timezone","severity":"info","detail":"All 3 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"order_date","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":3}]}},{"table":"stores","schema":"dbo","columns":[{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for each store in the retail operations system.","glossary_terms":["RetailDomainGlossary.StoreCode"],"cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"The \"name\" column in the \"stores\" table is a non-nullable nvarchar field storing the name of a retail store.","glossary_terms":[],"cardinality":5,"null_count":0,"data_range":{"min":"Airport Shop","max":"Suburb Store"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"name"},{"name":"code","type":"nvarchar(450)","nullable":false,"is_incremental":false,"column_description":"Unique alphanumeric identifier for a store, used for internal reference and operations.","glossary_terms":["RetailDomainGlossary.StoreCode"],"cardinality":5,"null_count":0,"data_range":{"min":"AIR","max":"SUB"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: nvarchar(450)","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"address","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"The \"address\" column in the \"stores\" table stores the street address of a retail store location as a nullable Unicode string.","glossary_terms":[],"cardinality":5,"null_count":0,"data_range":{"min":"1 Main St","max":"5 Main St"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.address","concept_confidence":0.55,"concept_evidence":["name token: address","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"address"},{"name":"city","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"The \"city\" column in the \"stores\" table stores the name of the city where a store is located, allowing null values.","glossary_terms":[],"cardinality":3,"null_count":0,"data_range":{"min":"Cork","max":"Limerick"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"state","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"The \"state\" column in the \"stores\" table stores the name of the state or province where a store is located, allowing null values.","glossary_terms":[],"cardinality":3,"null_count":0,"data_range":{"min":"Connacht","max":"Munster"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"postal_code","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"The \"postal_code\" column in the \"stores\" table stores the postal or ZIP code of a store location as a nullable string.","glossary_terms":[],"cardinality":5,"null_count":0,"data_range":{"min":"10000","max":"10004"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.address","concept_confidence":0.55,"concept_evidence":["name token: postal_code","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"postal_code"},{"name":"phone","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"The \"phone\" column in the \"stores\" table stores the contact phone number of a store as a nullable nvarchar value.","glossary_terms":[],"cardinality":5,"null_count":0,"data_range":{"min":"555-3000","max":"555-3004"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.phone","concept_confidence":1.0,"concept_evidence":["name token: phone","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: contact","value pattern: phone","sensitive hint: pii_contact"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"phone"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The `created_at` column stores the non-nullable timestamp indicating when a store record was initially created in the system.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":5,"null_count":0,"data_range":{"min":"2021-07-26 15:38:57.201565","max":"2025-01-31 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: stores"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The `updated_at` column records the timestamp of the most recent update to a store's record and cannot be null.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":5,"null_count":0,"data_range":{"min":"2021-07-26 15:38:57.201565","max":"2025-01-31 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: stores"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"}],"table_description":"The \"stores\" table stores information about retail store locations, including unique identifiers, names, codes, addresses, contact details, and timestamps for record creation and updates.","glossary_terms":["RetailDomainGlossary.StoreCode"],"primary_keys":["store_id"],"foreign_keys":[],"row_count":5,"field_classifications":{"phone":"contact","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{"address":"pii_address","postal_code":"pii_address","phone":"pii_contact"},"incremental_columns":["updated_at"],"join_candidates":[],"unit_summary":{"columns_with_units":0,"columns_without_units":10,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":false,"has_sensitive_fields":true,"row_count_projection_1y":17,"row_count_projection_2y":29,"row_count_projection_5y":65,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.address":2,"contact.person_name":1,"contact.phone":1,"identifier.foreign_key":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":["address","city","code","name","postal_code","state"]},"data_quality":{"findings":[{"column":"city","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 3 distinct value(s) ('Cork', 'Galway', 'Limerick') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Cork","Galway","Limerick"],"cardinality":3},{"column":"state","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 3 distinct value(s) ('Connacht', 'Leinster', 'Munster') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Connacht","Leinster","Munster"],"cardinality":3},{"column":"postal_code","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 5 distinct value(s) ('10000', '10001', '10002', '10003', '10004') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["10000","10001","10002","10003","10004"],"cardinality":5},{"column":"address","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"city","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"state","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"postal_code","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"phone","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}},{"table":"suppliers","schema":"dbo","columns":[{"name":"supplier_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for each supplier, serving as the primary key in the suppliers table.","glossary_terms":["RetailDomainGlossary.SupplierCode"],"cardinality":10,"null_count":0,"data_range":{"min":"33","max":"42"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"The \"name\" column in the \"suppliers\" table is a non-nullable nvarchar field intended to store the name of the supplier, though sample data indicates it is currently unused.","glossary_terms":[],"cardinality":10,"null_count":0,"data_range":{"min":"Supplier 1","max":"Supplier 9"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"name"},{"name":"contact_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"Stores the name of the primary contact person for a supplier, allowing null values.","glossary_terms":[],"cardinality":0,"null_count":10,"data_category":"nominal","semantic_class":"person_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: contact_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"contact_name"},{"name":"email","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"The \"email\" column in the \"suppliers\" table stores the email address of a supplier as a nullable nvarchar value for contact purposes.","glossary_terms":[],"cardinality":10,"null_count":0,"data_range":{"min":"supplier1@example.com","max":"supplier9@example.com"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.email","concept_confidence":1.0,"concept_evidence":["name token: email","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: contact","value pattern: email","sensitive hint: pii_contact"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"email"},{"name":"phone","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"The \"phone\" column in the \"suppliers\" table stores the contact phone number of a supplier as a nullable string.","glossary_terms":[],"cardinality":10,"null_count":0,"data_range":{"min":"555-2001","max":"555-2010"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.phone","concept_confidence":1.0,"concept_evidence":["name token: phone","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: contact","value pattern: phone","sensitive hint: pii_contact"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"phone"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"Records the timestamp when a supplier entry is initially created in the system, stored as a non-nullable datetime value.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":10,"null_count":0,"data_range":{"min":"2021-03-22 15:38:57.201565","max":"2024-02-25 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: suppliers"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The `updated_at` column stores the non-nullable timestamp of the most recent update to a supplier record in the `suppliers` table.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":10,"null_count":0,"data_range":{"min":"2021-03-22 15:38:57.201565","max":"2024-02-25 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: suppliers"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"}],"table_description":"The \"suppliers\" table stores information about suppliers, including their unique identifier, name, contact details, and timestamps for record creation and updates.","glossary_terms":["RetailDomainGlossary.SupplierCode"],"primary_keys":["supplier_id"],"foreign_keys":[],"row_count":10,"field_classifications":{"contact_name":"person_name","email":"contact","phone":"contact","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{"email":"pii_contact","phone":"pii_contact"},"incremental_columns":["updated_at"],"join_candidates":[],"unit_summary":{"columns_with_units":0,"columns_without_units":7,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":false,"has_sensitive_fields":true,"row_count_projection_1y":22,"row_count_projection_2y":35,"row_count_projection_5y":74,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.email":1,"contact.person_name":2,"contact.phone":1,"identifier.foreign_key":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":["contact_name","name"]},"data_quality":{"findings":[{"column":"email","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 10 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"phone","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 10 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}}]}</t>
+          <t>rs"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"amount"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The `created_at` column in the `sales_orders` table stores the non-nullable timestamp indicating when the sales order record was initially created.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":191,"null_count":0,"data_range":{"min":"2021-03-14 15:38:57.201565","max":"2026-03-11 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: sales_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The `updated_at` column records the timestamp of the most recent update to a sales order, stored as a non-nullable datetime2 value.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":191,"null_count":0,"data_range":{"min":"2021-03-14 15:38:57.201565","max":"2026-03-11 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: sales_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"sales_rep_employee_id","type":"bigint","nullable":true,"is_incremental":false,"column_description":"Sales representative foreign key for order ownership.","glossary_terms":[],"cardinality":0,"null_count":200,"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"}],"table_description":"Sales headers including assigned sales representative relationship.","glossary_terms":["RetailDomainGlossary.SalesOrder"],"primary_keys":["sales_order_id"],"foreign_keys":[{"column":"customer_id","references":"customers.customer_id"},{"column":"employee_id","references":"employees.employee_id"},{"column":"sales_rep_employee_id","references":"employees.employee_id"},{"column":"store_id","references":"stores.store_id"}],"row_count":200,"field_classifications":{"customer_id":"identifier","order_date":"temporal","status":"categorical","total_amount":"pricing","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"customer_id","target_table":"customers","target_column":"customer_id","confidence":"high"},{"column":"employee_id","target_table":"employees","target_column":"employee_id","confidence":"high"},{"column":"sales_rep_employee_id","target_table":"employees","target_column":"employee_id","confidence":"high"},{"column":"store_id","target_table":"stores","target_column":"store_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":10,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":242,"row_count_projection_2y":284,"row_count_projection_5y":412,"partition_columns_candidates":["order_date","created_at","updated_at"],"classification_summary":{"concept_counts":{"entity.status":1,"finance.currency_amount":1,"identifier.foreign_key":5,"temporal.created_at":1,"temporal.date_only":1,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"findings":[{"column":"status","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 3 distinct value(s) ('Completed', 'Pending', 'Shipped') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Completed","Pending","Shipped"],"cardinality":3},{"column":"customer_id","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 200 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":"order_date","check":"late_arriving_data","severity":"info","detail":"Data arrives promptly \u2014 max lag between 'order_date' and 'created_at' is 0.0h. Standard watermarking on 'created_at' is safe.","recommendation":"Use 'created_at' as the incremental watermark. No special lookback window needed.","business_date_column":"order_date","system_ts_column":"created_at","lag_stats":{"total_rows_compared":200,"min_lag_hours":0.0,"avg_lag_hours":0.0,"p95_lag_hours":0.0,"max_lag_hours":0.0,"max_lag_days":0.0,"rows_late_over_1d":0,"rows_late_over_7d":0},"recommended_lookback_days":1},{"column":null,"check":"timezone","severity":"info","detail":"All 3 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"order_date","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":3}]}},{"table":"stores","schema":"dbo","columns":[{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for each store in the retail operations system.","glossary_terms":["RetailDomainGlossary.StoreLocation"],"cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"The \"name\" column in the \"stores\" table is a non-nullable nvarchar field that stores the name of a retail store.","glossary_terms":["RetailDomainGlossary.PhysicalStore"],"cardinality":5,"null_count":0,"data_range":{"min":"Airport Shop","max":"Suburb Store"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"name"},{"name":"code","type":"nvarchar(450)","nullable":false,"is_incremental":false,"column_description":"Unique alphanumeric identifier for a store, used to distinguish stores within the retail system.","glossary_terms":["RetailDomainGlossary.StoreCode"],"cardinality":5,"null_count":0,"data_range":{"min":"AIR","max":"SUB"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: nvarchar(450)","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"address","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"The \"address\" column in the \"stores\" table stores the street address of a retail store location as a nullable Unicode string.","glossary_terms":[],"cardinality":5,"null_count":0,"data_range":{"min":"1 Main St","max":"5 Main St"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.address","concept_confidence":0.55,"concept_evidence":["name token: address","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"address"},{"name":"city","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"The \"city\" column in the \"stores\" table stores the name of the city where a store is located, allowing null values.","glossary_terms":[],"cardinality":3,"null_count":0,"data_range":{"min":"Cork","max":"Limerick"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"state","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"The \"state\" column in the \"stores\" table stores the name of the state or province where a store is located, allowing null values.","glossary_terms":["RetailDomainGlossary.StoreLocation"],"cardinality":3,"null_count":0,"data_range":{"min":"Connacht","max":"Munster"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"postal_code","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"The \"postal_code\" column in the \"stores\" table stores the postal or ZIP code of a store location as a nullable nvarchar value.","glossary_terms":[],"cardinality":5,"null_count":0,"data_range":{"min":"10000","max":"10004"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.address","concept_confidence":0.55,"concept_evidence":["name token: postal_code","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"postal_code"},{"name":"phone","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"Stores.phone is an optional nvarchar column storing the contact phone number for a store location.","glossary_terms":[],"cardinality":5,"null_count":0,"data_range":{"min":"555-3000","max":"555-3004"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.phone","concept_confidence":1.0,"concept_evidence":["name token: phone","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: contact","value pattern: phone","sensitive hint: pii_contact"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"phone"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The `created_at` column in the `stores` table records the non-nullable timestamp indicating when a store record was initially created.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":5,"null_count":0,"data_range":{"min":"2021-07-26 15:38:57.201565","max":"2025-01-31 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: stores"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The `updated_at` column records the timestamp of the most recent update to a store's record and cannot be null.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":5,"null_count":0,"data_range":{"min":"2021-07-26 15:38:57.201565","max":"2025-01-31 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: stores"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"}],"table_description":"The \"stores\" table stores information about retail store locations, including unique identifiers, names, addresses, contact details, and timestamps for record creation and updates.","glossary_terms":["RetailDomainGlossary.PhysicalStore","RetailDomainGlossary.StoreLocation","RetailDomainGlossary.StoreCode"],"primary_keys":["store_id"],"foreign_keys":[],"row_count":5,"field_classifications":{"phone":"contact","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{"address":"pii_address","postal_code":"pii_address","phone":"pii_contact"},"incremental_columns":["updated_at"],"join_candidates":[],"unit_summary":{"columns_with_units":0,"columns_without_units":10,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":false,"has_sensitive_fields":true,"row_count_projection_1y":17,"row_count_projection_2y":29,"row_count_projection_5y":65,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.address":2,"contact.person_name":1,"contact.phone":1,"identifier.foreign_key":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":["address","city","code","name","postal_code","state"]},"data_quality":{"findings":[{"column":"city","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 3 distinct value(s) ('Cork', 'Galway', 'Limerick') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Cork","Galway","Limerick"],"cardinality":3},{"column":"state","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 3 distinct value(s) ('Connacht', 'Leinster', 'Munster') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Connacht","Leinster","Munster"],"cardinality":3},{"column":"postal_code","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 5 distinct value(s) ('10000', '10001', '10002', '10003', '10004') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["10000","10001","10002","10003","10004"],"cardinality":5},{"column":"address","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"city","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"state","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"postal_code","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"phone","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}},{"table":"suppliers","schema":"dbo","columns":[{"name":"supplier_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for each supplier, serving as the primary key in the suppliers table.","glossary_terms":[],"cardinality":10,"null_count":0,"data_range":{"min":"33","max":"42"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"The \"name\" column in the \"suppliers\" table is a non-nullable nvarchar field intended to store the name of the supplier, though sample data indicates it is currently unused.","glossary_terms":[],"cardinality":10,"null_count":0,"data_range":{"min":"Supplier 1","max":"Supplier 9"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"name"},{"name":"contact_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"Stores the name of the primary contact person for a supplier, allowing null values.","glossary_terms":[],"cardinality":0,"null_count":10,"data_category":"nominal","semantic_class":"person_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: contact_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"contact_name"},{"name":"email","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"Stores the email address of the supplier, allowing null values for cases where no email is provided.","glossary_terms":[],"cardinality":10,"null_count":0,"data_range":{"min":"supplier1@example.com","max":"supplier9@example.com"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.email","concept_confidence":1.0,"concept_evidence":["name token: email","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: contact","value pattern: email","sensitive hint: pii_contact"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"email"},{"name":"phone","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"The \"phone\" column in the \"suppliers\" table stores the contact phone number of a supplier as a nullable string.","glossary_terms":[],"cardinality":10,"null_count":0,"data_range":{"min":"555-2001","max":"555-2010"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.phone","concept_confidence":1.0,"concept_evidence":["name token: phone","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: contact","value pattern: phone","sensitive hint: pii_contact"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"phone"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"Records the timestamp when a supplier entry is initially created in the system, stored as a non-nullable datetime value.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":10,"null_count":0,"data_range":{"min":"2021-03-22 15:38:57.201565","max":"2024-02-25 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: suppliers"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The `updated_at` column stores the non-nullable timestamp of the most recent update to a supplier record in the `suppliers` table.","glossary_terms":[],"column_timezone":"(UTC) Coordinated Universal Time","cardinality":10,"null_count":0,"data_range":{"min":"2021-03-22 15:38:57.201565","max":"2024-02-25 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: suppliers"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"}],"table_description":"The \"suppliers\" table stores information about suppliers, including their unique identifier, name, contact details, and timestamps for record creation and updates.","glossary_terms":["RetailDomainGlossary.Supplier","RetailDomainGlossary.SupplierCode","RetailDomainGlossary.SupplierPurchaseRelationship"],"primary_keys":["supplier_id"],"foreign_keys":[],"row_count":10,"field_classifications":{"contact_name":"person_name","email":"contact","phone":"contact","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{"email":"pii_contact","phone":"pii_contact"},"incremental_columns":["updated_at"],"join_candidates":[],"unit_summary":{"columns_with_units":0,"columns_without_units":7,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":false,"has_sensitive_fields":true,"row_count_projection_1y":22,"row_count_projection_2y":35,"row_count_projection_5y":74,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.email":1,"contact.person_name":2,"contact.phone":1,"identifier.foreign_key":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":["contact_name","name"]},"data_quality":{"findings":[{"column":"email","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 10 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"phone","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 10 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}}]}</t>
         </is>
       </c>
     </row>
@@ -10512,7 +10512,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-04-07T08:55:59.245988+00:00</t>
+          <t>2026-04-07T10:07:13.375975+00:00</t>
         </is>
       </c>
       <c r="C3" s="4" t="n"/>
@@ -15631,7 +15631,7 @@
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="80" customWidth="1" min="7" max="7"/>
     <col width="80" customWidth="1" min="8" max="8"/>
-    <col width="41" customWidth="1" min="9" max="9"/>
+    <col width="72" customWidth="1" min="9" max="9"/>
     <col width="80" customWidth="1" min="10" max="10"/>
     <col width="80" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
@@ -15767,12 +15767,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>The "customers" table stores information about retail customers, including their unique ID, name, contact details, and timestamps for record creation and updates.</t>
+          <t>The "customers" table stores information about retail system customers, including unique identifiers, names, contact details, and timestamps for record creation and updates.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>RetailDomainGlossary.CustomerIdentifier</t>
+          <t>RetailDomainGlossary.Customer, RetailDomainGlossary.CustomerIdentifier</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -16116,7 +16116,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Unique identifier for each customer in the retail operations system.</t>
+          <t>Unique identifier for each customer in the retail operations system, serving as the primary key for the customers table.</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -16207,7 +16207,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Stores the given name of a customer as a non-null Unicode string.</t>
+          <t>Stores the given name of a customer as a non-null, case-insensitive Unicode string.</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -16297,11 +16297,7 @@
           <t>The "last_name" column in the "customers" table stores the non-nullable family name of a customer as a case-insensitive Unicode string.</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>RetailDomainGlossary.Customer</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
           <t>contact.person_name</t>
@@ -16389,7 +16385,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Stores the email address of the customer, allowing null values for cases where an email is not provided.</t>
+          <t>Stores the email address of the customer, allowing null values, with a maximum length of 450 characters.</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -16654,7 +16650,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Tracks the timestamp of the most recent update to a customer record, ensuring accurate audit and change history.</t>
+          <t>The `updated_at` column in the `customers` table stores the non-nullable timestamp of the most recent update to a customer's record.</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -17170,7 +17166,7 @@
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="80" customWidth="1" min="7" max="7"/>
     <col width="80" customWidth="1" min="8" max="8"/>
-    <col width="32" customWidth="1" min="9" max="9"/>
+    <col width="80" customWidth="1" min="9" max="9"/>
     <col width="80" customWidth="1" min="10" max="10"/>
     <col width="80" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
@@ -17306,10 +17302,14 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>The `employees` table stores detailed information about retail system employees, including their unique identifiers, store assignments, personal details, job roles, hire dates, and record timestamps.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>The `employees` table stores detailed information about retail system employees, including their unique identifiers, store associations, personal details, roles, hire dates, and record timestamps for creation and updates.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>RetailDomainGlossary.Customer, RetailDomainGlossary.PhysicalStore, RetailDomainGlossary.Role, RetailDomainGlossary.Timestamp</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>{"concept_counts":{"contact.email":1,"contact.person_name":2,"entity.type":1,"identifier.foreign_key":2,"temporal.created_at":1,"temporal.date_only":1,"temporal.updated_at":1},"low_confidence_columns":["first_name","last_name"]}</t>
@@ -17838,10 +17838,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Identifies the store where the employee is assigned, referencing the `store_id` column in the `stores` table.</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
+          <t>Associates each employee with a specific store, referencing the unique identifier in the `stores.store_id` column.</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>RetailDomainGlossary.StoreLocation</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
@@ -17925,7 +17929,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Stores the given name of an employee, represented as a non-null Unicode string.</t>
+          <t>Stores the given name of an employee as a non-null Unicode string.</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -18012,7 +18016,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>The "last_name" column in the "employees" table stores the non-nullable family name of each employee as a case-insensitive Unicode string.</t>
+          <t>The "last_name" column in the "employees" table stores the non-nullable family name of an employee as a case-insensitive Unicode string.</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -18182,7 +18186,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Stores the job role or position of an employee within the organization, such as "Cashier" or "Sales," as a non-null text value.</t>
+          <t>Stores the job role or position of an employee within the organization, represented as a non-nullable text value.</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -18269,7 +18273,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>The `hire_date` column in the `employees` table stores the non-nullable date an employee was hired, used for tracking employment start dates.</t>
+          <t>The `hire_date` column in the `employees` table records the date an employee was hired, is mandatory, and uses the `date` data type.</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -18443,7 +18447,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>The `updated_at` column in the `employees` table stores the non-nullable timestamp of the most recent update to an employee record.</t>
+          <t>Tracks the timestamp of the most recent update to an employee record, ensuring accurate audit trails for changes.</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -19114,7 +19118,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>RetailDomainGlossary.Inventory, RetailDomainGlossary.InventoryByProductAndLocation</t>
+          <t>RetailDomainGlossary.Inventory, RetailDomainGlossary.InventoryTracking, RetailDomainGlossary.UnitOfMeasure</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -19679,10 +19683,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Represents the unique identifier of the store associated with the inventory record, referencing the `store_id` column in the `stores` table.</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
+          <t>Identifier linking inventory records to the associated store, referencing the `stores.store_id` column.</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>RetailDomainGlossary.StoreLocation</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
@@ -19765,7 +19773,11 @@
           <t>References the unique identifier of a product from the products table, linking inventory records to specific products.</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>RetailDomainGlossary.Product</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
@@ -19849,12 +19861,12 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>The `quantity_on_hand` column in the `inventory` table stores the current stock level of a product as a non-null integer.</t>
+          <t>Tracks the current quantity of a product available in inventory, expressed as a non-null integer.</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>RetailDomainGlossary.Inventory</t>
+          <t>RetailDomainGlossary.Inventory, RetailDomainGlossary.LocationLevelInventory</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -20034,11 +20046,7 @@
           <t>The `last_restocked_at` column records the timestamp of the most recent restocking event for an inventory item, allowing null values if the item has not been restocked.</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>RetailDomainGlossary.Replenishment</t>
-        </is>
-      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
           <t>temporal.event_time</t>
@@ -20288,7 +20296,7 @@
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Represents the monetary value of inventory stock, stored as a numeric value with two decimal places, and may be null.</t>
+          <t>Represents the monetary value of inventory stock, stored as a numeric value with up to 10 digits and 2 decimal places, and may be null.</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -20859,7 +20867,7 @@
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="80" customWidth="1" min="7" max="7"/>
     <col width="80" customWidth="1" min="8" max="8"/>
-    <col width="67" customWidth="1" min="9" max="9"/>
+    <col width="80" customWidth="1" min="9" max="9"/>
     <col width="80" customWidth="1" min="10" max="10"/>
     <col width="80" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
@@ -21000,7 +21008,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>RetailDomainGlossary.Inventory, RetailDomainGlossary.SupplierCode</t>
+          <t>RetailDomainGlossary.Product, RetailDomainGlossary.ProductCategory, RetailDomainGlossary.CostPrice, RetailDomainGlossary.UnitOfMeasure</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -21485,7 +21493,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>RetailDomainGlossary.Barcode</t>
+          <t>RetailDomainGlossary.Product</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -21568,7 +21576,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>RetailDomainGlossary.SupplierCode</t>
+          <t>RetailDomainGlossary.Supplier</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -21733,10 +21741,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Stores the name of the product as a non-null, case-insensitive Unicode string.</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
+          <t>The "name" column in the "products" table stores the non-nullable name of each product as a Unicode string.</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>RetailDomainGlossary.Product</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>contact.person_name</t>
@@ -21820,7 +21832,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Indicates the product's category classification, such as "Books," "Clothing," or "Electronics," stored as a non-nullable nvarchar value.</t>
+          <t>Indicates the product's category classification, such as "Books," "Clothing," or "Electronics," stored as a non-null, case-insensitive text value.</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -21911,7 +21923,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>The `unit_price` column stores the non-null selling price of a product as a numeric value with up to 10 digits and 2 decimal places, representing a currency amount.</t>
+          <t>The `unit_price` column stores the selling price of a product as a non-null numeric value with up to 10 digits and 2 decimal places, representing a currency amount.</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -22002,7 +22014,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>The `cost_price` column stores the non-null numeric cost amount (up to 10 digits with 2 decimal places) representing the purchase price of a product in the retail system.</t>
+          <t>The `cost_price` column in the `products` table stores the non-null numeric value representing the purchase cost of a product in currency format with up to 10 digits and 2 decimal places.</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -22500,10 +22512,14 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Represents the length measurement of a product in numeric format, allowing null values.</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
+          <t>Represents the length measurement of a product, stored as a numeric value with up to two decimal places, and may be null if not applicable.</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>RetailDomainGlossary.UnitOfMeasure</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="n">
         <v>0</v>
@@ -22669,11 +22685,7 @@
           <t>Stores optional textual details about a product, such as features or specifications.</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>RetailDomainGlossary.Product</t>
-        </is>
-      </c>
+      <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="n">
         <v>0.1</v>
@@ -22738,7 +22750,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>RetailDomainGlossary.SupplierPurchaseRelationship</t>
+          <t>RetailDomainGlossary.Supplier</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -23644,7 +23656,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>RetailDomainGlossary.OrderLine, RetailDomainGlossary.UnitOfMeasure, RetailDomainGlossary.CostPrice, RetailDomainGlossary.PurchaseOrder</t>
+          <t>RetailDomainGlossary.OrderLine, RetailDomainGlossary.Quantity, RetailDomainGlossary.UnitOfMeasure, RetailDomainGlossary.PurchaseOrder</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -24123,11 +24135,7 @@
           <t>Unique identifier for each purchase order item record in the `purchase_order_items` table.</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>RetailDomainGlossary.OrderLine</t>
-        </is>
-      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
@@ -24203,7 +24211,7 @@
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Represents the unique identifier of the associated purchase order, linking purchase order items to their parent purchase order in the `purchase_orders` table.</t>
+          <t>Identifier linking each purchase order item to its associated purchase order in the `purchase_orders` table.</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -24295,7 +24303,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>RetailDomainGlossary.ProductCategory</t>
+          <t>RetailDomainGlossary.Product</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -24381,14 +24389,10 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>The `quantity` column in the `purchase_order_items` table stores the non-null integer value representing the number of units of a product included in a specific purchase order item.</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>RetailDomainGlossary.UnitOfMeasure</t>
-        </is>
-      </c>
+          <t>The "quantity" column in the "purchase_order_items" table stores the non-null integer value representing the number of units of a product included in a specific purchase order item.</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
           <t>measure.quantity</t>
@@ -24579,7 +24583,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>The `created_at` column records the non-nullable timestamp indicating when each purchase order item record was created.</t>
+          <t>Records the timestamp when a purchase order item entry is created, stored as a non-nullable datetime value.</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -24758,7 +24762,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>RetailDomainGlossary.PurchaseOrder</t>
+          <t>RetailDomainGlossary.Quantity</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
